--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU133"/>
+  <dimension ref="A1:AU137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15:00</t>
+          <t>2026-10-09 10:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-09 10:30:00</t>
+          <t>2026-10-09 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-09 10:50:00</t>
+          <t>2026-10-09 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-09 11:00:00</t>
+          <t>2026-10-09 10:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-09 11:00:00</t>
+          <t>2026-10-09 10:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-09 11:00:00</t>
+          <t>2026-10-09 10:50:00</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-09 11:30:00</t>
+          <t>2026-10-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-09 11:45:00</t>
+          <t>2026-10-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-09 11:55:00</t>
+          <t>2026-10-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-09 12:00:00</t>
+          <t>2026-10-09 11:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-09 12:00:00</t>
+          <t>2026-10-09 11:45:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-09 12:30:00</t>
+          <t>2026-10-09 11:55:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-09 12:30:00</t>
+          <t>2026-10-09 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-09 13:00:00</t>
+          <t>2026-10-09 12:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-09 13:00:00</t>
+          <t>2026-10-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-09 13:00:00</t>
+          <t>2026-10-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-09 13:30:00</t>
+          <t>2026-10-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-09 13:30:00</t>
+          <t>2026-10-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-09 13:30:00</t>
+          <t>2026-10-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.61</v>
+        <v>12.1</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>6.25</v>
       </c>
       <c r="P51">
-        <v>2.36</v>
+        <v>1.2</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-09 13:30:00</t>
+          <t>2026-10-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.86</v>
+        <v>2.91</v>
       </c>
       <c r="O52">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="P52">
-        <v>3.67</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.84</v>
+        <v>3.93</v>
       </c>
       <c r="O53">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P53">
-        <v>4.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AB53">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.62</v>
+        <v>3.23</v>
       </c>
       <c r="O62">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="P62">
-        <v>4.69</v>
+        <v>2.07</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-09 14:30:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-09 14:30:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-09 14:30:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-10-09 14:45:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.2</v>
+        <v>3.94</v>
       </c>
       <c r="O71">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P71">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:45:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P73">
-        <v>3.72</v>
+        <v>3.33</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.88</v>
+        <v>2.34</v>
       </c>
       <c r="O76">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="P76">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87">
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15839,10 +15839,10 @@
         <v>0</v>
       </c>
       <c r="AC95">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE95">
         <v>0</v>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB97">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16491,10 +16491,10 @@
         <v>0</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G104">
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17703,27 +17703,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="AC108">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-09 16:15:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-09 20:30:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18610,10 +18610,10 @@
         <v>0</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 16:15:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,141 +21956,793 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>Loznica</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>0</v>
+      </c>
+      <c r="Z133">
+        <v>0</v>
+      </c>
+      <c r="AA133">
+        <v>0</v>
+      </c>
+      <c r="AB133">
+        <v>0</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>0</v>
+      </c>
+      <c r="AF133">
+        <v>0</v>
+      </c>
+      <c r="AG133">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <v>0</v>
+      </c>
+      <c r="AK133">
+        <v>0</v>
+      </c>
+      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AM133">
+        <v>-1</v>
+      </c>
+      <c r="AN133">
+        <v>-1</v>
+      </c>
+      <c r="AO133">
+        <v>-1</v>
+      </c>
+      <c r="AP133">
+        <v>-1</v>
+      </c>
+      <c r="AQ133">
+        <v>0</v>
+      </c>
+      <c r="AR133">
+        <v>0</v>
+      </c>
+      <c r="AS133">
+        <v>0</v>
+      </c>
+      <c r="AT133">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub</t>
+        </is>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
+        <v>0</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
+        <v>0</v>
+      </c>
+      <c r="AF134">
+        <v>0</v>
+      </c>
+      <c r="AG134">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+      <c r="AK134">
+        <v>0</v>
+      </c>
+      <c r="AL134">
+        <v>0</v>
+      </c>
+      <c r="AM134">
+        <v>-1</v>
+      </c>
+      <c r="AN134">
+        <v>-1</v>
+      </c>
+      <c r="AO134">
+        <v>-1</v>
+      </c>
+      <c r="AP134">
+        <v>-1</v>
+      </c>
+      <c r="AQ134">
+        <v>0</v>
+      </c>
+      <c r="AR134">
+        <v>0</v>
+      </c>
+      <c r="AS134">
+        <v>0</v>
+      </c>
+      <c r="AT134">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>-1</v>
+      </c>
+      <c r="AN135">
+        <v>-1</v>
+      </c>
+      <c r="AO135">
+        <v>-1</v>
+      </c>
+      <c r="AP135">
+        <v>-1</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
+        <v>0</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>0</v>
+      </c>
+      <c r="AG136">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>0</v>
+      </c>
+      <c r="AM136">
+        <v>-1</v>
+      </c>
+      <c r="AN136">
+        <v>-1</v>
+      </c>
+      <c r="AO136">
+        <v>-1</v>
+      </c>
+      <c r="AP136">
+        <v>-1</v>
+      </c>
+      <c r="AQ136">
+        <v>0</v>
+      </c>
+      <c r="AR136">
+        <v>0</v>
+      </c>
+      <c r="AS136">
+        <v>0</v>
+      </c>
+      <c r="AT136">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Naftagas</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Napredak</t>
         </is>
       </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>-1</v>
+      </c>
+      <c r="AN137">
+        <v>-1</v>
+      </c>
+      <c r="AO137">
+        <v>-1</v>
+      </c>
+      <c r="AP137">
+        <v>-1</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU137"/>
+  <dimension ref="A1:AU139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G13">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-09 11:30:00</t>
+          <t>2026-10-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-09 11:45:00</t>
+          <t>2026-10-09 11:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-09 11:55:00</t>
+          <t>2026-10-09 11:45:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-09 12:00:00</t>
+          <t>2026-10-09 11:55:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-09 12:30:00</t>
+          <t>2026-10-09 12:00:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-09 13:00:00</t>
+          <t>2026-10-09 12:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.91</v>
+        <v>12.1</v>
       </c>
       <c r="O52">
-        <v>3.21</v>
+        <v>6.25</v>
       </c>
       <c r="P52">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-09 13:30:00</t>
+          <t>2026-10-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.93</v>
+        <v>2.91</v>
       </c>
       <c r="O53">
-        <v>3.9</v>
+        <v>3.21</v>
       </c>
       <c r="P53">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.12</v>
+        <v>3.93</v>
       </c>
       <c r="O54">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P54">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,16 +9150,16 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="O55">
         <v>3.72</v>
       </c>
       <c r="P55">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O56">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P56">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,16 +9476,16 @@
         <v>0</v>
       </c>
       <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>2.25</v>
+      </c>
+      <c r="AD56">
         <v>1.55</v>
-      </c>
-      <c r="AB56">
-        <v>2.25</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="O57">
         <v>3.84</v>
       </c>
       <c r="P57">
-        <v>4.77</v>
+        <v>3.67</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB57">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:30:00</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G67">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-09 14:30:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-10-09 14:30:00</t>
+          <t>2026-10-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-10-09 14:45:00</t>
+          <t>2026-10-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.1</v>
+        <v>3.94</v>
       </c>
       <c r="O73">
         <v>3.42</v>
       </c>
       <c r="P73">
-        <v>3.33</v>
+        <v>2.06</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AB73">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-09 14:45:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O75">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P75">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB75">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="O76">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="P76">
-        <v>2.85</v>
+        <v>4.95</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P77">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16491,10 +16491,10 @@
         <v>0</v>
       </c>
       <c r="AC99">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD99">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE99">
         <v>0</v>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.17</v>
+        <v>1.45</v>
       </c>
       <c r="O101">
-        <v>3.84</v>
+        <v>5.44</v>
       </c>
       <c r="P101">
-        <v>3.41</v>
+        <v>7.08</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,16 +16811,16 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108">
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18610,10 +18610,10 @@
         <v>0</v>
       </c>
       <c r="AC112">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD112">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE112">
         <v>0</v>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-09 16:15:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18936,10 +18936,10 @@
         <v>0</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-10-09 17:00:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-09 20:30:00</t>
+          <t>2026-10-09 16:15:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,141 +22608,467 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>-1</v>
+      </c>
+      <c r="AN137">
+        <v>-1</v>
+      </c>
+      <c r="AO137">
+        <v>-1</v>
+      </c>
+      <c r="AP137">
+        <v>-1</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>Naftagas</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Napredak</t>
         </is>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G22">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G51">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P56">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,16 +9476,16 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O57">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P57">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,16 +9639,16 @@
         <v>0</v>
       </c>
       <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>2.25</v>
+      </c>
+      <c r="AD57">
         <v>1.55</v>
-      </c>
-      <c r="AB57">
-        <v>2.25</v>
-      </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G139">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G33">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O56">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P56">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,16 +9476,16 @@
         <v>0</v>
       </c>
       <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>2.25</v>
+      </c>
+      <c r="AD56">
         <v>1.55</v>
-      </c>
-      <c r="AB56">
-        <v>2.25</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O57">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P57">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,16 +9639,16 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC98">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE15">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G22">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>8.48</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q109">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.93</v>
+        <v>3.12</v>
       </c>
       <c r="O54">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P54">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,16 +9150,16 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.12</v>
+        <v>3.93</v>
       </c>
       <c r="O55">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P55">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,16 +9313,16 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC55">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE55">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU139"/>
+  <dimension ref="A1:AU137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G137">
@@ -22743,332 +22743,6 @@
         <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G37">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q62">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q99">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.12</v>
+        <v>3.93</v>
       </c>
       <c r="O54">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P54">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,16 +9150,16 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.93</v>
+        <v>3.12</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,16 +9313,16 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G93">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G129">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G120">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU137"/>
+  <dimension ref="A1:AU134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134">
@@ -22254,495 +22254,6 @@
         <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU134"/>
+  <dimension ref="A1:AU131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131">
@@ -21765,495 +21765,6 @@
         <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G93">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU131"/>
+  <dimension ref="A1:AU133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P56">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,16 +9476,16 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O57">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P57">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,16 +9639,16 @@
         <v>0</v>
       </c>
       <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>2.25</v>
+      </c>
+      <c r="AD57">
         <v>1.55</v>
-      </c>
-      <c r="AB57">
-        <v>2.25</v>
-      </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.88</v>
+        <v>2.41</v>
       </c>
       <c r="O80">
-        <v>4.52</v>
+        <v>3.31</v>
       </c>
       <c r="P80">
-        <v>1.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.49</v>
+        <v>3.88</v>
       </c>
       <c r="O81">
-        <v>4.98</v>
+        <v>4.52</v>
       </c>
       <c r="P81">
-        <v>5.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.88</v>
+        <v>1.49</v>
       </c>
       <c r="O82">
-        <v>3.38</v>
+        <v>4.98</v>
       </c>
       <c r="P82">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93">
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15:00</t>
+          <t>2026-10-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G95">
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-09 15:30:00</t>
+          <t>2026-10-09 15:15:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.8</v>
+        <v>2.74</v>
       </c>
       <c r="O97">
-        <v>4.03</v>
+        <v>3.36</v>
       </c>
       <c r="P97">
-        <v>4.11</v>
+        <v>2.42</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB97">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="O98">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
       <c r="P98">
-        <v>3.5</v>
+        <v>4.11</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB98">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="O99">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="P99">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16817,10 +16817,10 @@
         <v>0</v>
       </c>
       <c r="AC101">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD101">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE101">
         <v>0</v>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16980,10 +16980,10 @@
         <v>0</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-09 15:45:00</t>
+          <t>2026-10-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB103">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.39</v>
+        <v>2.17</v>
       </c>
       <c r="O104">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="P104">
-        <v>7.8</v>
+        <v>3.41</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="O105">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P105">
-        <v>3.74</v>
+        <v>7.8</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O106">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="P106">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O107">
-        <v>3.64</v>
+        <v>4.03</v>
       </c>
       <c r="P107">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="O108">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P108">
-        <v>2.76</v>
+        <v>3.92</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18936,10 +18936,10 @@
         <v>0</v>
       </c>
       <c r="AC114">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD114">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE114">
         <v>0</v>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>4.09</v>
+        <v>1.43</v>
       </c>
       <c r="O115">
-        <v>3.81</v>
+        <v>4.6</v>
       </c>
       <c r="P115">
-        <v>1.91</v>
+        <v>6.51</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,16 +19093,16 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-09 16:15:00</t>
+          <t>2026-10-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-09 17:00:00</t>
+          <t>2026-10-09 16:15:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-09 20:30:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G121">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,141 +21630,467 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>Loznica</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>0</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131">
+        <v>0</v>
+      </c>
+      <c r="V131">
+        <v>0</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
+      </c>
+      <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131">
+        <v>0</v>
+      </c>
+      <c r="Z131">
+        <v>0</v>
+      </c>
+      <c r="AA131">
+        <v>0</v>
+      </c>
+      <c r="AB131">
+        <v>0</v>
+      </c>
+      <c r="AC131">
+        <v>0</v>
+      </c>
+      <c r="AD131">
+        <v>0</v>
+      </c>
+      <c r="AE131">
+        <v>0</v>
+      </c>
+      <c r="AF131">
+        <v>0</v>
+      </c>
+      <c r="AG131">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
+        <v>0</v>
+      </c>
+      <c r="AK131">
+        <v>0</v>
+      </c>
+      <c r="AL131">
+        <v>0</v>
+      </c>
+      <c r="AM131">
+        <v>-1</v>
+      </c>
+      <c r="AN131">
+        <v>-1</v>
+      </c>
+      <c r="AO131">
+        <v>-1</v>
+      </c>
+      <c r="AP131">
+        <v>-1</v>
+      </c>
+      <c r="AQ131">
+        <v>0</v>
+      </c>
+      <c r="AR131">
+        <v>0</v>
+      </c>
+      <c r="AS131">
+        <v>0</v>
+      </c>
+      <c r="AT131">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub</t>
+        </is>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>0</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+      <c r="AA132">
+        <v>0</v>
+      </c>
+      <c r="AB132">
+        <v>0</v>
+      </c>
+      <c r="AC132">
+        <v>0</v>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132">
+        <v>0</v>
+      </c>
+      <c r="AF132">
+        <v>0</v>
+      </c>
+      <c r="AG132">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <v>0</v>
+      </c>
+      <c r="AK132">
+        <v>0</v>
+      </c>
+      <c r="AL132">
+        <v>0</v>
+      </c>
+      <c r="AM132">
+        <v>-1</v>
+      </c>
+      <c r="AN132">
+        <v>-1</v>
+      </c>
+      <c r="AO132">
+        <v>-1</v>
+      </c>
+      <c r="AP132">
+        <v>-1</v>
+      </c>
+      <c r="AQ132">
+        <v>0</v>
+      </c>
+      <c r="AR132">
+        <v>0</v>
+      </c>
+      <c r="AS132">
+        <v>0</v>
+      </c>
+      <c r="AT132">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>Voždovac</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>OFK Vršac</t>
         </is>
       </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+      <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133">
+        <v>0</v>
+      </c>
+      <c r="Z133">
+        <v>0</v>
+      </c>
+      <c r="AA133">
+        <v>0</v>
+      </c>
+      <c r="AB133">
+        <v>0</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>0</v>
+      </c>
+      <c r="AF133">
+        <v>0</v>
+      </c>
+      <c r="AG133">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <v>0</v>
+      </c>
+      <c r="AK133">
+        <v>0</v>
+      </c>
+      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AM133">
+        <v>-1</v>
+      </c>
+      <c r="AN133">
+        <v>-1</v>
+      </c>
+      <c r="AO133">
+        <v>-1</v>
+      </c>
+      <c r="AP133">
+        <v>-1</v>
+      </c>
+      <c r="AQ133">
+        <v>0</v>
+      </c>
+      <c r="AR133">
+        <v>0</v>
+      </c>
+      <c r="AS133">
+        <v>0</v>
+      </c>
+      <c r="AT133">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G96">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G22">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>1.55</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>3.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>1.2</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11402,40 +11402,40 @@
         <v>4.69</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
         <v>2</v>
@@ -11444,13 +11444,13 @@
         <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G94">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -644,34 +644,34 @@
         <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2">
         <v>1.81</v>
@@ -680,19 +680,19 @@
         <v>2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>3.28</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="O4">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="P4">
-        <v>4.65</v>
+        <v>3.74</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.76</v>
+      </c>
+      <c r="O5">
+        <v>3.77</v>
+      </c>
+      <c r="P5">
+        <v>4.65</v>
+      </c>
+      <c r="Q5">
+        <v>2.47</v>
+      </c>
+      <c r="R5">
+        <v>2.19</v>
+      </c>
+      <c r="S5">
+        <v>1.4</v>
+      </c>
+      <c r="T5">
+        <v>2.75</v>
+      </c>
+      <c r="U5">
+        <v>2.95</v>
+      </c>
+      <c r="V5">
+        <v>1.37</v>
+      </c>
+      <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.35</v>
+      </c>
+      <c r="Z5">
+        <v>3.03</v>
+      </c>
+      <c r="AA5">
         <v>2.06</v>
       </c>
-      <c r="O5">
-        <v>3.39</v>
-      </c>
-      <c r="P5">
-        <v>3.74</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,34 +1459,34 @@
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA7">
         <v>1.87</v>
@@ -1495,19 +1495,19 @@
         <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="O9">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="P9">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O10">
-        <v>3.86</v>
+        <v>3.49</v>
       </c>
       <c r="P10">
-        <v>3.7</v>
+        <v>3.33</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,40 +2763,40 @@
         <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
         <v>1.93</v>
@@ -2805,13 +2805,13 @@
         <v>1.86</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22">
@@ -5860,55 +5860,55 @@
         <v>3.06</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>2.87</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>2.55</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,34 +9120,34 @@
         <v>1.76</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AA54">
         <v>1.53</v>
@@ -9156,19 +9156,19 @@
         <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
         <v>2.25</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O56">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P56">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA56">
+        <v>1.53</v>
+      </c>
+      <c r="AB56">
+        <v>2.33</v>
+      </c>
+      <c r="AC56">
+        <v>2.25</v>
+      </c>
+      <c r="AD56">
         <v>1.55</v>
       </c>
-      <c r="AB56">
-        <v>2.25</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
-      </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O57">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P57">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD57">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9935,34 +9935,34 @@
         <v>4.77</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA59">
         <v>1.94</v>
@@ -9971,19 +9971,19 @@
         <v>1.86</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>3.59</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>2.07</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>4.46</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -13358,34 +13358,34 @@
         <v>2.82</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA80">
         <v>2.3</v>
@@ -13394,19 +13394,19 @@
         <v>1.6</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>7.8</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>3.74</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X106">
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>3.98</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X107">
         <v>0</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
+        <v>1.12</v>
+      </c>
+      <c r="O108">
+        <v>8.48</v>
+      </c>
+      <c r="P108">
+        <v>12.7</v>
+      </c>
+      <c r="Q108">
+        <v>1.4</v>
+      </c>
+      <c r="R108">
+        <v>3.51</v>
+      </c>
+      <c r="S108">
+        <v>1.18</v>
+      </c>
+      <c r="T108">
+        <v>5</v>
+      </c>
+      <c r="U108">
+        <v>1.85</v>
+      </c>
+      <c r="V108">
+        <v>1.85</v>
+      </c>
+      <c r="W108">
+        <v>1.25</v>
+      </c>
+      <c r="X108">
+        <v>0</v>
+      </c>
+      <c r="Y108">
+        <v>1.03</v>
+      </c>
+      <c r="Z108">
+        <v>8.1</v>
+      </c>
+      <c r="AA108">
+        <v>1.28</v>
+      </c>
+      <c r="AB108">
+        <v>3.4</v>
+      </c>
+      <c r="AC108">
+        <v>1.76</v>
+      </c>
+      <c r="AD108">
+        <v>2.06</v>
+      </c>
+      <c r="AE108">
+        <v>1.49</v>
+      </c>
+      <c r="AF108">
         <v>1.81</v>
       </c>
-      <c r="O108">
-        <v>3.64</v>
-      </c>
-      <c r="P108">
-        <v>3.92</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>0</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
-      <c r="V108">
-        <v>0</v>
-      </c>
-      <c r="W108">
-        <v>0</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>0</v>
-      </c>
-      <c r="Z108">
-        <v>0</v>
-      </c>
-      <c r="AA108">
-        <v>0</v>
-      </c>
-      <c r="AB108">
-        <v>0</v>
-      </c>
-      <c r="AC108">
-        <v>0</v>
-      </c>
-      <c r="AD108">
-        <v>0</v>
-      </c>
-      <c r="AE108">
-        <v>0</v>
-      </c>
-      <c r="AF108">
-        <v>0</v>
-      </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="O109">
-        <v>8.48</v>
+        <v>3.3</v>
       </c>
       <c r="P109">
-        <v>12.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="O110">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P110">
-        <v>2.76</v>
+        <v>3.92</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="O6">
-        <v>3.56</v>
+        <v>3.89</v>
       </c>
       <c r="P6">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.12</v>
+        <v>4.01</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="O7">
-        <v>3.89</v>
+        <v>3.56</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
+        <v>2.88</v>
+      </c>
+      <c r="U7">
+        <v>2.8</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.33</v>
+      </c>
+      <c r="Z7">
         <v>3.12</v>
       </c>
-      <c r="U7">
-        <v>2.45</v>
-      </c>
-      <c r="V7">
-        <v>1.44</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.2</v>
-      </c>
-      <c r="Z7">
-        <v>4.01</v>
-      </c>
       <c r="AA7">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G67">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="O107">
-        <v>4.03</v>
+        <v>8.48</v>
       </c>
       <c r="P107">
-        <v>3.98</v>
+        <v>12.7</v>
       </c>
       <c r="Q107">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="R107">
-        <v>2.66</v>
+        <v>3.51</v>
       </c>
       <c r="S107">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T107">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U107">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="V107">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W107">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X107">
         <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z107">
-        <v>5.22</v>
+        <v>8.1</v>
       </c>
       <c r="AA107">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AB107">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="AC107">
-        <v>2.19</v>
+        <v>1.76</v>
       </c>
       <c r="AD107">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AE107">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AF107">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG107">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK107">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="O108">
-        <v>8.48</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>12.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q108">
+        <v>2.92</v>
+      </c>
+      <c r="R108">
+        <v>2.2</v>
+      </c>
+      <c r="S108">
+        <v>1.3</v>
+      </c>
+      <c r="T108">
+        <v>3.2</v>
+      </c>
+      <c r="U108">
+        <v>2.63</v>
+      </c>
+      <c r="V108">
+        <v>1.44</v>
+      </c>
+      <c r="W108">
+        <v>1.06</v>
+      </c>
+      <c r="X108">
+        <v>0</v>
+      </c>
+      <c r="Y108">
+        <v>1.24</v>
+      </c>
+      <c r="Z108">
+        <v>3.7</v>
+      </c>
+      <c r="AA108">
+        <v>1.8</v>
+      </c>
+      <c r="AB108">
+        <v>2.01</v>
+      </c>
+      <c r="AC108">
+        <v>2.85</v>
+      </c>
+      <c r="AD108">
         <v>1.4</v>
       </c>
-      <c r="R108">
-        <v>3.51</v>
-      </c>
-      <c r="S108">
-        <v>1.18</v>
-      </c>
-      <c r="T108">
-        <v>5</v>
-      </c>
-      <c r="U108">
-        <v>1.85</v>
-      </c>
-      <c r="V108">
-        <v>1.85</v>
-      </c>
-      <c r="W108">
-        <v>1.25</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>1.03</v>
-      </c>
-      <c r="Z108">
-        <v>8.1</v>
-      </c>
-      <c r="AA108">
-        <v>1.28</v>
-      </c>
-      <c r="AB108">
-        <v>3.4</v>
-      </c>
-      <c r="AC108">
-        <v>1.76</v>
-      </c>
-      <c r="AD108">
-        <v>2.06</v>
-      </c>
       <c r="AE108">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG108">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK108">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="O109">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P109">
-        <v>2.76</v>
+        <v>3.92</v>
       </c>
       <c r="Q109">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="R109">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
         <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U109">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z109">
-        <v>3.7</v>
+        <v>4.32</v>
       </c>
       <c r="AA109">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB109">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="AC109">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="AD109">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE109">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF109">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK109">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O110">
-        <v>3.64</v>
+        <v>4.03</v>
       </c>
       <c r="P110">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="Q110">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R110">
+        <v>2.66</v>
+      </c>
+      <c r="S110">
+        <v>1.21</v>
+      </c>
+      <c r="T110">
+        <v>3.75</v>
+      </c>
+      <c r="U110">
+        <v>2.15</v>
+      </c>
+      <c r="V110">
+        <v>1.6</v>
+      </c>
+      <c r="W110">
+        <v>1.17</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>1.12</v>
+      </c>
+      <c r="Z110">
+        <v>5.22</v>
+      </c>
+      <c r="AA110">
+        <v>1.51</v>
+      </c>
+      <c r="AB110">
+        <v>2.51</v>
+      </c>
+      <c r="AC110">
+        <v>2.19</v>
+      </c>
+      <c r="AD110">
+        <v>1.67</v>
+      </c>
+      <c r="AE110">
+        <v>1.25</v>
+      </c>
+      <c r="AF110">
+        <v>1.53</v>
+      </c>
+      <c r="AG110">
+        <v>2.3</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.17</v>
+      </c>
+      <c r="AK110">
         <v>2.4</v>
-      </c>
-      <c r="S110">
-        <v>1.3</v>
-      </c>
-      <c r="T110">
-        <v>3.28</v>
-      </c>
-      <c r="U110">
-        <v>2.5</v>
-      </c>
-      <c r="V110">
-        <v>1.5</v>
-      </c>
-      <c r="W110">
-        <v>1.1</v>
-      </c>
-      <c r="X110">
-        <v>0</v>
-      </c>
-      <c r="Y110">
-        <v>1.17</v>
-      </c>
-      <c r="Z110">
-        <v>4.32</v>
-      </c>
-      <c r="AA110">
-        <v>1.65</v>
-      </c>
-      <c r="AB110">
-        <v>2.22</v>
-      </c>
-      <c r="AC110">
-        <v>2.49</v>
-      </c>
-      <c r="AD110">
-        <v>1.46</v>
-      </c>
-      <c r="AE110">
-        <v>1.17</v>
-      </c>
-      <c r="AF110">
-        <v>1.75</v>
-      </c>
-      <c r="AG110">
-        <v>1.95</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.14</v>
-      </c>
-      <c r="AK110">
-        <v>2.42</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G33">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
+        <v>1.12</v>
+      </c>
+      <c r="O106">
+        <v>8.48</v>
+      </c>
+      <c r="P106">
+        <v>12.7</v>
+      </c>
+      <c r="Q106">
+        <v>1.4</v>
+      </c>
+      <c r="R106">
+        <v>3.51</v>
+      </c>
+      <c r="S106">
+        <v>1.18</v>
+      </c>
+      <c r="T106">
+        <v>5</v>
+      </c>
+      <c r="U106">
+        <v>1.85</v>
+      </c>
+      <c r="V106">
+        <v>1.85</v>
+      </c>
+      <c r="W106">
+        <v>1.25</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106">
+        <v>1.03</v>
+      </c>
+      <c r="Z106">
+        <v>8.1</v>
+      </c>
+      <c r="AA106">
+        <v>1.28</v>
+      </c>
+      <c r="AB106">
+        <v>3.4</v>
+      </c>
+      <c r="AC106">
+        <v>1.76</v>
+      </c>
+      <c r="AD106">
+        <v>2.06</v>
+      </c>
+      <c r="AE106">
+        <v>1.49</v>
+      </c>
+      <c r="AF106">
         <v>1.81</v>
       </c>
-      <c r="O106">
-        <v>3.8</v>
-      </c>
-      <c r="P106">
-        <v>3.74</v>
-      </c>
-      <c r="Q106">
-        <v>2.17</v>
-      </c>
-      <c r="R106">
-        <v>2.54</v>
-      </c>
-      <c r="S106">
-        <v>1.24</v>
-      </c>
-      <c r="T106">
-        <v>3.38</v>
-      </c>
-      <c r="U106">
-        <v>2.2</v>
-      </c>
-      <c r="V106">
-        <v>1.62</v>
-      </c>
-      <c r="W106">
-        <v>1.15</v>
-      </c>
-      <c r="X106">
-        <v>0</v>
-      </c>
-      <c r="Y106">
-        <v>1.16</v>
-      </c>
-      <c r="Z106">
-        <v>4.91</v>
-      </c>
-      <c r="AA106">
-        <v>1.54</v>
-      </c>
-      <c r="AB106">
-        <v>2.27</v>
-      </c>
-      <c r="AC106">
-        <v>2.35</v>
-      </c>
-      <c r="AD106">
-        <v>1.57</v>
-      </c>
-      <c r="AE106">
-        <v>1.22</v>
-      </c>
-      <c r="AF106">
-        <v>1.57</v>
-      </c>
       <c r="AG106">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK106">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="O107">
-        <v>8.48</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>12.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q107">
+        <v>2.92</v>
+      </c>
+      <c r="R107">
+        <v>2.2</v>
+      </c>
+      <c r="S107">
+        <v>1.3</v>
+      </c>
+      <c r="T107">
+        <v>3.2</v>
+      </c>
+      <c r="U107">
+        <v>2.63</v>
+      </c>
+      <c r="V107">
+        <v>1.44</v>
+      </c>
+      <c r="W107">
+        <v>1.06</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>1.24</v>
+      </c>
+      <c r="Z107">
+        <v>3.7</v>
+      </c>
+      <c r="AA107">
+        <v>1.8</v>
+      </c>
+      <c r="AB107">
+        <v>2.01</v>
+      </c>
+      <c r="AC107">
+        <v>2.85</v>
+      </c>
+      <c r="AD107">
         <v>1.4</v>
       </c>
-      <c r="R107">
-        <v>3.51</v>
-      </c>
-      <c r="S107">
-        <v>1.18</v>
-      </c>
-      <c r="T107">
-        <v>5</v>
-      </c>
-      <c r="U107">
-        <v>1.85</v>
-      </c>
-      <c r="V107">
-        <v>1.85</v>
-      </c>
-      <c r="W107">
-        <v>1.25</v>
-      </c>
-      <c r="X107">
-        <v>0</v>
-      </c>
-      <c r="Y107">
-        <v>1.03</v>
-      </c>
-      <c r="Z107">
-        <v>8.1</v>
-      </c>
-      <c r="AA107">
-        <v>1.28</v>
-      </c>
-      <c r="AB107">
-        <v>3.4</v>
-      </c>
-      <c r="AC107">
-        <v>1.76</v>
-      </c>
-      <c r="AD107">
-        <v>2.06</v>
-      </c>
       <c r="AE107">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG107">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="O108">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P108">
-        <v>2.76</v>
+        <v>3.92</v>
       </c>
       <c r="Q108">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S108">
         <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U108">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
         <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z108">
-        <v>3.7</v>
+        <v>4.32</v>
       </c>
       <c r="AA108">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB108">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="AC108">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="AD108">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF108">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG108">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK108">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O109">
-        <v>3.64</v>
+        <v>4.03</v>
       </c>
       <c r="P109">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="Q109">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R109">
+        <v>2.66</v>
+      </c>
+      <c r="S109">
+        <v>1.21</v>
+      </c>
+      <c r="T109">
+        <v>3.75</v>
+      </c>
+      <c r="U109">
+        <v>2.15</v>
+      </c>
+      <c r="V109">
+        <v>1.6</v>
+      </c>
+      <c r="W109">
+        <v>1.17</v>
+      </c>
+      <c r="X109">
+        <v>0</v>
+      </c>
+      <c r="Y109">
+        <v>1.12</v>
+      </c>
+      <c r="Z109">
+        <v>5.22</v>
+      </c>
+      <c r="AA109">
+        <v>1.51</v>
+      </c>
+      <c r="AB109">
+        <v>2.51</v>
+      </c>
+      <c r="AC109">
+        <v>2.19</v>
+      </c>
+      <c r="AD109">
+        <v>1.67</v>
+      </c>
+      <c r="AE109">
+        <v>1.25</v>
+      </c>
+      <c r="AF109">
+        <v>1.53</v>
+      </c>
+      <c r="AG109">
+        <v>2.3</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.17</v>
+      </c>
+      <c r="AK109">
         <v>2.4</v>
-      </c>
-      <c r="S109">
-        <v>1.3</v>
-      </c>
-      <c r="T109">
-        <v>3.28</v>
-      </c>
-      <c r="U109">
-        <v>2.5</v>
-      </c>
-      <c r="V109">
-        <v>1.5</v>
-      </c>
-      <c r="W109">
-        <v>1.1</v>
-      </c>
-      <c r="X109">
-        <v>0</v>
-      </c>
-      <c r="Y109">
-        <v>1.17</v>
-      </c>
-      <c r="Z109">
-        <v>4.32</v>
-      </c>
-      <c r="AA109">
-        <v>1.65</v>
-      </c>
-      <c r="AB109">
-        <v>2.22</v>
-      </c>
-      <c r="AC109">
-        <v>2.49</v>
-      </c>
-      <c r="AD109">
-        <v>1.46</v>
-      </c>
-      <c r="AE109">
-        <v>1.17</v>
-      </c>
-      <c r="AF109">
-        <v>1.75</v>
-      </c>
-      <c r="AG109">
-        <v>1.95</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.14</v>
-      </c>
-      <c r="AK109">
-        <v>2.42</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,61 +18239,61 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O110">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="P110">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="Q110">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R110">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="S110">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="T110">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="U110">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V110">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W110">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>5.22</v>
+        <v>4.91</v>
       </c>
       <c r="AA110">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AB110">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="AC110">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD110">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE110">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF110">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
         <v>2.3</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU133"/>
+  <dimension ref="A1:AU132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>5.7</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X69">
         <v>0</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
         <v>0</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
         <v>0</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,34 +12217,34 @@
         <v>2.06</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA73">
         <v>2.25</v>
@@ -12253,19 +12253,19 @@
         <v>1.57</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>1.76</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
         <v>0</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>5.7</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
         <v>0</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,34 +16129,34 @@
         <v>2.42</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA97">
         <v>1.98</v>
@@ -16165,19 +16165,19 @@
         <v>1.83</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,34 +16292,34 @@
         <v>4.11</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AA98">
         <v>1.81</v>
@@ -16328,19 +16328,19 @@
         <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16944,40 +16944,40 @@
         <v>7.08</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC102">
         <v>1.9</v>
@@ -16986,13 +16986,13 @@
         <v>1.8</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -18411,55 +18411,55 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19226,34 +19226,34 @@
         <v>1.91</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA116">
         <v>1.87</v>
@@ -19262,19 +19262,19 @@
         <v>1.82</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">
@@ -21928,169 +21928,6 @@
         <v>0</v>
       </c>
       <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.93</v>
+        <v>3.12</v>
       </c>
       <c r="O54">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P54">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="Q54">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>1.57</v>
+      </c>
+      <c r="AB54">
+        <v>2.35</v>
+      </c>
+      <c r="AC54">
         <v>2.25</v>
       </c>
-      <c r="V54">
-        <v>1.57</v>
-      </c>
-      <c r="W54">
-        <v>1.11</v>
-      </c>
-      <c r="X54">
-        <v>1</v>
-      </c>
-      <c r="Y54">
-        <v>1.15</v>
-      </c>
-      <c r="Z54">
-        <v>4.58</v>
-      </c>
-      <c r="AA54">
-        <v>1.53</v>
-      </c>
-      <c r="AB54">
-        <v>2.3</v>
-      </c>
-      <c r="AC54">
-        <v>2.39</v>
-      </c>
       <c r="AD54">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE54">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.12</v>
+        <v>3.93</v>
       </c>
       <c r="O55">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P55">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AA55">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC55">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AD55">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
-        <v>4.02</v>
+        <v>3</v>
       </c>
       <c r="R66">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T66">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U66">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V66">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z66">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB66">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC66">
-        <v>3.53</v>
+        <v>3.46</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG66">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK66">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="O67">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
+        <v>2.11</v>
+      </c>
+      <c r="Q67">
+        <v>4.02</v>
+      </c>
+      <c r="R67">
+        <v>2.2</v>
+      </c>
+      <c r="S67">
+        <v>1.42</v>
+      </c>
+      <c r="T67">
         <v>2.8</v>
       </c>
-      <c r="Q67">
-        <v>3</v>
-      </c>
-      <c r="R67">
-        <v>2.1</v>
-      </c>
-      <c r="S67">
-        <v>1.44</v>
-      </c>
-      <c r="T67">
-        <v>2.68</v>
-      </c>
       <c r="U67">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V67">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z67">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="AA67">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB67">
+        <v>1.76</v>
+      </c>
+      <c r="AC67">
+        <v>3.53</v>
+      </c>
+      <c r="AD67">
+        <v>1.3</v>
+      </c>
+      <c r="AE67">
+        <v>1.06</v>
+      </c>
+      <c r="AF67">
         <v>1.78</v>
       </c>
-      <c r="AC67">
-        <v>3.46</v>
-      </c>
-      <c r="AD67">
-        <v>1.27</v>
-      </c>
-      <c r="AE67">
-        <v>1.04</v>
-      </c>
-      <c r="AF67">
-        <v>1.81</v>
-      </c>
       <c r="AG67">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12543,34 +12543,34 @@
         <v>3.33</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA75">
         <v>1.96</v>
@@ -12579,19 +12579,19 @@
         <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>4.95</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA76">
         <v>1.98</v>
@@ -12742,19 +12742,19 @@
         <v>1.81</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="O77">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="P77">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA77">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AB77">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>2.85</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
         <v>2.01</v>
@@ -13068,19 +13068,19 @@
         <v>1.79</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P79">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.85</v>
+        <v>1.55</v>
       </c>
       <c r="O91">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="P91">
-        <v>2.17</v>
+        <v>4.9</v>
       </c>
       <c r="Q91">
-        <v>3.23</v>
+        <v>1.99</v>
       </c>
       <c r="R91">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="S91">
+        <v>1.16</v>
+      </c>
+      <c r="T91">
+        <v>4.25</v>
+      </c>
+      <c r="U91">
+        <v>2.02</v>
+      </c>
+      <c r="V91">
+        <v>1.72</v>
+      </c>
+      <c r="W91">
         <v>1.17</v>
       </c>
-      <c r="T91">
-        <v>4.85</v>
-      </c>
-      <c r="U91">
-        <v>1.83</v>
-      </c>
-      <c r="V91">
-        <v>1.89</v>
-      </c>
-      <c r="W91">
-        <v>1.24</v>
-      </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z91">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA91">
+        <v>1.44</v>
+      </c>
+      <c r="AB91">
+        <v>2.7</v>
+      </c>
+      <c r="AC91">
+        <v>2.05</v>
+      </c>
+      <c r="AD91">
+        <v>1.71</v>
+      </c>
+      <c r="AE91">
         <v>1.25</v>
       </c>
-      <c r="AB91">
-        <v>3.28</v>
-      </c>
-      <c r="AC91">
-        <v>1.76</v>
-      </c>
-      <c r="AD91">
-        <v>1.98</v>
-      </c>
-      <c r="AE91">
-        <v>1.43</v>
-      </c>
       <c r="AF91">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AG91">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK91">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.55</v>
+        <v>2.21</v>
       </c>
       <c r="O92">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q92">
-        <v>1.99</v>
+        <v>2.69</v>
       </c>
       <c r="R92">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="S92">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T92">
-        <v>4.25</v>
+        <v>3.64</v>
       </c>
       <c r="U92">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V92">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W92">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z92">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA92">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB92">
         <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD92">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE92">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF92">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AG92">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="O94">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="Q94">
-        <v>2.69</v>
+        <v>3.23</v>
       </c>
       <c r="R94">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="S94">
+        <v>1.17</v>
+      </c>
+      <c r="T94">
+        <v>4.85</v>
+      </c>
+      <c r="U94">
+        <v>1.83</v>
+      </c>
+      <c r="V94">
+        <v>1.89</v>
+      </c>
+      <c r="W94">
+        <v>1.24</v>
+      </c>
+      <c r="X94">
+        <v>1.01</v>
+      </c>
+      <c r="Y94">
+        <v>1.03</v>
+      </c>
+      <c r="Z94">
+        <v>7.4</v>
+      </c>
+      <c r="AA94">
+        <v>1.25</v>
+      </c>
+      <c r="AB94">
+        <v>3.28</v>
+      </c>
+      <c r="AC94">
+        <v>1.76</v>
+      </c>
+      <c r="AD94">
+        <v>1.98</v>
+      </c>
+      <c r="AE94">
+        <v>1.43</v>
+      </c>
+      <c r="AF94">
+        <v>1.27</v>
+      </c>
+      <c r="AG94">
+        <v>3.42</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
         <v>1.21</v>
       </c>
-      <c r="T94">
-        <v>3.64</v>
-      </c>
-      <c r="U94">
-        <v>2.13</v>
-      </c>
-      <c r="V94">
-        <v>1.65</v>
-      </c>
-      <c r="W94">
-        <v>1.13</v>
-      </c>
-      <c r="X94">
-        <v>1.02</v>
-      </c>
-      <c r="Y94">
-        <v>1.08</v>
-      </c>
-      <c r="Z94">
-        <v>5.5</v>
-      </c>
-      <c r="AA94">
-        <v>1.4</v>
-      </c>
-      <c r="AB94">
-        <v>2.7</v>
-      </c>
-      <c r="AC94">
-        <v>2.11</v>
-      </c>
-      <c r="AD94">
-        <v>1.69</v>
-      </c>
-      <c r="AE94">
-        <v>1.23</v>
-      </c>
-      <c r="AF94">
+      <c r="AK94">
         <v>1.38</v>
-      </c>
-      <c r="AG94">
-        <v>2.81</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.23</v>
-      </c>
-      <c r="AK94">
-        <v>1.59</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.88</v>
+        <v>5.89</v>
       </c>
       <c r="O95">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="P95">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="Q95">
-        <v>3.45</v>
+        <v>5.59</v>
       </c>
       <c r="R95">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T95">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="U95">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="V95">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="W95">
+        <v>1.19</v>
+      </c>
+      <c r="X95">
+        <v>0</v>
+      </c>
+      <c r="Y95">
+        <v>1.08</v>
+      </c>
+      <c r="Z95">
+        <v>5.9</v>
+      </c>
+      <c r="AA95">
+        <v>1.43</v>
+      </c>
+      <c r="AB95">
+        <v>2.72</v>
+      </c>
+      <c r="AC95">
+        <v>2.05</v>
+      </c>
+      <c r="AD95">
+        <v>1.77</v>
+      </c>
+      <c r="AE95">
+        <v>1.3</v>
+      </c>
+      <c r="AF95">
+        <v>1.53</v>
+      </c>
+      <c r="AG95">
+        <v>2.32</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.11</v>
       </c>
-      <c r="X95">
-        <v>1.01</v>
-      </c>
-      <c r="Y95">
-        <v>1.17</v>
-      </c>
-      <c r="Z95">
-        <v>4.78</v>
-      </c>
-      <c r="AA95">
-        <v>1.53</v>
-      </c>
-      <c r="AB95">
-        <v>2.36</v>
-      </c>
-      <c r="AC95">
-        <v>2.33</v>
-      </c>
-      <c r="AD95">
-        <v>1.59</v>
-      </c>
-      <c r="AE95">
-        <v>1.21</v>
-      </c>
-      <c r="AF95">
-        <v>1.46</v>
-      </c>
-      <c r="AG95">
-        <v>2.5</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.2</v>
-      </c>
       <c r="AK95">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>5.89</v>
+        <v>2.88</v>
       </c>
       <c r="O96">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="P96">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="Q96">
-        <v>5.59</v>
+        <v>3.45</v>
       </c>
       <c r="R96">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="S96">
+        <v>1.25</v>
+      </c>
+      <c r="T96">
+        <v>3.42</v>
+      </c>
+      <c r="U96">
+        <v>2.28</v>
+      </c>
+      <c r="V96">
+        <v>1.62</v>
+      </c>
+      <c r="W96">
+        <v>1.11</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.17</v>
+      </c>
+      <c r="Z96">
+        <v>4.78</v>
+      </c>
+      <c r="AA96">
+        <v>1.53</v>
+      </c>
+      <c r="AB96">
+        <v>2.36</v>
+      </c>
+      <c r="AC96">
+        <v>2.33</v>
+      </c>
+      <c r="AD96">
+        <v>1.59</v>
+      </c>
+      <c r="AE96">
         <v>1.21</v>
       </c>
-      <c r="T96">
-        <v>3.96</v>
-      </c>
-      <c r="U96">
-        <v>2.05</v>
-      </c>
-      <c r="V96">
-        <v>1.77</v>
-      </c>
-      <c r="W96">
-        <v>1.19</v>
-      </c>
-      <c r="X96">
-        <v>0</v>
-      </c>
-      <c r="Y96">
-        <v>1.08</v>
-      </c>
-      <c r="Z96">
-        <v>5.9</v>
-      </c>
-      <c r="AA96">
-        <v>1.43</v>
-      </c>
-      <c r="AB96">
-        <v>2.72</v>
-      </c>
-      <c r="AC96">
-        <v>2.05</v>
-      </c>
-      <c r="AD96">
-        <v>1.77</v>
-      </c>
-      <c r="AE96">
-        <v>1.3</v>
-      </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG96">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16455,34 +16455,34 @@
         <v>3.5</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA99">
         <v>1.73</v>
@@ -16491,19 +16491,19 @@
         <v>1.98</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,55 +16618,55 @@
         <v>2.87</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>1.54</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,34 +17270,34 @@
         <v>3.41</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA104">
         <v>1.55</v>
@@ -17306,19 +17306,19 @@
         <v>2.3</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,80 +17913,80 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O108">
-        <v>3.64</v>
+        <v>4.03</v>
       </c>
       <c r="P108">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="Q108">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R108">
+        <v>2.66</v>
+      </c>
+      <c r="S108">
+        <v>1.21</v>
+      </c>
+      <c r="T108">
+        <v>3.75</v>
+      </c>
+      <c r="U108">
+        <v>2.15</v>
+      </c>
+      <c r="V108">
+        <v>1.6</v>
+      </c>
+      <c r="W108">
+        <v>1.17</v>
+      </c>
+      <c r="X108">
+        <v>0</v>
+      </c>
+      <c r="Y108">
+        <v>1.12</v>
+      </c>
+      <c r="Z108">
+        <v>5.22</v>
+      </c>
+      <c r="AA108">
+        <v>1.51</v>
+      </c>
+      <c r="AB108">
+        <v>2.51</v>
+      </c>
+      <c r="AC108">
+        <v>2.19</v>
+      </c>
+      <c r="AD108">
+        <v>1.67</v>
+      </c>
+      <c r="AE108">
+        <v>1.25</v>
+      </c>
+      <c r="AF108">
+        <v>1.53</v>
+      </c>
+      <c r="AG108">
+        <v>2.3</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108">
+        <v>1.17</v>
+      </c>
+      <c r="AK108">
         <v>2.4</v>
-      </c>
-      <c r="S108">
-        <v>1.3</v>
-      </c>
-      <c r="T108">
-        <v>3.28</v>
-      </c>
-      <c r="U108">
-        <v>2.5</v>
-      </c>
-      <c r="V108">
-        <v>1.5</v>
-      </c>
-      <c r="W108">
-        <v>1.1</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>1.17</v>
-      </c>
-      <c r="Z108">
-        <v>4.32</v>
-      </c>
-      <c r="AA108">
-        <v>1.65</v>
-      </c>
-      <c r="AB108">
-        <v>2.22</v>
-      </c>
-      <c r="AC108">
-        <v>2.49</v>
-      </c>
-      <c r="AD108">
-        <v>1.46</v>
-      </c>
-      <c r="AE108">
-        <v>1.17</v>
-      </c>
-      <c r="AF108">
-        <v>1.75</v>
-      </c>
-      <c r="AG108">
-        <v>1.95</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>1.14</v>
-      </c>
-      <c r="AK108">
-        <v>2.42</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,61 +18076,61 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O109">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="P109">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="Q109">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R109">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="S109">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="T109">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="U109">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V109">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>5.22</v>
+        <v>4.91</v>
       </c>
       <c r="AA109">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AB109">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="AC109">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD109">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE109">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
         <v>2.3</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18242,61 +18242,61 @@
         <v>1.81</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P110">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q110">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="R110">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="U110">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z110">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="AA110">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB110">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AC110">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD110">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF110">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG110">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19063,40 +19063,40 @@
         <v>6.51</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC115">
         <v>2.3</v>
@@ -19105,13 +19105,13 @@
         <v>1.55</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19552,34 +19552,34 @@
         <v>2.59</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA118">
         <v>2.35</v>
@@ -19588,19 +19588,19 @@
         <v>1.57</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P51">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,34 +11719,34 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.77</v>
+        <v>2.13</v>
       </c>
       <c r="O70">
-        <v>4.56</v>
+        <v>4.28</v>
       </c>
       <c r="P70">
-        <v>1.78</v>
+        <v>2.89</v>
       </c>
       <c r="Q70">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="R70">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T70">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U70">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V70">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W70">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>0</v>
@@ -11755,28 +11755,28 @@
         <v>1.08</v>
       </c>
       <c r="Z70">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA70">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AB70">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AD70">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE70">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF70">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AG70">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.13</v>
+        <v>3.04</v>
       </c>
       <c r="O71">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="P71">
-        <v>2.89</v>
+        <v>2.06</v>
       </c>
       <c r="Q71">
+        <v>3.45</v>
+      </c>
+      <c r="R71">
+        <v>2.4</v>
+      </c>
+      <c r="S71">
+        <v>1.23</v>
+      </c>
+      <c r="T71">
+        <v>3.78</v>
+      </c>
+      <c r="U71">
+        <v>2.11</v>
+      </c>
+      <c r="V71">
+        <v>1.72</v>
+      </c>
+      <c r="W71">
+        <v>1.18</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>1.1</v>
+      </c>
+      <c r="Z71">
+        <v>5.42</v>
+      </c>
+      <c r="AA71">
+        <v>1.47</v>
+      </c>
+      <c r="AB71">
+        <v>2.57</v>
+      </c>
+      <c r="AC71">
+        <v>2.15</v>
+      </c>
+      <c r="AD71">
+        <v>1.7</v>
+      </c>
+      <c r="AE71">
+        <v>1.27</v>
+      </c>
+      <c r="AF71">
+        <v>1.41</v>
+      </c>
+      <c r="AG71">
         <v>2.66</v>
       </c>
-      <c r="R71">
-        <v>2.62</v>
-      </c>
-      <c r="S71">
-        <v>1.21</v>
-      </c>
-      <c r="T71">
-        <v>3.9</v>
-      </c>
-      <c r="U71">
-        <v>2.05</v>
-      </c>
-      <c r="V71">
-        <v>1.7</v>
-      </c>
-      <c r="W71">
-        <v>1.2</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>1.08</v>
-      </c>
-      <c r="Z71">
-        <v>5.6</v>
-      </c>
-      <c r="AA71">
-        <v>1.38</v>
-      </c>
-      <c r="AB71">
-        <v>2.62</v>
-      </c>
-      <c r="AC71">
-        <v>1.97</v>
-      </c>
-      <c r="AD71">
-        <v>1.79</v>
-      </c>
-      <c r="AE71">
-        <v>1.34</v>
-      </c>
-      <c r="AF71">
-        <v>1.37</v>
-      </c>
-      <c r="AG71">
-        <v>2.75</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="AK71">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.04</v>
+        <v>3.77</v>
       </c>
       <c r="O72">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="P72">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="S72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="U72">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="V72">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
         <v>1.18</v>
@@ -12078,25 +12078,25 @@
         <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z72">
-        <v>5.42</v>
+        <v>6.1</v>
       </c>
       <c r="AA72">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB72">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="AC72">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD72">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE72">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF72">
         <v>1.41</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="AK72">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P77">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q77">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R77">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="V77">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W77">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z77">
-        <v>2.69</v>
+        <v>3.86</v>
       </c>
       <c r="AA77">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AB77">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
-        <v>4.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD77">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE77">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.32</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="O78">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="P78">
-        <v>2.85</v>
+        <v>3.72</v>
       </c>
       <c r="Q78">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U78">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="V78">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.36</v>
+      </c>
+      <c r="Z78">
+        <v>2.69</v>
+      </c>
+      <c r="AA78">
+        <v>2.29</v>
+      </c>
+      <c r="AB78">
+        <v>1.58</v>
+      </c>
+      <c r="AC78">
+        <v>4.25</v>
+      </c>
+      <c r="AD78">
+        <v>1.15</v>
+      </c>
+      <c r="AE78">
         <v>1</v>
       </c>
-      <c r="Y78">
-        <v>1.21</v>
-      </c>
-      <c r="Z78">
-        <v>3.58</v>
-      </c>
-      <c r="AA78">
-        <v>2.01</v>
-      </c>
-      <c r="AB78">
-        <v>1.79</v>
-      </c>
-      <c r="AC78">
-        <v>2.83</v>
-      </c>
-      <c r="AD78">
-        <v>1.33</v>
-      </c>
-      <c r="AE78">
-        <v>1.11</v>
-      </c>
       <c r="AF78">
+        <v>1.95</v>
+      </c>
+      <c r="AG78">
+        <v>1.75</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.32</v>
+      </c>
+      <c r="AK78">
         <v>1.62</v>
-      </c>
-      <c r="AG78">
-        <v>2.15</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.27</v>
-      </c>
-      <c r="AK78">
-        <v>1.63</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="O79">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P79">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q79">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U79">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W79">
+        <v>1.06</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>1.21</v>
+      </c>
+      <c r="Z79">
+        <v>3.58</v>
+      </c>
+      <c r="AA79">
+        <v>2.01</v>
+      </c>
+      <c r="AB79">
+        <v>1.79</v>
+      </c>
+      <c r="AC79">
+        <v>2.83</v>
+      </c>
+      <c r="AD79">
+        <v>1.33</v>
+      </c>
+      <c r="AE79">
         <v>1.11</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.18</v>
-      </c>
-      <c r="Z79">
-        <v>3.86</v>
-      </c>
-      <c r="AA79">
-        <v>1.93</v>
-      </c>
-      <c r="AB79">
-        <v>1.85</v>
-      </c>
-      <c r="AC79">
-        <v>2.74</v>
-      </c>
-      <c r="AD79">
-        <v>1.35</v>
-      </c>
-      <c r="AE79">
-        <v>1.09</v>
       </c>
       <c r="AF79">
         <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="O106">
-        <v>8.48</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>12.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q106">
+        <v>2.92</v>
+      </c>
+      <c r="R106">
+        <v>2.2</v>
+      </c>
+      <c r="S106">
+        <v>1.3</v>
+      </c>
+      <c r="T106">
+        <v>3.2</v>
+      </c>
+      <c r="U106">
+        <v>2.63</v>
+      </c>
+      <c r="V106">
+        <v>1.44</v>
+      </c>
+      <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106">
+        <v>1.24</v>
+      </c>
+      <c r="Z106">
+        <v>3.7</v>
+      </c>
+      <c r="AA106">
+        <v>1.8</v>
+      </c>
+      <c r="AB106">
+        <v>2.01</v>
+      </c>
+      <c r="AC106">
+        <v>2.85</v>
+      </c>
+      <c r="AD106">
         <v>1.4</v>
       </c>
-      <c r="R106">
-        <v>3.51</v>
-      </c>
-      <c r="S106">
-        <v>1.18</v>
-      </c>
-      <c r="T106">
-        <v>5</v>
-      </c>
-      <c r="U106">
-        <v>1.85</v>
-      </c>
-      <c r="V106">
-        <v>1.85</v>
-      </c>
-      <c r="W106">
-        <v>1.25</v>
-      </c>
-      <c r="X106">
-        <v>0</v>
-      </c>
-      <c r="Y106">
-        <v>1.03</v>
-      </c>
-      <c r="Z106">
-        <v>8.1</v>
-      </c>
-      <c r="AA106">
-        <v>1.28</v>
-      </c>
-      <c r="AB106">
-        <v>3.4</v>
-      </c>
-      <c r="AC106">
-        <v>1.76</v>
-      </c>
-      <c r="AD106">
-        <v>2.06</v>
-      </c>
       <c r="AE106">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>4.03</v>
       </c>
       <c r="P107">
-        <v>2.76</v>
+        <v>3.98</v>
       </c>
       <c r="Q107">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="S107">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T107">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U107">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V107">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X107">
         <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z107">
-        <v>3.7</v>
+        <v>5.22</v>
       </c>
       <c r="AA107">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AB107">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="AC107">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="AD107">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF107">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG107">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK107">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="O108">
-        <v>4.03</v>
+        <v>8.48</v>
       </c>
       <c r="P108">
-        <v>3.98</v>
+        <v>12.7</v>
       </c>
       <c r="Q108">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="R108">
-        <v>2.66</v>
+        <v>3.51</v>
       </c>
       <c r="S108">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T108">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U108">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="V108">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W108">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X108">
         <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z108">
-        <v>5.22</v>
+        <v>8.1</v>
       </c>
       <c r="AA108">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AB108">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="AC108">
-        <v>2.19</v>
+        <v>1.76</v>
       </c>
       <c r="AD108">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AE108">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AF108">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG108">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18079,61 +18079,61 @@
         <v>1.81</v>
       </c>
       <c r="O109">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P109">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q109">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="R109">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="U109">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z109">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="AA109">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB109">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AC109">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD109">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE109">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK109">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110">
@@ -18242,61 +18242,61 @@
         <v>1.81</v>
       </c>
       <c r="O110">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P110">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="Q110">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="R110">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T110">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="U110">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V110">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>4.32</v>
+        <v>4.91</v>
       </c>
       <c r="AA110">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB110">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AC110">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AD110">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE110">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF110">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19715,55 +19715,55 @@
         <v>4.13</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X119">
         <v>0</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.04</v>
+        <v>3.77</v>
       </c>
       <c r="O71">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="P71">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q71">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="R71">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="S71">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="U71">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="V71">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W71">
         <v>1.18</v>
@@ -11915,25 +11915,25 @@
         <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.42</v>
+        <v>6.1</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB71">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="AC71">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD71">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE71">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF71">
         <v>1.41</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="AK71">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.77</v>
+        <v>3.04</v>
       </c>
       <c r="O72">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="P72">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="Q72">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R72">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T72">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="U72">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="V72">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W72">
         <v>1.18</v>
@@ -12078,25 +12078,25 @@
         <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>6.1</v>
+        <v>5.42</v>
       </c>
       <c r="AA72">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="AC72">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD72">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE72">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF72">
         <v>1.41</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.16</v>
+        <v>1.73</v>
       </c>
       <c r="AK72">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="O78">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P78">
-        <v>3.72</v>
+        <v>2.85</v>
       </c>
       <c r="Q78">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="R78">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
+        <v>1.33</v>
+      </c>
+      <c r="T78">
+        <v>3.2</v>
+      </c>
+      <c r="U78">
+        <v>2.57</v>
+      </c>
+      <c r="V78">
         <v>1.43</v>
       </c>
-      <c r="T78">
-        <v>2.7</v>
-      </c>
-      <c r="U78">
-        <v>3.3</v>
-      </c>
-      <c r="V78">
-        <v>1.29</v>
-      </c>
       <c r="W78">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="AB78">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AC78">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="O79">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="P79">
-        <v>2.85</v>
+        <v>3.72</v>
       </c>
       <c r="Q79">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="V79">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
+        <v>1.36</v>
+      </c>
+      <c r="Z79">
+        <v>2.69</v>
+      </c>
+      <c r="AA79">
+        <v>2.29</v>
+      </c>
+      <c r="AB79">
+        <v>1.58</v>
+      </c>
+      <c r="AC79">
+        <v>4.25</v>
+      </c>
+      <c r="AD79">
+        <v>1.15</v>
+      </c>
+      <c r="AE79">
         <v>1</v>
       </c>
-      <c r="Y79">
-        <v>1.21</v>
-      </c>
-      <c r="Z79">
-        <v>3.58</v>
-      </c>
-      <c r="AA79">
-        <v>2.01</v>
-      </c>
-      <c r="AB79">
-        <v>1.79</v>
-      </c>
-      <c r="AC79">
-        <v>2.83</v>
-      </c>
-      <c r="AD79">
-        <v>1.33</v>
-      </c>
-      <c r="AE79">
-        <v>1.11</v>
-      </c>
       <c r="AF79">
+        <v>1.95</v>
+      </c>
+      <c r="AG79">
+        <v>1.75</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.32</v>
+      </c>
+      <c r="AK79">
         <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.15</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.27</v>
-      </c>
-      <c r="AK79">
-        <v>1.63</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109">
@@ -18079,61 +18079,61 @@
         <v>1.81</v>
       </c>
       <c r="O109">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P109">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="Q109">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T109">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="U109">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V109">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>4.32</v>
+        <v>4.91</v>
       </c>
       <c r="AA109">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB109">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AC109">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AD109">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE109">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18242,61 +18242,61 @@
         <v>1.81</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P110">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q110">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="R110">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="U110">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V110">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z110">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="AA110">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB110">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AC110">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD110">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF110">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG110">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1649,22 +1649,22 @@
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.07</v>
+        <v>3.72</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AB8">
         <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AD8">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
         <v>1.58</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="O31">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P31">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q31">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T31">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V31">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
         <v>1.15</v>
@@ -5416,10 +5416,10 @@
         <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.15</v>
       </c>
       <c r="AK31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="O34">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="P34">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="Q34">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="R34">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="S34">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="T34">
         <v>2.39</v>
       </c>
       <c r="U34">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="V34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z34">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AA34">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AB34">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AC34">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="AD34">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE34">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF34">
         <v>2.02</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6186,13 +6186,13 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="R36">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
         <v>3</v>
@@ -6201,7 +6201,7 @@
         <v>2.72</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.04</v>
@@ -6210,25 +6210,25 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z36">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC36">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
         <v>1.73</v>
@@ -6250,7 +6250,7 @@
         <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O37">
         <v>3.25</v>
@@ -6349,55 +6349,55 @@
         <v>2.8</v>
       </c>
       <c r="Q37">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U37">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="V37">
         <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AA37">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB37">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC37">
         <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6675,16 +6675,16 @@
         <v>1.55</v>
       </c>
       <c r="Q39">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S39">
         <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U39">
         <v>2.05</v>
@@ -6696,28 +6696,28 @@
         <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC39">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
         <v>1.5</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="AK39">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,19 +6835,19 @@
         <v>5.2</v>
       </c>
       <c r="P40">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Q40">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="R40">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="S40">
         <v>1.15</v>
       </c>
       <c r="T40">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="U40">
         <v>1.95</v>
@@ -6856,7 +6856,7 @@
         <v>1.73</v>
       </c>
       <c r="W40">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6883,10 +6883,10 @@
         <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
         <v>1.09</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O41">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="P41">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="Q41">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7028,19 +7028,19 @@
         <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB41">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC41">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD41">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
         <v>1.07</v>
@@ -7049,7 +7049,7 @@
         <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>3.75</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>3.25</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>2.24</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11586,7 +11586,7 @@
         <v>1.29</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
         <v>1.01</v>
@@ -11749,7 +11749,7 @@
         <v>1.2</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.08</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,58 +11882,58 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.77</v>
+        <v>3.04</v>
       </c>
       <c r="O71">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="P71">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="Q71">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R71">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T71">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="U71">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="V71">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W71">
         <v>1.18</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>6.1</v>
+        <v>5.42</v>
       </c>
       <c r="AA71">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB71">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="AC71">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD71">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE71">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF71">
         <v>1.41</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.16</v>
+        <v>1.73</v>
       </c>
       <c r="AK71">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,58 +12045,58 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.04</v>
+        <v>3.77</v>
       </c>
       <c r="O72">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="P72">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="S72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="U72">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="V72">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W72">
         <v>1.18</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z72">
-        <v>5.42</v>
+        <v>6.1</v>
       </c>
       <c r="AA72">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB72">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="AC72">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD72">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE72">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF72">
         <v>1.41</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="AK72">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="O78">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="P78">
-        <v>2.85</v>
+        <v>3.72</v>
       </c>
       <c r="Q78">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U78">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="V78">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.36</v>
+      </c>
+      <c r="Z78">
+        <v>2.69</v>
+      </c>
+      <c r="AA78">
+        <v>2.29</v>
+      </c>
+      <c r="AB78">
+        <v>1.58</v>
+      </c>
+      <c r="AC78">
+        <v>4.25</v>
+      </c>
+      <c r="AD78">
+        <v>1.15</v>
+      </c>
+      <c r="AE78">
         <v>1</v>
       </c>
-      <c r="Y78">
-        <v>1.21</v>
-      </c>
-      <c r="Z78">
-        <v>3.58</v>
-      </c>
-      <c r="AA78">
-        <v>2.01</v>
-      </c>
-      <c r="AB78">
-        <v>1.79</v>
-      </c>
-      <c r="AC78">
-        <v>2.83</v>
-      </c>
-      <c r="AD78">
-        <v>1.33</v>
-      </c>
-      <c r="AE78">
-        <v>1.11</v>
-      </c>
       <c r="AF78">
+        <v>1.95</v>
+      </c>
+      <c r="AG78">
+        <v>1.75</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.32</v>
+      </c>
+      <c r="AK78">
         <v>1.62</v>
-      </c>
-      <c r="AG78">
-        <v>2.15</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.27</v>
-      </c>
-      <c r="AK78">
-        <v>1.63</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="O79">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P79">
-        <v>3.72</v>
+        <v>2.85</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="R79">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
+        <v>1.33</v>
+      </c>
+      <c r="T79">
+        <v>3.2</v>
+      </c>
+      <c r="U79">
+        <v>2.57</v>
+      </c>
+      <c r="V79">
         <v>1.43</v>
       </c>
-      <c r="T79">
-        <v>2.7</v>
-      </c>
-      <c r="U79">
-        <v>3.3</v>
-      </c>
-      <c r="V79">
-        <v>1.29</v>
-      </c>
       <c r="W79">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="AB79">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AC79">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD79">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.9</v>
+        <v>1.37</v>
       </c>
       <c r="O89">
-        <v>3.78</v>
+        <v>5.6</v>
       </c>
       <c r="P89">
-        <v>2.24</v>
+        <v>7</v>
       </c>
       <c r="Q89">
-        <v>3.22</v>
+        <v>1.75</v>
       </c>
       <c r="R89">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S89">
         <v>1.18</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="U89">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>5.85</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB89">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AC89">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AD89">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF89">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK89">
-        <v>1.41</v>
+        <v>3.05</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="O90">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="P90">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="Q90">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="S90">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T90">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V90">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="AA90">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE90">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG90">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK90">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.55</v>
+        <v>2.21</v>
       </c>
       <c r="O91">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P91">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>1.99</v>
+        <v>2.69</v>
       </c>
       <c r="R91">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="S91">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T91">
-        <v>4.25</v>
+        <v>3.64</v>
       </c>
       <c r="U91">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V91">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z91">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
         <v>2.7</v>
       </c>
       <c r="AC91">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD91">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE91">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF91">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AG91">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK91">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P92">
+        <v>4.3</v>
+      </c>
+      <c r="Q92">
+        <v>1.91</v>
+      </c>
+      <c r="R92">
         <v>2.8</v>
       </c>
-      <c r="Q92">
-        <v>2.69</v>
-      </c>
-      <c r="R92">
-        <v>2.34</v>
-      </c>
       <c r="S92">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="T92">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="U92">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="V92">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="W92">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z92">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA92">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB92">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="AC92">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AD92">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="AE92">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AF92">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AG92">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK92">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.66</v>
+        <v>2.85</v>
       </c>
       <c r="O93">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P93">
-        <v>4.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q93">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="R93">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="S93">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T93">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="U93">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V93">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W93">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z93">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB93">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="AC93">
         <v>1.76</v>
       </c>
       <c r="AD93">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AE93">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF93">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AG93">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK93">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O94">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="P94">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="Q94">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="R94">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S94">
+        <v>1.18</v>
+      </c>
+      <c r="T94">
+        <v>3.9</v>
+      </c>
+      <c r="U94">
+        <v>2.03</v>
+      </c>
+      <c r="V94">
+        <v>1.71</v>
+      </c>
+      <c r="W94">
         <v>1.17</v>
       </c>
-      <c r="T94">
-        <v>4.85</v>
-      </c>
-      <c r="U94">
-        <v>1.83</v>
-      </c>
-      <c r="V94">
-        <v>1.89</v>
-      </c>
-      <c r="W94">
-        <v>1.24</v>
-      </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA94">
+        <v>1.4</v>
+      </c>
+      <c r="AB94">
+        <v>2.56</v>
+      </c>
+      <c r="AC94">
+        <v>2.09</v>
+      </c>
+      <c r="AD94">
+        <v>1.68</v>
+      </c>
+      <c r="AE94">
         <v>1.25</v>
       </c>
-      <c r="AB94">
-        <v>3.28</v>
-      </c>
-      <c r="AC94">
-        <v>1.76</v>
-      </c>
-      <c r="AD94">
-        <v>1.98</v>
-      </c>
-      <c r="AE94">
-        <v>1.43</v>
-      </c>
       <c r="AF94">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AG94">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15824,7 +15824,7 @@
         <v>1.19</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.08</v>
@@ -17128,7 +17128,7 @@
         <v>1.14</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
         <v>1.17</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18079,61 +18079,61 @@
         <v>1.81</v>
       </c>
       <c r="O109">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P109">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q109">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="R109">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="U109">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z109">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
       <c r="AA109">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB109">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AC109">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD109">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE109">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK109">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110">
@@ -18242,61 +18242,61 @@
         <v>1.81</v>
       </c>
       <c r="O110">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P110">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="Q110">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="R110">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T110">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="U110">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V110">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>4.32</v>
+        <v>4.91</v>
       </c>
       <c r="AA110">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB110">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AC110">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AD110">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE110">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF110">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X120">
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G122">
@@ -20204,55 +20204,55 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G123">
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE124">
         <v>0</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="R2">
         <v>2.1</v>
@@ -656,10 +656,10 @@
         <v>3.02</v>
       </c>
       <c r="U2">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA2">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC2">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AD2">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="O3">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T3">
         <v>3.24</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V3">
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC3">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AD3">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T4">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="U4">
         <v>3.3</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z4">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AB4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC4">
-        <v>4.32</v>
+        <v>4.65</v>
       </c>
       <c r="AD4">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE4">
         <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG4">
         <v>1.7</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,58 +1124,58 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="U5">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
         <v>1.02</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
       <c r="Y5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="AD5">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
         <v>1.97</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>3.89</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="AA6">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC6">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AK6">
         <v>1.3</v>
@@ -1459,49 +1459,49 @@
         <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U7">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z7">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="O9">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="P9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q9">
+        <v>2.32</v>
+      </c>
+      <c r="R9">
+        <v>2.38</v>
+      </c>
+      <c r="S9">
+        <v>1.25</v>
+      </c>
+      <c r="T9">
+        <v>3.6</v>
+      </c>
+      <c r="U9">
         <v>2.3</v>
       </c>
-      <c r="R9">
-        <v>2.4</v>
-      </c>
-      <c r="S9">
-        <v>1.24</v>
-      </c>
-      <c r="T9">
-        <v>3.4</v>
-      </c>
-      <c r="U9">
-        <v>2.21</v>
-      </c>
       <c r="V9">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC9">
         <v>2.3</v>
       </c>
       <c r="AD9">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
         <v>1.87</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>2.77</v>
@@ -1969,34 +1969,34 @@
         <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
         <v>1.69</v>
@@ -2274,55 +2274,55 @@
         <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>5.23</v>
+        <v>5.5</v>
       </c>
       <c r="R12">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S12">
         <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
         <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.46</v>
+        <v>5.65</v>
       </c>
       <c r="AA12">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AB12">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD12">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE12">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG12">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
         <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.14</v>
+        <v>4.66</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB13">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AC13">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="AD13">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,58 +2754,58 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
+        <v>4</v>
+      </c>
+      <c r="P15">
+        <v>2.41</v>
+      </c>
+      <c r="Q15">
+        <v>2.7</v>
+      </c>
+      <c r="R15">
+        <v>2.49</v>
+      </c>
+      <c r="S15">
+        <v>1.18</v>
+      </c>
+      <c r="T15">
         <v>4.4</v>
       </c>
-      <c r="P15">
-        <v>2.28</v>
-      </c>
-      <c r="Q15">
-        <v>3.09</v>
-      </c>
-      <c r="R15">
-        <v>2.62</v>
-      </c>
-      <c r="S15">
-        <v>1.13</v>
-      </c>
-      <c r="T15">
-        <v>4.65</v>
-      </c>
       <c r="U15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V15">
         <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>7.13</v>
+        <v>6.57</v>
       </c>
       <c r="AA15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB15">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD15">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE15">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AF15">
         <v>1.33</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>12.1</v>
+        <v>13</v>
       </c>
       <c r="O52">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
       <c r="P52">
         <v>1.2</v>
       </c>
       <c r="Q52">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="R52">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W52">
         <v>1.14</v>
@@ -8818,10 +8818,10 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA52">
         <v>1.5</v>
@@ -8830,19 +8830,19 @@
         <v>2.5</v>
       </c>
       <c r="AC52">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AD52">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE52">
         <v>1.23</v>
       </c>
       <c r="AF52">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AG52">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="O64">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q64">
         <v>3.2</v>
@@ -10762,10 +10762,10 @@
         <v>4.1</v>
       </c>
       <c r="U64">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V64">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
         <v>1.17</v>
@@ -10774,31 +10774,31 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB64">
         <v>2.7</v>
       </c>
       <c r="AC64">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AD64">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE64">
         <v>1.29</v>
       </c>
       <c r="AF64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG64">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK64">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O65">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="Q65">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R65">
         <v>2.38</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T65">
         <v>3.55</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="V65">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA65">
         <v>1.57</v>
       </c>
       <c r="AB65">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC65">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD65">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>1.17</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
         <v>1.14</v>
@@ -13705,7 +13705,7 @@
         <v>1.14</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.15</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O105">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="P105">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q105">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U105">
         <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W105">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB105">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AC105">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD105">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE105">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG105">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK105">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,19 +17587,19 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="Q106">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="R106">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
         <v>1.3</v>
@@ -17608,59 +17608,59 @@
         <v>3.2</v>
       </c>
       <c r="U106">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="V106">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W106">
         <v>1.06</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
+        <v>1.2</v>
+      </c>
+      <c r="Z106">
+        <v>3.68</v>
+      </c>
+      <c r="AA106">
+        <v>1.74</v>
+      </c>
+      <c r="AB106">
+        <v>1.94</v>
+      </c>
+      <c r="AC106">
+        <v>2.78</v>
+      </c>
+      <c r="AD106">
+        <v>1.34</v>
+      </c>
+      <c r="AE106">
+        <v>1.15</v>
+      </c>
+      <c r="AF106">
+        <v>1.6</v>
+      </c>
+      <c r="AG106">
+        <v>2.18</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.24</v>
       </c>
-      <c r="Z106">
-        <v>3.7</v>
-      </c>
-      <c r="AA106">
-        <v>1.8</v>
-      </c>
-      <c r="AB106">
-        <v>2.01</v>
-      </c>
-      <c r="AC106">
-        <v>2.85</v>
-      </c>
-      <c r="AD106">
-        <v>1.4</v>
-      </c>
-      <c r="AE106">
-        <v>1.11</v>
-      </c>
-      <c r="AF106">
-        <v>1.62</v>
-      </c>
-      <c r="AG106">
-        <v>2.15</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.22</v>
-      </c>
       <c r="AK106">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,61 +17750,61 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="O107">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="P107">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R107">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="S107">
         <v>1.21</v>
       </c>
       <c r="T107">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U107">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V107">
+        <v>1.63</v>
+      </c>
+      <c r="W107">
+        <v>1.12</v>
+      </c>
+      <c r="X107">
+        <v>1.02</v>
+      </c>
+      <c r="Y107">
+        <v>1.09</v>
+      </c>
+      <c r="Z107">
+        <v>5.11</v>
+      </c>
+      <c r="AA107">
+        <v>1.43</v>
+      </c>
+      <c r="AB107">
+        <v>2.52</v>
+      </c>
+      <c r="AC107">
+        <v>2.23</v>
+      </c>
+      <c r="AD107">
         <v>1.6</v>
-      </c>
-      <c r="W107">
-        <v>1.17</v>
-      </c>
-      <c r="X107">
-        <v>0</v>
-      </c>
-      <c r="Y107">
-        <v>1.12</v>
-      </c>
-      <c r="Z107">
-        <v>5.22</v>
-      </c>
-      <c r="AA107">
-        <v>1.51</v>
-      </c>
-      <c r="AB107">
-        <v>2.51</v>
-      </c>
-      <c r="AC107">
-        <v>2.19</v>
-      </c>
-      <c r="AD107">
-        <v>1.67</v>
       </c>
       <c r="AE107">
         <v>1.25</v>
       </c>
       <c r="AF107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG107">
         <v>2.3</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK107">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O108">
-        <v>8.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P108">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="Q108">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R108">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="S108">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T108">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="U108">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="V108">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="W108">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X108">
         <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z108">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA108">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AB108">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AC108">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AD108">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE108">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AF108">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG108">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="O109">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="Q109">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T109">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="U109">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V109">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>4.32</v>
+        <v>4.6</v>
       </c>
       <c r="AA109">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB109">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC109">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD109">
         <v>1.46</v>
       </c>
       <c r="AE109">
+        <v>1.15</v>
+      </c>
+      <c r="AF109">
+        <v>1.57</v>
+      </c>
+      <c r="AG109">
+        <v>2.3</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.17</v>
       </c>
-      <c r="AF109">
-        <v>1.75</v>
-      </c>
-      <c r="AG109">
-        <v>1.95</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.14</v>
-      </c>
       <c r="AK109">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P110">
-        <v>3.74</v>
+        <v>5.8</v>
       </c>
       <c r="Q110">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="R110">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U110">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V110">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W110">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
         <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>4.91</v>
+        <v>4.15</v>
       </c>
       <c r="AA110">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB110">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC110">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD110">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE110">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF110">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG110">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19736,7 +19736,7 @@
         <v>1.06</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
         <v>1.24</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G121">
@@ -20041,56 +20041,56 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>2.9</v>
+        <v>5.78</v>
       </c>
       <c r="R121">
         <v>2</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T121">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U121">
         <v>3.2</v>
       </c>
       <c r="V121">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
         <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z121">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA121">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB121">
+        <v>1.57</v>
+      </c>
+      <c r="AC121">
+        <v>4.3</v>
+      </c>
+      <c r="AD121">
+        <v>1.16</v>
+      </c>
+      <c r="AE121">
+        <v>1.02</v>
+      </c>
+      <c r="AF121">
+        <v>2.2</v>
+      </c>
+      <c r="AG121">
         <v>1.61</v>
       </c>
-      <c r="AC121">
-        <v>4.5</v>
-      </c>
-      <c r="AD121">
-        <v>1.17</v>
-      </c>
-      <c r="AE121">
-        <v>1.05</v>
-      </c>
-      <c r="AF121">
-        <v>2</v>
-      </c>
-      <c r="AG121">
-        <v>1.77</v>
-      </c>
       <c r="AH121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q122">
-        <v>5.78</v>
+        <v>2.65</v>
       </c>
       <c r="R122">
         <v>2</v>
       </c>
       <c r="S122">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U122">
         <v>3.2</v>
       </c>
       <c r="V122">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
         <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z122">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AA122">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB122">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC122">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD122">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE122">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF122">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG122">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK122">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,16 +20521,16 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R124">
         <v>2</v>
@@ -20572,13 +20572,13 @@
         <v>1.17</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF124">
         <v>2</v>
       </c>
       <c r="AG124">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK124">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL124">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P49">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q49">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
+        <v>2.38</v>
+      </c>
+      <c r="S49">
+        <v>1.25</v>
+      </c>
+      <c r="T49">
+        <v>3.4</v>
+      </c>
+      <c r="U49">
         <v>2.3</v>
       </c>
-      <c r="S49">
-        <v>1.3</v>
-      </c>
-      <c r="T49">
-        <v>3.3</v>
-      </c>
-      <c r="U49">
-        <v>2.4</v>
-      </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
         <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="O50">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB51">
+        <v>2.07</v>
+      </c>
+      <c r="AC51">
+        <v>2.7</v>
+      </c>
+      <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.1</v>
+      </c>
+      <c r="AF51">
+        <v>1.67</v>
+      </c>
+      <c r="AG51">
+        <v>2.05</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.29</v>
+      </c>
+      <c r="AK51">
         <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>2.97</v>
-      </c>
-      <c r="AD51">
-        <v>1.3</v>
-      </c>
-      <c r="AE51">
-        <v>1.07</v>
-      </c>
-      <c r="AF51">
-        <v>1.62</v>
-      </c>
-      <c r="AG51">
-        <v>2.15</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.3</v>
-      </c>
-      <c r="AK51">
-        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P56">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA56">
+        <v>1.55</v>
+      </c>
+      <c r="AB56">
+        <v>2.25</v>
+      </c>
+      <c r="AC56">
+        <v>2.34</v>
+      </c>
+      <c r="AD56">
+        <v>1.46</v>
+      </c>
+      <c r="AE56">
+        <v>1.17</v>
+      </c>
+      <c r="AF56">
         <v>1.53</v>
       </c>
-      <c r="AB56">
-        <v>2.33</v>
-      </c>
-      <c r="AC56">
-        <v>2.25</v>
-      </c>
-      <c r="AD56">
-        <v>1.55</v>
-      </c>
-      <c r="AE56">
-        <v>1.18</v>
-      </c>
-      <c r="AF56">
-        <v>1.44</v>
-      </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O57">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P57">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q57">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U57">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z57">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
+        <v>1.53</v>
+      </c>
+      <c r="AB57">
+        <v>2.33</v>
+      </c>
+      <c r="AC57">
+        <v>2.25</v>
+      </c>
+      <c r="AD57">
         <v>1.55</v>
       </c>
-      <c r="AB57">
-        <v>2.25</v>
-      </c>
-      <c r="AC57">
-        <v>2.34</v>
-      </c>
-      <c r="AD57">
-        <v>1.46</v>
-      </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123">
@@ -20367,7 +20367,7 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="R123">
         <v>2</v>
@@ -20379,59 +20379,59 @@
         <v>2.63</v>
       </c>
       <c r="U123">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V123">
+        <v>1.3</v>
+      </c>
+      <c r="W123">
+        <v>1.05</v>
+      </c>
+      <c r="X123">
+        <v>1.05</v>
+      </c>
+      <c r="Y123">
+        <v>1.4</v>
+      </c>
+      <c r="Z123">
+        <v>2.75</v>
+      </c>
+      <c r="AA123">
+        <v>2.25</v>
+      </c>
+      <c r="AB123">
+        <v>1.61</v>
+      </c>
+      <c r="AC123">
+        <v>4.5</v>
+      </c>
+      <c r="AD123">
+        <v>1.17</v>
+      </c>
+      <c r="AE123">
+        <v>1.05</v>
+      </c>
+      <c r="AF123">
+        <v>2</v>
+      </c>
+      <c r="AG123">
+        <v>1.77</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
         <v>1.32</v>
       </c>
-      <c r="W123">
-        <v>1.04</v>
-      </c>
-      <c r="X123">
-        <v>1.04</v>
-      </c>
-      <c r="Y123">
-        <v>1.37</v>
-      </c>
-      <c r="Z123">
-        <v>2.8</v>
-      </c>
-      <c r="AA123">
-        <v>2.2</v>
-      </c>
-      <c r="AB123">
-        <v>1.65</v>
-      </c>
-      <c r="AC123">
-        <v>3.9</v>
-      </c>
-      <c r="AD123">
-        <v>1.2</v>
-      </c>
-      <c r="AE123">
-        <v>1.03</v>
-      </c>
-      <c r="AF123">
-        <v>1.95</v>
-      </c>
-      <c r="AG123">
-        <v>1.78</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.3</v>
-      </c>
       <c r="AK123">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20530,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="R124">
         <v>2</v>
@@ -20542,59 +20542,59 @@
         <v>2.63</v>
       </c>
       <c r="U124">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V124">
+        <v>1.32</v>
+      </c>
+      <c r="W124">
+        <v>1.04</v>
+      </c>
+      <c r="X124">
+        <v>1.04</v>
+      </c>
+      <c r="Y124">
+        <v>1.37</v>
+      </c>
+      <c r="Z124">
+        <v>2.8</v>
+      </c>
+      <c r="AA124">
+        <v>2.2</v>
+      </c>
+      <c r="AB124">
+        <v>1.65</v>
+      </c>
+      <c r="AC124">
+        <v>3.9</v>
+      </c>
+      <c r="AD124">
+        <v>1.2</v>
+      </c>
+      <c r="AE124">
+        <v>1.03</v>
+      </c>
+      <c r="AF124">
+        <v>1.95</v>
+      </c>
+      <c r="AG124">
+        <v>1.78</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.3</v>
       </c>
-      <c r="W124">
-        <v>1.05</v>
-      </c>
-      <c r="X124">
-        <v>1.05</v>
-      </c>
-      <c r="Y124">
-        <v>1.4</v>
-      </c>
-      <c r="Z124">
-        <v>2.75</v>
-      </c>
-      <c r="AA124">
-        <v>2.25</v>
-      </c>
-      <c r="AB124">
-        <v>1.61</v>
-      </c>
-      <c r="AC124">
-        <v>4.5</v>
-      </c>
-      <c r="AD124">
-        <v>1.17</v>
-      </c>
-      <c r="AE124">
-        <v>1.05</v>
-      </c>
-      <c r="AF124">
-        <v>2</v>
-      </c>
-      <c r="AG124">
-        <v>1.77</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.32</v>
-      </c>
       <c r="AK124">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AL124">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="O56">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="P56">
-        <v>3.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q56">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA56">
+        <v>1.53</v>
+      </c>
+      <c r="AB56">
+        <v>2.33</v>
+      </c>
+      <c r="AC56">
+        <v>2.25</v>
+      </c>
+      <c r="AD56">
         <v>1.55</v>
       </c>
-      <c r="AB56">
-        <v>2.25</v>
-      </c>
-      <c r="AC56">
-        <v>2.34</v>
-      </c>
-      <c r="AD56">
-        <v>1.46</v>
-      </c>
       <c r="AE56">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.61</v>
+        <v>1.86</v>
       </c>
       <c r="O57">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="P57">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="Q57">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA57">
+        <v>1.55</v>
+      </c>
+      <c r="AB57">
+        <v>2.25</v>
+      </c>
+      <c r="AC57">
+        <v>2.34</v>
+      </c>
+      <c r="AD57">
+        <v>1.46</v>
+      </c>
+      <c r="AE57">
+        <v>1.17</v>
+      </c>
+      <c r="AF57">
         <v>1.53</v>
       </c>
-      <c r="AB57">
-        <v>2.33</v>
-      </c>
-      <c r="AC57">
-        <v>2.25</v>
-      </c>
-      <c r="AD57">
-        <v>1.55</v>
-      </c>
-      <c r="AE57">
-        <v>1.18</v>
-      </c>
-      <c r="AF57">
-        <v>1.44</v>
-      </c>
       <c r="AG57">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -4248,7 +4248,7 @@
         <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.03</v>
@@ -4260,10 +4260,10 @@
         <v>2.81</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB24">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC24">
         <v>3.7</v>
@@ -4272,7 +4272,7 @@
         <v>1.2</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
         <v>1.83</v>
@@ -5066,7 +5066,7 @@
         <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>1.36</v>
@@ -5078,7 +5078,7 @@
         <v>2.18</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC29">
         <v>3.94</v>
@@ -5229,7 +5229,7 @@
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
         <v>1.35</v>
@@ -5238,10 +5238,10 @@
         <v>2.74</v>
       </c>
       <c r="AA30">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB30">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC30">
         <v>4.15</v>
@@ -5371,49 +5371,49 @@
         <v>1.54</v>
       </c>
       <c r="Q31">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA31">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AB31">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AC31">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AD31">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE31">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
         <v>1.58</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="O39">
-        <v>4.89</v>
+        <v>4.1</v>
       </c>
       <c r="P39">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Q39">
         <v>5.25</v>
       </c>
       <c r="R39">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.22</v>
@@ -6832,7 +6832,7 @@
         <v>6.4</v>
       </c>
       <c r="O40">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="P40">
         <v>1.39</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="O41">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.36</v>
+        <v>4.5</v>
       </c>
       <c r="Q41">
         <v>2.25</v>
@@ -7194,7 +7194,7 @@
         <v>5.1</v>
       </c>
       <c r="AA42">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB42">
         <v>2.6</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
         <v>1.67</v>
@@ -7653,22 +7653,22 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="R45">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="S45">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U45">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
         <v>1.13</v>
@@ -7677,47 +7677,47 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
+        <v>1.18</v>
+      </c>
+      <c r="Z45">
+        <v>4.57</v>
+      </c>
+      <c r="AA45">
+        <v>1.58</v>
+      </c>
+      <c r="AB45">
+        <v>2.29</v>
+      </c>
+      <c r="AC45">
+        <v>2.45</v>
+      </c>
+      <c r="AD45">
+        <v>1.53</v>
+      </c>
+      <c r="AE45">
+        <v>1.2</v>
+      </c>
+      <c r="AF45">
+        <v>1.99</v>
+      </c>
+      <c r="AG45">
+        <v>1.71</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.13</v>
       </c>
-      <c r="Z45">
-        <v>4.5</v>
-      </c>
-      <c r="AA45">
-        <v>1.54</v>
-      </c>
-      <c r="AB45">
-        <v>2.27</v>
-      </c>
-      <c r="AC45">
-        <v>2.33</v>
-      </c>
-      <c r="AD45">
-        <v>1.48</v>
-      </c>
-      <c r="AE45">
-        <v>1.16</v>
-      </c>
-      <c r="AF45">
-        <v>2.05</v>
-      </c>
-      <c r="AG45">
-        <v>1.75</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.1</v>
-      </c>
       <c r="AK45">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8175,7 +8175,7 @@
         <v>2.18</v>
       </c>
       <c r="AB48">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC48">
         <v>4.15</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="O49">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q49">
         <v>2.3</v>
@@ -8335,7 +8335,7 @@
         <v>4.3</v>
       </c>
       <c r="AA49">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
         <v>2.25</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P50">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q51">
         <v>2.15</v>
@@ -8812,7 +8812,7 @@
         <v>1.64</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8824,10 +8824,10 @@
         <v>4.95</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC52">
         <v>2.16</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O53">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="P53">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="Q53">
         <v>3.4</v>
@@ -8963,16 +8963,16 @@
         <v>1.94</v>
       </c>
       <c r="S53">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T53">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U53">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="V53">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W53">
         <v>1.01</v>
@@ -8984,13 +8984,13 @@
         <v>1.37</v>
       </c>
       <c r="Z53">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA53">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB53">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC53">
         <v>3.98</v>
@@ -9021,7 +9021,7 @@
         <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="O54">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P54">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.93</v>
+        <v>3.4</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="P55">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q55">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
         <v>1.25</v>
       </c>
       <c r="T55">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U55">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V55">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W55">
         <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="AA55">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC55">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AD55">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AE55">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
         <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
         <v>1.24</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O56">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T56">
         <v>3.7</v>
       </c>
       <c r="U56">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V56">
         <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA56">
         <v>1.53</v>
       </c>
       <c r="AB56">
+        <v>2.4</v>
+      </c>
+      <c r="AC56">
         <v>2.33</v>
       </c>
-      <c r="AC56">
-        <v>2.25</v>
-      </c>
       <c r="AD56">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF56">
         <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O57">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R57">
         <v>2.4</v>
@@ -9618,7 +9618,7 @@
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U57">
         <v>2.3</v>
@@ -9633,31 +9633,31 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
         <v>4.6</v>
       </c>
       <c r="AA57">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC57">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD57">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
         <v>1.53</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9929,10 +9929,10 @@
         <v>1.84</v>
       </c>
       <c r="O59">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>4.77</v>
+        <v>4.3</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -9956,7 +9956,7 @@
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
         <v>1.26</v>
@@ -9965,7 +9965,7 @@
         <v>3.36</v>
       </c>
       <c r="AA59">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB59">
         <v>1.86</v>
@@ -9977,7 +9977,7 @@
         <v>1.27</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
         <v>1.82</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
         <v>2.05</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O60">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="P60">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q60">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R60">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="S60">
         <v>1.22</v>
@@ -10113,10 +10113,10 @@
         <v>2.01</v>
       </c>
       <c r="V60">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10125,16 +10125,16 @@
         <v>1.09</v>
       </c>
       <c r="Z60">
-        <v>5.98</v>
+        <v>5.35</v>
       </c>
       <c r="AA60">
         <v>1.38</v>
       </c>
       <c r="AB60">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD60">
         <v>1.78</v>
@@ -10146,7 +10146,7 @@
         <v>1.85</v>
       </c>
       <c r="AG60">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK60">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="O62">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="R62">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="S62">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T62">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U62">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="V62">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W62">
         <v>1.01</v>
@@ -10448,22 +10448,22 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
         <v>2.88</v>
       </c>
       <c r="AA62">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB62">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC62">
         <v>3.78</v>
       </c>
       <c r="AD62">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE62">
         <v>1.02</v>
@@ -10472,7 +10472,7 @@
         <v>1.92</v>
       </c>
       <c r="AG62">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="O63">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R63">
         <v>2.15</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U63">
         <v>2.25</v>
       </c>
       <c r="V63">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA63">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="AD63">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE63">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG63">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
         <v>1.29</v>
@@ -11076,55 +11076,55 @@
         <v>2.8</v>
       </c>
       <c r="Q66">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T66">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="U66">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V66">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
+        <v>1.05</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.31</v>
+      </c>
+      <c r="Z66">
+        <v>2.92</v>
+      </c>
+      <c r="AA66">
+        <v>2.05</v>
+      </c>
+      <c r="AB66">
+        <v>1.66</v>
+      </c>
+      <c r="AC66">
+        <v>3.58</v>
+      </c>
+      <c r="AD66">
+        <v>1.21</v>
+      </c>
+      <c r="AE66">
         <v>1.03</v>
       </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.34</v>
-      </c>
-      <c r="Z66">
-        <v>3.08</v>
-      </c>
-      <c r="AA66">
-        <v>2.03</v>
-      </c>
-      <c r="AB66">
-        <v>1.78</v>
-      </c>
-      <c r="AC66">
-        <v>3.46</v>
-      </c>
-      <c r="AD66">
-        <v>1.27</v>
-      </c>
-      <c r="AE66">
-        <v>1.04</v>
-      </c>
       <c r="AF66">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,58 +11230,58 @@
         </is>
       </c>
       <c r="N67">
+        <v>3.1</v>
+      </c>
+      <c r="O67">
         <v>3.2</v>
       </c>
-      <c r="O67">
-        <v>3.4</v>
-      </c>
       <c r="P67">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q67">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U67">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V67">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB67">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC67">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
         <v>1.78</v>
@@ -11393,22 +11393,22 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="O68">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P68">
-        <v>4.69</v>
+        <v>5</v>
       </c>
       <c r="Q68">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S68">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T68">
         <v>4.1</v>
@@ -11417,13 +11417,13 @@
         <v>1.95</v>
       </c>
       <c r="V68">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.07</v>
@@ -11438,10 +11438,10 @@
         <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD68">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE68">
         <v>1.27</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
         <v>2.51</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O69">
-        <v>5.72</v>
+        <v>4.5</v>
       </c>
       <c r="P69">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q69">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R69">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="S69">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="T69">
         <v>5.15</v>
       </c>
       <c r="U69">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V69">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="W69">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z69">
-        <v>8.949999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA69">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB69">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AC69">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AD69">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AE69">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AF69">
         <v>1.36</v>
       </c>
       <c r="AG69">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
         <v>2.45</v>
@@ -11719,34 +11719,34 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="O70">
-        <v>4.28</v>
+        <v>3.85</v>
       </c>
       <c r="P70">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="Q70">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R70">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S70">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U70">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V70">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W70">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
@@ -11764,13 +11764,13 @@
         <v>2.62</v>
       </c>
       <c r="AC70">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AD70">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AE70">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AF70">
         <v>1.37</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
         <v>1.61</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="O71">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="Q71">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S71">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T71">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="V71">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W71">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.42</v>
+        <v>5.6</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AB71">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AC71">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AD71">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE71">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
         <v>1.41</v>
       </c>
       <c r="AG71">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,58 +12045,58 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="O72">
-        <v>4.56</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="Q72">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R72">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
         <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U72">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="W72">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA72">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB72">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="AC72">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE72">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF72">
         <v>1.41</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="O73">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="P73">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q73">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S73">
         <v>1.44</v>
       </c>
       <c r="T73">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U73">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="V73">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
         <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z73">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA73">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB73">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC73">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="AD73">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
         <v>1.95</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12386,7 +12386,7 @@
         <v>2.62</v>
       </c>
       <c r="S74">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T74">
         <v>4.15</v>
@@ -12395,7 +12395,7 @@
         <v>1.98</v>
       </c>
       <c r="V74">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W74">
         <v>1.18</v>
@@ -12416,7 +12416,7 @@
         <v>2.56</v>
       </c>
       <c r="AC74">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD74">
         <v>1.67</v>
@@ -13524,19 +13524,19 @@
         <v>3.5</v>
       </c>
       <c r="R81">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="S81">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T81">
         <v>3.8</v>
       </c>
       <c r="U81">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V81">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W81">
         <v>1.17</v>
@@ -13548,28 +13548,28 @@
         <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>5.31</v>
+        <v>5.25</v>
       </c>
       <c r="AA81">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AC81">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AD81">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AE81">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF81">
         <v>1.44</v>
       </c>
       <c r="AG81">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AK81">
         <v>1.18</v>
@@ -13684,25 +13684,25 @@
         <v>5.7</v>
       </c>
       <c r="Q82">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R82">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="U82">
         <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.02</v>
@@ -13711,28 +13711,28 @@
         <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB82">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AC82">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD82">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE82">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG82">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="O83">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O84">
-        <v>7.03</v>
+        <v>7</v>
       </c>
       <c r="P84">
-        <v>10.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q84">
         <v>1.53</v>
       </c>
       <c r="R84">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="S84">
         <v>1.12</v>
@@ -14037,10 +14037,10 @@
         <v>1.04</v>
       </c>
       <c r="Z84">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA84">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB84">
         <v>4.65</v>
@@ -14052,7 +14052,7 @@
         <v>2.56</v>
       </c>
       <c r="AE84">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF84">
         <v>1.36</v>
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="O85">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="P85">
-        <v>5.76</v>
+        <v>5.5</v>
       </c>
       <c r="Q85">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R85">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S85">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T85">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="U85">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V85">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W85">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14200,22 +14200,22 @@
         <v>1.04</v>
       </c>
       <c r="Z85">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="AA85">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB85">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC85">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AD85">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE85">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK85">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O86">
         <v>4.33</v>
@@ -14339,7 +14339,7 @@
         <v>2.24</v>
       </c>
       <c r="R86">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="S86">
         <v>1.11</v>
@@ -14354,7 +14354,7 @@
         <v>2.08</v>
       </c>
       <c r="W86">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X86">
         <v>1</v>
@@ -14363,7 +14363,7 @@
         <v>1.01</v>
       </c>
       <c r="Z86">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA86">
         <v>1.17</v>
@@ -14384,7 +14384,7 @@
         <v>1.22</v>
       </c>
       <c r="AG86">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="O87">
+        <v>4.2</v>
+      </c>
+      <c r="P87">
         <v>4.3</v>
-      </c>
-      <c r="P87">
-        <v>4.4</v>
       </c>
       <c r="Q87">
         <v>2.14</v>
@@ -14529,10 +14529,10 @@
         <v>5.55</v>
       </c>
       <c r="AA87">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB87">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC87">
         <v>2.11</v>
@@ -14544,7 +14544,7 @@
         <v>1.23</v>
       </c>
       <c r="AF87">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG87">
         <v>2.56</v>
@@ -14653,10 +14653,10 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O88">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
         <v>3.04</v>
@@ -14677,7 +14677,7 @@
         <v>2.38</v>
       </c>
       <c r="V88">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W88">
         <v>1.11</v>
@@ -14695,13 +14695,13 @@
         <v>1.65</v>
       </c>
       <c r="AB88">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AC88">
         <v>2.49</v>
       </c>
       <c r="AD88">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
         <v>1.14</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK88">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14822,10 +14822,10 @@
         <v>5.6</v>
       </c>
       <c r="P89">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q89">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R89">
         <v>2.7</v>
@@ -14849,7 +14849,7 @@
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z89">
         <v>5.85</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O90">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P90">
         <v>4.9</v>
       </c>
       <c r="Q90">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R90">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="S90">
         <v>1.16</v>
@@ -15003,7 +15003,7 @@
         <v>2.02</v>
       </c>
       <c r="V90">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W90">
         <v>1.17</v>
@@ -15015,22 +15015,22 @@
         <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA90">
         <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AC90">
         <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF90">
         <v>1.48</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="O91">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P91">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q91">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="S91">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="U91">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V91">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W91">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="AA91">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB91">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AC91">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AD91">
         <v>1.69</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF91">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="O92">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P92">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q92">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R92">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S92">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T92">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="U92">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V92">
         <v>1.9</v>
       </c>
       <c r="W92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z92">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA92">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB92">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AC92">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AD92">
         <v>1.99</v>
       </c>
       <c r="AE92">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF92">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG92">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK92">
         <v>2.2</v>
@@ -15474,16 +15474,16 @@
         <v>4.2</v>
       </c>
       <c r="P93">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q93">
         <v>3.23</v>
       </c>
       <c r="R93">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="S93">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T93">
         <v>4.85</v>
@@ -15495,7 +15495,7 @@
         <v>1.89</v>
       </c>
       <c r="W93">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15522,10 +15522,10 @@
         <v>1.43</v>
       </c>
       <c r="AF93">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AG93">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK93">
         <v>1.38</v>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O94">
         <v>3.78</v>
       </c>
       <c r="P94">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="Q94">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="R94">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S94">
         <v>1.18</v>
       </c>
       <c r="T94">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U94">
         <v>2.03</v>
@@ -15667,13 +15667,13 @@
         <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>5.2</v>
+        <v>5.58</v>
       </c>
       <c r="AA94">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB94">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AC94">
         <v>2.09</v>
@@ -15794,34 +15794,34 @@
         </is>
       </c>
       <c r="N95">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="O95">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P95">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Q95">
-        <v>5.59</v>
+        <v>5</v>
       </c>
       <c r="R95">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="S95">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T95">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="U95">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V95">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="W95">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X95">
         <v>1.01</v>
@@ -15830,19 +15830,19 @@
         <v>1.08</v>
       </c>
       <c r="Z95">
-        <v>5.9</v>
+        <v>5.65</v>
       </c>
       <c r="AA95">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB95">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="AC95">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AD95">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AE95">
         <v>1.3</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK95">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O96">
+        <v>3.65</v>
+      </c>
+      <c r="P96">
+        <v>2.16</v>
+      </c>
+      <c r="Q96">
+        <v>3.38</v>
+      </c>
+      <c r="R96">
+        <v>2.26</v>
+      </c>
+      <c r="S96">
+        <v>1.22</v>
+      </c>
+      <c r="T96">
         <v>3.52</v>
       </c>
-      <c r="P96">
-        <v>2.11</v>
-      </c>
-      <c r="Q96">
-        <v>3.45</v>
-      </c>
-      <c r="R96">
-        <v>2.44</v>
-      </c>
-      <c r="S96">
-        <v>1.25</v>
-      </c>
-      <c r="T96">
-        <v>3.42</v>
-      </c>
       <c r="U96">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="V96">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W96">
         <v>1.11</v>
@@ -15990,22 +15990,22 @@
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
         <v>1.53</v>
       </c>
       <c r="AB96">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AC96">
         <v>2.33</v>
       </c>
       <c r="AD96">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AE96">
         <v>1.21</v>
@@ -16014,7 +16014,7 @@
         <v>1.46</v>
       </c>
       <c r="AG96">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="O97">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="P97">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="Q97">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S97">
         <v>1.37</v>
@@ -16159,22 +16159,22 @@
         <v>3.34</v>
       </c>
       <c r="AA97">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB97">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC97">
         <v>3.08</v>
       </c>
       <c r="AD97">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE97">
         <v>1.06</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG97">
         <v>2.08</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O98">
-        <v>4.03</v>
+        <v>3.55</v>
       </c>
       <c r="P98">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="Q98">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R98">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U98">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="V98">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W98">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.21</v>
       </c>
       <c r="Z98">
-        <v>3.93</v>
+        <v>3.58</v>
       </c>
       <c r="AA98">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
         <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD98">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF98">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O99">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P99">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q99">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R99">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
         <v>1.29</v>
       </c>
       <c r="T99">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="U99">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V99">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="W99">
         <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z99">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA99">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB99">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AC99">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD99">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE99">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
         <v>1.55</v>
       </c>
       <c r="AG99">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="O102">
-        <v>5.44</v>
+        <v>5.25</v>
       </c>
       <c r="P102">
-        <v>7.08</v>
+        <v>7.2</v>
       </c>
       <c r="Q102">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R102">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="S102">
         <v>1.2</v>
@@ -16980,13 +16980,13 @@
         <v>2.88</v>
       </c>
       <c r="AC102">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AD102">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE102">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF102">
         <v>1.58</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK102">
         <v>3.17</v>
@@ -17098,58 +17098,58 @@
         </is>
       </c>
       <c r="N103">
-        <v>5.55</v>
+        <v>4.35</v>
       </c>
       <c r="O103">
-        <v>4.52</v>
+        <v>3.95</v>
       </c>
       <c r="P103">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q103">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="R103">
         <v>2.4</v>
       </c>
       <c r="S103">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T103">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W103">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z103">
-        <v>4.39</v>
+        <v>4.1</v>
       </c>
       <c r="AA103">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB103">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AC103">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD103">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE103">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.15</v>
+        <v>2.18</v>
       </c>
       <c r="AK103">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -18411,7 +18411,7 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R111">
         <v>2.44</v>
@@ -18432,7 +18432,7 @@
         <v>1.08</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
         <v>1.15</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK111">
         <v>2</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="O114">
         <v>3.2</v>
@@ -18900,7 +18900,7 @@
         <v>2.65</v>
       </c>
       <c r="Q114">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="R114">
         <v>2.03</v>
@@ -18918,22 +18918,22 @@
         <v>1.33</v>
       </c>
       <c r="W114">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z114">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="AA114">
         <v>2.1</v>
       </c>
       <c r="AB114">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC114">
         <v>3.4</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AK114">
         <v>1.51</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O115">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P115">
-        <v>6.51</v>
+        <v>4.95</v>
       </c>
       <c r="Q115">
         <v>2.03</v>
@@ -19075,7 +19075,7 @@
         <v>3.6</v>
       </c>
       <c r="U115">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V115">
         <v>1.6</v>
@@ -19084,7 +19084,7 @@
         <v>1.11</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
         <v>1.12</v>
@@ -19093,13 +19093,13 @@
         <v>4.65</v>
       </c>
       <c r="AA115">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB115">
         <v>2.28</v>
       </c>
       <c r="AC115">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD115">
         <v>1.55</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK115">
         <v>2.38</v>
@@ -19217,16 +19217,16 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.09</v>
+        <v>3.65</v>
       </c>
       <c r="O116">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="Q116">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="R116">
         <v>2.03</v>
@@ -19235,7 +19235,7 @@
         <v>1.4</v>
       </c>
       <c r="T116">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U116">
         <v>2.78</v>
@@ -19244,7 +19244,7 @@
         <v>1.37</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
         <v>1</v>
@@ -19253,16 +19253,16 @@
         <v>1.3</v>
       </c>
       <c r="Z116">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="AA116">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AB116">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC116">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="AD116">
         <v>1.32</v>
@@ -19274,7 +19274,7 @@
         <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>4.6</v>
       </c>
       <c r="AA120">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB120">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC120">
         <v>2.4</v>
@@ -20074,7 +20074,7 @@
         <v>2.35</v>
       </c>
       <c r="AB121">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC121">
         <v>4.3</v>
@@ -20204,10 +20204,10 @@
         <v>3.34</v>
       </c>
       <c r="Q122">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S122">
         <v>1.44</v>
@@ -20228,7 +20228,7 @@
         <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z122">
         <v>2.75</v>
@@ -20240,19 +20240,19 @@
         <v>1.61</v>
       </c>
       <c r="AC122">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD122">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF122">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG122">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>1.3</v>
       </c>
       <c r="AK122">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G123">
@@ -20367,71 +20367,71 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R123">
         <v>2</v>
       </c>
       <c r="S123">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T123">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U123">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V123">
+        <v>1.32</v>
+      </c>
+      <c r="W123">
+        <v>1.04</v>
+      </c>
+      <c r="X123">
+        <v>1.04</v>
+      </c>
+      <c r="Y123">
+        <v>1.37</v>
+      </c>
+      <c r="Z123">
+        <v>2.8</v>
+      </c>
+      <c r="AA123">
+        <v>2.2</v>
+      </c>
+      <c r="AB123">
+        <v>1.65</v>
+      </c>
+      <c r="AC123">
+        <v>3.9</v>
+      </c>
+      <c r="AD123">
+        <v>1.2</v>
+      </c>
+      <c r="AE123">
+        <v>1.03</v>
+      </c>
+      <c r="AF123">
+        <v>1.95</v>
+      </c>
+      <c r="AG123">
+        <v>1.78</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
         <v>1.3</v>
       </c>
-      <c r="W123">
-        <v>1.05</v>
-      </c>
-      <c r="X123">
-        <v>1.05</v>
-      </c>
-      <c r="Y123">
-        <v>1.4</v>
-      </c>
-      <c r="Z123">
-        <v>2.75</v>
-      </c>
-      <c r="AA123">
-        <v>2.25</v>
-      </c>
-      <c r="AB123">
-        <v>1.61</v>
-      </c>
-      <c r="AC123">
-        <v>4.5</v>
-      </c>
-      <c r="AD123">
-        <v>1.17</v>
-      </c>
-      <c r="AE123">
-        <v>1.05</v>
-      </c>
-      <c r="AF123">
-        <v>2</v>
-      </c>
-      <c r="AG123">
-        <v>1.77</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.32</v>
-      </c>
       <c r="AK123">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G124">
@@ -20530,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R124">
         <v>2</v>
@@ -20542,34 +20542,34 @@
         <v>2.63</v>
       </c>
       <c r="U124">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V124">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
         <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z124">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA124">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB124">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC124">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD124">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE124">
         <v>1.03</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK124">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU132"/>
+  <dimension ref="A1:AU125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>1.83</v>
       </c>
       <c r="O9">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
         <v>3.6</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
         <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -2289,7 +2289,7 @@
         <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W12">
         <v>1.14</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R15">
         <v>2.49</v>
@@ -7816,40 +7816,40 @@
         <v>2.87</v>
       </c>
       <c r="Q46">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
         <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="AA46">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC46">
         <v>2.56</v>
@@ -7858,13 +7858,13 @@
         <v>1.4</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O47">
         <v>4.1</v>
       </c>
       <c r="P47">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U47">
         <v>2.47</v>
@@ -7997,37 +7997,37 @@
         <v>1.46</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA47">
         <v>1.71</v>
       </c>
       <c r="AB47">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC47">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
         <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
         <v>2.3</v>
@@ -8516,7 +8516,7 @@
         <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
         <v>3.3</v>
@@ -8649,7 +8649,7 @@
         <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.03</v>
@@ -10756,10 +10756,10 @@
         <v>2.45</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T64">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="U64">
         <v>2</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="O75">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q75">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="R75">
         <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U75">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.3</v>
+      </c>
+      <c r="Z75">
+        <v>3.05</v>
+      </c>
+      <c r="AA75">
+        <v>1.98</v>
+      </c>
+      <c r="AB75">
+        <v>1.77</v>
+      </c>
+      <c r="AC75">
+        <v>3.34</v>
+      </c>
+      <c r="AD75">
+        <v>1.24</v>
+      </c>
+      <c r="AE75">
         <v>1.06</v>
       </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
+      <c r="AF75">
+        <v>1.95</v>
+      </c>
+      <c r="AG75">
+        <v>1.8</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.25</v>
       </c>
-      <c r="Z75">
-        <v>3.28</v>
-      </c>
-      <c r="AA75">
-        <v>1.96</v>
-      </c>
-      <c r="AB75">
-        <v>1.83</v>
-      </c>
-      <c r="AC75">
-        <v>3.28</v>
-      </c>
-      <c r="AD75">
-        <v>1.25</v>
-      </c>
-      <c r="AE75">
-        <v>1.05</v>
-      </c>
-      <c r="AF75">
-        <v>1.74</v>
-      </c>
-      <c r="AG75">
-        <v>1.98</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.28</v>
-      </c>
       <c r="AK75">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76">
+        <v>3.6</v>
+      </c>
+      <c r="P76">
+        <v>3.18</v>
+      </c>
+      <c r="Q76">
+        <v>2.62</v>
+      </c>
+      <c r="R76">
+        <v>2.3</v>
+      </c>
+      <c r="S76">
+        <v>1.3</v>
+      </c>
+      <c r="T76">
+        <v>3.1</v>
+      </c>
+      <c r="U76">
+        <v>2.42</v>
+      </c>
+      <c r="V76">
+        <v>1.48</v>
+      </c>
+      <c r="W76">
+        <v>1.08</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.2</v>
+      </c>
+      <c r="Z76">
+        <v>3.86</v>
+      </c>
+      <c r="AA76">
+        <v>1.73</v>
+      </c>
+      <c r="AB76">
+        <v>2</v>
+      </c>
+      <c r="AC76">
+        <v>2.8</v>
+      </c>
+      <c r="AD76">
+        <v>1.4</v>
+      </c>
+      <c r="AE76">
+        <v>1.09</v>
+      </c>
+      <c r="AF76">
+        <v>1.62</v>
+      </c>
+      <c r="AG76">
+        <v>2.19</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
+        <v>1.25</v>
+      </c>
+      <c r="AK76">
         <v>1.67</v>
-      </c>
-      <c r="O76">
-        <v>3.72</v>
-      </c>
-      <c r="P76">
-        <v>4.95</v>
-      </c>
-      <c r="Q76">
-        <v>2.18</v>
-      </c>
-      <c r="R76">
-        <v>2.15</v>
-      </c>
-      <c r="S76">
-        <v>1.36</v>
-      </c>
-      <c r="T76">
-        <v>2.8</v>
-      </c>
-      <c r="U76">
-        <v>2.75</v>
-      </c>
-      <c r="V76">
-        <v>1.36</v>
-      </c>
-      <c r="W76">
-        <v>1.07</v>
-      </c>
-      <c r="X76">
-        <v>1.02</v>
-      </c>
-      <c r="Y76">
-        <v>1.32</v>
-      </c>
-      <c r="Z76">
-        <v>3.05</v>
-      </c>
-      <c r="AA76">
-        <v>1.98</v>
-      </c>
-      <c r="AB76">
-        <v>1.81</v>
-      </c>
-      <c r="AC76">
-        <v>3.34</v>
-      </c>
-      <c r="AD76">
-        <v>1.24</v>
-      </c>
-      <c r="AE76">
-        <v>1.06</v>
-      </c>
-      <c r="AF76">
-        <v>1.95</v>
-      </c>
-      <c r="AG76">
-        <v>1.8</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.24</v>
-      </c>
-      <c r="AK76">
-        <v>2.21</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O77">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q77">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="R77">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
+        <v>1.43</v>
+      </c>
+      <c r="T77">
+        <v>2.57</v>
+      </c>
+      <c r="U77">
+        <v>3</v>
+      </c>
+      <c r="V77">
         <v>1.3</v>
       </c>
-      <c r="T77">
-        <v>3.1</v>
-      </c>
-      <c r="U77">
-        <v>2.55</v>
-      </c>
-      <c r="V77">
-        <v>1.44</v>
-      </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y77">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>3.86</v>
+        <v>2.75</v>
       </c>
       <c r="AA77">
+        <v>2.19</v>
+      </c>
+      <c r="AB77">
+        <v>1.58</v>
+      </c>
+      <c r="AC77">
+        <v>4.4</v>
+      </c>
+      <c r="AD77">
+        <v>1.15</v>
+      </c>
+      <c r="AE77">
+        <v>1</v>
+      </c>
+      <c r="AF77">
         <v>1.93</v>
       </c>
-      <c r="AB77">
-        <v>1.85</v>
-      </c>
-      <c r="AC77">
-        <v>2.74</v>
-      </c>
-      <c r="AD77">
-        <v>1.35</v>
-      </c>
-      <c r="AE77">
-        <v>1.09</v>
-      </c>
-      <c r="AF77">
-        <v>1.62</v>
-      </c>
       <c r="AG77">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="O78">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P78">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
+        <v>1.32</v>
+      </c>
+      <c r="T78">
+        <v>2.84</v>
+      </c>
+      <c r="U78">
+        <v>2.57</v>
+      </c>
+      <c r="V78">
         <v>1.43</v>
       </c>
-      <c r="T78">
-        <v>2.7</v>
-      </c>
-      <c r="U78">
-        <v>3.3</v>
-      </c>
-      <c r="V78">
-        <v>1.29</v>
-      </c>
       <c r="W78">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>2.69</v>
+        <v>3.9</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>1.77</v>
       </c>
       <c r="AB78">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AC78">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="O79">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q79">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
         <v>1.33</v>
       </c>
       <c r="T79">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U79">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="V79">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W79">
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z79">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="AA79">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AB79">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC79">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AD79">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG79">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,55 +13349,55 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="O80">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="P80">
         <v>2.82</v>
       </c>
       <c r="Q80">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R80">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S80">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T80">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="U80">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V80">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W80">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z80">
         <v>2.66</v>
       </c>
       <c r="AA80">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AB80">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC80">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="AD80">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE80">
         <v>1.01</v>
@@ -13406,7 +13406,7 @@
         <v>1.89</v>
       </c>
       <c r="AG80">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.88</v>
+        <v>1.49</v>
       </c>
       <c r="O81">
-        <v>4.52</v>
+        <v>4.98</v>
       </c>
       <c r="P81">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="Q81">
+        <v>1.9</v>
+      </c>
+      <c r="R81">
+        <v>2.5</v>
+      </c>
+      <c r="S81">
+        <v>1.22</v>
+      </c>
+      <c r="T81">
         <v>3.5</v>
       </c>
-      <c r="R81">
-        <v>2.55</v>
-      </c>
-      <c r="S81">
-        <v>1.17</v>
-      </c>
-      <c r="T81">
-        <v>3.8</v>
-      </c>
       <c r="U81">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA81">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB81">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AC81">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AD81">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE81">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AG81">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="AK81">
-        <v>1.18</v>
+        <v>2.63</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.49</v>
+        <v>3.88</v>
       </c>
       <c r="O82">
-        <v>4.98</v>
+        <v>4.52</v>
       </c>
       <c r="P82">
-        <v>5.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q82">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="R82">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T82">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U82">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V82">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA82">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB82">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AC82">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AD82">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE82">
+        <v>1.27</v>
+      </c>
+      <c r="AF82">
+        <v>1.44</v>
+      </c>
+      <c r="AG82">
+        <v>2.57</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.85</v>
+      </c>
+      <c r="AK82">
         <v>1.18</v>
-      </c>
-      <c r="AF82">
-        <v>1.64</v>
-      </c>
-      <c r="AG82">
-        <v>2.07</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.06</v>
-      </c>
-      <c r="AK82">
-        <v>2.63</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16609,28 +16609,28 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="O100">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q100">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R100">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S100">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="U100">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="V100">
         <v>1.61</v>
@@ -16642,25 +16642,25 @@
         <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA100">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB100">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC100">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD100">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF100">
         <v>1.44</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
         <v>1.62</v>
@@ -17261,16 +17261,16 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P104">
-        <v>3.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q104">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R104">
         <v>2.31</v>
@@ -17282,7 +17282,7 @@
         <v>3.42</v>
       </c>
       <c r="U104">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V104">
         <v>1.59</v>
@@ -17300,13 +17300,13 @@
         <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB104">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AD104">
         <v>1.66</v>
@@ -17315,10 +17315,10 @@
         <v>1.21</v>
       </c>
       <c r="AF104">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>2.13</v>
       </c>
       <c r="V107">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W107">
         <v>1.12</v>
@@ -17795,7 +17795,7 @@
         <v>2.52</v>
       </c>
       <c r="AC107">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD107">
         <v>1.6</v>
@@ -17916,10 +17916,10 @@
         <v>1.13</v>
       </c>
       <c r="O108">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="P108">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q108">
         <v>1.41</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O110">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P110">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q110">
         <v>1.92</v>
@@ -18737,55 +18737,55 @@
         <v>4.2</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S118">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T118">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U118">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z118">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA118">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AD118">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE118">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF118">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG118">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK118">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-09 17:30:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.79</v>
+        <v>2.61</v>
       </c>
       <c r="O119">
-        <v>4.03</v>
+        <v>3.32</v>
       </c>
       <c r="P119">
-        <v>4.13</v>
+        <v>2.59</v>
       </c>
       <c r="Q119">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="R119">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="S119">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T119">
-        <v>2.99</v>
+        <v>2.49</v>
       </c>
       <c r="U119">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="V119">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Z119">
-        <v>3.67</v>
+        <v>2.55</v>
       </c>
       <c r="AA119">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AB119">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AC119">
-        <v>2.83</v>
+        <v>4.44</v>
       </c>
       <c r="AD119">
+        <v>1.15</v>
+      </c>
+      <c r="AE119">
+        <v>1.01</v>
+      </c>
+      <c r="AF119">
+        <v>1.98</v>
+      </c>
+      <c r="AG119">
+        <v>1.72</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.33</v>
       </c>
-      <c r="AE119">
-        <v>1.1</v>
-      </c>
-      <c r="AF119">
-        <v>1.66</v>
-      </c>
-      <c r="AG119">
-        <v>2.07</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.22</v>
-      </c>
       <c r="AK119">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-09 20:30:00</t>
+          <t>2026-10-09 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q120">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="R120">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S120">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="T120">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U120">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="V120">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="W120">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z120">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA120">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB120">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC120">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="AD120">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AG120">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK120">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00:00</t>
+          <t>2026-10-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G121">
@@ -20041,55 +20041,55 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>5.78</v>
+        <v>1.7</v>
       </c>
       <c r="R121">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="S121">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="T121">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U121">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="V121">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="Z121">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA121">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AB121">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AC121">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD121">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="AE121">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AF121">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG121">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK121">
-        <v>1.14</v>
+        <v>3.6</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,65 +20195,65 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>2.57</v>
+        <v>5.78</v>
       </c>
       <c r="R122">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S122">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T122">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U122">
         <v>3.2</v>
       </c>
       <c r="V122">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
         <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z122">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA122">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB122">
+        <v>1.55</v>
+      </c>
+      <c r="AC122">
+        <v>4.3</v>
+      </c>
+      <c r="AD122">
+        <v>1.16</v>
+      </c>
+      <c r="AE122">
+        <v>1.02</v>
+      </c>
+      <c r="AF122">
+        <v>2.2</v>
+      </c>
+      <c r="AG122">
         <v>1.61</v>
       </c>
-      <c r="AC122">
-        <v>4</v>
-      </c>
-      <c r="AD122">
-        <v>1.19</v>
-      </c>
-      <c r="AE122">
-        <v>1.03</v>
-      </c>
-      <c r="AF122">
-        <v>2.02</v>
-      </c>
-      <c r="AG122">
-        <v>1.72</v>
-      </c>
       <c r="AH122" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK122">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q123">
+        <v>2.57</v>
+      </c>
+      <c r="R123">
+        <v>2.04</v>
+      </c>
+      <c r="S123">
+        <v>1.44</v>
+      </c>
+      <c r="T123">
+        <v>2.63</v>
+      </c>
+      <c r="U123">
+        <v>3.2</v>
+      </c>
+      <c r="V123">
+        <v>1.3</v>
+      </c>
+      <c r="W123">
+        <v>1.05</v>
+      </c>
+      <c r="X123">
+        <v>1.05</v>
+      </c>
+      <c r="Y123">
+        <v>1.38</v>
+      </c>
+      <c r="Z123">
+        <v>2.75</v>
+      </c>
+      <c r="AA123">
+        <v>2.25</v>
+      </c>
+      <c r="AB123">
+        <v>1.61</v>
+      </c>
+      <c r="AC123">
         <v>4</v>
       </c>
-      <c r="R123">
-        <v>2</v>
-      </c>
-      <c r="S123">
-        <v>1.4</v>
-      </c>
-      <c r="T123">
-        <v>2.75</v>
-      </c>
-      <c r="U123">
-        <v>3</v>
-      </c>
-      <c r="V123">
-        <v>1.32</v>
-      </c>
-      <c r="W123">
-        <v>1.04</v>
-      </c>
-      <c r="X123">
-        <v>1.04</v>
-      </c>
-      <c r="Y123">
-        <v>1.37</v>
-      </c>
-      <c r="Z123">
-        <v>2.8</v>
-      </c>
-      <c r="AA123">
-        <v>2.2</v>
-      </c>
-      <c r="AB123">
-        <v>1.65</v>
-      </c>
-      <c r="AC123">
-        <v>3.9</v>
-      </c>
       <c r="AD123">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE123">
         <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG123">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20530,46 +20530,46 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="R124">
         <v>2</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V124">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
         <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z124">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA124">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB124">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC124">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD124">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE124">
         <v>1.03</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125">
@@ -20693,55 +20693,55 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20787,1147 +20787,6 @@
         <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
-        <v>0</v>
-      </c>
-      <c r="AB126">
-        <v>0</v>
-      </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-10-09 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
         <is>
           <t>2026-10-09 21:00:00</t>
         </is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -18752,7 +18752,7 @@
         <v>2.2</v>
       </c>
       <c r="V113">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W113">
         <v>1.17</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,19 +20358,19 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="R123">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S123">
         <v>1.44</v>
@@ -20388,7 +20388,7 @@
         <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
         <v>1.38</v>
@@ -20412,10 +20412,10 @@
         <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG123">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK123">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,19 +20684,19 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="R125">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S125">
         <v>1.44</v>
@@ -20714,7 +20714,7 @@
         <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y125">
         <v>1.38</v>
@@ -20738,10 +20738,10 @@
         <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG125">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
         <v>3.1</v>
@@ -1652,10 +1652,10 @@
         <v>3.72</v>
       </c>
       <c r="AA8">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC8">
         <v>2.84</v>
@@ -1664,7 +1664,7 @@
         <v>1.37</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
         <v>1.58</v>
@@ -10651,7 +10651,7 @@
         <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q118">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1791,10 +1791,10 @@
         <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -1806,31 +1806,31 @@
         <v>1.15</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
         <v>2.31</v>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>2.1</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="P10">
         <v>3.05</v>
       </c>
       <c r="Q10">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
         <v>2.77</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1978,13 +1978,13 @@
         <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
@@ -1996,7 +1996,7 @@
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4230,22 +4230,22 @@
         <v>3.15</v>
       </c>
       <c r="Q24">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4254,22 +4254,22 @@
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="AD24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
@@ -4278,7 +4278,7 @@
         <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
         <v>1.52</v>
@@ -5045,10 +5045,10 @@
         <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="R29">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
         <v>1.44</v>
@@ -5057,10 +5057,10 @@
         <v>2.45</v>
       </c>
       <c r="U29">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5072,16 +5072,16 @@
         <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB29">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC29">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AD29">
         <v>1.17</v>
@@ -5090,10 +5090,10 @@
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>4.7</v>
       </c>
       <c r="P31">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="Q31">
         <v>5</v>
@@ -5377,10 +5377,10 @@
         <v>2.5</v>
       </c>
       <c r="S31">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
         <v>2.08</v>
@@ -5407,7 +5407,7 @@
         <v>2.41</v>
       </c>
       <c r="AC31">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD31">
         <v>1.58</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>2.38</v>
       </c>
       <c r="AK31">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O34">
         <v>3.36</v>
       </c>
       <c r="P34">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="Q34">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="R34">
         <v>1.86</v>
@@ -6186,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
         <v>1.33</v>
@@ -6201,10 +6201,10 @@
         <v>2.72</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6216,16 +6216,16 @@
         <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AD36">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AK36">
         <v>1.33</v>
@@ -6349,19 +6349,19 @@
         <v>2.8</v>
       </c>
       <c r="Q37">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="U37">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="V37">
         <v>1.36</v>
@@ -6391,13 +6391,13 @@
         <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
         <v>1.47</v>
@@ -6678,7 +6678,7 @@
         <v>5.25</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
         <v>1.22</v>
@@ -6705,25 +6705,25 @@
         <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB39">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD39">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
         <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>2.4</v>
       </c>
       <c r="AK39">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,22 +6832,22 @@
         <v>6.4</v>
       </c>
       <c r="O40">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="P40">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Q40">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="R40">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
         <v>1.15</v>
       </c>
       <c r="T40">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U40">
         <v>1.95</v>
@@ -6856,7 +6856,7 @@
         <v>1.73</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6886,7 +6886,7 @@
         <v>1.49</v>
       </c>
       <c r="AG40">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
         <v>1.09</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q41">
         <v>2.25</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
         <v>1.39</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
         <v>2.62</v>
@@ -7019,7 +7019,7 @@
         <v>1.41</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.03</v>
@@ -7031,10 +7031,10 @@
         <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB41">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
         <v>3.3</v>
@@ -7049,7 +7049,7 @@
         <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R42">
         <v>2.5</v>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7653,46 +7653,46 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V45">
         <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC45">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD45">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE45">
         <v>1.2</v>
@@ -7701,7 +7701,7 @@
         <v>1.99</v>
       </c>
       <c r="AG45">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK45">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,40 +7816,40 @@
         <v>2.87</v>
       </c>
       <c r="Q46">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
         <v>3.4</v>
       </c>
       <c r="U46">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC46">
         <v>2.56</v>
@@ -7864,7 +7864,7 @@
         <v>1.54</v>
       </c>
       <c r="AG46">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK46">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
         <v>2.47</v>
@@ -8006,7 +8006,7 @@
         <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AA47">
         <v>1.71</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
         <v>2.3</v>
@@ -8172,10 +8172,10 @@
         <v>2.74</v>
       </c>
       <c r="AA48">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB48">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC48">
         <v>4.15</v>
@@ -8335,10 +8335,10 @@
         <v>4.3</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC49">
         <v>2.43</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.15</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.28</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8800,7 +8800,7 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
         <v>4</v>
@@ -8812,7 +8812,7 @@
         <v>1.64</v>
       </c>
       <c r="W52">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8957,7 +8957,7 @@
         <v>2.54</v>
       </c>
       <c r="Q53">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="R53">
         <v>1.94</v>
@@ -8981,13 +8981,13 @@
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z53">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="AA53">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB53">
         <v>1.66</v>
@@ -9292,10 +9292,10 @@
         <v>1.25</v>
       </c>
       <c r="T55">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U55">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
         <v>1.56</v>
@@ -9304,25 +9304,25 @@
         <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="AA55">
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AD55">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
         <v>1.17</v>
@@ -9331,7 +9331,7 @@
         <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9446,13 +9446,13 @@
         <v>2.44</v>
       </c>
       <c r="Q56">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="S56">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
         <v>3.7</v>
@@ -9464,13 +9464,13 @@
         <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
         <v>4.75</v>
@@ -9488,7 +9488,7 @@
         <v>1.56</v>
       </c>
       <c r="AE56">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF56">
         <v>1.44</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9645,35 +9645,35 @@
         <v>2.35</v>
       </c>
       <c r="AC57">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AD57">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE57">
+        <v>1.15</v>
+      </c>
+      <c r="AF57">
+        <v>1.5</v>
+      </c>
+      <c r="AG57">
+        <v>2.4</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.22</v>
       </c>
-      <c r="AF57">
-        <v>1.53</v>
-      </c>
-      <c r="AG57">
-        <v>2.31</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.23</v>
-      </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O59">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="P59">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -9956,7 +9956,7 @@
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.26</v>
@@ -9965,10 +9965,10 @@
         <v>3.36</v>
       </c>
       <c r="AA59">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB59">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC59">
         <v>3.3</v>
@@ -10092,10 +10092,10 @@
         <v>1.26</v>
       </c>
       <c r="O60">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="P60">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Q60">
         <v>1.54</v>
@@ -10107,46 +10107,46 @@
         <v>1.22</v>
       </c>
       <c r="T60">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="V60">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z60">
-        <v>5.35</v>
+        <v>5.05</v>
       </c>
       <c r="AA60">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AC60">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AD60">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE60">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF60">
         <v>1.85</v>
       </c>
       <c r="AG60">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK60">
         <v>3.52</v>
@@ -10424,16 +10424,16 @@
         <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R62">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S62">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T62">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U62">
         <v>3.08</v>
@@ -10445,7 +10445,7 @@
         <v>1.01</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.32</v>
@@ -10454,16 +10454,16 @@
         <v>2.88</v>
       </c>
       <c r="AA62">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB62">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC62">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="AD62">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE62">
         <v>1.02</v>
@@ -10472,7 +10472,7 @@
         <v>1.92</v>
       </c>
       <c r="AG62">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10590,13 +10590,13 @@
         <v>3.6</v>
       </c>
       <c r="R63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="U63">
         <v>2.25</v>
@@ -10620,7 +10620,7 @@
         <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC63">
         <v>2.42</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
+        <v>2.1</v>
+      </c>
+      <c r="Q66">
+        <v>4.05</v>
+      </c>
+      <c r="R66">
+        <v>2.05</v>
+      </c>
+      <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
         <v>2.8</v>
       </c>
-      <c r="Q66">
-        <v>3.12</v>
-      </c>
-      <c r="R66">
-        <v>2</v>
-      </c>
-      <c r="S66">
-        <v>1.37</v>
-      </c>
-      <c r="T66">
-        <v>2.69</v>
-      </c>
       <c r="U66">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="V66">
         <v>1.36</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC66">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="AD66">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE66">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,61 +11230,61 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="O67">
         <v>3.2</v>
       </c>
       <c r="P67">
+        <v>2.75</v>
+      </c>
+      <c r="Q67">
+        <v>3.12</v>
+      </c>
+      <c r="R67">
         <v>2.1</v>
       </c>
-      <c r="Q67">
-        <v>4.05</v>
-      </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T67">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U67">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="V67">
         <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z67">
         <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC67">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD67">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
         <v>1.91</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK67">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11399,25 +11399,25 @@
         <v>4.6</v>
       </c>
       <c r="P68">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q68">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R68">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="V68">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W68">
         <v>1.17</v>
@@ -11426,31 +11426,31 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
-        <v>5.9</v>
+        <v>6.39</v>
       </c>
       <c r="AA68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB68">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC68">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD68">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE68">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,16 +11565,16 @@
         <v>4.8</v>
       </c>
       <c r="Q69">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R69">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="S69">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="T69">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="U69">
         <v>1.8</v>
@@ -11607,7 +11607,7 @@
         <v>2.02</v>
       </c>
       <c r="AE69">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF69">
         <v>1.36</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK69">
         <v>2.45</v>
@@ -11728,34 +11728,34 @@
         <v>2.95</v>
       </c>
       <c r="Q70">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R70">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S70">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T70">
         <v>4.5</v>
       </c>
       <c r="U70">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V70">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z70">
-        <v>5.6</v>
+        <v>5.82</v>
       </c>
       <c r="AA70">
         <v>1.38</v>
@@ -11773,10 +11773,10 @@
         <v>1.26</v>
       </c>
       <c r="AF70">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG70">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK70">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>1.76</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R71">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S71">
         <v>1.17</v>
@@ -11906,7 +11906,7 @@
         <v>1.98</v>
       </c>
       <c r="V71">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -11918,7 +11918,7 @@
         <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.6</v>
+        <v>5.82</v>
       </c>
       <c r="AA71">
         <v>1.38</v>
@@ -12057,7 +12057,7 @@
         <v>3.45</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S72">
         <v>1.22</v>
@@ -12072,13 +12072,13 @@
         <v>1.63</v>
       </c>
       <c r="W72">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
         <v>5.1</v>
@@ -12102,7 +12102,7 @@
         <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK72">
         <v>1.33</v>
@@ -12217,7 +12217,7 @@
         <v>2.2</v>
       </c>
       <c r="Q73">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R73">
         <v>2</v>
@@ -12229,7 +12229,7 @@
         <v>2.5</v>
       </c>
       <c r="U73">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V73">
         <v>1.3</v>
@@ -12241,7 +12241,7 @@
         <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z73">
         <v>2.83</v>
@@ -12259,7 +12259,7 @@
         <v>1.21</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
         <v>1.95</v>
@@ -12374,16 +12374,16 @@
         <v>1.47</v>
       </c>
       <c r="O74">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P74">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q74">
         <v>1.85</v>
       </c>
       <c r="R74">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
         <v>1.22</v>
@@ -12392,10 +12392,10 @@
         <v>4.15</v>
       </c>
       <c r="U74">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V74">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W74">
         <v>1.18</v>
@@ -12404,16 +12404,16 @@
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z74">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AA74">
         <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="AC74">
         <v>2.08</v>
@@ -12428,7 +12428,7 @@
         <v>1.55</v>
       </c>
       <c r="AG74">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T75">
         <v>2.88</v>
@@ -12567,7 +12567,7 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z75">
         <v>3.05</v>
@@ -12576,7 +12576,7 @@
         <v>1.98</v>
       </c>
       <c r="AB75">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC75">
         <v>3.34</v>
@@ -12588,7 +12588,7 @@
         <v>1.06</v>
       </c>
       <c r="AF75">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG75">
         <v>1.8</v>
@@ -12700,10 +12700,10 @@
         <v>2</v>
       </c>
       <c r="O76">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P76">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="Q76">
         <v>2.62</v>
@@ -12718,43 +12718,43 @@
         <v>3.1</v>
       </c>
       <c r="U76">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="V76">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.21</v>
+      </c>
+      <c r="Z76">
+        <v>3.7</v>
+      </c>
+      <c r="AA76">
+        <v>1.85</v>
+      </c>
+      <c r="AB76">
+        <v>1.97</v>
+      </c>
+      <c r="AC76">
+        <v>3.1</v>
+      </c>
+      <c r="AD76">
+        <v>1.33</v>
+      </c>
+      <c r="AE76">
         <v>1.08</v>
-      </c>
-      <c r="X76">
-        <v>1.04</v>
-      </c>
-      <c r="Y76">
-        <v>1.2</v>
-      </c>
-      <c r="Z76">
-        <v>3.86</v>
-      </c>
-      <c r="AA76">
-        <v>1.73</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76">
-        <v>2.8</v>
-      </c>
-      <c r="AD76">
-        <v>1.4</v>
-      </c>
-      <c r="AE76">
-        <v>1.09</v>
       </c>
       <c r="AF76">
         <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="O77">
         <v>3.2</v>
@@ -12875,22 +12875,22 @@
         <v>2.07</v>
       </c>
       <c r="S77">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T77">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="U77">
         <v>3</v>
       </c>
       <c r="V77">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
         <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.4</v>
@@ -12899,13 +12899,13 @@
         <v>2.75</v>
       </c>
       <c r="AA77">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB77">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC77">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD77">
         <v>1.15</v>
@@ -12914,10 +12914,10 @@
         <v>1</v>
       </c>
       <c r="AF77">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13038,10 +13038,10 @@
         <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
         <v>2.57</v>
@@ -13050,22 +13050,22 @@
         <v>1.43</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
         <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC78">
         <v>2.83</v>
@@ -13080,7 +13080,7 @@
         <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -13198,46 +13198,46 @@
         <v>2.48</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
         <v>1.33</v>
       </c>
       <c r="T79">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V79">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W79">
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="AA79">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB79">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC79">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD79">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF79">
         <v>1.74</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
         <v>1.72</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.49</v>
+        <v>3.88</v>
       </c>
       <c r="O81">
-        <v>4.98</v>
+        <v>4.52</v>
       </c>
       <c r="P81">
-        <v>5.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q81">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S81">
         <v>1.22</v>
       </c>
       <c r="T81">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U81">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V81">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA81">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AC81">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AD81">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE81">
+        <v>1.27</v>
+      </c>
+      <c r="AF81">
+        <v>1.44</v>
+      </c>
+      <c r="AG81">
+        <v>2.57</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.85</v>
+      </c>
+      <c r="AK81">
         <v>1.18</v>
-      </c>
-      <c r="AF81">
-        <v>1.64</v>
-      </c>
-      <c r="AG81">
-        <v>2.07</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.06</v>
-      </c>
-      <c r="AK81">
-        <v>2.63</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.88</v>
+        <v>1.49</v>
       </c>
       <c r="O82">
-        <v>4.52</v>
+        <v>4.98</v>
       </c>
       <c r="P82">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="Q82">
+        <v>1.91</v>
+      </c>
+      <c r="R82">
+        <v>2.32</v>
+      </c>
+      <c r="S82">
+        <v>1.22</v>
+      </c>
+      <c r="T82">
         <v>3.5</v>
       </c>
-      <c r="R82">
-        <v>2.55</v>
-      </c>
-      <c r="S82">
-        <v>1.17</v>
-      </c>
-      <c r="T82">
-        <v>3.8</v>
-      </c>
       <c r="U82">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>5.25</v>
+        <v>5.02</v>
       </c>
       <c r="AA82">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB82">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AC82">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AD82">
+        <v>1.53</v>
+      </c>
+      <c r="AE82">
+        <v>1.2</v>
+      </c>
+      <c r="AF82">
         <v>1.62</v>
       </c>
-      <c r="AE82">
-        <v>1.27</v>
-      </c>
-      <c r="AF82">
-        <v>1.44</v>
-      </c>
       <c r="AG82">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>1.18</v>
+        <v>2.42</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,7 +13844,7 @@
         <v>3.25</v>
       </c>
       <c r="P83">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
       <c r="P84">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q84">
         <v>1.53</v>
@@ -14016,19 +14016,19 @@
         <v>3.35</v>
       </c>
       <c r="S84">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T84">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="U84">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V84">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="W84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X84">
         <v>1</v>
@@ -14037,10 +14037,10 @@
         <v>1.04</v>
       </c>
       <c r="Z84">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA84">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB84">
         <v>4.65</v>
@@ -14058,7 +14058,7 @@
         <v>1.36</v>
       </c>
       <c r="AG84">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14173,10 +14173,10 @@
         <v>5.5</v>
       </c>
       <c r="Q85">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R85">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S85">
         <v>1.14</v>
@@ -14185,7 +14185,7 @@
         <v>4.6</v>
       </c>
       <c r="U85">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V85">
         <v>1.85</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK85">
         <v>3.1</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O86">
         <v>4.33</v>
@@ -14336,7 +14336,7 @@
         <v>3.19</v>
       </c>
       <c r="Q86">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R86">
         <v>2.9</v>
@@ -14357,13 +14357,13 @@
         <v>1.33</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z86">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AA86">
         <v>1.17</v>
@@ -14378,10 +14378,10 @@
         <v>2.28</v>
       </c>
       <c r="AE86">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF86">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG86">
         <v>3.8</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK86">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14502,13 +14502,13 @@
         <v>2.14</v>
       </c>
       <c r="R87">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="U87">
         <v>2.11</v>
@@ -14517,7 +14517,7 @@
         <v>1.66</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14529,13 +14529,13 @@
         <v>5.55</v>
       </c>
       <c r="AA87">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB87">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC87">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AD87">
         <v>1.67</v>
@@ -14659,13 +14659,13 @@
         <v>3.7</v>
       </c>
       <c r="P88">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q88">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="R88">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
         <v>1.3</v>
@@ -14677,7 +14677,7 @@
         <v>2.38</v>
       </c>
       <c r="V88">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W88">
         <v>1.11</v>
@@ -14695,13 +14695,13 @@
         <v>1.65</v>
       </c>
       <c r="AB88">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AC88">
         <v>2.49</v>
       </c>
       <c r="AD88">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE88">
         <v>1.14</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK88">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>6</v>
       </c>
       <c r="Q89">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R89">
         <v>2.7</v>
@@ -14849,19 +14849,19 @@
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z89">
         <v>5.85</v>
       </c>
       <c r="AA89">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AC89">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AD89">
         <v>1.76</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK89">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,34 +14979,34 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O90">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
         <v>4.9</v>
       </c>
       <c r="Q90">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R90">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="S90">
         <v>1.16</v>
       </c>
       <c r="T90">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U90">
         <v>2.02</v>
       </c>
       <c r="V90">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
         <v>1.02</v>
@@ -15015,28 +15015,28 @@
         <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA90">
         <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AC90">
         <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE90">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
         <v>1.48</v>
       </c>
       <c r="AG90">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
         <v>2.5</v>
@@ -15154,7 +15154,7 @@
         <v>2.7</v>
       </c>
       <c r="R91">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="S91">
         <v>1.22</v>
@@ -15184,10 +15184,10 @@
         <v>1.47</v>
       </c>
       <c r="AB91">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AC91">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AD91">
         <v>1.69</v>
@@ -15196,10 +15196,10 @@
         <v>1.24</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG91">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15311,13 +15311,13 @@
         <v>4.3</v>
       </c>
       <c r="P92">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q92">
         <v>2</v>
       </c>
       <c r="R92">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S92">
         <v>1.13</v>
@@ -15326,7 +15326,7 @@
         <v>4.7</v>
       </c>
       <c r="U92">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V92">
         <v>1.9</v>
@@ -15344,10 +15344,10 @@
         <v>8</v>
       </c>
       <c r="AA92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB92">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC92">
         <v>1.75</v>
@@ -15378,7 +15378,7 @@
         <v>1.18</v>
       </c>
       <c r="AK92">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,25 +15477,25 @@
         <v>2.1</v>
       </c>
       <c r="Q93">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="R93">
         <v>2.51</v>
       </c>
       <c r="S93">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T93">
         <v>4.85</v>
       </c>
       <c r="U93">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V93">
         <v>1.89</v>
       </c>
       <c r="W93">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15516,7 +15516,7 @@
         <v>1.76</v>
       </c>
       <c r="AD93">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE93">
         <v>1.43</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK93">
         <v>1.38</v>
@@ -15637,7 +15637,7 @@
         <v>3.78</v>
       </c>
       <c r="P94">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="Q94">
         <v>3.3</v>
@@ -15649,16 +15649,16 @@
         <v>1.18</v>
       </c>
       <c r="T94">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U94">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V94">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W94">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
         <v>1.02</v>
@@ -15667,13 +15667,13 @@
         <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>5.58</v>
+        <v>5.46</v>
       </c>
       <c r="AA94">
         <v>1.47</v>
       </c>
       <c r="AB94">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AC94">
         <v>2.09</v>
@@ -15803,16 +15803,16 @@
         <v>1.45</v>
       </c>
       <c r="Q95">
-        <v>5</v>
+        <v>5.59</v>
       </c>
       <c r="R95">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="S95">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T95">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="U95">
         <v>2.02</v>
@@ -15827,10 +15827,10 @@
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>5.65</v>
+        <v>5.72</v>
       </c>
       <c r="AA95">
         <v>1.36</v>
@@ -15845,7 +15845,7 @@
         <v>1.7</v>
       </c>
       <c r="AE95">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF95">
         <v>1.53</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK95">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,16 +15966,16 @@
         <v>2.16</v>
       </c>
       <c r="Q96">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="R96">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="S96">
         <v>1.22</v>
       </c>
       <c r="T96">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U96">
         <v>2.19</v>
@@ -15993,7 +15993,7 @@
         <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="AA96">
         <v>1.53</v>
@@ -16008,7 +16008,7 @@
         <v>1.48</v>
       </c>
       <c r="AE96">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF96">
         <v>1.46</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK96">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,10 +16129,10 @@
         <v>2.56</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R97">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S97">
         <v>1.37</v>
@@ -16153,25 +16153,25 @@
         <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA97">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AB97">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC97">
         <v>3.08</v>
       </c>
       <c r="AD97">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE97">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
         <v>1.73</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AK97">
         <v>1.42</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O98">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P98">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -16301,10 +16301,10 @@
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U98">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V98">
         <v>1.45</v>
@@ -16322,16 +16322,16 @@
         <v>3.58</v>
       </c>
       <c r="AA98">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC98">
         <v>2.74</v>
       </c>
       <c r="AD98">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE98">
         <v>1.1</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O99">
         <v>3.45</v>
@@ -16455,7 +16455,7 @@
         <v>3.3</v>
       </c>
       <c r="Q99">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R99">
         <v>2.3</v>
@@ -16464,7 +16464,7 @@
         <v>1.29</v>
       </c>
       <c r="T99">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="U99">
         <v>2.3</v>
@@ -16476,10 +16476,10 @@
         <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
         <v>4.3</v>
@@ -16488,7 +16488,7 @@
         <v>1.61</v>
       </c>
       <c r="AB99">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC99">
         <v>2.43</v>
@@ -16503,7 +16503,7 @@
         <v>1.55</v>
       </c>
       <c r="AG99">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK99">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16630,7 +16630,7 @@
         <v>3.7</v>
       </c>
       <c r="U100">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="V100">
         <v>1.61</v>
@@ -16654,13 +16654,13 @@
         <v>2.34</v>
       </c>
       <c r="AC100">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD100">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE100">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF100">
         <v>1.44</v>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O102">
         <v>5.25</v>
@@ -16944,10 +16944,10 @@
         <v>7.2</v>
       </c>
       <c r="Q102">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R102">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="S102">
         <v>1.2</v>
@@ -16959,10 +16959,10 @@
         <v>2.01</v>
       </c>
       <c r="V102">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W102">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -16980,16 +16980,16 @@
         <v>2.88</v>
       </c>
       <c r="AC102">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AD102">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE102">
         <v>1.33</v>
       </c>
       <c r="AF102">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG102">
         <v>2.26</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
         <v>3.17</v>
@@ -17149,13 +17149,13 @@
         <v>1.42</v>
       </c>
       <c r="AE103">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>2.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK103">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17264,7 +17264,7 @@
         <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="P104">
         <v>2.75</v>
@@ -17276,22 +17276,22 @@
         <v>2.31</v>
       </c>
       <c r="S104">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="V104">
         <v>1.59</v>
       </c>
       <c r="W104">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
         <v>1.12</v>
@@ -17318,7 +17318,7 @@
         <v>1.44</v>
       </c>
       <c r="AG104">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -18411,28 +18411,28 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R111">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S111">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T111">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U111">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="V111">
         <v>1.49</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.15</v>
@@ -18441,13 +18441,13 @@
         <v>4.3</v>
       </c>
       <c r="AA111">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB111">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC111">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD111">
         <v>1.49</v>
@@ -18459,7 +18459,7 @@
         <v>1.59</v>
       </c>
       <c r="AG111">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18737,22 +18737,22 @@
         <v>4.2</v>
       </c>
       <c r="Q113">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U113">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V113">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W113">
         <v>1.17</v>
@@ -18764,7 +18764,7 @@
         <v>1.12</v>
       </c>
       <c r="Z113">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA113">
         <v>1.53</v>
@@ -18779,13 +18779,13 @@
         <v>1.55</v>
       </c>
       <c r="AE113">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF113">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG113">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK113">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O114">
         <v>3.2</v>
@@ -18912,28 +18912,28 @@
         <v>2.9</v>
       </c>
       <c r="U114">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="V114">
         <v>1.33</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z114">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AA114">
         <v>2.1</v>
       </c>
       <c r="AB114">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AC114">
         <v>3.4</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK114">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,10 +19057,10 @@
         <v>1.54</v>
       </c>
       <c r="O115">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P115">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="Q115">
         <v>2.03</v>
@@ -19084,7 +19084,7 @@
         <v>1.11</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
         <v>1.12</v>
@@ -19096,19 +19096,19 @@
         <v>1.53</v>
       </c>
       <c r="AB115">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AC115">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AD115">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE115">
         <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG115">
         <v>2.25</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK115">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O116">
         <v>3.4</v>
       </c>
       <c r="P116">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q116">
         <v>3.74</v>
@@ -19250,22 +19250,22 @@
         <v>1</v>
       </c>
       <c r="Y116">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB116">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC116">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="AD116">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE116">
         <v>1.06</v>
@@ -20041,10 +20041,10 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R121">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S121">
         <v>1.24</v>
@@ -20053,10 +20053,10 @@
         <v>3.6</v>
       </c>
       <c r="U121">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="V121">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W121">
         <v>1.13</v>
@@ -20065,31 +20065,31 @@
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z121">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA121">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB121">
+        <v>2.27</v>
+      </c>
+      <c r="AC121">
         <v>2.3</v>
       </c>
-      <c r="AC121">
-        <v>2.4</v>
-      </c>
       <c r="AD121">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE121">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF121">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AG121">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK121">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,43 +20204,43 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>5.78</v>
+        <v>5</v>
       </c>
       <c r="R122">
         <v>2</v>
       </c>
       <c r="S122">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U122">
         <v>3.2</v>
       </c>
       <c r="V122">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
         <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z122">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AA122">
         <v>2.35</v>
       </c>
       <c r="AB122">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC122">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD122">
         <v>1.16</v>
@@ -20249,7 +20249,7 @@
         <v>1.02</v>
       </c>
       <c r="AF122">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG122">
         <v>1.61</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20370,7 +20370,7 @@
         <v>2.88</v>
       </c>
       <c r="R123">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S123">
         <v>1.44</v>
@@ -20391,10 +20391,10 @@
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z123">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA123">
         <v>2.25</v>
@@ -20403,19 +20403,19 @@
         <v>1.61</v>
       </c>
       <c r="AC123">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AD123">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE123">
         <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG123">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK123">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20530,10 +20530,10 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S124">
         <v>1.4</v>
@@ -20542,10 +20542,10 @@
         <v>2.75</v>
       </c>
       <c r="U124">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="V124">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W124">
         <v>1.04</v>
@@ -20554,10 +20554,10 @@
         <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z124">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA124">
         <v>2.2</v>
@@ -20566,16 +20566,16 @@
         <v>1.65</v>
       </c>
       <c r="AC124">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AD124">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE124">
         <v>1.03</v>
       </c>
       <c r="AF124">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG124">
         <v>1.78</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK124">
         <v>1.25</v>
@@ -20693,10 +20693,10 @@
         <v>3.34</v>
       </c>
       <c r="Q125">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="R125">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="S125">
         <v>1.44</v>
@@ -20717,10 +20717,10 @@
         <v>1.05</v>
       </c>
       <c r="Y125">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z125">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AA125">
         <v>2.25</v>
@@ -20729,19 +20729,19 @@
         <v>1.61</v>
       </c>
       <c r="AC125">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AD125">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE125">
         <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AG125">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.74</v>
+        <v>3.24</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>2.87</v>
+        <v>3.55</v>
       </c>
       <c r="AD6">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="O7">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="R7">
+        <v>2.31</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
+        <v>2.4</v>
+      </c>
+      <c r="V7">
+        <v>1.46</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.19</v>
+      </c>
+      <c r="Z7">
+        <v>3.74</v>
+      </c>
+      <c r="AA7">
+        <v>1.72</v>
+      </c>
+      <c r="AB7">
+        <v>1.96</v>
+      </c>
+      <c r="AC7">
+        <v>2.87</v>
+      </c>
+      <c r="AD7">
+        <v>1.34</v>
+      </c>
+      <c r="AE7">
+        <v>1.1</v>
+      </c>
+      <c r="AF7">
+        <v>1.6</v>
+      </c>
+      <c r="AG7">
         <v>2.15</v>
       </c>
-      <c r="S7">
-        <v>1.38</v>
-      </c>
-      <c r="T7">
-        <v>2.64</v>
-      </c>
-      <c r="U7">
-        <v>2.88</v>
-      </c>
-      <c r="V7">
-        <v>1.36</v>
-      </c>
-      <c r="W7">
-        <v>1.02</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1.32</v>
-      </c>
-      <c r="Z7">
-        <v>3.24</v>
-      </c>
-      <c r="AA7">
-        <v>2</v>
-      </c>
-      <c r="AB7">
-        <v>1.77</v>
-      </c>
-      <c r="AC7">
-        <v>3.55</v>
-      </c>
-      <c r="AD7">
-        <v>1.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.04</v>
-      </c>
-      <c r="AF7">
-        <v>1.75</v>
-      </c>
-      <c r="AG7">
-        <v>1.95</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AK7">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
+        <v>1.4</v>
+      </c>
+      <c r="O109">
+        <v>4.4</v>
+      </c>
+      <c r="P109">
+        <v>5.4</v>
+      </c>
+      <c r="Q109">
+        <v>1.87</v>
+      </c>
+      <c r="R109">
+        <v>2.4</v>
+      </c>
+      <c r="S109">
+        <v>1.25</v>
+      </c>
+      <c r="T109">
+        <v>3.4</v>
+      </c>
+      <c r="U109">
         <v>2.23</v>
       </c>
-      <c r="O109">
-        <v>3.4</v>
-      </c>
-      <c r="P109">
-        <v>2.95</v>
-      </c>
-      <c r="Q109">
-        <v>2.75</v>
-      </c>
-      <c r="R109">
-        <v>2.2</v>
-      </c>
-      <c r="S109">
-        <v>1.3</v>
-      </c>
-      <c r="T109">
-        <v>3.2</v>
-      </c>
-      <c r="U109">
-        <v>2.54</v>
-      </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA109">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O110">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P110">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q110">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="R110">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T110">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="U110">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="V110">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="W110">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
         <v>1.02</v>
       </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
       <c r="Z110">
-        <v>4.15</v>
+        <v>8</v>
       </c>
       <c r="AA110">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB110">
-        <v>2.15</v>
+        <v>3.76</v>
       </c>
       <c r="AC110">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD110">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="AE110">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF110">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG110">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK110">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>2.23</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="P111">
-        <v>9.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="Q111">
+        <v>2.75</v>
+      </c>
+      <c r="R111">
+        <v>2.2</v>
+      </c>
+      <c r="S111">
+        <v>1.3</v>
+      </c>
+      <c r="T111">
+        <v>3.2</v>
+      </c>
+      <c r="U111">
+        <v>2.54</v>
+      </c>
+      <c r="V111">
         <v>1.41</v>
       </c>
-      <c r="R111">
-        <v>3.36</v>
-      </c>
-      <c r="S111">
-        <v>1.13</v>
-      </c>
-      <c r="T111">
-        <v>4.9</v>
-      </c>
-      <c r="U111">
-        <v>1.79</v>
-      </c>
-      <c r="V111">
-        <v>1.98</v>
-      </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>3.68</v>
       </c>
       <c r="AA111">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="O8">
         <v>3.35</v>
@@ -1625,7 +1625,7 @@
         <v>2.5</v>
       </c>
       <c r="R8">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.29</v>
@@ -6705,7 +6705,7 @@
         <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
         <v>2.56</v>
@@ -8954,13 +8954,13 @@
         <v>6.9</v>
       </c>
       <c r="P53">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Q53">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="S53">
         <v>1.19</v>
@@ -8969,10 +8969,10 @@
         <v>4</v>
       </c>
       <c r="U53">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V53">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W53">
         <v>1.19</v>
@@ -8981,10 +8981,10 @@
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z53">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="AA53">
         <v>1.4</v>
@@ -8993,19 +8993,19 @@
         <v>2.75</v>
       </c>
       <c r="AC53">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AD53">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE53">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF53">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AG53">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -11728,10 +11728,10 @@
         <v>4.8</v>
       </c>
       <c r="Q70">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R70">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="S70">
         <v>1.15</v>
@@ -11764,10 +11764,10 @@
         <v>3.6</v>
       </c>
       <c r="AC70">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AD70">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AE70">
         <v>1.44</v>
@@ -16944,55 +16944,55 @@
         <v>6.4</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.13</v>
+        <v>2.23</v>
       </c>
       <c r="O110">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>9.800000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="Q110">
+        <v>2.75</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>1.3</v>
+      </c>
+      <c r="T110">
+        <v>3.2</v>
+      </c>
+      <c r="U110">
+        <v>2.54</v>
+      </c>
+      <c r="V110">
         <v>1.41</v>
       </c>
-      <c r="R110">
-        <v>3.36</v>
-      </c>
-      <c r="S110">
-        <v>1.13</v>
-      </c>
-      <c r="T110">
-        <v>4.9</v>
-      </c>
-      <c r="U110">
-        <v>1.79</v>
-      </c>
-      <c r="V110">
-        <v>1.98</v>
-      </c>
       <c r="W110">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z110">
-        <v>8</v>
+        <v>3.68</v>
       </c>
       <c r="AA110">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="AB110">
-        <v>3.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC110">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD110">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF110">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG110">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.23</v>
+        <v>1.13</v>
       </c>
       <c r="O111">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="P111">
-        <v>2.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q111">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>3.36</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="T111">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="U111">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y111">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="Z111">
-        <v>3.68</v>
+        <v>8</v>
       </c>
       <c r="AA111">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AB111">
-        <v>1.94</v>
+        <v>3.76</v>
       </c>
       <c r="AC111">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="AE111">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF111">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG111">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AK111">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
+        <v>3.05</v>
+      </c>
+      <c r="O119">
+        <v>2.9</v>
+      </c>
+      <c r="P119">
+        <v>2.33</v>
+      </c>
+      <c r="Q119">
+        <v>3.5</v>
+      </c>
+      <c r="R119">
+        <v>2</v>
+      </c>
+      <c r="S119">
+        <v>1.43</v>
+      </c>
+      <c r="T119">
+        <v>2.48</v>
+      </c>
+      <c r="U119">
         <v>3</v>
       </c>
-      <c r="O119">
-        <v>2.88</v>
-      </c>
-      <c r="P119">
-        <v>2.3</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>2.55</v>
@@ -825,7 +825,7 @@
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -837,7 +837,7 @@
         <v>4.26</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
         <v>2.08</v>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>2.7</v>
@@ -1136,7 +1136,7 @@
         <v>2.39</v>
       </c>
       <c r="R5">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1166,7 +1166,7 @@
         <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
         <v>3.74</v>
@@ -1296,7 +1296,7 @@
         <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
         <v>2.15</v>
@@ -1453,7 +1453,7 @@
         <v>2.93</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
         <v>2.12</v>
@@ -1462,7 +1462,7 @@
         <v>3.17</v>
       </c>
       <c r="R7">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
         <v>3.6</v>
@@ -1797,7 +1797,7 @@
         <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="V9">
         <v>1.57</v>
@@ -1818,7 +1818,7 @@
         <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC9">
         <v>2.45</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="O10">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
         <v>3.05</v>
@@ -1951,7 +1951,7 @@
         <v>2.74</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.37</v>
@@ -2467,7 +2467,7 @@
         <v>4.45</v>
       </c>
       <c r="AA13">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
         <v>2.31</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
         <v>1.65</v>
@@ -5241,7 +5241,7 @@
         <v>2.18</v>
       </c>
       <c r="AB30">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
         <v>4.15</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="O31">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="P31">
         <v>1.43</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5860,40 +5860,40 @@
         <v>2.85</v>
       </c>
       <c r="Q34">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="R34">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="S34">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T34">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="U34">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="V34">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W34">
         <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z34">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AA34">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC34">
         <v>4.55</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>2.22</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
         <v>3</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
         <v>2.8</v>
       </c>
       <c r="Q37">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
         <v>1.37</v>
@@ -6413,7 +6413,7 @@
         <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>6.4</v>
+        <v>5.45</v>
       </c>
       <c r="O40">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="P40">
         <v>1.35</v>
@@ -6865,19 +6865,19 @@
         <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>6.3</v>
+        <v>6.04</v>
       </c>
       <c r="AA40">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="AC40">
         <v>1.96</v>
       </c>
       <c r="AD40">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE40">
         <v>1.28</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
         <v>4.8</v>
@@ -7034,7 +7034,7 @@
         <v>1.95</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
         <v>3.3</v>
@@ -7173,7 +7173,7 @@
         <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U42">
         <v>2.1</v>
@@ -7197,7 +7197,7 @@
         <v>1.47</v>
       </c>
       <c r="AB42">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
         <v>2.08</v>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7825,10 +7825,10 @@
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
         <v>1.57</v>
@@ -7849,7 +7849,7 @@
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC46">
         <v>2.35</v>
@@ -7880,7 +7880,7 @@
         <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7985,16 +7985,16 @@
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
         <v>1.12</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O48">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q48">
         <v>2.15</v>
@@ -8187,10 +8187,10 @@
         <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>1.55</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.02</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.11</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8800,7 +8800,7 @@
         <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
         <v>3.3</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
         <v>1.94</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
         <v>2.54</v>
@@ -9280,7 +9280,7 @@
         <v>3.68</v>
       </c>
       <c r="P55">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O56">
         <v>4.18</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
         <v>3.7</v>
@@ -9673,7 +9673,7 @@
         <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>1.84</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="P58">
         <v>3.7</v>
@@ -9790,7 +9790,7 @@
         <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9805,7 +9805,7 @@
         <v>1.61</v>
       </c>
       <c r="AB58">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC58">
         <v>2.32</v>
@@ -9817,10 +9817,10 @@
         <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG58">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O60">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q60">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="R60">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S60">
         <v>1.39</v>
@@ -10128,7 +10128,7 @@
         <v>3.36</v>
       </c>
       <c r="AA60">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB60">
         <v>1.87</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O61">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="P61">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="Q61">
         <v>1.54</v>
@@ -10291,7 +10291,7 @@
         <v>5.05</v>
       </c>
       <c r="AA61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
         <v>2.72</v>
@@ -10306,10 +10306,10 @@
         <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG61">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10581,16 +10581,16 @@
         <v>1.85</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
         <v>3.6</v>
       </c>
       <c r="Q63">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R63">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S63">
         <v>1.45</v>
@@ -10611,19 +10611,19 @@
         <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z63">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA63">
         <v>2.15</v>
       </c>
       <c r="AB63">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC63">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="AD63">
         <v>1.24</v>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R64">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V64">
         <v>1.57</v>
@@ -10780,16 +10780,16 @@
         <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB64">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC64">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD64">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE64">
         <v>1.16</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q67">
         <v>4.05</v>
@@ -11248,7 +11248,7 @@
         <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -11269,10 +11269,10 @@
         <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB67">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC67">
         <v>3.53</v>
@@ -11284,7 +11284,7 @@
         <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
         <v>1.95</v>
@@ -11399,7 +11399,7 @@
         <v>3.2</v>
       </c>
       <c r="P68">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
         <v>3.12</v>
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O69">
+        <v>4.5</v>
+      </c>
+      <c r="P69">
         <v>4.6</v>
-      </c>
-      <c r="P69">
-        <v>4.8</v>
       </c>
       <c r="Q69">
         <v>1.85</v>
       </c>
       <c r="R69">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="S69">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U69">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="V69">
         <v>1.72</v>
       </c>
       <c r="W69">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,19 +11592,19 @@
         <v>1.12</v>
       </c>
       <c r="Z69">
-        <v>6.39</v>
+        <v>6.34</v>
       </c>
       <c r="AA69">
         <v>1.4</v>
       </c>
       <c r="AB69">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AC69">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AD69">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AE69">
         <v>1.33</v>
@@ -11613,7 +11613,7 @@
         <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK69">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,49 +11882,49 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.09</v>
+        <v>3.8</v>
       </c>
       <c r="O71">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>2.95</v>
+        <v>1.76</v>
       </c>
       <c r="Q71">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="R71">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="S71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
         <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
         <v>5.82</v>
       </c>
       <c r="AA71">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB71">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC71">
         <v>2.02</v>
@@ -11936,10 +11936,10 @@
         <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG71">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>1.76</v>
+        <v>2.95</v>
       </c>
       <c r="Q72">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="R72">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S72">
         <v>1.17</v>
       </c>
       <c r="T72">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V72">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="AA72">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB72">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD72">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF72">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG72">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12232,7 +12232,7 @@
         <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W73">
         <v>1.18</v>
@@ -12247,10 +12247,10 @@
         <v>5.1</v>
       </c>
       <c r="AA73">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB73">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC73">
         <v>2.1</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
         <v>1.33</v>
@@ -12377,7 +12377,7 @@
         <v>3.24</v>
       </c>
       <c r="P74">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q74">
         <v>4</v>
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O75">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P75">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q75">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S75">
         <v>1.22</v>
       </c>
       <c r="T75">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="U75">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="V75">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W75">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z75">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD75">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE75">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF75">
         <v>1.55</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK75">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="O76">
         <v>3.5</v>
@@ -12736,10 +12736,10 @@
         <v>3.05</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB76">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC76">
         <v>3.34</v>
@@ -12751,10 +12751,10 @@
         <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12863,16 +12863,16 @@
         <v>2</v>
       </c>
       <c r="O77">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
         <v>1.3</v>
@@ -12881,7 +12881,7 @@
         <v>3.1</v>
       </c>
       <c r="U77">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V77">
         <v>1.44</v>
@@ -12902,7 +12902,7 @@
         <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC77">
         <v>3.1</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
         <v>1.7</v>
@@ -13032,10 +13032,10 @@
         <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="R78">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S78">
         <v>1.48</v>
@@ -13065,10 +13065,10 @@
         <v>2.29</v>
       </c>
       <c r="AB78">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC78">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="AD78">
         <v>1.15</v>
@@ -13096,7 +13096,7 @@
         <v>1.33</v>
       </c>
       <c r="AK78">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13189,13 +13189,13 @@
         <v>2.15</v>
       </c>
       <c r="O79">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
         <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R79">
         <v>2.3</v>
@@ -13370,10 +13370,10 @@
         <v>2.7</v>
       </c>
       <c r="U80">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V80">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
         <v>1.06</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="O81">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -13699,7 +13699,7 @@
         <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13856,7 +13856,7 @@
         <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U83">
         <v>2.04</v>
@@ -13880,7 +13880,7 @@
         <v>1.47</v>
       </c>
       <c r="AB83">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AC83">
         <v>2.12</v>
@@ -13892,7 +13892,7 @@
         <v>1.27</v>
       </c>
       <c r="AF83">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG83">
         <v>2.57</v>
@@ -14004,10 +14004,10 @@
         <v>4</v>
       </c>
       <c r="O84">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O85">
         <v>7</v>
       </c>
       <c r="P85">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q85">
         <v>1.53</v>
       </c>
       <c r="R85">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="S85">
         <v>1.11</v>
       </c>
       <c r="T85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U85">
         <v>1.57</v>
@@ -14197,31 +14197,31 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z85">
         <v>14</v>
       </c>
       <c r="AA85">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB85">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AC85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD85">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AE85">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AF85">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG85">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK85">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O86">
         <v>5.3</v>
@@ -14369,7 +14369,7 @@
         <v>1.33</v>
       </c>
       <c r="AB86">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AC86">
         <v>1.79</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK86">
         <v>3.1</v>
@@ -14496,7 +14496,7 @@
         <v>4.33</v>
       </c>
       <c r="P87">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -14563,7 +14563,7 @@
         <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O88">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q88">
         <v>2.14</v>
@@ -14692,10 +14692,10 @@
         <v>5.55</v>
       </c>
       <c r="AA88">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC88">
         <v>2.14</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14819,13 +14819,13 @@
         <v>2.19</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q89">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R89">
         <v>2.3</v>
@@ -14837,10 +14837,10 @@
         <v>3.25</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V89">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W89">
         <v>1.11</v>
@@ -14870,7 +14870,7 @@
         <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG89">
         <v>2.3</v>
@@ -14889,7 +14889,7 @@
         <v>1.33</v>
       </c>
       <c r="AK89">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O90">
         <v>5.6</v>
       </c>
       <c r="P90">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q90">
         <v>1.73</v>
@@ -14994,13 +14994,13 @@
         <v>2.7</v>
       </c>
       <c r="S90">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V90">
         <v>1.75</v>
@@ -15021,7 +15021,7 @@
         <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC90">
         <v>2.01</v>
@@ -15036,7 +15036,7 @@
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="O91">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P91">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q91">
         <v>1.97</v>
@@ -15184,7 +15184,7 @@
         <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC91">
         <v>2.05</v>
@@ -15323,7 +15323,7 @@
         <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="U92">
         <v>2.12</v>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O93">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P93">
         <v>4.2</v>
@@ -15541,7 +15541,7 @@
         <v>1.18</v>
       </c>
       <c r="AK93">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O94">
         <v>4.2</v>
       </c>
       <c r="P94">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q94">
         <v>3.15</v>
@@ -15652,13 +15652,13 @@
         <v>4.85</v>
       </c>
       <c r="U94">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V94">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W94">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X94">
         <v>1.01</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AK94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,16 +15794,16 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="O95">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="P95">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q95">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R95">
         <v>2.4</v>
@@ -15815,13 +15815,13 @@
         <v>3.9</v>
       </c>
       <c r="U95">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V95">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W95">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15830,28 +15830,28 @@
         <v>1.1</v>
       </c>
       <c r="Z95">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="AA95">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB95">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="AC95">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AD95">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF95">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15990,25 +15990,25 @@
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z96">
-        <v>5.72</v>
+        <v>6</v>
       </c>
       <c r="AA96">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AC96">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AD96">
         <v>1.7</v>
       </c>
       <c r="AE96">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF96">
         <v>1.53</v>
@@ -16135,7 +16135,7 @@
         <v>2.44</v>
       </c>
       <c r="S97">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
         <v>3.8</v>
@@ -16144,19 +16144,19 @@
         <v>2.19</v>
       </c>
       <c r="V97">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="AA97">
         <v>1.53</v>
@@ -16171,13 +16171,13 @@
         <v>1.48</v>
       </c>
       <c r="AE97">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG97">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK97">
         <v>1.36</v>
@@ -16316,22 +16316,22 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z98">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA98">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AB98">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
         <v>3.08</v>
       </c>
       <c r="AD98">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE98">
         <v>1.11</v>
@@ -16340,7 +16340,7 @@
         <v>1.73</v>
       </c>
       <c r="AG98">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P99">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -16485,10 +16485,10 @@
         <v>3.58</v>
       </c>
       <c r="AA99">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB99">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC99">
         <v>2.74</v>
@@ -16615,7 +16615,7 @@
         <v>3.45</v>
       </c>
       <c r="P100">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q100">
         <v>2.45</v>
@@ -16648,7 +16648,7 @@
         <v>4.3</v>
       </c>
       <c r="AA100">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB100">
         <v>2.25</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
         <v>2.8</v>
@@ -16793,7 +16793,7 @@
         <v>3.7</v>
       </c>
       <c r="U101">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="V101">
         <v>1.61</v>
@@ -17098,25 +17098,25 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O103">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P103">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Q103">
         <v>1.75</v>
       </c>
       <c r="R103">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="S103">
         <v>1.2</v>
       </c>
       <c r="T103">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U103">
         <v>2.01</v>
@@ -17131,19 +17131,19 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z103">
-        <v>5.85</v>
+        <v>6.5</v>
       </c>
       <c r="AA103">
         <v>1.35</v>
       </c>
       <c r="AB103">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AC103">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD103">
         <v>1.8</v>
@@ -17152,7 +17152,7 @@
         <v>1.33</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
         <v>2.26</v>
@@ -17171,7 +17171,7 @@
         <v>1.08</v>
       </c>
       <c r="AK103">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>3.95</v>
       </c>
       <c r="P104">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q104">
         <v>5.03</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O105">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q105">
         <v>2.65</v>
@@ -17439,49 +17439,49 @@
         <v>2.31</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W105">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z105">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA105">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC105">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD105">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE105">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF105">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17789,7 +17789,7 @@
         <v>5.37</v>
       </c>
       <c r="AA107">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB107">
         <v>2.64</v>
@@ -17916,10 +17916,10 @@
         <v>1.7</v>
       </c>
       <c r="O108">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P108">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q108">
         <v>2.22</v>
@@ -17955,7 +17955,7 @@
         <v>1.54</v>
       </c>
       <c r="AB108">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="AC108">
         <v>2.38</v>
@@ -18149,7 +18149,7 @@
         <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P110">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q110">
         <v>2.75</v>
@@ -18278,10 +18278,10 @@
         <v>3.68</v>
       </c>
       <c r="AA110">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC110">
         <v>2.78</v>
@@ -18405,10 +18405,10 @@
         <v>1.13</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="P111">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Q111">
         <v>1.41</v>
@@ -18432,7 +18432,7 @@
         <v>1.29</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.02</v>
@@ -18441,7 +18441,7 @@
         <v>8</v>
       </c>
       <c r="AA111">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB111">
         <v>3.76</v>
@@ -18586,7 +18586,7 @@
         <v>3.3</v>
       </c>
       <c r="U112">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V112">
         <v>1.49</v>
@@ -18604,10 +18604,10 @@
         <v>4.3</v>
       </c>
       <c r="AA112">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB112">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC112">
         <v>2.62</v>
@@ -18638,7 +18638,7 @@
         <v>1.19</v>
       </c>
       <c r="AK112">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>4.2</v>
       </c>
       <c r="Q114">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
         <v>2.36</v>
@@ -19057,10 +19057,10 @@
         <v>2.7</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P115">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q115">
         <v>3.3</v>
@@ -19090,28 +19090,28 @@
         <v>1.35</v>
       </c>
       <c r="Z115">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AA115">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB115">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC115">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF115">
         <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK115">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19223,7 +19223,7 @@
         <v>4.6</v>
       </c>
       <c r="P116">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q116">
         <v>2.03</v>
@@ -19250,25 +19250,25 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA116">
+        <v>1.52</v>
+      </c>
+      <c r="AB116">
+        <v>2.45</v>
+      </c>
+      <c r="AC116">
+        <v>2.45</v>
+      </c>
+      <c r="AD116">
         <v>1.53</v>
       </c>
-      <c r="AB116">
-        <v>2.4</v>
-      </c>
-      <c r="AC116">
-        <v>2.22</v>
-      </c>
-      <c r="AD116">
-        <v>1.56</v>
-      </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF116">
         <v>1.57</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="O117">
         <v>3.4</v>
       </c>
       <c r="P117">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q117">
         <v>3.74</v>
@@ -19398,7 +19398,7 @@
         <v>1.4</v>
       </c>
       <c r="T117">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U117">
         <v>2.78</v>
@@ -19419,7 +19419,7 @@
         <v>3.2</v>
       </c>
       <c r="AA117">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB117">
         <v>1.78</v>
@@ -19872,7 +19872,7 @@
         <v>2.61</v>
       </c>
       <c r="O120">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="P120">
         <v>2.8</v>
@@ -19908,7 +19908,7 @@
         <v>2.55</v>
       </c>
       <c r="AA120">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB120">
         <v>1.54</v>
@@ -20038,7 +20038,7 @@
         <v>3.75</v>
       </c>
       <c r="P121">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q121">
         <v>2.1</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="O22">
         <v>4.6</v>
       </c>
       <c r="P22">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P54">
-        <v>2.54</v>
+        <v>2.81</v>
       </c>
       <c r="Q54">
-        <v>3.43</v>
+        <v>3.16</v>
       </c>
       <c r="R54">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S54">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T54">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U54">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="V54">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W54">
         <v>1.01</v>
@@ -9153,10 +9153,10 @@
         <v>2.24</v>
       </c>
       <c r="AB54">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC54">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD54">
         <v>1.17</v>
@@ -9165,10 +9165,10 @@
         <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG54">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10907,10 +10907,10 @@
         <v>2.75</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -11070,7 +11070,7 @@
         <v>1.66</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
         <v>4.2</v>
@@ -11112,13 +11112,13 @@
         <v>2.38</v>
       </c>
       <c r="AC66">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD66">
         <v>1.51</v>
       </c>
       <c r="AE66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
         <v>1.57</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="O72">
         <v>3.85</v>
       </c>
       <c r="P72">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q72">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="R72">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S72">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U72">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA72">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB72">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AC72">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE72">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF72">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>2.09</v>
       </c>
       <c r="O73">
         <v>3.85</v>
       </c>
       <c r="P73">
+        <v>2.95</v>
+      </c>
+      <c r="Q73">
+        <v>2.52</v>
+      </c>
+      <c r="R73">
+        <v>2.42</v>
+      </c>
+      <c r="S73">
+        <v>1.17</v>
+      </c>
+      <c r="T73">
+        <v>4.5</v>
+      </c>
+      <c r="U73">
         <v>2.05</v>
       </c>
-      <c r="Q73">
-        <v>3.45</v>
-      </c>
-      <c r="R73">
-        <v>2.39</v>
-      </c>
-      <c r="S73">
-        <v>1.22</v>
-      </c>
-      <c r="T73">
-        <v>3.9</v>
-      </c>
-      <c r="U73">
-        <v>2.1</v>
-      </c>
       <c r="V73">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W73">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA73">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB73">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD73">
+        <v>1.69</v>
+      </c>
+      <c r="AE73">
+        <v>1.29</v>
+      </c>
+      <c r="AF73">
+        <v>1.36</v>
+      </c>
+      <c r="AG73">
+        <v>2.88</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.32</v>
+      </c>
+      <c r="AK73">
         <v>1.67</v>
-      </c>
-      <c r="AE73">
-        <v>1.27</v>
-      </c>
-      <c r="AF73">
-        <v>1.41</v>
-      </c>
-      <c r="AG73">
-        <v>2.62</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.25</v>
-      </c>
-      <c r="AK73">
-        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -17590,16 +17590,16 @@
         <v>1.36</v>
       </c>
       <c r="O106">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="P106">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S106">
         <v>1.25</v>
@@ -17608,13 +17608,13 @@
         <v>3.6</v>
       </c>
       <c r="U106">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V106">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="O109">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q109">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="V109">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W109">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z109">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="AA109">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC109">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD109">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.09</v>
+        <v>1.13</v>
       </c>
       <c r="O110">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="P110">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="Q110">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>3.36</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="T110">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="U110">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="V110">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="Z110">
-        <v>3.68</v>
+        <v>8</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB110">
-        <v>2.05</v>
+        <v>3.76</v>
       </c>
       <c r="AC110">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD110">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="AE110">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF110">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG110">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AK110">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="O111">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="Q111">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="R111">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
       <c r="S111">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="V111">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>4.15</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>5.87</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB12">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AD12">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R13">
+        <v>2.62</v>
+      </c>
+      <c r="S13">
+        <v>1.17</v>
+      </c>
+      <c r="T13">
+        <v>3.92</v>
+      </c>
+      <c r="U13">
+        <v>2.08</v>
+      </c>
+      <c r="V13">
+        <v>1.68</v>
+      </c>
+      <c r="W13">
+        <v>1.17</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>5.87</v>
+      </c>
+      <c r="AA13">
+        <v>1.39</v>
+      </c>
+      <c r="AB13">
+        <v>2.59</v>
+      </c>
+      <c r="AC13">
+        <v>2.16</v>
+      </c>
+      <c r="AD13">
+        <v>1.71</v>
+      </c>
+      <c r="AE13">
+        <v>1.23</v>
+      </c>
+      <c r="AF13">
+        <v>1.57</v>
+      </c>
+      <c r="AG13">
         <v>2.3</v>
       </c>
-      <c r="S13">
-        <v>1.29</v>
-      </c>
-      <c r="T13">
-        <v>3.4</v>
-      </c>
-      <c r="U13">
-        <v>2.3</v>
-      </c>
-      <c r="V13">
-        <v>1.53</v>
-      </c>
-      <c r="W13">
-        <v>1.09</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.14</v>
-      </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.6</v>
-      </c>
-      <c r="AB13">
-        <v>2.31</v>
-      </c>
-      <c r="AC13">
-        <v>2.48</v>
-      </c>
-      <c r="AD13">
-        <v>1.45</v>
-      </c>
-      <c r="AE13">
-        <v>1.14</v>
-      </c>
-      <c r="AF13">
-        <v>1.5</v>
-      </c>
-      <c r="AG13">
-        <v>2.45</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P109">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q109">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="R109">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U109">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA109">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="O110">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="P110">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="Q110">
+        <v>2.75</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>1.3</v>
+      </c>
+      <c r="T110">
+        <v>3.2</v>
+      </c>
+      <c r="U110">
+        <v>2.54</v>
+      </c>
+      <c r="V110">
         <v>1.41</v>
       </c>
-      <c r="R110">
-        <v>3.36</v>
-      </c>
-      <c r="S110">
-        <v>1.13</v>
-      </c>
-      <c r="T110">
-        <v>4.9</v>
-      </c>
-      <c r="U110">
-        <v>1.79</v>
-      </c>
-      <c r="V110">
-        <v>1.98</v>
-      </c>
       <c r="W110">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z110">
-        <v>8</v>
+        <v>3.68</v>
       </c>
       <c r="AA110">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>3.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC110">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD110">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF110">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG110">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O111">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="P111">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="Q111">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="R111">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="S111">
+        <v>1.13</v>
+      </c>
+      <c r="T111">
+        <v>4.9</v>
+      </c>
+      <c r="U111">
+        <v>1.79</v>
+      </c>
+      <c r="V111">
+        <v>1.98</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.02</v>
+      </c>
+      <c r="Z111">
+        <v>8</v>
+      </c>
+      <c r="AA111">
         <v>1.25</v>
       </c>
-      <c r="T111">
-        <v>3.4</v>
-      </c>
-      <c r="U111">
-        <v>2.23</v>
-      </c>
-      <c r="V111">
-        <v>1.53</v>
-      </c>
-      <c r="W111">
-        <v>1.12</v>
-      </c>
-      <c r="X111">
+      <c r="AB111">
+        <v>3.76</v>
+      </c>
+      <c r="AC111">
+        <v>1.65</v>
+      </c>
+      <c r="AD111">
+        <v>2.18</v>
+      </c>
+      <c r="AE111">
+        <v>1.47</v>
+      </c>
+      <c r="AF111">
+        <v>1.77</v>
+      </c>
+      <c r="AG111">
+        <v>1.92</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
         <v>1.02</v>
       </c>
-      <c r="Y111">
-        <v>1.16</v>
-      </c>
-      <c r="Z111">
-        <v>4.15</v>
-      </c>
-      <c r="AA111">
-        <v>1.6</v>
-      </c>
-      <c r="AB111">
-        <v>2.15</v>
-      </c>
-      <c r="AC111">
-        <v>2.55</v>
-      </c>
-      <c r="AD111">
-        <v>1.44</v>
-      </c>
-      <c r="AE111">
-        <v>1.15</v>
-      </c>
-      <c r="AF111">
-        <v>1.76</v>
-      </c>
-      <c r="AG111">
-        <v>1.95</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.2</v>
-      </c>
       <c r="AK111">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -686,13 +686,13 @@
         <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
         <v>2.55</v>
@@ -819,7 +819,7 @@
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V3">
         <v>1.5</v>
@@ -855,7 +855,7 @@
         <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>2.34</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
         <v>2.7</v>
@@ -991,13 +991,13 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA4">
         <v>2.52</v>
@@ -1006,19 +1006,19 @@
         <v>1.53</v>
       </c>
       <c r="AC4">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
         <v>2.39</v>
@@ -1154,13 +1154,13 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
         <v>2.12</v>
@@ -1172,16 +1172,16 @@
         <v>3.74</v>
       </c>
       <c r="AD5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
         <v>2</v>
@@ -1465,7 +1465,7 @@
         <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
         <v>3.25</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -1628,10 +1628,10 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
         <v>2.38</v>
@@ -1646,31 +1646,31 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AA8">
         <v>1.77</v>
       </c>
       <c r="AB8">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1782,16 +1782,16 @@
         <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q9">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
         <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
         <v>3.4</v>
@@ -1812,28 +1812,28 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="AA9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AD9">
         <v>1.52</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="O10">
         <v>3.25</v>
@@ -1963,7 +1963,7 @@
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1978,7 +1978,7 @@
         <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
         <v>1.95</v>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,65 +2265,65 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R12">
+        <v>2.62</v>
+      </c>
+      <c r="S12">
+        <v>1.17</v>
+      </c>
+      <c r="T12">
+        <v>3.92</v>
+      </c>
+      <c r="U12">
+        <v>2.08</v>
+      </c>
+      <c r="V12">
+        <v>1.68</v>
+      </c>
+      <c r="W12">
+        <v>1.17</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.08</v>
+      </c>
+      <c r="Z12">
+        <v>5.87</v>
+      </c>
+      <c r="AA12">
+        <v>1.39</v>
+      </c>
+      <c r="AB12">
+        <v>2.59</v>
+      </c>
+      <c r="AC12">
+        <v>2.16</v>
+      </c>
+      <c r="AD12">
+        <v>1.71</v>
+      </c>
+      <c r="AE12">
+        <v>1.23</v>
+      </c>
+      <c r="AF12">
+        <v>1.57</v>
+      </c>
+      <c r="AG12">
         <v>2.3</v>
       </c>
-      <c r="S12">
-        <v>1.29</v>
-      </c>
-      <c r="T12">
-        <v>3.4</v>
-      </c>
-      <c r="U12">
-        <v>2.3</v>
-      </c>
-      <c r="V12">
-        <v>1.53</v>
-      </c>
-      <c r="W12">
-        <v>1.09</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.14</v>
-      </c>
-      <c r="Z12">
-        <v>4.45</v>
-      </c>
-      <c r="AA12">
-        <v>1.6</v>
-      </c>
-      <c r="AB12">
-        <v>2.31</v>
-      </c>
-      <c r="AC12">
-        <v>2.48</v>
-      </c>
-      <c r="AD12">
-        <v>1.45</v>
-      </c>
-      <c r="AE12">
-        <v>1.14</v>
-      </c>
-      <c r="AF12">
-        <v>1.5</v>
-      </c>
-      <c r="AG12">
-        <v>2.45</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>5.87</v>
+        <v>4.45</v>
       </c>
       <c r="AA13">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="AC13">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AD13">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AE13">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>6.57</v>
       </c>
       <c r="AA15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
         <v>1.93</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P20">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
         <v>2.3</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>8.6</v>
+        <v>7.28</v>
       </c>
       <c r="O22">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P22">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>1.27</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.05</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
         <v>1.54</v>
@@ -5223,7 +5223,7 @@
         <v>3.18</v>
       </c>
       <c r="V30">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5241,7 +5241,7 @@
         <v>2.18</v>
       </c>
       <c r="AB30">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC30">
         <v>4.15</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O34">
         <v>3.36</v>
       </c>
       <c r="P34">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
         <v>3.27</v>
@@ -5878,7 +5878,7 @@
         <v>1.26</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.06</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
         <v>1.5</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O39">
         <v>4.1</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P40">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Q40">
         <v>5</v>
@@ -6998,7 +6998,7 @@
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q41">
         <v>2.25</v>
@@ -7031,7 +7031,7 @@
         <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
         <v>1.87</v>
@@ -7173,7 +7173,7 @@
         <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="U42">
         <v>2.1</v>
@@ -7659,19 +7659,19 @@
         <v>1.97</v>
       </c>
       <c r="S45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
         <v>3.2</v>
       </c>
       <c r="V45">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
         <v>1.05</v>
@@ -7686,7 +7686,7 @@
         <v>2.25</v>
       </c>
       <c r="AB45">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC45">
         <v>3.94</v>
@@ -7717,7 +7717,7 @@
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8148,7 +8148,7 @@
         <v>2.21</v>
       </c>
       <c r="S48">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
         <v>3.1</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>3.78</v>
       </c>
       <c r="AA52">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB52">
         <v>2.07</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="O53">
         <v>6.9</v>
       </c>
       <c r="P53">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Q53">
         <v>10.5</v>
@@ -9117,7 +9117,7 @@
         <v>3.15</v>
       </c>
       <c r="P54">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
         <v>3.16</v>
@@ -9277,7 +9277,7 @@
         <v>2.75</v>
       </c>
       <c r="O55">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
         <v>2.1</v>
@@ -9440,7 +9440,7 @@
         <v>3.25</v>
       </c>
       <c r="O56">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
         <v>1.84</v>
@@ -9476,10 +9476,10 @@
         <v>4.61</v>
       </c>
       <c r="AA56">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB56">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC56">
         <v>2.44</v>
@@ -9603,16 +9603,16 @@
         <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q57">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9621,13 +9621,13 @@
         <v>3.7</v>
       </c>
       <c r="U57">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="V57">
         <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,28 +9636,28 @@
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AD57">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE57">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG57">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O58">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="P58">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
       </c>
       <c r="R58">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S58">
         <v>1.25</v>
@@ -9805,22 +9805,22 @@
         <v>1.61</v>
       </c>
       <c r="AB58">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AD58">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE58">
         <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
         <v>4.4</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -10270,7 +10270,7 @@
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
         <v>2.03</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>1.85</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q63">
         <v>2.52</v>
@@ -10747,7 +10747,7 @@
         <v>3.5</v>
       </c>
       <c r="P64">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q64">
         <v>3.5</v>
@@ -10759,7 +10759,7 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U64">
         <v>2.4</v>
@@ -11070,7 +11070,7 @@
         <v>1.66</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
         <v>4.2</v>
@@ -11082,7 +11082,7 @@
         <v>2.52</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T66">
         <v>3.6</v>
@@ -11106,7 +11106,7 @@
         <v>4.71</v>
       </c>
       <c r="AA66">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB66">
         <v>2.38</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
+        <v>3.1</v>
+      </c>
+      <c r="O67">
         <v>3.2</v>
       </c>
-      <c r="O67">
-        <v>3.3</v>
-      </c>
       <c r="P67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q67">
         <v>4.05</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O68">
         <v>3.2</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q68">
         <v>3.12</v>
@@ -11466,7 +11466,7 @@
         <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11580,7 +11580,7 @@
         <v>2.04</v>
       </c>
       <c r="V69">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W69">
         <v>1.18</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="O70">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -11734,19 +11734,19 @@
         <v>2.9</v>
       </c>
       <c r="S70">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T70">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U70">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V70">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W70">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X70">
         <v>1.01</v>
@@ -11755,28 +11755,28 @@
         <v>1.05</v>
       </c>
       <c r="Z70">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA70">
         <v>1.25</v>
       </c>
       <c r="AB70">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC70">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD70">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE70">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF70">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG70">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O71">
         <v>4</v>
@@ -11933,7 +11933,7 @@
         <v>1.68</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
         <v>1.41</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="O72">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P72">
+        <v>2.68</v>
+      </c>
+      <c r="Q72">
+        <v>2.52</v>
+      </c>
+      <c r="R72">
+        <v>2.42</v>
+      </c>
+      <c r="S72">
+        <v>1.17</v>
+      </c>
+      <c r="T72">
+        <v>4.5</v>
+      </c>
+      <c r="U72">
         <v>2.05</v>
       </c>
-      <c r="Q72">
-        <v>3.45</v>
-      </c>
-      <c r="R72">
-        <v>2.39</v>
-      </c>
-      <c r="S72">
-        <v>1.22</v>
-      </c>
-      <c r="T72">
-        <v>3.9</v>
-      </c>
-      <c r="U72">
-        <v>2.1</v>
-      </c>
       <c r="V72">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W72">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA72">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB72">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD72">
+        <v>1.69</v>
+      </c>
+      <c r="AE72">
+        <v>1.25</v>
+      </c>
+      <c r="AF72">
+        <v>1.36</v>
+      </c>
+      <c r="AG72">
+        <v>2.88</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>1.32</v>
+      </c>
+      <c r="AK72">
         <v>1.67</v>
-      </c>
-      <c r="AE72">
-        <v>1.27</v>
-      </c>
-      <c r="AF72">
-        <v>1.41</v>
-      </c>
-      <c r="AG72">
-        <v>2.62</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.25</v>
-      </c>
-      <c r="AK72">
-        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.09</v>
+        <v>2.99</v>
       </c>
       <c r="O73">
         <v>3.85</v>
       </c>
       <c r="P73">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q73">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="R73">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S73">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U73">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W73">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z73">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA73">
+        <v>1.44</v>
+      </c>
+      <c r="AB73">
+        <v>2.6</v>
+      </c>
+      <c r="AC73">
+        <v>2.1</v>
+      </c>
+      <c r="AD73">
+        <v>1.67</v>
+      </c>
+      <c r="AE73">
+        <v>1.27</v>
+      </c>
+      <c r="AF73">
+        <v>1.41</v>
+      </c>
+      <c r="AG73">
+        <v>2.62</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.25</v>
+      </c>
+      <c r="AK73">
         <v>1.36</v>
-      </c>
-      <c r="AB73">
-        <v>2.88</v>
-      </c>
-      <c r="AC73">
-        <v>2.01</v>
-      </c>
-      <c r="AD73">
-        <v>1.69</v>
-      </c>
-      <c r="AE73">
-        <v>1.29</v>
-      </c>
-      <c r="AF73">
-        <v>1.36</v>
-      </c>
-      <c r="AG73">
-        <v>2.88</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.32</v>
-      </c>
-      <c r="AK73">
-        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,10 +12374,10 @@
         <v>3.4</v>
       </c>
       <c r="O74">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q74">
         <v>4</v>
@@ -12389,37 +12389,37 @@
         <v>1.44</v>
       </c>
       <c r="T74">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U74">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V74">
         <v>1.3</v>
       </c>
       <c r="W74">
+        <v>1.06</v>
+      </c>
+      <c r="X74">
         <v>1.05</v>
-      </c>
-      <c r="X74">
-        <v>1.03</v>
       </c>
       <c r="Y74">
         <v>1.39</v>
       </c>
       <c r="Z74">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AA74">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB74">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC74">
-        <v>4.43</v>
+        <v>4.1</v>
       </c>
       <c r="AD74">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE74">
         <v>1.01</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O75">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="P75">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q75">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R75">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="S75">
         <v>1.22</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P76">
         <v>5.25</v>
@@ -12709,7 +12709,7 @@
         <v>2.2</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
         <v>1.42</v>
@@ -12896,13 +12896,13 @@
         <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC77">
         <v>3.1</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P78">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
         <v>3.05</v>
@@ -13192,7 +13192,7 @@
         <v>3.3</v>
       </c>
       <c r="P79">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q79">
         <v>2.7</v>
@@ -13201,7 +13201,7 @@
         <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
         <v>3.2</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O80">
         <v>3.4</v>
       </c>
       <c r="P80">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q80">
         <v>2.48</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
         <v>3</v>
       </c>
       <c r="P81">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -14004,7 +14004,7 @@
         <v>4</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P84">
         <v>1.9</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB84">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>8.5</v>
       </c>
       <c r="Q85">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R85">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="S85">
         <v>1.11</v>
@@ -14197,16 +14197,16 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z85">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AA85">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC85">
         <v>1.36</v>
@@ -14215,13 +14215,13 @@
         <v>2.7</v>
       </c>
       <c r="AE85">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AF85">
         <v>1.33</v>
       </c>
       <c r="AG85">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK85">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O87">
         <v>4.33</v>
@@ -14526,7 +14526,7 @@
         <v>1.02</v>
       </c>
       <c r="Z87">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AA87">
         <v>1.17</v>
@@ -14819,10 +14819,10 @@
         <v>2.19</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P89">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q89">
         <v>2.6</v>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O91">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P91">
         <v>4.85</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -15344,7 +15344,7 @@
         <v>5.53</v>
       </c>
       <c r="AA92">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AB92">
         <v>2.59</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O93">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P93">
         <v>4.2</v>
       </c>
       <c r="Q93">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R93">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S93">
         <v>1.13</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O94">
         <v>4.2</v>
       </c>
       <c r="P94">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q94">
         <v>3.15</v>
@@ -15658,7 +15658,7 @@
         <v>1.91</v>
       </c>
       <c r="W94">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X94">
         <v>1.01</v>
@@ -15794,10 +15794,10 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="O95">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="P95">
         <v>2.13</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="O96">
         <v>4.8</v>
       </c>
       <c r="P96">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q96">
         <v>5.59</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="O97">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q97">
         <v>3.45</v>
@@ -16286,7 +16286,7 @@
         <v>2.73</v>
       </c>
       <c r="O98">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P98">
         <v>2.56</v>
@@ -16356,7 +16356,7 @@
         <v>1.35</v>
       </c>
       <c r="AK98">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="O99">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -16682,7 +16682,7 @@
         <v>1.29</v>
       </c>
       <c r="AK100">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>2.8</v>
       </c>
       <c r="Q101">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R101">
         <v>2.38</v>
@@ -16793,10 +16793,10 @@
         <v>3.7</v>
       </c>
       <c r="U101">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="V101">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W101">
         <v>1.13</v>
@@ -16814,22 +16814,22 @@
         <v>1.51</v>
       </c>
       <c r="AB101">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC101">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD101">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE101">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF101">
         <v>1.44</v>
       </c>
       <c r="AG101">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>6.4</v>
       </c>
       <c r="Q102">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="R102">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="S102">
+        <v>1.33</v>
+      </c>
+      <c r="T102">
+        <v>3</v>
+      </c>
+      <c r="U102">
+        <v>2.64</v>
+      </c>
+      <c r="V102">
         <v>1.38</v>
       </c>
-      <c r="T102">
-        <v>2.64</v>
-      </c>
-      <c r="U102">
-        <v>2.76</v>
-      </c>
-      <c r="V102">
-        <v>1.35</v>
-      </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA102">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB102">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC102">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD102">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE102">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF102">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG102">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK102">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,16 +17101,16 @@
         <v>1.36</v>
       </c>
       <c r="O103">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P103">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q103">
         <v>1.75</v>
       </c>
       <c r="R103">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="S103">
         <v>1.2</v>
@@ -17125,16 +17125,16 @@
         <v>1.79</v>
       </c>
       <c r="W103">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z103">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="AA103">
         <v>1.35</v>
@@ -17143,13 +17143,13 @@
         <v>3</v>
       </c>
       <c r="AC103">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD103">
         <v>1.8</v>
       </c>
       <c r="AE103">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF103">
         <v>1.73</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK103">
         <v>3</v>
@@ -17267,7 +17267,7 @@
         <v>3.95</v>
       </c>
       <c r="P104">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q104">
         <v>5.03</v>
@@ -17430,7 +17430,7 @@
         <v>3.75</v>
       </c>
       <c r="P105">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q105">
         <v>2.65</v>
@@ -17454,7 +17454,7 @@
         <v>1.14</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
         <v>1.11</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O107">
         <v>4.05</v>
@@ -17759,7 +17759,7 @@
         <v>4.3</v>
       </c>
       <c r="Q107">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R107">
         <v>2.37</v>
@@ -17916,10 +17916,10 @@
         <v>1.7</v>
       </c>
       <c r="O108">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P108">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q108">
         <v>2.22</v>
@@ -17934,10 +17934,10 @@
         <v>3.38</v>
       </c>
       <c r="U108">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V108">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W108">
         <v>1.15</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK108">
         <v>1.96</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O109">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P109">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q109">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="S109">
+        <v>1.13</v>
+      </c>
+      <c r="T109">
+        <v>4.9</v>
+      </c>
+      <c r="U109">
+        <v>1.79</v>
+      </c>
+      <c r="V109">
+        <v>1.98</v>
+      </c>
+      <c r="W109">
+        <v>1.29</v>
+      </c>
+      <c r="X109">
+        <v>1.01</v>
+      </c>
+      <c r="Y109">
+        <v>1.02</v>
+      </c>
+      <c r="Z109">
+        <v>8</v>
+      </c>
+      <c r="AA109">
         <v>1.25</v>
       </c>
-      <c r="T109">
-        <v>3.4</v>
-      </c>
-      <c r="U109">
-        <v>2.23</v>
-      </c>
-      <c r="V109">
-        <v>1.53</v>
-      </c>
-      <c r="W109">
-        <v>1.12</v>
-      </c>
-      <c r="X109">
+      <c r="AB109">
+        <v>3.76</v>
+      </c>
+      <c r="AC109">
+        <v>1.65</v>
+      </c>
+      <c r="AD109">
+        <v>2.18</v>
+      </c>
+      <c r="AE109">
+        <v>1.47</v>
+      </c>
+      <c r="AF109">
+        <v>1.77</v>
+      </c>
+      <c r="AG109">
+        <v>1.92</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.02</v>
       </c>
-      <c r="Y109">
-        <v>1.16</v>
-      </c>
-      <c r="Z109">
-        <v>4.15</v>
-      </c>
-      <c r="AA109">
-        <v>1.6</v>
-      </c>
-      <c r="AB109">
-        <v>2.15</v>
-      </c>
-      <c r="AC109">
-        <v>2.55</v>
-      </c>
-      <c r="AD109">
-        <v>1.44</v>
-      </c>
-      <c r="AE109">
-        <v>1.15</v>
-      </c>
-      <c r="AF109">
-        <v>1.76</v>
-      </c>
-      <c r="AG109">
-        <v>1.95</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.2</v>
-      </c>
       <c r="AK109">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U110">
         <v>2.54</v>
@@ -18281,7 +18281,7 @@
         <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC110">
         <v>2.78</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="O111">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="Q111">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="R111">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="V111">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>4.15</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>2.52</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>4.2</v>
       </c>
       <c r="Q114">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R114">
         <v>2.36</v>
@@ -18930,10 +18930,10 @@
         <v>4.8</v>
       </c>
       <c r="AA114">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB114">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC114">
         <v>2.24</v>
@@ -19060,7 +19060,7 @@
         <v>3.35</v>
       </c>
       <c r="P115">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q115">
         <v>3.3</v>
@@ -19090,13 +19090,13 @@
         <v>1.35</v>
       </c>
       <c r="Z115">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AA115">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB115">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC115">
         <v>3.8</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="O116">
         <v>4.6</v>
       </c>
       <c r="P116">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q116">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="R116">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S116">
         <v>1.25</v>
@@ -19238,7 +19238,7 @@
         <v>3.6</v>
       </c>
       <c r="U116">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V116">
         <v>1.6</v>
@@ -19250,28 +19250,28 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z116">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA116">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB116">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AC116">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD116">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE116">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF116">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG116">
         <v>2.25</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK116">
         <v>2.5</v>
@@ -19380,19 +19380,19 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="O117">
         <v>3.4</v>
       </c>
       <c r="P117">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q117">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="R117">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S117">
         <v>1.4</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19724,7 +19724,7 @@
         <v>1.43</v>
       </c>
       <c r="T119">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U119">
         <v>3</v>
@@ -19872,16 +19872,16 @@
         <v>2.61</v>
       </c>
       <c r="O120">
+        <v>3</v>
+      </c>
+      <c r="P120">
         <v>2.9</v>
-      </c>
-      <c r="P120">
-        <v>2.8</v>
       </c>
       <c r="Q120">
         <v>3.04</v>
       </c>
       <c r="R120">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S120">
         <v>1.45</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O45">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P45">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="Q45">
         <v>2.7</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O62">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O65">
         <v>3.6</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
         <v>1.41</v>
@@ -17590,61 +17590,61 @@
         <v>1.36</v>
       </c>
       <c r="O106">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="P106">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q106">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R106">
         <v>2.5</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="U106">
         <v>2.4</v>
       </c>
       <c r="V106">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W106">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA106">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB106">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AC106">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD106">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE106">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O121">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P121">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -20050,7 +20050,7 @@
         <v>1.32</v>
       </c>
       <c r="T121">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="U121">
         <v>2.48</v>
@@ -20071,10 +20071,10 @@
         <v>3.7</v>
       </c>
       <c r="AA121">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB121">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC121">
         <v>2.81</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>5.87</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB12">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AD12">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R13">
+        <v>2.62</v>
+      </c>
+      <c r="S13">
+        <v>1.17</v>
+      </c>
+      <c r="T13">
+        <v>3.92</v>
+      </c>
+      <c r="U13">
+        <v>2.08</v>
+      </c>
+      <c r="V13">
+        <v>1.68</v>
+      </c>
+      <c r="W13">
+        <v>1.17</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>5.87</v>
+      </c>
+      <c r="AA13">
+        <v>1.39</v>
+      </c>
+      <c r="AB13">
+        <v>2.59</v>
+      </c>
+      <c r="AC13">
+        <v>2.16</v>
+      </c>
+      <c r="AD13">
+        <v>1.71</v>
+      </c>
+      <c r="AE13">
+        <v>1.23</v>
+      </c>
+      <c r="AF13">
+        <v>1.57</v>
+      </c>
+      <c r="AG13">
         <v>2.3</v>
       </c>
-      <c r="S13">
-        <v>1.29</v>
-      </c>
-      <c r="T13">
-        <v>3.4</v>
-      </c>
-      <c r="U13">
-        <v>2.3</v>
-      </c>
-      <c r="V13">
-        <v>1.53</v>
-      </c>
-      <c r="W13">
-        <v>1.09</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.14</v>
-      </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.6</v>
-      </c>
-      <c r="AB13">
-        <v>2.31</v>
-      </c>
-      <c r="AC13">
-        <v>2.48</v>
-      </c>
-      <c r="AD13">
-        <v>1.45</v>
-      </c>
-      <c r="AE13">
-        <v>1.14</v>
-      </c>
-      <c r="AF13">
-        <v>1.49</v>
-      </c>
-      <c r="AG13">
-        <v>2.44</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -10418,10 +10418,10 @@
         <v>1.42</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>7</v>
+        <v>8.02</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="O109">
-        <v>7.7</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>9.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="Q109">
+        <v>2.75</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>1.3</v>
+      </c>
+      <c r="T109">
+        <v>2.85</v>
+      </c>
+      <c r="U109">
+        <v>2.54</v>
+      </c>
+      <c r="V109">
         <v>1.41</v>
       </c>
-      <c r="R109">
-        <v>3.36</v>
-      </c>
-      <c r="S109">
-        <v>1.13</v>
-      </c>
-      <c r="T109">
-        <v>4.9</v>
-      </c>
-      <c r="U109">
-        <v>1.79</v>
-      </c>
-      <c r="V109">
-        <v>1.98</v>
-      </c>
       <c r="W109">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z109">
-        <v>8</v>
+        <v>3.68</v>
       </c>
       <c r="AA109">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
-        <v>3.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC109">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD109">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK109">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="O110">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P110">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q110">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U110">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V110">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA110">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB110">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC110">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AD110">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE110">
         <v>1.15</v>
       </c>
       <c r="AF110">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG110">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O111">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P111">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q111">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="S111">
+        <v>1.13</v>
+      </c>
+      <c r="T111">
+        <v>4.9</v>
+      </c>
+      <c r="U111">
+        <v>1.79</v>
+      </c>
+      <c r="V111">
+        <v>1.98</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.02</v>
+      </c>
+      <c r="Z111">
+        <v>8</v>
+      </c>
+      <c r="AA111">
         <v>1.25</v>
       </c>
-      <c r="T111">
-        <v>3.4</v>
-      </c>
-      <c r="U111">
-        <v>2.23</v>
-      </c>
-      <c r="V111">
-        <v>1.53</v>
-      </c>
-      <c r="W111">
-        <v>1.14</v>
-      </c>
-      <c r="X111">
+      <c r="AB111">
+        <v>3.76</v>
+      </c>
+      <c r="AC111">
+        <v>1.65</v>
+      </c>
+      <c r="AD111">
+        <v>2.18</v>
+      </c>
+      <c r="AE111">
+        <v>1.47</v>
+      </c>
+      <c r="AF111">
+        <v>1.77</v>
+      </c>
+      <c r="AG111">
+        <v>1.92</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
         <v>1.02</v>
       </c>
-      <c r="Y111">
-        <v>1.16</v>
-      </c>
-      <c r="Z111">
-        <v>4.15</v>
-      </c>
-      <c r="AA111">
-        <v>1.6</v>
-      </c>
-      <c r="AB111">
-        <v>2.15</v>
-      </c>
-      <c r="AC111">
-        <v>2.47</v>
-      </c>
-      <c r="AD111">
-        <v>1.44</v>
-      </c>
-      <c r="AE111">
-        <v>1.15</v>
-      </c>
-      <c r="AF111">
-        <v>1.76</v>
-      </c>
-      <c r="AG111">
-        <v>1.95</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.2</v>
-      </c>
       <c r="AK111">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="O113">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P113">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q113">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
         <v>3.4</v>
@@ -1667,10 +1667,10 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="Q24">
         <v>2.88</v>
@@ -4248,7 +4248,7 @@
         <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.03</v>
@@ -4260,7 +4260,7 @@
         <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
         <v>1.65</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="O26">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="P26">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="Q29">
         <v>2.85</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="Q30">
         <v>2.87</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S30">
         <v>1.43</v>
@@ -5235,7 +5235,7 @@
         <v>1.35</v>
       </c>
       <c r="Z30">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA30">
         <v>2.18</v>
@@ -5253,7 +5253,7 @@
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG30">
         <v>1.78</v>
@@ -5272,7 +5272,7 @@
         <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.8</v>
+        <v>4.74</v>
       </c>
       <c r="O39">
         <v>4.1</v>
       </c>
       <c r="P39">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q39">
         <v>5.25</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AK39">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="O49">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P49">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="Q49">
         <v>3.12</v>
@@ -8314,7 +8314,7 @@
         <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="U49">
         <v>3</v>
@@ -8326,7 +8326,7 @@
         <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
         <v>1.35</v>
@@ -8347,7 +8347,7 @@
         <v>1.16</v>
       </c>
       <c r="AE49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
         <v>1.87</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>12.5</v>
+        <v>10.63</v>
       </c>
       <c r="O53">
         <v>6.9</v>
@@ -8957,55 +8957,55 @@
         <v>1.2</v>
       </c>
       <c r="Q53">
-        <v>10.5</v>
+        <v>9.65</v>
       </c>
       <c r="R53">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="S53">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
         <v>4</v>
       </c>
       <c r="U53">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="V53">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W53">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA53">
         <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AC53">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AD53">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AE53">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG53">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -14007,7 +14007,7 @@
         <v>3.34</v>
       </c>
       <c r="P84">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="O102">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="P102">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="Q102">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R102">
         <v>2.4</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T102">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U102">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="V102">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA102">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AB102">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC102">
-        <v>2.92</v>
+        <v>2.43</v>
       </c>
       <c r="AD102">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE102">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF102">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK102">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P109">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q109">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="R109">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U109">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA109">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O110">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P110">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q110">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="S110">
+        <v>1.13</v>
+      </c>
+      <c r="T110">
+        <v>4.9</v>
+      </c>
+      <c r="U110">
+        <v>1.79</v>
+      </c>
+      <c r="V110">
+        <v>1.98</v>
+      </c>
+      <c r="W110">
+        <v>1.29</v>
+      </c>
+      <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.02</v>
+      </c>
+      <c r="Z110">
+        <v>8</v>
+      </c>
+      <c r="AA110">
         <v>1.25</v>
       </c>
-      <c r="T110">
-        <v>3.4</v>
-      </c>
-      <c r="U110">
-        <v>2.23</v>
-      </c>
-      <c r="V110">
-        <v>1.53</v>
-      </c>
-      <c r="W110">
-        <v>1.14</v>
-      </c>
-      <c r="X110">
+      <c r="AB110">
+        <v>3.76</v>
+      </c>
+      <c r="AC110">
+        <v>1.65</v>
+      </c>
+      <c r="AD110">
+        <v>2.18</v>
+      </c>
+      <c r="AE110">
+        <v>1.47</v>
+      </c>
+      <c r="AF110">
+        <v>1.77</v>
+      </c>
+      <c r="AG110">
+        <v>1.92</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
         <v>1.02</v>
       </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
-      <c r="Z110">
-        <v>4.15</v>
-      </c>
-      <c r="AA110">
-        <v>1.6</v>
-      </c>
-      <c r="AB110">
-        <v>2.15</v>
-      </c>
-      <c r="AC110">
-        <v>2.47</v>
-      </c>
-      <c r="AD110">
-        <v>1.44</v>
-      </c>
-      <c r="AE110">
-        <v>1.15</v>
-      </c>
-      <c r="AF110">
-        <v>1.76</v>
-      </c>
-      <c r="AG110">
-        <v>1.95</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.2</v>
-      </c>
       <c r="AK110">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>3.35</v>
       </c>
       <c r="P111">
-        <v>9.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="Q111">
+        <v>2.75</v>
+      </c>
+      <c r="R111">
+        <v>2.2</v>
+      </c>
+      <c r="S111">
+        <v>1.3</v>
+      </c>
+      <c r="T111">
+        <v>2.85</v>
+      </c>
+      <c r="U111">
+        <v>2.54</v>
+      </c>
+      <c r="V111">
         <v>1.41</v>
       </c>
-      <c r="R111">
-        <v>3.36</v>
-      </c>
-      <c r="S111">
-        <v>1.13</v>
-      </c>
-      <c r="T111">
-        <v>4.9</v>
-      </c>
-      <c r="U111">
-        <v>1.79</v>
-      </c>
-      <c r="V111">
-        <v>1.98</v>
-      </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>3.68</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="O119">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P119">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q119">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R119">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S119">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T119">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U119">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="V119">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W119">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X119">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y119">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Z119">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AA119">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AB119">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC119">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD119">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE119">
         <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG119">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.36</v>
       </c>
       <c r="AK119">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
         <v>3.35</v>
       </c>
       <c r="P2">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -686,13 +686,13 @@
         <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         <v>1.98</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q3">
         <v>2.55</v>
@@ -834,7 +834,7 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="AA3">
         <v>1.66</v>
@@ -843,7 +843,7 @@
         <v>2.08</v>
       </c>
       <c r="AC3">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AD3">
         <v>1.45</v>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
         <v>2.9</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q4">
         <v>2.7</v>
@@ -1000,10 +1000,10 @@
         <v>2.7</v>
       </c>
       <c r="AA4">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AB4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC4">
         <v>4.5</v>
@@ -1015,7 +1015,7 @@
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
@@ -1145,7 +1145,7 @@
         <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V5">
         <v>1.36</v>
@@ -1154,7 +1154,7 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.36</v>
@@ -1175,13 +1175,13 @@
         <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
         <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="AD6">
         <v>1.28</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
         <v>3.17</v>
@@ -1474,7 +1474,7 @@
         <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1495,7 +1495,7 @@
         <v>1.96</v>
       </c>
       <c r="AC7">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD7">
         <v>1.34</v>
@@ -1779,7 +1779,7 @@
         <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
         <v>3.55</v>
@@ -1812,7 +1812,7 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.98</v>
+        <v>5.04</v>
       </c>
       <c r="AA9">
         <v>1.61</v>
@@ -1821,13 +1821,13 @@
         <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AD9">
         <v>1.52</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
         <v>1.5</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O10">
         <v>3.25</v>
@@ -1957,13 +1957,13 @@
         <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1975,7 +1975,7 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
         <v>2.3</v>
@@ -2304,13 +2304,13 @@
         <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB12">
         <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
         <v>1.45</v>
@@ -2319,10 +2319,10 @@
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>5.87</v>
+        <v>5.95</v>
       </c>
       <c r="AA13">
         <v>1.39</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
         <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
         <v>1.18</v>
@@ -2790,7 +2790,7 @@
         <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="AA15">
         <v>1.36</v>
@@ -2799,10 +2799,10 @@
         <v>3.1</v>
       </c>
       <c r="AC15">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD15">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE15">
         <v>1.32</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.74</v>
+        <v>2.69</v>
       </c>
       <c r="O20">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>6.34</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>7.28</v>
+        <v>1.74</v>
       </c>
       <c r="O22">
-        <v>4.33</v>
+        <v>3.48</v>
       </c>
       <c r="P22">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="O31">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="P31">
         <v>1.43</v>
       </c>
       <c r="Q31">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
         <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U31">
         <v>2.08</v>
@@ -5407,7 +5407,7 @@
         <v>2.41</v>
       </c>
       <c r="AC31">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD31">
         <v>1.58</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
         <v>3.36</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q34">
         <v>3.27</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6222,7 +6222,7 @@
         <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AD36">
         <v>1.32</v>
@@ -6358,10 +6358,10 @@
         <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="U37">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="V37">
         <v>1.36</v>
@@ -6379,7 +6379,7 @@
         <v>3.14</v>
       </c>
       <c r="AA37">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB37">
         <v>1.75</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O40">
         <v>4.8</v>
       </c>
       <c r="P40">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q40">
         <v>5</v>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R42">
         <v>2.5</v>
@@ -7176,10 +7176,10 @@
         <v>3.9</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V42">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W42">
         <v>1.18</v>
@@ -7194,19 +7194,19 @@
         <v>5.1</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AC42">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD42">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
         <v>1.4</v>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="O43">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P43">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7674,7 +7674,7 @@
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y45">
         <v>1.36</v>
@@ -8027,7 +8027,7 @@
         <v>1.54</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
         <v>2.25</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -8474,43 +8474,43 @@
         <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AA50">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB50">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
         <v>1.55</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O51">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -8643,10 +8643,10 @@
         <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.11</v>
@@ -8655,10 +8655,10 @@
         <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA51">
         <v>1.8</v>
@@ -8667,19 +8667,19 @@
         <v>2</v>
       </c>
       <c r="AC51">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
         <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O52">
         <v>3.7</v>
       </c>
       <c r="P52">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q52">
         <v>2.15</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S52">
         <v>1.3</v>
@@ -8812,31 +8812,31 @@
         <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
         <v>1.73</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
         <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
         <v>1.67</v>
@@ -8858,7 +8858,7 @@
         <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="O54">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="P54">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q54">
         <v>3.16</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O55">
         <v>3.6</v>
@@ -9639,10 +9639,10 @@
         <v>5.05</v>
       </c>
       <c r="AA57">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
         <v>2.22</v>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O58">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="P58">
         <v>3.6</v>
@@ -9784,16 +9784,16 @@
         <v>3.45</v>
       </c>
       <c r="U58">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
         <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.18</v>
@@ -9808,7 +9808,7 @@
         <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD58">
         <v>1.51</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10273,10 +10273,10 @@
         <v>3.9</v>
       </c>
       <c r="U61">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W61">
         <v>1.15</v>
@@ -10418,10 +10418,10 @@
         <v>1.42</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>8.02</v>
+        <v>7</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10581,58 +10581,58 @@
         <v>1.85</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q63">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="R63">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="V63">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
         <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB63">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC63">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="AD63">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
         <v>1.8</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O65">
         <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q65">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R65">
         <v>2.45</v>
@@ -10946,7 +10946,7 @@
         <v>1.4</v>
       </c>
       <c r="AB65">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AC65">
         <v>2.09</v>
@@ -10977,7 +10977,7 @@
         <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
         <v>3.8</v>
       </c>
       <c r="P66">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q66">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="R66">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="S66">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
         <v>3.6</v>
@@ -11100,10 +11100,10 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="AA66">
         <v>1.6</v>
@@ -11112,10 +11112,10 @@
         <v>2.38</v>
       </c>
       <c r="AC66">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD66">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE66">
         <v>1.17</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>3.1</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
         <v>2.1</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O69">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P69">
         <v>4.6</v>
@@ -11577,7 +11577,7 @@
         <v>4.2</v>
       </c>
       <c r="U69">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V69">
         <v>1.76</v>
@@ -11589,22 +11589,22 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.34</v>
+        <v>6.1</v>
       </c>
       <c r="AA69">
         <v>1.4</v>
       </c>
       <c r="AB69">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD69">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE69">
         <v>1.33</v>
@@ -11613,7 +11613,7 @@
         <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.17</v>
       </c>
       <c r="AK69">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>3.4</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P71">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q71">
         <v>3.9</v>
@@ -11906,7 +11906,7 @@
         <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W71">
         <v>1.18</v>
@@ -11918,7 +11918,7 @@
         <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.82</v>
+        <v>5.76</v>
       </c>
       <c r="AA71">
         <v>1.36</v>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="O72">
         <v>3.6</v>
       </c>
       <c r="P72">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="Q72">
         <v>2.52</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="O73">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q73">
         <v>3.45</v>
@@ -12226,16 +12226,16 @@
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
         <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
         <v>1.02</v>
@@ -12247,10 +12247,10 @@
         <v>5.1</v>
       </c>
       <c r="AA73">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB73">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC73">
         <v>2.1</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK73">
         <v>1.36</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O74">
         <v>3.3</v>
       </c>
       <c r="P74">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q74">
         <v>4</v>
@@ -12386,7 +12386,7 @@
         <v>2</v>
       </c>
       <c r="S74">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T74">
         <v>2.6</v>
@@ -12404,31 +12404,31 @@
         <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AA74">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB74">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC74">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="AD74">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE74">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF74">
         <v>1.95</v>
       </c>
       <c r="AG74">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK74">
         <v>1.3</v>
@@ -12579,7 +12579,7 @@
         <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD75">
         <v>1.76</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK75">
         <v>2.8</v>
@@ -12700,7 +12700,7 @@
         <v>1.63</v>
       </c>
       <c r="O76">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
         <v>5.25</v>
@@ -12718,7 +12718,7 @@
         <v>2.88</v>
       </c>
       <c r="U76">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V76">
         <v>1.36</v>
@@ -12914,10 +12914,10 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
         <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="S78">
         <v>1.48</v>
@@ -13065,7 +13065,7 @@
         <v>2.29</v>
       </c>
       <c r="AB78">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC78">
         <v>4.36</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O81">
         <v>3</v>
@@ -13539,7 +13539,7 @@
         <v>1.27</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK81">
         <v>1.5</v>
@@ -13705,10 +13705,10 @@
         <v>1.12</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
         <v>5.02</v>
@@ -13868,7 +13868,7 @@
         <v>1.17</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
         <v>1.14</v>
@@ -14197,16 +14197,16 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z85">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AA85">
         <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AC85">
         <v>1.36</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O87">
         <v>4.33</v>
       </c>
       <c r="P87">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -14523,10 +14523,10 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z87">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="AA87">
         <v>1.17</v>
@@ -14710,7 +14710,7 @@
         <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="O89">
         <v>3.42</v>
@@ -14873,7 +14873,7 @@
         <v>1.55</v>
       </c>
       <c r="AG89">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14982,10 +14982,10 @@
         <v>1.35</v>
       </c>
       <c r="O90">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="P90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q90">
         <v>1.73</v>
@@ -15311,7 +15311,7 @@
         <v>3.7</v>
       </c>
       <c r="P92">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -15471,7 +15471,7 @@
         <v>1.6</v>
       </c>
       <c r="O93">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="P93">
         <v>4.2</v>
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O94">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P94">
         <v>2.1</v>
@@ -15794,10 +15794,10 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O95">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
         <v>2.13</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O96">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P96">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q96">
-        <v>5.59</v>
+        <v>5.4</v>
       </c>
       <c r="R96">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="S96">
         <v>1.18</v>
       </c>
       <c r="T96">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U96">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V96">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W96">
         <v>1.15</v>
@@ -15996,25 +15996,25 @@
         <v>6</v>
       </c>
       <c r="AA96">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB96">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC96">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD96">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE96">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG96">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK96">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
         <v>3.45</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P99">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -17101,16 +17101,16 @@
         <v>1.36</v>
       </c>
       <c r="O103">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="P103">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="Q103">
         <v>1.75</v>
       </c>
       <c r="R103">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="S103">
         <v>1.2</v>
@@ -17152,7 +17152,7 @@
         <v>1.35</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG103">
         <v>2.26</v>
@@ -17478,7 +17478,7 @@
         <v>1.22</v>
       </c>
       <c r="AF105">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG105">
         <v>2.7</v>
@@ -17596,7 +17596,7 @@
         <v>6.5</v>
       </c>
       <c r="Q106">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R106">
         <v>2.5</v>
@@ -17611,7 +17611,7 @@
         <v>2.4</v>
       </c>
       <c r="V106">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W106">
         <v>1.12</v>
@@ -17620,10 +17620,10 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z106">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA106">
         <v>1.66</v>
@@ -17635,7 +17635,7 @@
         <v>2.52</v>
       </c>
       <c r="AD106">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE106">
         <v>1.13</v>
@@ -17660,7 +17660,7 @@
         <v>1.17</v>
       </c>
       <c r="AK106">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17756,7 +17756,7 @@
         <v>4.05</v>
       </c>
       <c r="P107">
-        <v>4.3</v>
+        <v>4.87</v>
       </c>
       <c r="Q107">
         <v>2.05</v>
@@ -17780,7 +17780,7 @@
         <v>1.12</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
         <v>1.09</v>
@@ -17807,7 +17807,7 @@
         <v>1.5</v>
       </c>
       <c r="AG107">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>1.57</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF108">
         <v>1.57</v>
@@ -18121,13 +18121,13 @@
         <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="AD109">
         <v>1.44</v>
       </c>
       <c r="AE109">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
         <v>1.76</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
+        <v>2.09</v>
+      </c>
+      <c r="O110">
+        <v>3.35</v>
+      </c>
+      <c r="P110">
+        <v>2.9</v>
+      </c>
+      <c r="Q110">
+        <v>2.75</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>1.3</v>
+      </c>
+      <c r="T110">
+        <v>2.85</v>
+      </c>
+      <c r="U110">
+        <v>2.54</v>
+      </c>
+      <c r="V110">
+        <v>1.41</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.03</v>
+      </c>
+      <c r="Y110">
+        <v>1.2</v>
+      </c>
+      <c r="Z110">
+        <v>3.68</v>
+      </c>
+      <c r="AA110">
+        <v>1.75</v>
+      </c>
+      <c r="AB110">
+        <v>1.94</v>
+      </c>
+      <c r="AC110">
+        <v>2.78</v>
+      </c>
+      <c r="AD110">
+        <v>1.39</v>
+      </c>
+      <c r="AE110">
         <v>1.13</v>
       </c>
-      <c r="O110">
-        <v>7.7</v>
-      </c>
-      <c r="P110">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q110">
-        <v>1.41</v>
-      </c>
-      <c r="R110">
-        <v>3.36</v>
-      </c>
-      <c r="S110">
-        <v>1.13</v>
-      </c>
-      <c r="T110">
-        <v>4.9</v>
-      </c>
-      <c r="U110">
-        <v>1.79</v>
-      </c>
-      <c r="V110">
-        <v>1.98</v>
-      </c>
-      <c r="W110">
-        <v>1.29</v>
-      </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
-      <c r="Y110">
-        <v>1.02</v>
-      </c>
-      <c r="Z110">
-        <v>8</v>
-      </c>
-      <c r="AA110">
-        <v>1.25</v>
-      </c>
-      <c r="AB110">
-        <v>3.76</v>
-      </c>
-      <c r="AC110">
-        <v>1.65</v>
-      </c>
-      <c r="AD110">
-        <v>2.18</v>
-      </c>
-      <c r="AE110">
-        <v>1.47</v>
-      </c>
       <c r="AF110">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG110">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.09</v>
+        <v>1.13</v>
       </c>
       <c r="O111">
-        <v>3.35</v>
+        <v>7.7</v>
       </c>
       <c r="P111">
-        <v>2.9</v>
+        <v>10.85</v>
       </c>
       <c r="Q111">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>3.36</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="T111">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="U111">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="Z111">
-        <v>3.68</v>
+        <v>8</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB111">
-        <v>1.94</v>
+        <v>3.76</v>
       </c>
       <c r="AC111">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="AE111">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF111">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG111">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AK111">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="O113">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="P113">
-        <v>13</v>
+        <v>10.58</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O114">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>4.2</v>
+        <v>3.87</v>
       </c>
       <c r="Q114">
         <v>2.18</v>
@@ -19057,7 +19057,7 @@
         <v>2.7</v>
       </c>
       <c r="O115">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
         <v>2.65</v>
@@ -19087,13 +19087,13 @@
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z115">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AA115">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AB115">
         <v>1.84</v>
@@ -19111,7 +19111,7 @@
         <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>4.6</v>
       </c>
       <c r="P116">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q116">
         <v>1.95</v>
@@ -19235,13 +19235,13 @@
         <v>1.25</v>
       </c>
       <c r="T116">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U116">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V116">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W116">
         <v>1.11</v>
@@ -19271,7 +19271,7 @@
         <v>1.22</v>
       </c>
       <c r="AF116">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG116">
         <v>2.25</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O117">
         <v>3.4</v>
       </c>
       <c r="P117">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q117">
         <v>3.68</v>
@@ -19395,43 +19395,43 @@
         <v>2.12</v>
       </c>
       <c r="S117">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T117">
         <v>2.88</v>
       </c>
       <c r="U117">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V117">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W117">
         <v>1.04</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z117">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA117">
         <v>1.9</v>
       </c>
       <c r="AB117">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC117">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD117">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE117">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
         <v>1.75</v>
@@ -20035,7 +20035,7 @@
         <v>1.7</v>
       </c>
       <c r="O121">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
         <v>3.95</v>
@@ -20071,10 +20071,10 @@
         <v>3.7</v>
       </c>
       <c r="AA121">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB121">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC121">
         <v>2.81</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="O61">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q61">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V61">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z61">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB61">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AC61">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD61">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE61">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF61">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG61">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK61">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-09 13:45:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P62">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,65 +13023,65 @@
         </is>
       </c>
       <c r="N78">
+        <v>2.1</v>
+      </c>
+      <c r="O78">
+        <v>3.4</v>
+      </c>
+      <c r="P78">
+        <v>3.15</v>
+      </c>
+      <c r="Q78">
+        <v>2.48</v>
+      </c>
+      <c r="R78">
         <v>2.2</v>
       </c>
-      <c r="O78">
-        <v>3.2</v>
-      </c>
-      <c r="P78">
-        <v>3.1</v>
-      </c>
-      <c r="Q78">
-        <v>2.8</v>
-      </c>
-      <c r="R78">
-        <v>1.96</v>
-      </c>
       <c r="S78">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U78">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V78">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="AB78">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC78">
-        <v>4.36</v>
+        <v>3.28</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AF78">
+        <v>1.74</v>
+      </c>
+      <c r="AG78">
         <v>1.95</v>
       </c>
-      <c r="AG78">
-        <v>1.75</v>
-      </c>
       <c r="AH78" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,77 +13186,77 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
+        <v>3.1</v>
+      </c>
+      <c r="Q79">
         <v>2.8</v>
       </c>
-      <c r="Q79">
-        <v>2.7</v>
-      </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S79">
+        <v>1.48</v>
+      </c>
+      <c r="T79">
+        <v>2.41</v>
+      </c>
+      <c r="U79">
+        <v>3</v>
+      </c>
+      <c r="V79">
+        <v>1.29</v>
+      </c>
+      <c r="W79">
+        <v>1.06</v>
+      </c>
+      <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
+        <v>1.4</v>
+      </c>
+      <c r="Z79">
+        <v>2.75</v>
+      </c>
+      <c r="AA79">
+        <v>2.29</v>
+      </c>
+      <c r="AB79">
+        <v>1.57</v>
+      </c>
+      <c r="AC79">
+        <v>4.36</v>
+      </c>
+      <c r="AD79">
+        <v>1.15</v>
+      </c>
+      <c r="AE79">
+        <v>1</v>
+      </c>
+      <c r="AF79">
+        <v>1.95</v>
+      </c>
+      <c r="AG79">
+        <v>1.75</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.33</v>
-      </c>
-      <c r="T79">
-        <v>3.2</v>
-      </c>
-      <c r="U79">
-        <v>2.57</v>
-      </c>
-      <c r="V79">
-        <v>1.43</v>
-      </c>
-      <c r="W79">
-        <v>1.07</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
-        <v>1.21</v>
-      </c>
-      <c r="Z79">
-        <v>3.58</v>
-      </c>
-      <c r="AA79">
-        <v>1.8</v>
-      </c>
-      <c r="AB79">
-        <v>2</v>
-      </c>
-      <c r="AC79">
-        <v>2.83</v>
-      </c>
-      <c r="AD79">
-        <v>1.33</v>
-      </c>
-      <c r="AE79">
-        <v>1.11</v>
-      </c>
-      <c r="AF79">
-        <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.13</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.26</v>
       </c>
       <c r="AK79">
         <v>1.62</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q80">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
         <v>1.33</v>
       </c>
       <c r="T80">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U80">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC80">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O109">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P109">
-        <v>5.4</v>
+        <v>10.85</v>
       </c>
       <c r="Q109">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="S109">
+        <v>1.13</v>
+      </c>
+      <c r="T109">
+        <v>4.9</v>
+      </c>
+      <c r="U109">
+        <v>1.79</v>
+      </c>
+      <c r="V109">
+        <v>1.98</v>
+      </c>
+      <c r="W109">
+        <v>1.29</v>
+      </c>
+      <c r="X109">
+        <v>1.01</v>
+      </c>
+      <c r="Y109">
+        <v>1.02</v>
+      </c>
+      <c r="Z109">
+        <v>8</v>
+      </c>
+      <c r="AA109">
         <v>1.25</v>
       </c>
-      <c r="T109">
-        <v>3.4</v>
-      </c>
-      <c r="U109">
-        <v>2.23</v>
-      </c>
-      <c r="V109">
-        <v>1.53</v>
-      </c>
-      <c r="W109">
-        <v>1.14</v>
-      </c>
-      <c r="X109">
+      <c r="AB109">
+        <v>3.76</v>
+      </c>
+      <c r="AC109">
+        <v>1.65</v>
+      </c>
+      <c r="AD109">
+        <v>2.18</v>
+      </c>
+      <c r="AE109">
+        <v>1.47</v>
+      </c>
+      <c r="AF109">
+        <v>1.77</v>
+      </c>
+      <c r="AG109">
+        <v>1.92</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.02</v>
       </c>
-      <c r="Y109">
-        <v>1.16</v>
-      </c>
-      <c r="Z109">
-        <v>4.15</v>
-      </c>
-      <c r="AA109">
-        <v>1.6</v>
-      </c>
-      <c r="AB109">
-        <v>2.15</v>
-      </c>
-      <c r="AC109">
-        <v>2.51</v>
-      </c>
-      <c r="AD109">
-        <v>1.44</v>
-      </c>
-      <c r="AE109">
-        <v>1.2</v>
-      </c>
-      <c r="AF109">
-        <v>1.76</v>
-      </c>
-      <c r="AG109">
-        <v>1.95</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.2</v>
-      </c>
       <c r="AK109">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>10.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q111">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="R111">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="V111">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>4.15</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>2.52</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,58 +12697,58 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="O76">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S76">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T76">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U76">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z76">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AA76">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AB76">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC76">
-        <v>3.34</v>
+        <v>4.36</v>
       </c>
       <c r="AD76">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF76">
         <v>1.95</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q77">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T77">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="V77">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12893,31 +12893,31 @@
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA77">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AC77">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD77">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R78">
         <v>2.2</v>
       </c>
       <c r="S78">
+        <v>1.3</v>
+      </c>
+      <c r="T78">
+        <v>3.1</v>
+      </c>
+      <c r="U78">
+        <v>2.6</v>
+      </c>
+      <c r="V78">
+        <v>1.44</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.21</v>
+      </c>
+      <c r="Z78">
+        <v>3.8</v>
+      </c>
+      <c r="AA78">
+        <v>1.81</v>
+      </c>
+      <c r="AB78">
+        <v>2.01</v>
+      </c>
+      <c r="AC78">
+        <v>3.1</v>
+      </c>
+      <c r="AD78">
         <v>1.33</v>
       </c>
-      <c r="T78">
-        <v>2.7</v>
-      </c>
-      <c r="U78">
-        <v>2.88</v>
-      </c>
-      <c r="V78">
-        <v>1.36</v>
-      </c>
-      <c r="W78">
-        <v>1.06</v>
-      </c>
-      <c r="X78">
-        <v>1.01</v>
-      </c>
-      <c r="Y78">
-        <v>1.25</v>
-      </c>
-      <c r="Z78">
-        <v>3.28</v>
-      </c>
-      <c r="AA78">
-        <v>1.92</v>
-      </c>
-      <c r="AB78">
-        <v>1.9</v>
-      </c>
-      <c r="AC78">
-        <v>3.28</v>
-      </c>
-      <c r="AD78">
-        <v>1.25</v>
-      </c>
       <c r="AE78">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,65 +13186,65 @@
         </is>
       </c>
       <c r="N79">
+        <v>2.1</v>
+      </c>
+      <c r="O79">
+        <v>3.4</v>
+      </c>
+      <c r="P79">
+        <v>3.15</v>
+      </c>
+      <c r="Q79">
+        <v>2.48</v>
+      </c>
+      <c r="R79">
         <v>2.2</v>
       </c>
-      <c r="O79">
-        <v>3.2</v>
-      </c>
-      <c r="P79">
-        <v>3.1</v>
-      </c>
-      <c r="Q79">
-        <v>2.8</v>
-      </c>
-      <c r="R79">
-        <v>1.96</v>
-      </c>
       <c r="S79">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V79">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA79">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="AB79">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC79">
-        <v>4.36</v>
+        <v>3.28</v>
       </c>
       <c r="AD79">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AF79">
+        <v>1.74</v>
+      </c>
+      <c r="AG79">
         <v>1.95</v>
       </c>
-      <c r="AG79">
-        <v>1.75</v>
-      </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL79">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1643,7 +1643,7 @@
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>1.22</v>
@@ -1652,7 +1652,7 @@
         <v>4.2</v>
       </c>
       <c r="AA8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
         <v>2.05</v>
@@ -1667,10 +1667,10 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P11">
-        <v>5.8</v>
+        <v>6.13</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="O14">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P17">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>6.34</v>
+        <v>1.74</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="P21">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="Q21">
-        <v>6.79</v>
+        <v>2.31</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V21">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA21">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG21">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.74</v>
+        <v>6.34</v>
       </c>
       <c r="O22">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="P22">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="Q22">
-        <v>2.31</v>
+        <v>6.79</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD22">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P26">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>8.68</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O28">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="P28">
-        <v>9.35</v>
+        <v>8.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>5.25</v>
       </c>
       <c r="O31">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P31">
         <v>1.43</v>
@@ -5377,7 +5377,7 @@
         <v>2.45</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
         <v>4</v>
@@ -5389,13 +5389,13 @@
         <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
         <v>5.1</v>
@@ -5407,7 +5407,7 @@
         <v>2.41</v>
       </c>
       <c r="AC31">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD31">
         <v>1.58</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.18</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P35">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q36">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="U36">
-        <v>2.72</v>
+        <v>3.02</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
+        <v>1.27</v>
+      </c>
+      <c r="Z36">
+        <v>3.14</v>
+      </c>
+      <c r="AA36">
+        <v>2.04</v>
+      </c>
+      <c r="AB36">
+        <v>1.75</v>
+      </c>
+      <c r="AC36">
+        <v>3.34</v>
+      </c>
+      <c r="AD36">
         <v>1.24</v>
-      </c>
-      <c r="Z36">
-        <v>3.34</v>
-      </c>
-      <c r="AA36">
-        <v>1.87</v>
-      </c>
-      <c r="AB36">
-        <v>1.8</v>
-      </c>
-      <c r="AC36">
-        <v>3.24</v>
-      </c>
-      <c r="AD36">
-        <v>1.32</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="R37">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>3.02</v>
+        <v>2.72</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA37">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE37">
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="O39">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P39">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q39">
         <v>5.25</v>
@@ -6711,7 +6711,7 @@
         <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD39">
         <v>1.66</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK39">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6865,19 +6865,19 @@
         <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>6.04</v>
+        <v>6.12</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AC40">
         <v>1.96</v>
       </c>
       <c r="AD40">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE40">
         <v>1.28</v>
@@ -6902,7 +6902,7 @@
         <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q42">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S42">
         <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V42">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W42">
         <v>1.18</v>
@@ -7191,10 +7191,10 @@
         <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA42">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB42">
         <v>2.49</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
         <v>1.55</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.23</v>
+        <v>2.08</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD50">
         <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
         <v>3.1</v>
@@ -8652,50 +8652,50 @@
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
+        <v>1.18</v>
+      </c>
+      <c r="Z51">
+        <v>3.86</v>
+      </c>
+      <c r="AA51">
+        <v>1.75</v>
+      </c>
+      <c r="AB51">
+        <v>1.97</v>
+      </c>
+      <c r="AC51">
+        <v>2.69</v>
+      </c>
+      <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.11</v>
+      </c>
+      <c r="AF51">
+        <v>1.75</v>
+      </c>
+      <c r="AG51">
+        <v>2</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.2</v>
       </c>
-      <c r="Z51">
-        <v>3.68</v>
-      </c>
-      <c r="AA51">
-        <v>1.8</v>
-      </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>2.88</v>
-      </c>
-      <c r="AD51">
-        <v>1.32</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.62</v>
-      </c>
-      <c r="AG51">
-        <v>2.13</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.3</v>
-      </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>4.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q52">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
         <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
         <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA52">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB52">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,61 +8948,61 @@
         </is>
       </c>
       <c r="N53">
-        <v>10.63</v>
+        <v>8.5</v>
       </c>
       <c r="O53">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="P53">
         <v>1.2</v>
       </c>
       <c r="Q53">
-        <v>9.65</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R53">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="S53">
         <v>1.25</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U53">
         <v>2.15</v>
       </c>
       <c r="V53">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z53">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA53">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB53">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AC53">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD53">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF53">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG53">
         <v>1.67</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AK53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P59">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10255,61 +10255,61 @@
         <v>1.42</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>7</v>
+        <v>6.77</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O69">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P69">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q69">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R69">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="S69">
         <v>1.16</v>
@@ -11577,7 +11577,7 @@
         <v>4.2</v>
       </c>
       <c r="U69">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V69">
         <v>1.76</v>
@@ -11592,7 +11592,7 @@
         <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA69">
         <v>1.4</v>
@@ -11601,10 +11601,10 @@
         <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AD69">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE69">
         <v>1.33</v>
@@ -11613,7 +11613,7 @@
         <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O70">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P70">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,22 +11882,22 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O71">
         <v>3.75</v>
       </c>
       <c r="P71">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q71">
-        <v>3.9</v>
+        <v>3.49</v>
       </c>
       <c r="R71">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T71">
         <v>4.1</v>
@@ -11906,10 +11906,10 @@
         <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W71">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11918,7 +11918,7 @@
         <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
       <c r="AA71">
         <v>1.36</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK71">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="O72">
         <v>3.6</v>
@@ -12054,7 +12054,7 @@
         <v>2.87</v>
       </c>
       <c r="Q72">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="R72">
         <v>2.42</v>
@@ -12066,13 +12066,13 @@
         <v>4.5</v>
       </c>
       <c r="U72">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V72">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12090,19 +12090,19 @@
         <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD72">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE72">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG72">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="O73">
         <v>3.55</v>
@@ -12220,28 +12220,28 @@
         <v>3.45</v>
       </c>
       <c r="R73">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="S73">
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U73">
         <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
         <v>5.1</v>
@@ -12259,13 +12259,13 @@
         <v>1.67</v>
       </c>
       <c r="AE73">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF73">
         <v>1.41</v>
       </c>
       <c r="AG73">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="AK73">
         <v>1.36</v>
@@ -12576,10 +12576,10 @@
         <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AD75">
         <v>1.76</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK75">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,58 +12697,58 @@
         </is>
       </c>
       <c r="N76">
+        <v>1.63</v>
+      </c>
+      <c r="O76">
+        <v>3.7</v>
+      </c>
+      <c r="P76">
+        <v>5.25</v>
+      </c>
+      <c r="Q76">
         <v>2.2</v>
       </c>
-      <c r="O76">
-        <v>3.2</v>
-      </c>
-      <c r="P76">
-        <v>3.1</v>
-      </c>
-      <c r="Q76">
-        <v>2.8</v>
-      </c>
       <c r="R76">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T76">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="V76">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z76">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA76">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="AB76">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AC76">
-        <v>4.36</v>
+        <v>3.34</v>
       </c>
       <c r="AD76">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
         <v>1.95</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q77">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD77">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK77">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,77 +13349,77 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
+        <v>3.1</v>
+      </c>
+      <c r="Q80">
         <v>2.8</v>
       </c>
-      <c r="Q80">
-        <v>2.7</v>
-      </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="S80">
+        <v>1.48</v>
+      </c>
+      <c r="T80">
+        <v>2.41</v>
+      </c>
+      <c r="U80">
+        <v>3</v>
+      </c>
+      <c r="V80">
+        <v>1.29</v>
+      </c>
+      <c r="W80">
+        <v>1.06</v>
+      </c>
+      <c r="X80">
+        <v>1.02</v>
+      </c>
+      <c r="Y80">
+        <v>1.4</v>
+      </c>
+      <c r="Z80">
+        <v>2.75</v>
+      </c>
+      <c r="AA80">
+        <v>2.29</v>
+      </c>
+      <c r="AB80">
+        <v>1.57</v>
+      </c>
+      <c r="AC80">
+        <v>4.36</v>
+      </c>
+      <c r="AD80">
+        <v>1.15</v>
+      </c>
+      <c r="AE80">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <v>1.95</v>
+      </c>
+      <c r="AG80">
+        <v>1.75</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.33</v>
-      </c>
-      <c r="T80">
-        <v>3.2</v>
-      </c>
-      <c r="U80">
-        <v>2.57</v>
-      </c>
-      <c r="V80">
-        <v>1.43</v>
-      </c>
-      <c r="W80">
-        <v>1.07</v>
-      </c>
-      <c r="X80">
-        <v>1</v>
-      </c>
-      <c r="Y80">
-        <v>1.21</v>
-      </c>
-      <c r="Z80">
-        <v>3.58</v>
-      </c>
-      <c r="AA80">
-        <v>1.8</v>
-      </c>
-      <c r="AB80">
-        <v>2</v>
-      </c>
-      <c r="AC80">
-        <v>2.83</v>
-      </c>
-      <c r="AD80">
-        <v>1.33</v>
-      </c>
-      <c r="AE80">
-        <v>1.11</v>
-      </c>
-      <c r="AF80">
-        <v>1.62</v>
-      </c>
-      <c r="AG80">
-        <v>2.13</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.26</v>
       </c>
       <c r="AK80">
         <v>1.62</v>
@@ -14185,7 +14185,7 @@
         <v>6</v>
       </c>
       <c r="U85">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V85">
         <v>2.4</v>
@@ -14197,28 +14197,28 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z85">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA85">
         <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC85">
         <v>1.36</v>
       </c>
       <c r="AD85">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE85">
         <v>1.83</v>
       </c>
       <c r="AF85">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG85">
         <v>3</v>
@@ -14237,7 +14237,7 @@
         <v>1.1</v>
       </c>
       <c r="AK85">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14333,7 +14333,7 @@
         <v>5.3</v>
       </c>
       <c r="P86">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q86">
         <v>1.67</v>
@@ -14348,7 +14348,7 @@
         <v>4.6</v>
       </c>
       <c r="U86">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="V86">
         <v>1.85</v>
@@ -14372,13 +14372,13 @@
         <v>3.25</v>
       </c>
       <c r="AC86">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AD86">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AE86">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF86">
         <v>1.44</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK86">
         <v>3.1</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK87">
         <v>1.85</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O88">
         <v>3.8</v>
@@ -14662,16 +14662,16 @@
         <v>4</v>
       </c>
       <c r="Q88">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S88">
         <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="U88">
         <v>2.11</v>
@@ -14698,7 +14698,7 @@
         <v>2.88</v>
       </c>
       <c r="AC88">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD88">
         <v>1.67</v>
@@ -14710,7 +14710,7 @@
         <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK88">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14822,7 +14822,7 @@
         <v>3.42</v>
       </c>
       <c r="P89">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q89">
         <v>2.6</v>
@@ -14837,7 +14837,7 @@
         <v>3.25</v>
       </c>
       <c r="U89">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V89">
         <v>1.53</v>
@@ -14849,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z89">
         <v>3.98</v>
@@ -14858,16 +14858,16 @@
         <v>1.65</v>
       </c>
       <c r="AB89">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AC89">
         <v>2.49</v>
       </c>
       <c r="AD89">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
         <v>1.55</v>
@@ -14991,7 +14991,7 @@
         <v>1.73</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="S90">
         <v>1.2</v>
@@ -15015,7 +15015,7 @@
         <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>5.85</v>
+        <v>6.08</v>
       </c>
       <c r="AA90">
         <v>1.4</v>
@@ -15024,7 +15024,7 @@
         <v>3.1</v>
       </c>
       <c r="AC90">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD90">
         <v>1.76</v>
@@ -15199,7 +15199,7 @@
         <v>1.48</v>
       </c>
       <c r="AG91">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>2.12</v>
       </c>
       <c r="V92">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W92">
         <v>1.18</v>
@@ -15341,7 +15341,7 @@
         <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>5.53</v>
+        <v>5.68</v>
       </c>
       <c r="AA92">
         <v>1.39</v>
@@ -15350,10 +15350,10 @@
         <v>2.59</v>
       </c>
       <c r="AC92">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AD92">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE92">
         <v>1.24</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
         <v>1.55</v>
@@ -15471,13 +15471,13 @@
         <v>1.6</v>
       </c>
       <c r="O93">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P93">
         <v>4.2</v>
       </c>
       <c r="Q93">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R93">
         <v>2.75</v>
@@ -15489,7 +15489,7 @@
         <v>4.7</v>
       </c>
       <c r="U93">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V93">
         <v>1.9</v>
@@ -15513,10 +15513,10 @@
         <v>3.4</v>
       </c>
       <c r="AC93">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD93">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AE93">
         <v>1.4</v>
@@ -15640,22 +15640,22 @@
         <v>2.1</v>
       </c>
       <c r="Q94">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="R94">
         <v>2.51</v>
       </c>
       <c r="S94">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T94">
         <v>4.85</v>
       </c>
       <c r="U94">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V94">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W94">
         <v>1.25</v>
@@ -15679,10 +15679,10 @@
         <v>1.76</v>
       </c>
       <c r="AD94">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE94">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF94">
         <v>1.33</v>
@@ -15800,16 +15800,16 @@
         <v>3.6</v>
       </c>
       <c r="P95">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q95">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R95">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S95">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
         <v>3.9</v>
@@ -15830,16 +15830,16 @@
         <v>1.1</v>
       </c>
       <c r="Z95">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="AA95">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB95">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AC95">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AD95">
         <v>1.66</v>
@@ -15848,10 +15848,10 @@
         <v>1.24</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG95">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="O96">
         <v>4.2</v>
@@ -15966,16 +15966,16 @@
         <v>1.47</v>
       </c>
       <c r="Q96">
-        <v>5.4</v>
+        <v>4.14</v>
       </c>
       <c r="R96">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="S96">
         <v>1.18</v>
       </c>
       <c r="T96">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U96">
         <v>2.04</v>
@@ -15996,10 +15996,10 @@
         <v>6</v>
       </c>
       <c r="AA96">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC96">
         <v>2.02</v>
@@ -16008,13 +16008,13 @@
         <v>1.68</v>
       </c>
       <c r="AE96">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF96">
         <v>1.51</v>
       </c>
       <c r="AG96">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16123,16 +16123,16 @@
         <v>2.8</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q97">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="R97">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16156,7 +16156,7 @@
         <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA97">
         <v>1.53</v>
@@ -16174,7 +16174,7 @@
         <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG97">
         <v>2.5</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK97">
         <v>1.36</v>
@@ -16938,77 +16938,77 @@
         <v>1.35</v>
       </c>
       <c r="O102">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P102">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Q102">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R102">
         <v>2.4</v>
       </c>
       <c r="S102">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U102">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V102">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W102">
         <v>1.09</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y102">
         <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA102">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB102">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC102">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD102">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE102">
+        <v>1.14</v>
+      </c>
+      <c r="AF102">
+        <v>1.85</v>
+      </c>
+      <c r="AG102">
+        <v>1.79</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.13</v>
       </c>
-      <c r="AF102">
-        <v>1.82</v>
-      </c>
-      <c r="AG102">
-        <v>1.82</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.14</v>
-      </c>
       <c r="AK102">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17110,7 +17110,7 @@
         <v>1.75</v>
       </c>
       <c r="R103">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="S103">
         <v>1.2</v>
@@ -17131,25 +17131,25 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z103">
-        <v>5.85</v>
+        <v>7</v>
       </c>
       <c r="AA103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB103">
         <v>3</v>
       </c>
       <c r="AC103">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AD103">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE103">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF103">
         <v>1.75</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK103">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="O109">
-        <v>7.7</v>
+        <v>4.4</v>
       </c>
       <c r="P109">
-        <v>10.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q109">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="R109">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="U109">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="V109">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>8</v>
+        <v>4.15</v>
       </c>
       <c r="AA109">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>1.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD109">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG109">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>5.5</v>
+        <v>2.52</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="O111">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="P111">
-        <v>5.4</v>
+        <v>10.85</v>
       </c>
       <c r="Q111">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="S111">
+        <v>1.13</v>
+      </c>
+      <c r="T111">
+        <v>4.9</v>
+      </c>
+      <c r="U111">
+        <v>1.79</v>
+      </c>
+      <c r="V111">
+        <v>1.98</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.02</v>
+      </c>
+      <c r="Z111">
+        <v>8</v>
+      </c>
+      <c r="AA111">
         <v>1.25</v>
       </c>
-      <c r="T111">
-        <v>3.4</v>
-      </c>
-      <c r="U111">
-        <v>2.23</v>
-      </c>
-      <c r="V111">
-        <v>1.53</v>
-      </c>
-      <c r="W111">
-        <v>1.14</v>
-      </c>
-      <c r="X111">
+      <c r="AB111">
+        <v>3.76</v>
+      </c>
+      <c r="AC111">
+        <v>1.65</v>
+      </c>
+      <c r="AD111">
+        <v>2.18</v>
+      </c>
+      <c r="AE111">
+        <v>1.47</v>
+      </c>
+      <c r="AF111">
+        <v>1.77</v>
+      </c>
+      <c r="AG111">
+        <v>1.92</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
         <v>1.02</v>
       </c>
-      <c r="Y111">
-        <v>1.16</v>
-      </c>
-      <c r="Z111">
-        <v>4.15</v>
-      </c>
-      <c r="AA111">
-        <v>1.6</v>
-      </c>
-      <c r="AB111">
-        <v>2.15</v>
-      </c>
-      <c r="AC111">
-        <v>2.51</v>
-      </c>
-      <c r="AD111">
-        <v>1.44</v>
-      </c>
-      <c r="AE111">
-        <v>1.2</v>
-      </c>
-      <c r="AF111">
-        <v>1.76</v>
-      </c>
-      <c r="AG111">
-        <v>1.95</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.2</v>
-      </c>
       <c r="AK111">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,25 +18565,25 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q112">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="R112">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T112">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U112">
         <v>2.39</v>
@@ -18592,7 +18592,7 @@
         <v>1.49</v>
       </c>
       <c r="W112">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18610,10 +18610,10 @@
         <v>2.2</v>
       </c>
       <c r="AC112">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AD112">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE112">
         <v>1.12</v>
@@ -18638,7 +18638,7 @@
         <v>1.19</v>
       </c>
       <c r="AK112">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O113">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="P113">
-        <v>10.58</v>
+        <v>12.48</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19706,52 +19706,52 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="O119">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P119">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q119">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R119">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S119">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T119">
         <v>2.3</v>
       </c>
       <c r="U119">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="V119">
         <v>1.22</v>
       </c>
       <c r="W119">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X119">
         <v>1.07</v>
       </c>
       <c r="Y119">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Z119">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA119">
-        <v>2.49</v>
+        <v>2.71</v>
       </c>
       <c r="AB119">
         <v>1.44</v>
       </c>
       <c r="AC119">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AD119">
         <v>1.11</v>
@@ -19760,10 +19760,10 @@
         <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG119">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK119">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="O2">
         <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -650,7 +650,7 @@
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
         <v>3.02</v>
@@ -686,13 +686,13 @@
         <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
         <v>1.61</v>
       </c>
       <c r="AG2">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
         <v>3.05</v>
       </c>
       <c r="Q3">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -819,13 +819,13 @@
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,7 +834,7 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="AA3">
         <v>1.66</v>
@@ -846,10 +846,10 @@
         <v>2.69</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
         <v>1.57</v>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4">
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA4">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="AB4">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AC4">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
+        <v>2.14</v>
+      </c>
+      <c r="O5">
+        <v>2.9</v>
+      </c>
+      <c r="P5">
+        <v>3.25</v>
+      </c>
+      <c r="Q5">
+        <v>2.7</v>
+      </c>
+      <c r="R5">
+        <v>1.9</v>
+      </c>
+      <c r="S5">
+        <v>1.48</v>
+      </c>
+      <c r="T5">
+        <v>2.42</v>
+      </c>
+      <c r="U5">
+        <v>3.3</v>
+      </c>
+      <c r="V5">
+        <v>1.29</v>
+      </c>
+      <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
+        <v>1.07</v>
+      </c>
+      <c r="Y5">
+        <v>1.44</v>
+      </c>
+      <c r="Z5">
+        <v>2.7</v>
+      </c>
+      <c r="AA5">
+        <v>2.42</v>
+      </c>
+      <c r="AB5">
+        <v>1.52</v>
+      </c>
+      <c r="AC5">
+        <v>4.5</v>
+      </c>
+      <c r="AD5">
+        <v>1.2</v>
+      </c>
+      <c r="AE5">
+        <v>1.05</v>
+      </c>
+      <c r="AF5">
+        <v>2.03</v>
+      </c>
+      <c r="AG5">
         <v>1.75</v>
       </c>
-      <c r="O5">
-        <v>3.5</v>
-      </c>
-      <c r="P5">
-        <v>4.6</v>
-      </c>
-      <c r="Q5">
-        <v>2.39</v>
-      </c>
-      <c r="R5">
-        <v>2.1</v>
-      </c>
-      <c r="S5">
-        <v>1.4</v>
-      </c>
-      <c r="T5">
-        <v>2.75</v>
-      </c>
-      <c r="U5">
-        <v>3.22</v>
-      </c>
-      <c r="V5">
-        <v>1.36</v>
-      </c>
-      <c r="W5">
-        <v>1.07</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>1.36</v>
-      </c>
-      <c r="Z5">
-        <v>3.1</v>
-      </c>
-      <c r="AA5">
-        <v>2.12</v>
-      </c>
-      <c r="AB5">
-        <v>1.67</v>
-      </c>
-      <c r="AC5">
-        <v>3.74</v>
-      </c>
-      <c r="AD5">
-        <v>1.22</v>
-      </c>
-      <c r="AE5">
-        <v>1.03</v>
-      </c>
-      <c r="AF5">
-        <v>1.95</v>
-      </c>
-      <c r="AG5">
-        <v>1.73</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
         <v>1.38</v>
@@ -1326,13 +1326,13 @@
         <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB6">
         <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="AD6">
         <v>1.28</v>
@@ -1465,7 +1465,7 @@
         <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
         <v>3.25</v>
@@ -1474,7 +1474,7 @@
         <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1495,19 +1495,19 @@
         <v>1.96</v>
       </c>
       <c r="AC7">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AD7">
         <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1779,22 +1779,22 @@
         <v>1.8</v>
       </c>
       <c r="O9">
+        <v>3.8</v>
+      </c>
+      <c r="P9">
         <v>3.75</v>
       </c>
-      <c r="P9">
-        <v>3.55</v>
-      </c>
       <c r="Q9">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
         <v>2.21</v>
@@ -1812,28 +1812,28 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD9">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE9">
         <v>1.22</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG9">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R10">
         <v>2.2</v>
@@ -1957,13 +1957,13 @@
         <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1975,28 +1975,28 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
         <v>2.3</v>
@@ -2304,13 +2304,13 @@
         <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB12">
         <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AD12">
         <v>1.45</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P13">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -2464,7 +2464,7 @@
         <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA13">
         <v>1.39</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
         <v>2.35</v>
@@ -2790,19 +2790,19 @@
         <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>6.67</v>
+        <v>6.78</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB15">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE15">
         <v>1.32</v>
@@ -2811,7 +2811,7 @@
         <v>1.33</v>
       </c>
       <c r="AG15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.69</v>
+        <v>4.9</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="Q20">
-        <v>3.58</v>
+        <v>6.27</v>
       </c>
       <c r="R20">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="V20">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
         <v>1.09</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA20">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.74</v>
+        <v>3.54</v>
       </c>
       <c r="O21">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q21">
-        <v>2.31</v>
+        <v>4.3</v>
       </c>
       <c r="R21">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U21">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC21">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AD21">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>6.34</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>4.5</v>
@@ -3904,7 +3904,7 @@
         <v>1.37</v>
       </c>
       <c r="Q22">
-        <v>6.79</v>
+        <v>6.45</v>
       </c>
       <c r="R22">
         <v>2.32</v>
@@ -3916,10 +3916,10 @@
         <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
         <v>1.11</v>
@@ -3934,7 +3934,7 @@
         <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB22">
         <v>2.17</v>
@@ -3949,7 +3949,7 @@
         <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
         <v>1.89</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="Q24">
         <v>2.88</v>
       </c>
       <c r="R24">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U24">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC24">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AD24">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>8.68</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,19 +5045,19 @@
         <v>3.11</v>
       </c>
       <c r="Q29">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R29">
         <v>1.95</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U29">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
         <v>1.27</v>
@@ -5069,16 +5069,16 @@
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z29">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AA29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
         <v>4</v>
@@ -5090,7 +5090,7 @@
         <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
         <v>1.75</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5211,19 +5211,19 @@
         <v>2.87</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T30">
         <v>2.48</v>
       </c>
       <c r="U30">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5232,16 +5232,16 @@
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z30">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA30">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB30">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC30">
         <v>4.15</v>
@@ -5253,10 +5253,10 @@
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>11.9</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>2.7</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5857,10 +5857,10 @@
         <v>3.36</v>
       </c>
       <c r="P34">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q34">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="R34">
         <v>1.82</v>
@@ -5878,7 +5878,7 @@
         <v>1.26</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1.06</v>
@@ -5890,16 +5890,16 @@
         <v>2.43</v>
       </c>
       <c r="AA34">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AB34">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC34">
         <v>4.55</v>
       </c>
       <c r="AD34">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE34">
         <v>1</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -6192,49 +6192,49 @@
         <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AD36">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
         <v>1.5</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q37">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="S37">
         <v>1.35</v>
@@ -6379,16 +6379,16 @@
         <v>3.34</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
         <v>3.24</v>
       </c>
       <c r="AD37">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE37">
         <v>1.06</v>
@@ -6512,55 +6512,55 @@
         <v>4.66</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AD39">
         <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF39">
         <v>1.5</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
         <v>3.5</v>
@@ -7001,7 +7001,7 @@
         <v>4.33</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R41">
         <v>2.16</v>
@@ -7019,7 +7019,7 @@
         <v>1.41</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1.03</v>
@@ -7034,7 +7034,7 @@
         <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC41">
         <v>3.3</v>
@@ -7644,16 +7644,16 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P45">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="Q45">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
         <v>1.97</v>
@@ -7662,16 +7662,16 @@
         <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="U45">
         <v>3.2</v>
       </c>
       <c r="V45">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
         <v>1.06</v>
@@ -7686,19 +7686,19 @@
         <v>2.25</v>
       </c>
       <c r="AB45">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC45">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE45">
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
         <v>1.77</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
         <v>1.62</v>
@@ -7816,13 +7816,13 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>8</v>
+        <v>8.68</v>
       </c>
       <c r="R46">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
         <v>3.8</v>
@@ -7840,31 +7840,31 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA46">
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD46">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE46">
         <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG46">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>2.87</v>
       </c>
       <c r="Q47">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
         <v>3.3</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK47">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="Q48">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
         <v>2.21</v>
@@ -8166,7 +8166,7 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z48">
         <v>3.9</v>
@@ -8190,7 +8190,7 @@
         <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
         <v>2.25</v>
@@ -8305,22 +8305,22 @@
         <v>2.73</v>
       </c>
       <c r="Q49">
+        <v>3.48</v>
+      </c>
+      <c r="R49">
+        <v>1.87</v>
+      </c>
+      <c r="S49">
+        <v>1.5</v>
+      </c>
+      <c r="T49">
+        <v>2.5</v>
+      </c>
+      <c r="U49">
         <v>3.12</v>
       </c>
-      <c r="R49">
-        <v>1.94</v>
-      </c>
-      <c r="S49">
-        <v>1.4</v>
-      </c>
-      <c r="T49">
-        <v>2.44</v>
-      </c>
-      <c r="U49">
-        <v>3</v>
-      </c>
       <c r="V49">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W49">
         <v>1.03</v>
@@ -8329,31 +8329,31 @@
         <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z49">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA49">
         <v>2.25</v>
       </c>
       <c r="AB49">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC49">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AD49">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF49">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
         <v>1.44</v>
@@ -9120,7 +9120,7 @@
         <v>2.81</v>
       </c>
       <c r="Q54">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
         <v>1.93</v>
@@ -9135,7 +9135,7 @@
         <v>3.22</v>
       </c>
       <c r="V54">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W54">
         <v>1.01</v>
@@ -9144,13 +9144,13 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z54">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AA54">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB54">
         <v>1.65</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O56">
         <v>3.5</v>
@@ -9455,7 +9455,7 @@
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
         <v>2.25</v>
@@ -9470,10 +9470,10 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>4.61</v>
+        <v>5</v>
       </c>
       <c r="AA56">
         <v>1.53</v>
@@ -9482,10 +9482,10 @@
         <v>2.45</v>
       </c>
       <c r="AC56">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AD56">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE56">
         <v>1.17</v>
@@ -9494,7 +9494,7 @@
         <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
         <v>2.4</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="R57">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9633,7 +9633,7 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
         <v>5.05</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="O58">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P58">
         <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R58">
         <v>2.27</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T58">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U58">
         <v>2.25</v>
@@ -9802,7 +9802,7 @@
         <v>4.6</v>
       </c>
       <c r="AA58">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB58">
         <v>2.35</v>
@@ -9811,16 +9811,16 @@
         <v>2.45</v>
       </c>
       <c r="AD58">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE58">
         <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>4.4</v>
+        <v>4.04</v>
       </c>
       <c r="Q60">
         <v>2.29</v>
@@ -10104,10 +10104,10 @@
         <v>2.08</v>
       </c>
       <c r="S60">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T60">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U60">
         <v>2.89</v>
@@ -10116,37 +10116,37 @@
         <v>1.39</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z60">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AA60">
         <v>1.95</v>
       </c>
       <c r="AB60">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC60">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AD60">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG60">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10457,13 +10457,13 @@
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AC62">
         <v>2.22</v>
       </c>
       <c r="AD62">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
         <v>1.24</v>
@@ -10472,7 +10472,7 @@
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10590,13 +10590,13 @@
         <v>2.49</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U63">
         <v>2.95</v>
@@ -10608,7 +10608,7 @@
         <v>1.02</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
         <v>1.33</v>
@@ -10620,10 +10620,10 @@
         <v>2.1</v>
       </c>
       <c r="AB63">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC63">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="AD63">
         <v>1.27</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10744,25 +10744,25 @@
         <v>3.84</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q64">
         <v>3.5</v>
       </c>
       <c r="R64">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S64">
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="U64">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="V64">
         <v>1.57</v>
@@ -10789,10 +10789,10 @@
         <v>2.49</v>
       </c>
       <c r="AD64">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE64">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
         <v>1.47</v>
@@ -10910,19 +10910,19 @@
         <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
       </c>
       <c r="R65">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
         <v>1.19</v>
       </c>
       <c r="T65">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U65">
         <v>2</v>
@@ -10946,7 +10946,7 @@
         <v>1.4</v>
       </c>
       <c r="AB65">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AC65">
         <v>2.09</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="AK65">
         <v>1.37</v>
@@ -11076,16 +11076,16 @@
         <v>4.1</v>
       </c>
       <c r="Q66">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R66">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="S66">
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
         <v>2.25</v>
@@ -11094,16 +11094,16 @@
         <v>1.57</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="AA66">
         <v>1.6</v>
@@ -11112,13 +11112,13 @@
         <v>2.38</v>
       </c>
       <c r="AC66">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="AD66">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE66">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
         <v>1.57</v>
@@ -11233,7 +11233,7 @@
         <v>3.1</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
         <v>2.1</v>
@@ -11248,10 +11248,10 @@
         <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U67">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V67">
         <v>1.36</v>
@@ -11260,7 +11260,7 @@
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.28</v>
@@ -11269,19 +11269,19 @@
         <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC67">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="AD67">
         <v>1.23</v>
       </c>
       <c r="AE67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
         <v>1.8</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
+        <v>1.24</v>
+      </c>
+      <c r="AK67">
         <v>1.25</v>
-      </c>
-      <c r="AK67">
-        <v>1.29</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11426,10 +11426,10 @@
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z68">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA68">
         <v>2.05</v>
@@ -11466,7 +11466,7 @@
         <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O70">
         <v>4.25</v>
       </c>
       <c r="P70">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O74">
         <v>3.3</v>
@@ -12389,13 +12389,13 @@
         <v>1.42</v>
       </c>
       <c r="T74">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U74">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V74">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W74">
         <v>1.06</v>
@@ -12407,22 +12407,22 @@
         <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AA74">
         <v>2.25</v>
       </c>
       <c r="AB74">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC74">
-        <v>4.12</v>
+        <v>3.96</v>
       </c>
       <c r="AD74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE74">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF74">
         <v>1.95</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
         <v>1.3</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q76">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U76">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
         <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA76">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD76">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK76">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,37 +12860,37 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O77">
         <v>3.3</v>
       </c>
       <c r="P77">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V77">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.21</v>
@@ -12899,25 +12899,25 @@
         <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q78">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R78">
         <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U78">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
+        <v>1.06</v>
+      </c>
+      <c r="X78">
+        <v>1.03</v>
+      </c>
+      <c r="Y78">
+        <v>1.24</v>
+      </c>
+      <c r="Z78">
+        <v>3.34</v>
+      </c>
+      <c r="AA78">
+        <v>1.92</v>
+      </c>
+      <c r="AB78">
+        <v>1.9</v>
+      </c>
+      <c r="AC78">
+        <v>3.4</v>
+      </c>
+      <c r="AD78">
+        <v>1.29</v>
+      </c>
+      <c r="AE78">
         <v>1.07</v>
       </c>
-      <c r="X78">
-        <v>1.02</v>
-      </c>
-      <c r="Y78">
-        <v>1.21</v>
-      </c>
-      <c r="Z78">
-        <v>3.8</v>
-      </c>
-      <c r="AA78">
-        <v>1.81</v>
-      </c>
-      <c r="AB78">
-        <v>2.01</v>
-      </c>
-      <c r="AC78">
-        <v>3.1</v>
-      </c>
-      <c r="AD78">
-        <v>1.33</v>
-      </c>
-      <c r="AE78">
-        <v>1.08</v>
-      </c>
       <c r="AF78">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG78">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T79">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U79">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AA79">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="AB79">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC79">
-        <v>3.28</v>
+        <v>4.32</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE79">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AG79">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK79">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,80 +13349,80 @@
         </is>
       </c>
       <c r="N80">
+        <v>1.59</v>
+      </c>
+      <c r="O80">
+        <v>3.88</v>
+      </c>
+      <c r="P80">
+        <v>5.25</v>
+      </c>
+      <c r="Q80">
         <v>2.2</v>
       </c>
-      <c r="O80">
+      <c r="R80">
+        <v>2.15</v>
+      </c>
+      <c r="S80">
+        <v>1.42</v>
+      </c>
+      <c r="T80">
+        <v>2.88</v>
+      </c>
+      <c r="U80">
+        <v>2.71</v>
+      </c>
+      <c r="V80">
+        <v>1.36</v>
+      </c>
+      <c r="W80">
+        <v>1.07</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.32</v>
+      </c>
+      <c r="Z80">
+        <v>3.08</v>
+      </c>
+      <c r="AA80">
+        <v>1.94</v>
+      </c>
+      <c r="AB80">
+        <v>1.74</v>
+      </c>
+      <c r="AC80">
         <v>3.2</v>
       </c>
-      <c r="P80">
-        <v>3.1</v>
-      </c>
-      <c r="Q80">
-        <v>2.8</v>
-      </c>
-      <c r="R80">
-        <v>1.96</v>
-      </c>
-      <c r="S80">
-        <v>1.48</v>
-      </c>
-      <c r="T80">
-        <v>2.41</v>
-      </c>
-      <c r="U80">
-        <v>3</v>
-      </c>
-      <c r="V80">
-        <v>1.29</v>
-      </c>
-      <c r="W80">
-        <v>1.06</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>1.4</v>
-      </c>
-      <c r="Z80">
-        <v>2.75</v>
-      </c>
-      <c r="AA80">
+      <c r="AD80">
+        <v>1.26</v>
+      </c>
+      <c r="AE80">
+        <v>1.1</v>
+      </c>
+      <c r="AF80">
+        <v>1.91</v>
+      </c>
+      <c r="AG80">
+        <v>1.8</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
+        <v>1.25</v>
+      </c>
+      <c r="AK80">
         <v>2.29</v>
-      </c>
-      <c r="AB80">
-        <v>1.57</v>
-      </c>
-      <c r="AC80">
-        <v>4.36</v>
-      </c>
-      <c r="AD80">
-        <v>1.15</v>
-      </c>
-      <c r="AE80">
-        <v>1</v>
-      </c>
-      <c r="AF80">
-        <v>1.95</v>
-      </c>
-      <c r="AG80">
-        <v>1.75</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.33</v>
-      </c>
-      <c r="AK80">
-        <v>1.62</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
         <v>3</v>
@@ -13566,7 +13566,7 @@
         <v>1.01</v>
       </c>
       <c r="AF81">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG81">
         <v>1.8</v>
@@ -13699,7 +13699,7 @@
         <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13708,22 +13708,22 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z82">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="AA82">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB82">
         <v>2.35</v>
       </c>
       <c r="AC82">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD82">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE82">
         <v>1.2</v>
@@ -13748,7 +13748,7 @@
         <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13853,7 +13853,7 @@
         <v>2.55</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
         <v>3.75</v>
@@ -13865,16 +13865,16 @@
         <v>1.65</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
         <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="AA83">
         <v>1.47</v>
@@ -13886,7 +13886,7 @@
         <v>2.12</v>
       </c>
       <c r="AD83">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE83">
         <v>1.27</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O84">
         <v>3.34</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -16292,13 +16292,13 @@
         <v>2.56</v>
       </c>
       <c r="Q98">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R98">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
         <v>2.79</v>
@@ -16316,13 +16316,13 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AA98">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB98">
         <v>1.78</v>
@@ -16334,7 +16334,7 @@
         <v>1.29</v>
       </c>
       <c r="AE98">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF98">
         <v>1.73</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O99">
+        <v>3.4</v>
+      </c>
+      <c r="P99">
         <v>3.8</v>
-      </c>
-      <c r="P99">
-        <v>3.7</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -16494,7 +16494,7 @@
         <v>2.74</v>
       </c>
       <c r="AD99">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
@@ -16612,7 +16612,7 @@
         <v>1.91</v>
       </c>
       <c r="O100">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
         <v>3.1</v>
@@ -16624,13 +16624,13 @@
         <v>2.3</v>
       </c>
       <c r="S100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="U100">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V100">
         <v>1.55</v>
@@ -16642,7 +16642,7 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
         <v>4.3</v>
@@ -16654,7 +16654,7 @@
         <v>2.25</v>
       </c>
       <c r="AC100">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD100">
         <v>1.44</v>
@@ -16796,7 +16796,7 @@
         <v>2.21</v>
       </c>
       <c r="V101">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W101">
         <v>1.13</v>
@@ -16811,7 +16811,7 @@
         <v>5</v>
       </c>
       <c r="AA101">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB101">
         <v>2.35</v>
@@ -17264,7 +17264,7 @@
         <v>4.35</v>
       </c>
       <c r="O104">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P104">
         <v>1.57</v>
@@ -17439,43 +17439,43 @@
         <v>2.31</v>
       </c>
       <c r="S105">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U105">
         <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W105">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA105">
         <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AC105">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD105">
         <v>1.68</v>
       </c>
       <c r="AE105">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17596,16 +17596,16 @@
         <v>6.5</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R106">
         <v>2.5</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U106">
         <v>2.4</v>
@@ -17620,31 +17620,31 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z106">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA106">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB106">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC106">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AD106">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE106">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG106">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17774,7 +17774,7 @@
         <v>2.13</v>
       </c>
       <c r="V107">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W107">
         <v>1.12</v>
@@ -17786,13 +17786,13 @@
         <v>1.09</v>
       </c>
       <c r="Z107">
-        <v>5.37</v>
+        <v>5.45</v>
       </c>
       <c r="AA107">
         <v>1.47</v>
       </c>
       <c r="AB107">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AC107">
         <v>2.15</v>
@@ -17801,7 +17801,7 @@
         <v>1.6</v>
       </c>
       <c r="AE107">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF107">
         <v>1.5</v>
@@ -17916,7 +17916,7 @@
         <v>1.7</v>
       </c>
       <c r="O108">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P108">
         <v>3.8</v>
@@ -17934,7 +17934,7 @@
         <v>3.38</v>
       </c>
       <c r="U108">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="V108">
         <v>1.51</v>
@@ -17946,13 +17946,13 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z108">
-        <v>4.91</v>
+        <v>4.81</v>
       </c>
       <c r="AA108">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB108">
         <v>2.45</v>
@@ -17961,10 +17961,10 @@
         <v>2.38</v>
       </c>
       <c r="AD108">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE108">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
         <v>1.57</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
+        <v>2.08</v>
+      </c>
+      <c r="O109">
+        <v>3.35</v>
+      </c>
+      <c r="P109">
+        <v>2.91</v>
+      </c>
+      <c r="Q109">
+        <v>2.8</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>1.3</v>
+      </c>
+      <c r="T109">
+        <v>2.85</v>
+      </c>
+      <c r="U109">
+        <v>2.54</v>
+      </c>
+      <c r="V109">
+        <v>1.41</v>
+      </c>
+      <c r="W109">
+        <v>1.06</v>
+      </c>
+      <c r="X109">
+        <v>1.01</v>
+      </c>
+      <c r="Y109">
+        <v>1.2</v>
+      </c>
+      <c r="Z109">
+        <v>3.68</v>
+      </c>
+      <c r="AA109">
+        <v>1.75</v>
+      </c>
+      <c r="AB109">
+        <v>1.94</v>
+      </c>
+      <c r="AC109">
+        <v>2.78</v>
+      </c>
+      <c r="AD109">
         <v>1.4</v>
       </c>
-      <c r="O109">
-        <v>4.4</v>
-      </c>
-      <c r="P109">
-        <v>5.4</v>
-      </c>
-      <c r="Q109">
-        <v>1.91</v>
-      </c>
-      <c r="R109">
-        <v>2.3</v>
-      </c>
-      <c r="S109">
-        <v>1.25</v>
-      </c>
-      <c r="T109">
-        <v>3.4</v>
-      </c>
-      <c r="U109">
-        <v>2.23</v>
-      </c>
-      <c r="V109">
+      <c r="AE109">
+        <v>1.1</v>
+      </c>
+      <c r="AF109">
+        <v>1.6</v>
+      </c>
+      <c r="AG109">
+        <v>2.18</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.24</v>
+      </c>
+      <c r="AK109">
         <v>1.53</v>
-      </c>
-      <c r="W109">
-        <v>1.14</v>
-      </c>
-      <c r="X109">
-        <v>1.02</v>
-      </c>
-      <c r="Y109">
-        <v>1.16</v>
-      </c>
-      <c r="Z109">
-        <v>4.15</v>
-      </c>
-      <c r="AA109">
-        <v>1.6</v>
-      </c>
-      <c r="AB109">
-        <v>2.15</v>
-      </c>
-      <c r="AC109">
-        <v>2.51</v>
-      </c>
-      <c r="AD109">
-        <v>1.44</v>
-      </c>
-      <c r="AE109">
-        <v>1.2</v>
-      </c>
-      <c r="AF109">
-        <v>1.76</v>
-      </c>
-      <c r="AG109">
-        <v>1.95</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.2</v>
-      </c>
-      <c r="AK109">
-        <v>2.52</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,65 +18239,65 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="O110">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P110">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q110">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U110">
+        <v>2.23</v>
+      </c>
+      <c r="V110">
+        <v>1.53</v>
+      </c>
+      <c r="W110">
+        <v>1.12</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
+        <v>1.16</v>
+      </c>
+      <c r="Z110">
+        <v>4.15</v>
+      </c>
+      <c r="AA110">
+        <v>1.6</v>
+      </c>
+      <c r="AB110">
+        <v>2.15</v>
+      </c>
+      <c r="AC110">
         <v>2.54</v>
       </c>
-      <c r="V110">
-        <v>1.41</v>
-      </c>
-      <c r="W110">
-        <v>1.06</v>
-      </c>
-      <c r="X110">
-        <v>1.03</v>
-      </c>
-      <c r="Y110">
+      <c r="AD110">
+        <v>1.44</v>
+      </c>
+      <c r="AE110">
         <v>1.2</v>
       </c>
-      <c r="Z110">
-        <v>3.68</v>
-      </c>
-      <c r="AA110">
-        <v>1.75</v>
-      </c>
-      <c r="AB110">
+      <c r="AF110">
+        <v>1.76</v>
+      </c>
+      <c r="AG110">
         <v>1.94</v>
       </c>
-      <c r="AC110">
-        <v>2.78</v>
-      </c>
-      <c r="AD110">
-        <v>1.39</v>
-      </c>
-      <c r="AE110">
-        <v>1.13</v>
-      </c>
-      <c r="AF110">
-        <v>1.62</v>
-      </c>
-      <c r="AG110">
-        <v>2.15</v>
-      </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK110">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,22 +18411,22 @@
         <v>10.85</v>
       </c>
       <c r="Q111">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R111">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="S111">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T111">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="U111">
         <v>1.79</v>
       </c>
       <c r="V111">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W111">
         <v>1.29</v>
@@ -18438,22 +18438,22 @@
         <v>1.02</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AA111">
         <v>1.25</v>
       </c>
       <c r="AB111">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AC111">
         <v>1.65</v>
       </c>
       <c r="AD111">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AE111">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF111">
         <v>1.77</v>
@@ -18897,10 +18897,10 @@
         <v>3.8</v>
       </c>
       <c r="P114">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="Q114">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
         <v>2.36</v>
@@ -18921,13 +18921,13 @@
         <v>1.17</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z114">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA114">
         <v>1.47</v>
@@ -18939,7 +18939,7 @@
         <v>2.24</v>
       </c>
       <c r="AD114">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE114">
         <v>1.19</v>
@@ -18948,7 +18948,7 @@
         <v>1.51</v>
       </c>
       <c r="AG114">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,10 +19057,10 @@
         <v>2.7</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q115">
         <v>3.3</v>
@@ -19069,31 +19069,31 @@
         <v>2.03</v>
       </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="V115">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W115">
         <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z115">
         <v>2.89</v>
       </c>
       <c r="AA115">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AB115">
         <v>1.84</v>
@@ -19108,10 +19108,10 @@
         <v>1.07</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>1.49</v>
       </c>
       <c r="O116">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P116">
         <v>5.4</v>
@@ -19229,7 +19229,7 @@
         <v>1.95</v>
       </c>
       <c r="R116">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S116">
         <v>1.25</v>
@@ -19250,25 +19250,25 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z116">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA116">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB116">
         <v>2.33</v>
       </c>
       <c r="AC116">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD116">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE116">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF116">
         <v>1.57</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK116">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O117">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P117">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q117">
         <v>3.68</v>
       </c>
       <c r="R117">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S117">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T117">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U117">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="V117">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W117">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X117">
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA117">
+        <v>1.87</v>
+      </c>
+      <c r="AB117">
         <v>1.9</v>
       </c>
-      <c r="AB117">
-        <v>1.82</v>
-      </c>
       <c r="AC117">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="AD117">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE117">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="O118">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="O119">
         <v>2.8</v>
@@ -19745,7 +19745,7 @@
         <v>2.33</v>
       </c>
       <c r="AA119">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AB119">
         <v>1.44</v>
@@ -19779,7 +19779,7 @@
         <v>1.4</v>
       </c>
       <c r="AK119">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19881,19 +19881,19 @@
         <v>3.04</v>
       </c>
       <c r="R120">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S120">
         <v>1.45</v>
       </c>
       <c r="T120">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U120">
         <v>3.25</v>
       </c>
       <c r="V120">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W120">
         <v>1.05</v>
@@ -19914,7 +19914,7 @@
         <v>1.54</v>
       </c>
       <c r="AC120">
-        <v>4.44</v>
+        <v>4.71</v>
       </c>
       <c r="AD120">
         <v>1.15</v>
@@ -19923,10 +19923,10 @@
         <v>1.01</v>
       </c>
       <c r="AF120">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG120">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="O121">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P121">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -20050,7 +20050,7 @@
         <v>1.32</v>
       </c>
       <c r="T121">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U121">
         <v>2.48</v>
@@ -20065,10 +20065,10 @@
         <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z121">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA121">
         <v>1.75</v>
@@ -20077,19 +20077,19 @@
         <v>2.05</v>
       </c>
       <c r="AC121">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE121">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG121">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q4">
+        <v>2.7</v>
+      </c>
+      <c r="R4">
+        <v>1.9</v>
+      </c>
+      <c r="S4">
+        <v>1.48</v>
+      </c>
+      <c r="T4">
         <v>2.42</v>
       </c>
-      <c r="R4">
-        <v>2.21</v>
-      </c>
-      <c r="S4">
-        <v>1.4</v>
-      </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
       <c r="U4">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
         <v>1.07</v>
       </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA4">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AB4">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="O5">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
         <v>1.02</v>
       </c>
-      <c r="X5">
-        <v>1.07</v>
-      </c>
       <c r="Y5">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.28</v>
+      </c>
+      <c r="T6">
+        <v>3.25</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+      <c r="V6">
+        <v>1.48</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.19</v>
+      </c>
+      <c r="Z6">
+        <v>3.74</v>
+      </c>
+      <c r="AA6">
+        <v>1.72</v>
+      </c>
+      <c r="AB6">
+        <v>1.96</v>
+      </c>
+      <c r="AC6">
+        <v>2.78</v>
+      </c>
+      <c r="AD6">
+        <v>1.34</v>
+      </c>
+      <c r="AE6">
+        <v>1.14</v>
+      </c>
+      <c r="AF6">
+        <v>1.6</v>
+      </c>
+      <c r="AG6">
         <v>2.18</v>
       </c>
-      <c r="S6">
-        <v>1.38</v>
-      </c>
-      <c r="T6">
-        <v>2.64</v>
-      </c>
-      <c r="U6">
-        <v>2.88</v>
-      </c>
-      <c r="V6">
-        <v>1.36</v>
-      </c>
-      <c r="W6">
-        <v>1.02</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.51</v>
+      </c>
+      <c r="AK6">
         <v>1.3</v>
-      </c>
-      <c r="Z6">
-        <v>3.4</v>
-      </c>
-      <c r="AA6">
-        <v>2.04</v>
-      </c>
-      <c r="AB6">
-        <v>1.78</v>
-      </c>
-      <c r="AC6">
-        <v>3.6</v>
-      </c>
-      <c r="AD6">
-        <v>1.28</v>
-      </c>
-      <c r="AE6">
-        <v>1.04</v>
-      </c>
-      <c r="AF6">
-        <v>1.75</v>
-      </c>
-      <c r="AG6">
-        <v>1.95</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.4</v>
-      </c>
-      <c r="AK6">
-        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
+        <v>1.38</v>
+      </c>
+      <c r="T7">
+        <v>2.64</v>
+      </c>
+      <c r="U7">
+        <v>2.88</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.02</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.3</v>
+      </c>
+      <c r="Z7">
+        <v>3.4</v>
+      </c>
+      <c r="AA7">
+        <v>2.04</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>3.6</v>
+      </c>
+      <c r="AD7">
         <v>1.28</v>
       </c>
-      <c r="T7">
-        <v>3.25</v>
-      </c>
-      <c r="U7">
-        <v>2.4</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.19</v>
-      </c>
-      <c r="Z7">
-        <v>3.74</v>
-      </c>
-      <c r="AA7">
-        <v>1.72</v>
-      </c>
-      <c r="AB7">
-        <v>1.96</v>
-      </c>
-      <c r="AC7">
-        <v>2.78</v>
-      </c>
-      <c r="AD7">
-        <v>1.34</v>
-      </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q20">
-        <v>6.27</v>
+        <v>4.3</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U20">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB20">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AC20">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.54</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="Q21">
-        <v>4.3</v>
+        <v>6.45</v>
       </c>
       <c r="R21">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
         <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
         <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="O22">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="Q22">
-        <v>6.45</v>
+        <v>6.27</v>
       </c>
       <c r="R22">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U22">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA22">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AC22">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AD22">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
         <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK22">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD50">
         <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="R51">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
         <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="AA51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U52">
         <v>2.5</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>1.42</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
         <v>6.77</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q76">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R76">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
         <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U76">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V76">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W76">
+        <v>1.06</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
+        <v>1.24</v>
+      </c>
+      <c r="Z76">
+        <v>3.34</v>
+      </c>
+      <c r="AA76">
+        <v>1.92</v>
+      </c>
+      <c r="AB76">
+        <v>1.9</v>
+      </c>
+      <c r="AC76">
+        <v>3.4</v>
+      </c>
+      <c r="AD76">
+        <v>1.29</v>
+      </c>
+      <c r="AE76">
         <v>1.07</v>
       </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>1.22</v>
-      </c>
-      <c r="Z76">
-        <v>3.58</v>
-      </c>
-      <c r="AA76">
-        <v>1.8</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76">
-        <v>2.83</v>
-      </c>
-      <c r="AD76">
-        <v>1.33</v>
-      </c>
-      <c r="AE76">
-        <v>1.1</v>
-      </c>
       <c r="AF76">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG76">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
         <v>3.3</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q77">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="U77">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V77">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
         <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD77">
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK77">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T78">
-        <v>2.96</v>
+        <v>2.41</v>
       </c>
       <c r="U78">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.4</v>
+      </c>
+      <c r="Z78">
+        <v>2.75</v>
+      </c>
+      <c r="AA78">
+        <v>2.29</v>
+      </c>
+      <c r="AB78">
+        <v>1.57</v>
+      </c>
+      <c r="AC78">
+        <v>4.32</v>
+      </c>
+      <c r="AD78">
+        <v>1.15</v>
+      </c>
+      <c r="AE78">
         <v>1.03</v>
       </c>
-      <c r="Y78">
-        <v>1.24</v>
-      </c>
-      <c r="Z78">
-        <v>3.34</v>
-      </c>
-      <c r="AA78">
-        <v>1.92</v>
-      </c>
-      <c r="AB78">
-        <v>1.9</v>
-      </c>
-      <c r="AC78">
-        <v>3.4</v>
-      </c>
-      <c r="AD78">
-        <v>1.29</v>
-      </c>
-      <c r="AE78">
-        <v>1.07</v>
-      </c>
       <c r="AF78">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK78">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
+        <v>1.59</v>
+      </c>
+      <c r="O79">
+        <v>3.88</v>
+      </c>
+      <c r="P79">
+        <v>5.25</v>
+      </c>
+      <c r="Q79">
         <v>2.2</v>
       </c>
-      <c r="O79">
+      <c r="R79">
+        <v>2.15</v>
+      </c>
+      <c r="S79">
+        <v>1.42</v>
+      </c>
+      <c r="T79">
+        <v>2.88</v>
+      </c>
+      <c r="U79">
+        <v>2.71</v>
+      </c>
+      <c r="V79">
+        <v>1.36</v>
+      </c>
+      <c r="W79">
+        <v>1.07</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.32</v>
+      </c>
+      <c r="Z79">
+        <v>3.08</v>
+      </c>
+      <c r="AA79">
+        <v>1.94</v>
+      </c>
+      <c r="AB79">
+        <v>1.74</v>
+      </c>
+      <c r="AC79">
         <v>3.2</v>
       </c>
-      <c r="P79">
-        <v>3.1</v>
-      </c>
-      <c r="Q79">
-        <v>2.8</v>
-      </c>
-      <c r="R79">
-        <v>2.07</v>
-      </c>
-      <c r="S79">
-        <v>1.48</v>
-      </c>
-      <c r="T79">
-        <v>2.41</v>
-      </c>
-      <c r="U79">
-        <v>3</v>
-      </c>
-      <c r="V79">
-        <v>1.29</v>
-      </c>
-      <c r="W79">
-        <v>1.06</v>
-      </c>
-      <c r="X79">
-        <v>1.02</v>
-      </c>
-      <c r="Y79">
-        <v>1.4</v>
-      </c>
-      <c r="Z79">
-        <v>2.75</v>
-      </c>
-      <c r="AA79">
+      <c r="AD79">
+        <v>1.26</v>
+      </c>
+      <c r="AE79">
+        <v>1.1</v>
+      </c>
+      <c r="AF79">
+        <v>1.91</v>
+      </c>
+      <c r="AG79">
+        <v>1.8</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.25</v>
+      </c>
+      <c r="AK79">
         <v>2.29</v>
-      </c>
-      <c r="AB79">
-        <v>1.57</v>
-      </c>
-      <c r="AC79">
-        <v>4.32</v>
-      </c>
-      <c r="AD79">
-        <v>1.15</v>
-      </c>
-      <c r="AE79">
-        <v>1.03</v>
-      </c>
-      <c r="AF79">
-        <v>1.95</v>
-      </c>
-      <c r="AG79">
-        <v>1.75</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.33</v>
-      </c>
-      <c r="AK79">
-        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="O80">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q80">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="R80">
         <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U80">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AB80">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC80">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD80">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="O89">
-        <v>3.42</v>
+        <v>4.8</v>
       </c>
       <c r="P89">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z89">
-        <v>3.98</v>
+        <v>6.08</v>
       </c>
       <c r="AA89">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="AC89">
-        <v>2.49</v>
+        <v>2.02</v>
       </c>
       <c r="AD89">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AE89">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF89">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,22 +14979,22 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="O90">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="Q90">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="R90">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T90">
         <v>4</v>
@@ -15003,40 +15003,40 @@
         <v>2.02</v>
       </c>
       <c r="V90">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.07</v>
       </c>
       <c r="Z90">
-        <v>6.08</v>
+        <v>5.8</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE90">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG90">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O91">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P91">
-        <v>4.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q91">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="S91">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U91">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V91">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W91">
         <v>1.18</v>
@@ -15175,31 +15175,31 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.8</v>
+        <v>5.68</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB91">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC91">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE91">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF91">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AG91">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="O92">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="P92">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="Q92">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="R92">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T92">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="U92">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="V92">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="W92">
+        <v>1.25</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.05</v>
+      </c>
+      <c r="Z92">
+        <v>8</v>
+      </c>
+      <c r="AA92">
+        <v>1.29</v>
+      </c>
+      <c r="AB92">
+        <v>3.4</v>
+      </c>
+      <c r="AC92">
+        <v>1.73</v>
+      </c>
+      <c r="AD92">
+        <v>2.03</v>
+      </c>
+      <c r="AE92">
+        <v>1.4</v>
+      </c>
+      <c r="AF92">
+        <v>1.33</v>
+      </c>
+      <c r="AG92">
+        <v>3</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.18</v>
       </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>1.13</v>
-      </c>
-      <c r="Z92">
-        <v>5.68</v>
-      </c>
-      <c r="AA92">
-        <v>1.39</v>
-      </c>
-      <c r="AB92">
-        <v>2.59</v>
-      </c>
-      <c r="AC92">
-        <v>2.15</v>
-      </c>
-      <c r="AD92">
-        <v>1.68</v>
-      </c>
-      <c r="AE92">
-        <v>1.24</v>
-      </c>
-      <c r="AF92">
-        <v>1.37</v>
-      </c>
-      <c r="AG92">
-        <v>2.86</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.22</v>
-      </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,31 +15468,31 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.6</v>
+        <v>2.65</v>
       </c>
       <c r="O93">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q93">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="R93">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="S93">
         <v>1.13</v>
       </c>
       <c r="T93">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="U93">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V93">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W93">
         <v>1.25</v>
@@ -15501,31 +15501,31 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z93">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AA93">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB93">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AC93">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AD93">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AE93">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF93">
         <v>1.33</v>
       </c>
       <c r="AG93">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AK93">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="O94">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P94">
         <v>2.1</v>
       </c>
       <c r="Q94">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="R94">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="S94">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T94">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="U94">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V94">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="W94">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>7.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA94">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AB94">
-        <v>3.28</v>
+        <v>2.61</v>
       </c>
       <c r="AC94">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AD94">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AE94">
+        <v>1.24</v>
+      </c>
+      <c r="AF94">
+        <v>1.36</v>
+      </c>
+      <c r="AG94">
+        <v>2.8</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <v>1.22</v>
+      </c>
+      <c r="AK94">
         <v>1.38</v>
-      </c>
-      <c r="AF94">
-        <v>1.33</v>
-      </c>
-      <c r="AG94">
-        <v>3.1</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.67</v>
-      </c>
-      <c r="AK94">
-        <v>1.4</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="O95">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="P95">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="Q95">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="R95">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="V95">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z95">
-        <v>5.55</v>
+        <v>3.98</v>
       </c>
       <c r="AA95">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB95">
-        <v>2.61</v>
+        <v>2.22</v>
       </c>
       <c r="AC95">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="AD95">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE95">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF95">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AG95">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK95">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.08</v>
+        <v>1.13</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>7.7</v>
       </c>
       <c r="P109">
-        <v>2.91</v>
+        <v>10.85</v>
       </c>
       <c r="Q109">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="R109">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>4.65</v>
       </c>
       <c r="U109">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="V109">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="Z109">
-        <v>3.68</v>
+        <v>7.7</v>
       </c>
       <c r="AA109">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB109">
-        <v>1.94</v>
+        <v>3.8</v>
       </c>
       <c r="AC109">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD109">
-        <v>1.4</v>
+        <v>2.19</v>
       </c>
       <c r="AE109">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="AF109">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AG109">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AK109">
-        <v>1.53</v>
+        <v>5.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>2.08</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>3.35</v>
       </c>
       <c r="P111">
-        <v>10.85</v>
+        <v>2.91</v>
       </c>
       <c r="Q111">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="R111">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="S111">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="T111">
-        <v>4.65</v>
+        <v>2.85</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="V111">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="W111">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z111">
-        <v>7.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>3.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="AD111">
-        <v>2.19</v>
+        <v>1.4</v>
       </c>
       <c r="AE111">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="AK111">
-        <v>5.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18785,7 +18785,7 @@
         <v>2.75</v>
       </c>
       <c r="AG113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4">
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
         <v>1.02</v>
       </c>
-      <c r="X4">
-        <v>1.07</v>
-      </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA4">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AB4">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AC4">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q5">
+        <v>2.7</v>
+      </c>
+      <c r="R5">
+        <v>1.9</v>
+      </c>
+      <c r="S5">
+        <v>1.48</v>
+      </c>
+      <c r="T5">
         <v>2.42</v>
       </c>
-      <c r="R5">
-        <v>2.21</v>
-      </c>
-      <c r="S5">
-        <v>1.4</v>
-      </c>
-      <c r="T5">
-        <v>2.75</v>
-      </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
         <v>1.07</v>
       </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AC5">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AG5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>1.37</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>6.45</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AC19">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q20">
-        <v>4.3</v>
+        <v>6.27</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA20">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="AC20">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AD20">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>1.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>6.45</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AC21">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AD21">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q22">
-        <v>6.27</v>
+        <v>4.3</v>
       </c>
       <c r="R22">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T22">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U22">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB22">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AC22">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="AD22">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="V36">
         <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB36">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
+        <v>1.43</v>
+      </c>
+      <c r="AK36">
         <v>1.33</v>
-      </c>
-      <c r="AK36">
-        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="Q37">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U37">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V37">
         <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC37">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AD37">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE37">
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q50">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD50">
         <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q51">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
         <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
+        <v>1.18</v>
+      </c>
+      <c r="Z51">
+        <v>3.86</v>
+      </c>
+      <c r="AA51">
+        <v>1.75</v>
+      </c>
+      <c r="AB51">
+        <v>1.97</v>
+      </c>
+      <c r="AC51">
+        <v>2.69</v>
+      </c>
+      <c r="AD51">
+        <v>1.36</v>
+      </c>
+      <c r="AE51">
+        <v>1.11</v>
+      </c>
+      <c r="AF51">
+        <v>1.75</v>
+      </c>
+      <c r="AG51">
+        <v>2</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.2</v>
       </c>
-      <c r="Z51">
-        <v>3.68</v>
-      </c>
-      <c r="AA51">
-        <v>1.8</v>
-      </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>2.88</v>
-      </c>
-      <c r="AD51">
-        <v>1.38</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.61</v>
-      </c>
-      <c r="AG51">
-        <v>2.09</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.3</v>
-      </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
         <v>2.5</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AA52">
+        <v>1.66</v>
+      </c>
+      <c r="AB52">
+        <v>2.05</v>
+      </c>
+      <c r="AC52">
+        <v>2.62</v>
+      </c>
+      <c r="AD52">
+        <v>1.38</v>
+      </c>
+      <c r="AE52">
+        <v>1.12</v>
+      </c>
+      <c r="AF52">
+        <v>1.56</v>
+      </c>
+      <c r="AG52">
+        <v>2.18</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.3</v>
+      </c>
+      <c r="AK52">
         <v>1.75</v>
-      </c>
-      <c r="AB52">
-        <v>1.97</v>
-      </c>
-      <c r="AC52">
-        <v>2.69</v>
-      </c>
-      <c r="AD52">
-        <v>1.36</v>
-      </c>
-      <c r="AE52">
-        <v>1.11</v>
-      </c>
-      <c r="AF52">
-        <v>1.75</v>
-      </c>
-      <c r="AG52">
-        <v>2</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.2</v>
-      </c>
-      <c r="AK52">
-        <v>2.02</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10273,43 +10273,43 @@
         <v>2.7</v>
       </c>
       <c r="U61">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V61">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
         <v>1.07</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y61">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z61">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA61">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AB61">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC61">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AD61">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE61">
         <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG61">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O76">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T76">
-        <v>2.96</v>
+        <v>2.41</v>
       </c>
       <c r="U76">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V76">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W76">
         <v>1.06</v>
       </c>
       <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.4</v>
+      </c>
+      <c r="Z76">
+        <v>2.75</v>
+      </c>
+      <c r="AA76">
+        <v>2.29</v>
+      </c>
+      <c r="AB76">
+        <v>1.57</v>
+      </c>
+      <c r="AC76">
+        <v>4.32</v>
+      </c>
+      <c r="AD76">
+        <v>1.15</v>
+      </c>
+      <c r="AE76">
         <v>1.03</v>
       </c>
-      <c r="Y76">
-        <v>1.24</v>
-      </c>
-      <c r="Z76">
-        <v>3.34</v>
-      </c>
-      <c r="AA76">
-        <v>1.92</v>
-      </c>
-      <c r="AB76">
-        <v>1.9</v>
-      </c>
-      <c r="AC76">
-        <v>3.4</v>
-      </c>
-      <c r="AD76">
-        <v>1.29</v>
-      </c>
-      <c r="AE76">
-        <v>1.07</v>
-      </c>
       <c r="AF76">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q77">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U77">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
+        <v>1.03</v>
+      </c>
+      <c r="Y77">
+        <v>1.24</v>
+      </c>
+      <c r="Z77">
+        <v>3.34</v>
+      </c>
+      <c r="AA77">
+        <v>1.92</v>
+      </c>
+      <c r="AB77">
+        <v>1.9</v>
+      </c>
+      <c r="AC77">
+        <v>3.4</v>
+      </c>
+      <c r="AD77">
+        <v>1.29</v>
+      </c>
+      <c r="AE77">
         <v>1.07</v>
       </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>1.22</v>
-      </c>
-      <c r="Z77">
-        <v>3.58</v>
-      </c>
-      <c r="AA77">
-        <v>1.8</v>
-      </c>
-      <c r="AB77">
-        <v>2</v>
-      </c>
-      <c r="AC77">
-        <v>2.83</v>
-      </c>
-      <c r="AD77">
-        <v>1.33</v>
-      </c>
-      <c r="AE77">
-        <v>1.1</v>
-      </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG77">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="U78">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="V78">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC78">
-        <v>4.32</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
+        <v>2.08</v>
+      </c>
+      <c r="O110">
+        <v>3.35</v>
+      </c>
+      <c r="P110">
+        <v>2.91</v>
+      </c>
+      <c r="Q110">
+        <v>2.8</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>1.3</v>
+      </c>
+      <c r="T110">
+        <v>2.85</v>
+      </c>
+      <c r="U110">
+        <v>2.54</v>
+      </c>
+      <c r="V110">
+        <v>1.41</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.2</v>
+      </c>
+      <c r="Z110">
+        <v>3.68</v>
+      </c>
+      <c r="AA110">
+        <v>1.75</v>
+      </c>
+      <c r="AB110">
+        <v>1.94</v>
+      </c>
+      <c r="AC110">
+        <v>2.78</v>
+      </c>
+      <c r="AD110">
         <v>1.4</v>
       </c>
-      <c r="O110">
-        <v>4.4</v>
-      </c>
-      <c r="P110">
-        <v>5.5</v>
-      </c>
-      <c r="Q110">
-        <v>1.86</v>
-      </c>
-      <c r="R110">
-        <v>2.3</v>
-      </c>
-      <c r="S110">
-        <v>1.25</v>
-      </c>
-      <c r="T110">
-        <v>3.3</v>
-      </c>
-      <c r="U110">
-        <v>2.23</v>
-      </c>
-      <c r="V110">
+      <c r="AE110">
+        <v>1.1</v>
+      </c>
+      <c r="AF110">
+        <v>1.6</v>
+      </c>
+      <c r="AG110">
+        <v>2.18</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.24</v>
+      </c>
+      <c r="AK110">
         <v>1.53</v>
-      </c>
-      <c r="W110">
-        <v>1.12</v>
-      </c>
-      <c r="X110">
-        <v>1.02</v>
-      </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
-      <c r="Z110">
-        <v>4.15</v>
-      </c>
-      <c r="AA110">
-        <v>1.6</v>
-      </c>
-      <c r="AB110">
-        <v>2.15</v>
-      </c>
-      <c r="AC110">
-        <v>2.54</v>
-      </c>
-      <c r="AD110">
-        <v>1.44</v>
-      </c>
-      <c r="AE110">
-        <v>1.2</v>
-      </c>
-      <c r="AF110">
-        <v>1.76</v>
-      </c>
-      <c r="AG110">
-        <v>1.94</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.05</v>
-      </c>
-      <c r="AK110">
-        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,65 +18402,65 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="O111">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>2.91</v>
+        <v>5.5</v>
       </c>
       <c r="Q111">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U111">
+        <v>2.23</v>
+      </c>
+      <c r="V111">
+        <v>1.53</v>
+      </c>
+      <c r="W111">
+        <v>1.12</v>
+      </c>
+      <c r="X111">
+        <v>1.02</v>
+      </c>
+      <c r="Y111">
+        <v>1.16</v>
+      </c>
+      <c r="Z111">
+        <v>4.15</v>
+      </c>
+      <c r="AA111">
+        <v>1.6</v>
+      </c>
+      <c r="AB111">
+        <v>2.15</v>
+      </c>
+      <c r="AC111">
         <v>2.54</v>
       </c>
-      <c r="V111">
-        <v>1.41</v>
-      </c>
-      <c r="W111">
-        <v>1.06</v>
-      </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
+      <c r="AD111">
+        <v>1.44</v>
+      </c>
+      <c r="AE111">
         <v>1.2</v>
       </c>
-      <c r="Z111">
-        <v>3.68</v>
-      </c>
-      <c r="AA111">
-        <v>1.75</v>
-      </c>
-      <c r="AB111">
+      <c r="AF111">
+        <v>1.76</v>
+      </c>
+      <c r="AG111">
         <v>1.94</v>
       </c>
-      <c r="AC111">
-        <v>2.78</v>
-      </c>
-      <c r="AD111">
-        <v>1.4</v>
-      </c>
-      <c r="AE111">
-        <v>1.1</v>
-      </c>
-      <c r="AF111">
-        <v>1.6</v>
-      </c>
-      <c r="AG111">
-        <v>2.18</v>
-      </c>
       <c r="AH111" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK111">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18782,7 +18782,7 @@
         <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AG113">
         <v>1.33</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q4">
+        <v>2.7</v>
+      </c>
+      <c r="R4">
+        <v>1.9</v>
+      </c>
+      <c r="S4">
+        <v>1.48</v>
+      </c>
+      <c r="T4">
         <v>2.42</v>
       </c>
-      <c r="R4">
-        <v>2.21</v>
-      </c>
-      <c r="S4">
-        <v>1.4</v>
-      </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
       <c r="U4">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
         <v>1.07</v>
       </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA4">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AB4">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="O5">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
         <v>1.02</v>
       </c>
-      <c r="X5">
-        <v>1.07</v>
-      </c>
       <c r="Y5">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
+        <v>1.38</v>
+      </c>
+      <c r="T6">
+        <v>2.64</v>
+      </c>
+      <c r="U6">
+        <v>2.88</v>
+      </c>
+      <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1.3</v>
+      </c>
+      <c r="Z6">
+        <v>3.4</v>
+      </c>
+      <c r="AA6">
+        <v>2.04</v>
+      </c>
+      <c r="AB6">
+        <v>1.78</v>
+      </c>
+      <c r="AC6">
+        <v>3.6</v>
+      </c>
+      <c r="AD6">
         <v>1.28</v>
       </c>
-      <c r="T6">
-        <v>3.25</v>
-      </c>
-      <c r="U6">
-        <v>2.4</v>
-      </c>
-      <c r="V6">
-        <v>1.48</v>
-      </c>
-      <c r="W6">
-        <v>1.11</v>
-      </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.19</v>
-      </c>
-      <c r="Z6">
-        <v>3.74</v>
-      </c>
-      <c r="AA6">
-        <v>1.72</v>
-      </c>
-      <c r="AB6">
-        <v>1.96</v>
-      </c>
-      <c r="AC6">
-        <v>2.78</v>
-      </c>
-      <c r="AD6">
-        <v>1.34</v>
-      </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="R7">
+        <v>2.3</v>
+      </c>
+      <c r="S7">
+        <v>1.28</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
+        <v>2.4</v>
+      </c>
+      <c r="V7">
+        <v>1.48</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.19</v>
+      </c>
+      <c r="Z7">
+        <v>3.74</v>
+      </c>
+      <c r="AA7">
+        <v>1.72</v>
+      </c>
+      <c r="AB7">
+        <v>1.96</v>
+      </c>
+      <c r="AC7">
+        <v>2.78</v>
+      </c>
+      <c r="AD7">
+        <v>1.34</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
+        <v>1.6</v>
+      </c>
+      <c r="AG7">
         <v>2.18</v>
       </c>
-      <c r="S7">
-        <v>1.38</v>
-      </c>
-      <c r="T7">
-        <v>2.64</v>
-      </c>
-      <c r="U7">
-        <v>2.88</v>
-      </c>
-      <c r="V7">
-        <v>1.36</v>
-      </c>
-      <c r="W7">
-        <v>1.02</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.51</v>
+      </c>
+      <c r="AK7">
         <v>1.3</v>
-      </c>
-      <c r="Z7">
-        <v>3.4</v>
-      </c>
-      <c r="AA7">
-        <v>2.04</v>
-      </c>
-      <c r="AB7">
-        <v>1.78</v>
-      </c>
-      <c r="AC7">
-        <v>3.6</v>
-      </c>
-      <c r="AD7">
-        <v>1.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.04</v>
-      </c>
-      <c r="AF7">
-        <v>1.75</v>
-      </c>
-      <c r="AG7">
-        <v>1.95</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.4</v>
-      </c>
-      <c r="AK7">
-        <v>1.37</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
         <v>3</v>
@@ -1652,10 +1652,10 @@
         <v>4.2</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
         <v>2.88</v>
@@ -2105,61 +2105,61 @@
         <v>1.4</v>
       </c>
       <c r="O11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>6.13</v>
+        <v>5.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.1</v>
+      </c>
+      <c r="O14">
+        <v>3.2</v>
+      </c>
+      <c r="P14">
+        <v>2.95</v>
+      </c>
+      <c r="Q14">
+        <v>2.75</v>
+      </c>
+      <c r="R14">
         <v>2.15</v>
       </c>
-      <c r="O14">
-        <v>3.1</v>
-      </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA14">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
         <v>2.55</v>
@@ -2926,55 +2926,55 @@
         <v>2.89</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P17">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="Q19">
-        <v>6.45</v>
+        <v>6.27</v>
       </c>
       <c r="R19">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AC19">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AD19">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q20">
-        <v>6.27</v>
+        <v>4.3</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U20">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB20">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AC20">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.54</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P22">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="Q22">
-        <v>4.3</v>
+        <v>6.45</v>
       </c>
       <c r="R22">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S22">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
         <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AB22">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AC22">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AD22">
         <v>1.43</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.75</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>2.37</v>
+      </c>
+      <c r="Q23">
+        <v>3.5</v>
+      </c>
+      <c r="R23">
+        <v>1.91</v>
+      </c>
+      <c r="S23">
+        <v>1.52</v>
+      </c>
+      <c r="T23">
         <v>2.32</v>
       </c>
-      <c r="O23">
-        <v>2.99</v>
-      </c>
-      <c r="P23">
-        <v>2.91</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
+        <v>2.95</v>
+      </c>
+      <c r="P24">
+        <v>3.17</v>
+      </c>
+      <c r="Q24">
+        <v>2.7</v>
+      </c>
+      <c r="R24">
+        <v>2.05</v>
+      </c>
+      <c r="S24">
+        <v>1.42</v>
+      </c>
+      <c r="T24">
+        <v>2.75</v>
+      </c>
+      <c r="U24">
         <v>2.9</v>
       </c>
-      <c r="P24">
-        <v>2.94</v>
-      </c>
-      <c r="Q24">
-        <v>2.88</v>
-      </c>
-      <c r="R24">
-        <v>2</v>
-      </c>
-      <c r="S24">
-        <v>1.44</v>
-      </c>
-      <c r="T24">
-        <v>2.45</v>
-      </c>
-      <c r="U24">
-        <v>3.06</v>
-      </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
         <v>1.03</v>
@@ -4254,31 +4254,31 @@
         <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AC24">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="AD24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE24">
         <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="O25">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O26">
         <v>2.8</v>
       </c>
       <c r="P26">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q26">
         <v>3.3</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O28">
         <v>4.8</v>
@@ -4882,46 +4882,46 @@
         <v>8.5</v>
       </c>
       <c r="Q28">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R28">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.33</v>
+        <v>2.85</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.09</v>
@@ -4930,7 +4930,7 @@
         <v>2.28</v>
       </c>
       <c r="AG28">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
+        <v>2.15</v>
+      </c>
+      <c r="O29">
+        <v>3.25</v>
+      </c>
+      <c r="P29">
+        <v>2.88</v>
+      </c>
+      <c r="Q29">
+        <v>2.77</v>
+      </c>
+      <c r="R29">
         <v>2.1</v>
       </c>
-      <c r="O29">
-        <v>3.1</v>
-      </c>
-      <c r="P29">
-        <v>3.11</v>
-      </c>
-      <c r="Q29">
-        <v>2.83</v>
-      </c>
-      <c r="R29">
-        <v>1.95</v>
-      </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="U29">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB29">
+        <v>1.73</v>
+      </c>
+      <c r="AC29">
+        <v>3.34</v>
+      </c>
+      <c r="AD29">
+        <v>1.24</v>
+      </c>
+      <c r="AE29">
+        <v>1.06</v>
+      </c>
+      <c r="AF29">
+        <v>1.74</v>
+      </c>
+      <c r="AG29">
+        <v>1.91</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.28</v>
+      </c>
+      <c r="AK29">
         <v>1.57</v>
-      </c>
-      <c r="AC29">
-        <v>4</v>
-      </c>
-      <c r="AD29">
-        <v>1.17</v>
-      </c>
-      <c r="AE29">
-        <v>1.03</v>
-      </c>
-      <c r="AF29">
-        <v>1.95</v>
-      </c>
-      <c r="AG29">
-        <v>1.75</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.26</v>
-      </c>
-      <c r="AK29">
-        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,77 +5202,77 @@
         <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="V30">
+        <v>1.32</v>
+      </c>
+      <c r="W30">
+        <v>1.06</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.37</v>
+      </c>
+      <c r="Z30">
+        <v>3.08</v>
+      </c>
+      <c r="AA30">
+        <v>1.98</v>
+      </c>
+      <c r="AB30">
+        <v>1.73</v>
+      </c>
+      <c r="AC30">
+        <v>3.6</v>
+      </c>
+      <c r="AD30">
+        <v>1.22</v>
+      </c>
+      <c r="AE30">
+        <v>1.06</v>
+      </c>
+      <c r="AF30">
+        <v>1.77</v>
+      </c>
+      <c r="AG30">
+        <v>1.91</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.29</v>
       </c>
-      <c r="W30">
-        <v>1.03</v>
-      </c>
-      <c r="X30">
-        <v>1.05</v>
-      </c>
-      <c r="Y30">
-        <v>1.39</v>
-      </c>
-      <c r="Z30">
-        <v>2.74</v>
-      </c>
-      <c r="AA30">
-        <v>2.17</v>
-      </c>
-      <c r="AB30">
-        <v>1.57</v>
-      </c>
-      <c r="AC30">
-        <v>4.15</v>
-      </c>
-      <c r="AD30">
-        <v>1.16</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
-      <c r="AF30">
-        <v>1.95</v>
-      </c>
-      <c r="AG30">
-        <v>1.75</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.3</v>
-      </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P31">
         <v>1.43</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O35">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="P35">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>4.3</v>
       </c>
       <c r="P39">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q39">
         <v>5.25</v>
@@ -6684,7 +6684,7 @@
         <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U39">
         <v>2.05</v>
@@ -6693,7 +6693,7 @@
         <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6702,28 +6702,28 @@
         <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB39">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AC39">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE39">
         <v>1.29</v>
       </c>
       <c r="AF39">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AK39">
         <v>1.15</v>
@@ -6865,13 +6865,13 @@
         <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>6.12</v>
+        <v>6.21</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AC40">
         <v>1.96</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O41">
         <v>3.5</v>
@@ -7001,7 +7001,7 @@
         <v>4.33</v>
       </c>
       <c r="Q41">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R41">
         <v>2.16</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.32</v>
+        <v>4.8</v>
       </c>
       <c r="O44">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P49">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
         <v>3.48</v>
@@ -8314,16 +8314,16 @@
         <v>1.5</v>
       </c>
       <c r="T49">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="U49">
         <v>3.12</v>
       </c>
       <c r="V49">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
         <v>1.05</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q50">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
         <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
+        <v>1.18</v>
+      </c>
+      <c r="Z50">
+        <v>3.86</v>
+      </c>
+      <c r="AA50">
+        <v>1.68</v>
+      </c>
+      <c r="AB50">
+        <v>2.02</v>
+      </c>
+      <c r="AC50">
+        <v>2.69</v>
+      </c>
+      <c r="AD50">
+        <v>1.36</v>
+      </c>
+      <c r="AE50">
+        <v>1.11</v>
+      </c>
+      <c r="AF50">
+        <v>1.75</v>
+      </c>
+      <c r="AG50">
+        <v>2</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.2</v>
       </c>
-      <c r="Z50">
-        <v>3.68</v>
-      </c>
-      <c r="AA50">
-        <v>1.8</v>
-      </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>2.88</v>
-      </c>
-      <c r="AD50">
-        <v>1.38</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.61</v>
-      </c>
-      <c r="AG50">
-        <v>2.09</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.3</v>
-      </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
         <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AA51">
+        <v>1.66</v>
+      </c>
+      <c r="AB51">
+        <v>2.05</v>
+      </c>
+      <c r="AC51">
+        <v>2.62</v>
+      </c>
+      <c r="AD51">
+        <v>1.38</v>
+      </c>
+      <c r="AE51">
+        <v>1.12</v>
+      </c>
+      <c r="AF51">
+        <v>1.56</v>
+      </c>
+      <c r="AG51">
+        <v>2.18</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.3</v>
+      </c>
+      <c r="AK51">
         <v>1.75</v>
-      </c>
-      <c r="AB51">
-        <v>1.97</v>
-      </c>
-      <c r="AC51">
-        <v>2.69</v>
-      </c>
-      <c r="AD51">
-        <v>1.36</v>
-      </c>
-      <c r="AE51">
-        <v>1.11</v>
-      </c>
-      <c r="AF51">
-        <v>1.75</v>
-      </c>
-      <c r="AG51">
-        <v>2</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.2</v>
-      </c>
-      <c r="AK51">
-        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
         <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="O53">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="P53">
         <v>1.2</v>
       </c>
       <c r="Q53">
-        <v>8.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="R53">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W53">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AA53">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB53">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AC53">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AD53">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE53">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG53">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="O59">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>2.89</v>
       </c>
       <c r="V60">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W60">
         <v>1.04</v>
@@ -10131,7 +10131,7 @@
         <v>1.95</v>
       </c>
       <c r="AB60">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC60">
         <v>3.36</v>
@@ -10276,7 +10276,7 @@
         <v>2.99</v>
       </c>
       <c r="V61">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
         <v>1.07</v>
@@ -10744,25 +10744,25 @@
         <v>3.84</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R64">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S64">
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="V64">
         <v>1.57</v>
@@ -10777,7 +10777,7 @@
         <v>1.12</v>
       </c>
       <c r="Z64">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA64">
         <v>1.62</v>
@@ -10789,16 +10789,16 @@
         <v>2.49</v>
       </c>
       <c r="AD64">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE64">
         <v>1.2</v>
       </c>
       <c r="AF64">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -11556,37 +11556,37 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O69">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P69">
         <v>5</v>
       </c>
       <c r="Q69">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R69">
         <v>2.62</v>
       </c>
       <c r="S69">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T69">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U69">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="V69">
         <v>1.76</v>
       </c>
       <c r="W69">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
         <v>1.1</v>
@@ -11595,25 +11595,25 @@
         <v>6.5</v>
       </c>
       <c r="AA69">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB69">
         <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD69">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG69">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11719,31 +11719,31 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="O70">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="P70">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="Q70">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R70">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S70">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T70">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U70">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V70">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W70">
         <v>1.26</v>
@@ -11761,16 +11761,16 @@
         <v>1.25</v>
       </c>
       <c r="AB70">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC70">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD70">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE70">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF70">
         <v>1.33</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="O71">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P71">
         <v>1.78</v>
       </c>
       <c r="Q71">
-        <v>3.49</v>
+        <v>4.23</v>
       </c>
       <c r="R71">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="S71">
         <v>1.16</v>
@@ -11906,7 +11906,7 @@
         <v>2.05</v>
       </c>
       <c r="V71">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
         <v>2.87</v>
       </c>
       <c r="Q72">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="R72">
         <v>2.42</v>
@@ -12118,7 +12118,7 @@
         <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="O73">
         <v>3.55</v>
       </c>
       <c r="P73">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q73">
         <v>3.45</v>
       </c>
       <c r="R73">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="S73">
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
         <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W73">
         <v>1.18</v>
@@ -12256,7 +12256,7 @@
         <v>2.1</v>
       </c>
       <c r="AD73">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE73">
         <v>1.28</v>
@@ -12281,7 +12281,7 @@
         <v>1.18</v>
       </c>
       <c r="AK73">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12537,16 +12537,16 @@
         <v>1.44</v>
       </c>
       <c r="O75">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q75">
         <v>1.81</v>
       </c>
       <c r="R75">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="S75">
         <v>1.22</v>
@@ -12579,10 +12579,10 @@
         <v>2.88</v>
       </c>
       <c r="AC75">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD75">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE75">
         <v>1.28</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="R79">
         <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U79">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC79">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD79">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF79">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="O80">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q80">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="R80">
         <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U80">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z80">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA80">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB80">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC80">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD80">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE80">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG80">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14167,16 +14167,16 @@
         <v>1.25</v>
       </c>
       <c r="O85">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="P85">
         <v>8.5</v>
       </c>
       <c r="Q85">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R85">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="S85">
         <v>1.11</v>
@@ -14185,10 +14185,10 @@
         <v>6</v>
       </c>
       <c r="U85">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V85">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="W85">
         <v>1.4</v>
@@ -14203,19 +14203,19 @@
         <v>15</v>
       </c>
       <c r="AA85">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AB85">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AC85">
         <v>1.36</v>
       </c>
       <c r="AD85">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE85">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF85">
         <v>1.36</v>
@@ -14237,7 +14237,7 @@
         <v>1.1</v>
       </c>
       <c r="AK85">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14400,7 +14400,7 @@
         <v>1.09</v>
       </c>
       <c r="AK86">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="O87">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>3.19</v>
+        <v>3.9</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
       </c>
       <c r="R87">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="S87">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>5.05</v>
+        <v>3.78</v>
       </c>
       <c r="U87">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="V87">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="W87">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>10</v>
+        <v>5.55</v>
       </c>
       <c r="AA87">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AB87">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AC87">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AD87">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE87">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AF87">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AG87">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="P88">
+        <v>6.5</v>
+      </c>
+      <c r="Q88">
+        <v>1.73</v>
+      </c>
+      <c r="R88">
+        <v>2.56</v>
+      </c>
+      <c r="S88">
+        <v>1.2</v>
+      </c>
+      <c r="T88">
         <v>4</v>
       </c>
-      <c r="Q88">
-        <v>2.11</v>
-      </c>
-      <c r="R88">
-        <v>2.34</v>
-      </c>
-      <c r="S88">
-        <v>1.22</v>
-      </c>
-      <c r="T88">
-        <v>3.78</v>
-      </c>
       <c r="U88">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="V88">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="W88">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z88">
-        <v>5.55</v>
+        <v>6.17</v>
       </c>
       <c r="AA88">
         <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC88">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AD88">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE88">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF88">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG88">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK88">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,22 +14816,22 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="O89">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="Q89">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="R89">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T89">
         <v>4</v>
@@ -14840,40 +14840,40 @@
         <v>2.02</v>
       </c>
       <c r="V89">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.07</v>
       </c>
       <c r="Z89">
-        <v>6.08</v>
+        <v>5.8</v>
       </c>
       <c r="AA89">
         <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC89">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD89">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE89">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG89">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK89">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O90">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>4.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q90">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="R90">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="S90">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U90">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V90">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W90">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AA90">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AB90">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC90">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD90">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE90">
+        <v>1.27</v>
+      </c>
+      <c r="AF90">
+        <v>1.34</v>
+      </c>
+      <c r="AG90">
+        <v>2.99</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.25</v>
       </c>
-      <c r="AF90">
-        <v>1.48</v>
-      </c>
-      <c r="AG90">
-        <v>2.47</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.17</v>
-      </c>
       <c r="AK90">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="P91">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="R91">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="U91">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="V91">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z91">
-        <v>5.68</v>
+        <v>8</v>
       </c>
       <c r="AA91">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AB91">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AD91">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AE91">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AF91">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AG91">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.6</v>
+        <v>2.85</v>
       </c>
       <c r="O92">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q92">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="R92">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S92">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="U92">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="V92">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="W92">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z92">
-        <v>8</v>
+        <v>6.03</v>
       </c>
       <c r="AA92">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AB92">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AC92">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AD92">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="AE92">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AF92">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG92">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15483,19 +15483,19 @@
         <v>2.51</v>
       </c>
       <c r="S93">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T93">
         <v>4.85</v>
       </c>
       <c r="U93">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V93">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W93">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="O94">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P94">
+        <v>3.19</v>
+      </c>
+      <c r="Q94">
         <v>2.1</v>
       </c>
-      <c r="Q94">
-        <v>3.34</v>
-      </c>
       <c r="R94">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S94">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T94">
-        <v>3.9</v>
+        <v>5.05</v>
       </c>
       <c r="U94">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="V94">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="W94">
+        <v>1.3</v>
+      </c>
+      <c r="X94">
+        <v>1.01</v>
+      </c>
+      <c r="Y94">
+        <v>1.05</v>
+      </c>
+      <c r="Z94">
+        <v>10</v>
+      </c>
+      <c r="AA94">
         <v>1.17</v>
       </c>
-      <c r="X94">
-        <v>1.02</v>
-      </c>
-      <c r="Y94">
-        <v>1.1</v>
-      </c>
-      <c r="Z94">
-        <v>5.55</v>
-      </c>
-      <c r="AA94">
-        <v>1.47</v>
-      </c>
       <c r="AB94">
-        <v>2.61</v>
+        <v>4</v>
       </c>
       <c r="AC94">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AD94">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="AE94">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="AF94">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG94">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15800,13 +15800,13 @@
         <v>3.42</v>
       </c>
       <c r="P95">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
       </c>
       <c r="R95">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
         <v>1.3</v>
@@ -15815,7 +15815,7 @@
         <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V95">
         <v>1.53</v>
@@ -15833,10 +15833,10 @@
         <v>3.98</v>
       </c>
       <c r="AA95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB95">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AC95">
         <v>2.49</v>
@@ -15845,7 +15845,7 @@
         <v>1.48</v>
       </c>
       <c r="AE95">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF95">
         <v>1.55</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="O96">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P96">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q96">
-        <v>4.14</v>
+        <v>5.05</v>
       </c>
       <c r="R96">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="S96">
         <v>1.18</v>
@@ -16126,13 +16126,13 @@
         <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q97">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16150,7 +16150,7 @@
         <v>1.15</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
         <v>1.15</v>
@@ -16292,10 +16292,10 @@
         <v>2.56</v>
       </c>
       <c r="Q98">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R98">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
         <v>1.36</v>
@@ -16316,22 +16316,22 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z98">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="AA98">
         <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC98">
         <v>3.08</v>
       </c>
       <c r="AD98">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE98">
         <v>1.1</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O102">
         <v>4.4</v>
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O103">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="P103">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="Q103">
         <v>1.75</v>
       </c>
       <c r="R103">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="S103">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="V103">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W103">
         <v>1.2</v>
@@ -17131,31 +17131,31 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z103">
         <v>7</v>
       </c>
       <c r="AA103">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB103">
         <v>3</v>
       </c>
       <c r="AC103">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AD103">
         <v>1.76</v>
       </c>
       <c r="AE103">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF103">
         <v>1.75</v>
       </c>
       <c r="AG103">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.08</v>
       </c>
       <c r="AK103">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="O107">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P107">
-        <v>4.87</v>
+        <v>3.8</v>
       </c>
       <c r="Q107">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="R107">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="T107">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="U107">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="V107">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>5.45</v>
+        <v>4.81</v>
       </c>
       <c r="AA107">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC107">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AD107">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE107">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.17</v>
       </c>
       <c r="AK107">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="O108">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P108">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q108">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="V108">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W108">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z108">
-        <v>4.81</v>
+        <v>3.68</v>
       </c>
       <c r="AA108">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB108">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="AC108">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AD108">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG108">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="O109">
-        <v>7.7</v>
+        <v>4.05</v>
       </c>
       <c r="P109">
-        <v>10.85</v>
+        <v>4.87</v>
       </c>
       <c r="Q109">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="R109">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="S109">
+        <v>1.21</v>
+      </c>
+      <c r="T109">
+        <v>3.58</v>
+      </c>
+      <c r="U109">
+        <v>2.13</v>
+      </c>
+      <c r="V109">
+        <v>1.68</v>
+      </c>
+      <c r="W109">
         <v>1.12</v>
-      </c>
-      <c r="T109">
-        <v>4.65</v>
-      </c>
-      <c r="U109">
-        <v>1.79</v>
-      </c>
-      <c r="V109">
-        <v>1.99</v>
-      </c>
-      <c r="W109">
-        <v>1.29</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Z109">
-        <v>7.7</v>
+        <v>5.45</v>
       </c>
       <c r="AA109">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AB109">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="AC109">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD109">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="AE109">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AF109">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG109">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,65 +18239,65 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="O110">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P110">
-        <v>2.91</v>
+        <v>5.5</v>
       </c>
       <c r="Q110">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U110">
+        <v>2.23</v>
+      </c>
+      <c r="V110">
+        <v>1.53</v>
+      </c>
+      <c r="W110">
+        <v>1.12</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
+        <v>1.16</v>
+      </c>
+      <c r="Z110">
+        <v>4.15</v>
+      </c>
+      <c r="AA110">
+        <v>1.6</v>
+      </c>
+      <c r="AB110">
+        <v>2.15</v>
+      </c>
+      <c r="AC110">
         <v>2.54</v>
       </c>
-      <c r="V110">
-        <v>1.41</v>
-      </c>
-      <c r="W110">
-        <v>1.06</v>
-      </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
-      <c r="Y110">
+      <c r="AD110">
+        <v>1.44</v>
+      </c>
+      <c r="AE110">
         <v>1.2</v>
       </c>
-      <c r="Z110">
-        <v>3.68</v>
-      </c>
-      <c r="AA110">
-        <v>1.75</v>
-      </c>
-      <c r="AB110">
+      <c r="AF110">
+        <v>1.76</v>
+      </c>
+      <c r="AG110">
         <v>1.94</v>
       </c>
-      <c r="AC110">
-        <v>2.78</v>
-      </c>
-      <c r="AD110">
-        <v>1.4</v>
-      </c>
-      <c r="AE110">
-        <v>1.1</v>
-      </c>
-      <c r="AF110">
-        <v>1.6</v>
-      </c>
-      <c r="AG110">
-        <v>2.18</v>
-      </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK110">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
+        <v>1.13</v>
+      </c>
+      <c r="O111">
+        <v>7.7</v>
+      </c>
+      <c r="P111">
+        <v>10.85</v>
+      </c>
+      <c r="Q111">
         <v>1.4</v>
       </c>
-      <c r="O111">
-        <v>4.4</v>
-      </c>
-      <c r="P111">
+      <c r="R111">
+        <v>3.24</v>
+      </c>
+      <c r="S111">
+        <v>1.12</v>
+      </c>
+      <c r="T111">
+        <v>4.65</v>
+      </c>
+      <c r="U111">
+        <v>1.79</v>
+      </c>
+      <c r="V111">
+        <v>1.99</v>
+      </c>
+      <c r="W111">
+        <v>1.29</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.02</v>
+      </c>
+      <c r="Z111">
+        <v>7.7</v>
+      </c>
+      <c r="AA111">
+        <v>1.25</v>
+      </c>
+      <c r="AB111">
+        <v>3.8</v>
+      </c>
+      <c r="AC111">
+        <v>1.65</v>
+      </c>
+      <c r="AD111">
+        <v>2.19</v>
+      </c>
+      <c r="AE111">
+        <v>1.46</v>
+      </c>
+      <c r="AF111">
+        <v>1.77</v>
+      </c>
+      <c r="AG111">
+        <v>1.92</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.02</v>
+      </c>
+      <c r="AK111">
         <v>5.5</v>
-      </c>
-      <c r="Q111">
-        <v>1.86</v>
-      </c>
-      <c r="R111">
-        <v>2.3</v>
-      </c>
-      <c r="S111">
-        <v>1.25</v>
-      </c>
-      <c r="T111">
-        <v>3.3</v>
-      </c>
-      <c r="U111">
-        <v>2.23</v>
-      </c>
-      <c r="V111">
-        <v>1.53</v>
-      </c>
-      <c r="W111">
-        <v>1.12</v>
-      </c>
-      <c r="X111">
-        <v>1.02</v>
-      </c>
-      <c r="Y111">
-        <v>1.16</v>
-      </c>
-      <c r="Z111">
-        <v>4.15</v>
-      </c>
-      <c r="AA111">
-        <v>1.6</v>
-      </c>
-      <c r="AB111">
-        <v>2.15</v>
-      </c>
-      <c r="AC111">
-        <v>2.54</v>
-      </c>
-      <c r="AD111">
-        <v>1.44</v>
-      </c>
-      <c r="AE111">
-        <v>1.2</v>
-      </c>
-      <c r="AF111">
-        <v>1.76</v>
-      </c>
-      <c r="AG111">
-        <v>1.94</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.05</v>
-      </c>
-      <c r="AK111">
-        <v>2.52</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18568,10 +18568,10 @@
         <v>1.85</v>
       </c>
       <c r="O112">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="P112">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="Q112">
         <v>2.29</v>
@@ -18604,13 +18604,13 @@
         <v>4.3</v>
       </c>
       <c r="AA112">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB112">
         <v>2.2</v>
       </c>
       <c r="AC112">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AD112">
         <v>1.47</v>
@@ -18622,7 +18622,7 @@
         <v>1.59</v>
       </c>
       <c r="AG112">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O118">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P118">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q118">
         <v>3.92</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O119">
         <v>2.8</v>
@@ -19763,7 +19763,7 @@
         <v>2.15</v>
       </c>
       <c r="AG119">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
         <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -650,7 +650,7 @@
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>3.02</v>
@@ -686,7 +686,7 @@
         <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>1.61</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,27 +787,27 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="O3">
+        <v>3.5</v>
+      </c>
+      <c r="P3">
         <v>3.4</v>
       </c>
-      <c r="P3">
-        <v>3.05</v>
-      </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -819,13 +819,13 @@
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V3">
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,19 +834,19 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
         <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC3">
         <v>2.69</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE3">
         <v>1.13</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -868,37 +868,37 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
         <v>2.9</v>
@@ -970,7 +970,7 @@
         <v>3.25</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
         <v>1.9</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
         <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1145,7 +1145,7 @@
         <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="V5">
         <v>1.36</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.3</v>
+      </c>
+      <c r="T6">
+        <v>3.2</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+      <c r="V6">
+        <v>1.48</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.19</v>
+      </c>
+      <c r="Z6">
+        <v>3.74</v>
+      </c>
+      <c r="AA6">
+        <v>1.72</v>
+      </c>
+      <c r="AB6">
+        <v>1.96</v>
+      </c>
+      <c r="AC6">
+        <v>2.78</v>
+      </c>
+      <c r="AD6">
+        <v>1.34</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>1.6</v>
+      </c>
+      <c r="AG6">
         <v>2.18</v>
       </c>
-      <c r="S6">
-        <v>1.38</v>
-      </c>
-      <c r="T6">
-        <v>2.64</v>
-      </c>
-      <c r="U6">
-        <v>2.88</v>
-      </c>
-      <c r="V6">
-        <v>1.36</v>
-      </c>
-      <c r="W6">
-        <v>1.02</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.51</v>
+      </c>
+      <c r="AK6">
         <v>1.3</v>
-      </c>
-      <c r="Z6">
-        <v>3.4</v>
-      </c>
-      <c r="AA6">
-        <v>2.04</v>
-      </c>
-      <c r="AB6">
-        <v>1.78</v>
-      </c>
-      <c r="AC6">
-        <v>3.6</v>
-      </c>
-      <c r="AD6">
-        <v>1.28</v>
-      </c>
-      <c r="AE6">
-        <v>1.04</v>
-      </c>
-      <c r="AF6">
-        <v>1.75</v>
-      </c>
-      <c r="AG6">
-        <v>1.95</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.4</v>
-      </c>
-      <c r="AK6">
-        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
+        <v>3.05</v>
+      </c>
+      <c r="P7">
+        <v>2.45</v>
+      </c>
+      <c r="Q7">
+        <v>3.1</v>
+      </c>
+      <c r="R7">
+        <v>2.18</v>
+      </c>
+      <c r="S7">
+        <v>1.38</v>
+      </c>
+      <c r="T7">
+        <v>2.88</v>
+      </c>
+      <c r="U7">
+        <v>2.88</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.02</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
         <v>3.3</v>
       </c>
-      <c r="P7">
-        <v>2.06</v>
-      </c>
-      <c r="Q7">
-        <v>3.17</v>
-      </c>
-      <c r="R7">
-        <v>2.3</v>
-      </c>
-      <c r="S7">
-        <v>1.28</v>
-      </c>
-      <c r="T7">
-        <v>3.25</v>
-      </c>
-      <c r="U7">
-        <v>2.4</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.19</v>
-      </c>
-      <c r="Z7">
-        <v>3.74</v>
-      </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AB7">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>2.78</v>
+        <v>3.62</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
@@ -1794,13 +1794,13 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W9">
         <v>1.15</v>
@@ -1812,16 +1812,16 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="AA9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
         <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD9">
         <v>1.49</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
         <v>3.48</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q10">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
         <v>2.2</v>
@@ -1984,7 +1984,7 @@
         <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD10">
         <v>1.3</v>
@@ -2268,10 +2268,10 @@
         <v>2.33</v>
       </c>
       <c r="O12">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q12">
         <v>3.3</v>
@@ -2310,7 +2310,7 @@
         <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
         <v>1.45</v>
@@ -2322,7 +2322,7 @@
         <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.45</v>
+        <v>6.6</v>
       </c>
       <c r="O13">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="P13">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S13">
         <v>1.17</v>
       </c>
       <c r="T13">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V13">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W13">
         <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z13">
         <v>6.5</v>
       </c>
       <c r="AA13">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB13">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AC13">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AD13">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AE13">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2769,10 +2769,10 @@
         <v>2.45</v>
       </c>
       <c r="S15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U15">
         <v>1.95</v>
@@ -2781,7 +2781,7 @@
         <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,7 +2790,7 @@
         <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>6.78</v>
+        <v>6.91</v>
       </c>
       <c r="AA15">
         <v>1.31</v>
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
         <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="U18">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="V18">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
+        <v>1.05</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1.17</v>
+      </c>
+      <c r="Z18">
+        <v>2.9</v>
+      </c>
+      <c r="AA18">
+        <v>1.8</v>
+      </c>
+      <c r="AB18">
+        <v>1.76</v>
+      </c>
+      <c r="AC18">
+        <v>2.7</v>
+      </c>
+      <c r="AD18">
+        <v>1.29</v>
+      </c>
+      <c r="AE18">
+        <v>1.1</v>
+      </c>
+      <c r="AF18">
+        <v>1.47</v>
+      </c>
+      <c r="AG18">
+        <v>1.93</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.09</v>
       </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.22</v>
-      </c>
-      <c r="Z18">
-        <v>3.5</v>
-      </c>
-      <c r="AA18">
-        <v>1.85</v>
-      </c>
-      <c r="AB18">
-        <v>1.95</v>
-      </c>
-      <c r="AC18">
-        <v>2.88</v>
-      </c>
-      <c r="AD18">
-        <v>1.32</v>
-      </c>
-      <c r="AE18">
-        <v>1.09</v>
-      </c>
-      <c r="AF18">
-        <v>1.61</v>
-      </c>
-      <c r="AG18">
-        <v>2.09</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.24</v>
-      </c>
       <c r="AK18">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="Q19">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="AA19">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB19">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AD19">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG19">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
         <v>1.05</v>
@@ -3572,31 +3572,31 @@
         <v>3.54</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q20">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
         <v>3.18</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="V20">
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3608,22 +3608,22 @@
         <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AC20">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>3.42</v>
+        <v>2.63</v>
       </c>
       <c r="AA21">
+        <v>1.9</v>
+      </c>
+      <c r="AB21">
         <v>1.8</v>
       </c>
-      <c r="AB21">
-        <v>1.87</v>
-      </c>
       <c r="AC21">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
+        <v>1.07</v>
+      </c>
+      <c r="AF21">
+        <v>1.62</v>
+      </c>
+      <c r="AG21">
+        <v>1.86</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.09</v>
       </c>
-      <c r="AF21">
-        <v>1.7</v>
-      </c>
-      <c r="AG21">
-        <v>1.96</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.22</v>
-      </c>
       <c r="AK21">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>4.5</v>
       </c>
       <c r="P22">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q22">
         <v>6.45</v>
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="O27">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="P27">
-        <v>8.68</v>
+        <v>7.6</v>
       </c>
       <c r="Q27">
         <v>1.73</v>
@@ -4725,13 +4725,13 @@
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4752,7 +4752,7 @@
         <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC27">
         <v>3.06</v>
@@ -4764,10 +4764,10 @@
         <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AG27">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
         <v>3.42</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O32">
-        <v>5.95</v>
+        <v>6.2</v>
       </c>
       <c r="P32">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q32">
         <v>1.57</v>
       </c>
       <c r="R32">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S32">
         <v>1.22</v>
@@ -5546,7 +5546,7 @@
         <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V32">
         <v>1.64</v>
@@ -5564,25 +5564,25 @@
         <v>6.22</v>
       </c>
       <c r="AA32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB32">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC32">
         <v>2.09</v>
       </c>
       <c r="AD32">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE32">
         <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG32">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,52 +5688,52 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
         <v>2.95</v>
       </c>
       <c r="P33">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="Q33">
+        <v>3.1</v>
+      </c>
+      <c r="R33">
+        <v>1.91</v>
+      </c>
+      <c r="S33">
+        <v>1.4</v>
+      </c>
+      <c r="T33">
+        <v>2.75</v>
+      </c>
+      <c r="U33">
         <v>3.2</v>
-      </c>
-      <c r="R33">
-        <v>1.93</v>
-      </c>
-      <c r="S33">
-        <v>1.43</v>
-      </c>
-      <c r="T33">
-        <v>2.48</v>
-      </c>
-      <c r="U33">
-        <v>2.99</v>
       </c>
       <c r="V33">
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AA33">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD33">
         <v>1.21</v>
@@ -5742,10 +5742,10 @@
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,16 +5860,16 @@
         <v>2.74</v>
       </c>
       <c r="Q34">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="R34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T34">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U34">
         <v>3.26</v>
@@ -5884,19 +5884,19 @@
         <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z34">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AA34">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB34">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC34">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AD34">
         <v>1.17</v>
@@ -5905,10 +5905,10 @@
         <v>1</v>
       </c>
       <c r="AF34">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG34">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
         <v>2.38</v>
@@ -6222,7 +6222,7 @@
         <v>1.9</v>
       </c>
       <c r="AC36">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="AD36">
         <v>1.27</v>
@@ -6361,7 +6361,7 @@
         <v>2.8</v>
       </c>
       <c r="U37">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V37">
         <v>1.4</v>
@@ -6379,7 +6379,7 @@
         <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB37">
         <v>1.83</v>
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O38">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>4.66</v>
+        <v>4.4</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6545,7 +6545,7 @@
         <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC38">
         <v>2.82</v>
@@ -6557,10 +6557,10 @@
         <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
         <v>2.15</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q41">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="R41">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="U41">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC41">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7644,16 +7644,16 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O45">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P45">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="Q45">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R45">
         <v>1.97</v>
@@ -7662,7 +7662,7 @@
         <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
         <v>3.2</v>
@@ -7680,7 +7680,7 @@
         <v>1.36</v>
       </c>
       <c r="Z45">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA45">
         <v>2.25</v>
@@ -7701,7 +7701,7 @@
         <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q46">
-        <v>8.68</v>
+        <v>8.5</v>
       </c>
       <c r="R46">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.8</v>
@@ -7837,34 +7837,34 @@
         <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA46">
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC46">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE46">
         <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG46">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="Q47">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="R47">
         <v>2.3</v>
@@ -8142,7 +8142,7 @@
         <v>4.65</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R48">
         <v>2.21</v>
@@ -8190,7 +8190,7 @@
         <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
         <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
+        <v>1.56</v>
+      </c>
+      <c r="AG50">
+        <v>2.18</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.3</v>
+      </c>
+      <c r="AK50">
         <v>1.75</v>
-      </c>
-      <c r="AG50">
-        <v>2</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.2</v>
-      </c>
-      <c r="AK50">
-        <v>2.02</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AA51">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AD51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O54">
         <v>3.38</v>
@@ -9135,7 +9135,7 @@
         <v>3.22</v>
       </c>
       <c r="V54">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W54">
         <v>1.01</v>
@@ -9144,13 +9144,13 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Z54">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AA54">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB54">
         <v>1.65</v>
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
         <v>2.1</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
         <v>1.84</v>
@@ -9455,7 +9455,7 @@
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
         <v>2.25</v>
@@ -9476,10 +9476,10 @@
         <v>5</v>
       </c>
       <c r="AA56">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC56">
         <v>2.33</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>1.24</v>
@@ -9609,7 +9609,7 @@
         <v>2.4</v>
       </c>
       <c r="Q57">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="R57">
         <v>2.38</v>
@@ -9633,16 +9633,16 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z57">
         <v>5.05</v>
       </c>
       <c r="AA57">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC57">
         <v>2.22</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
         <v>1.44</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O58">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P58">
         <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
         <v>2.27</v>
@@ -9793,13 +9793,13 @@
         <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA58">
         <v>1.6</v>
@@ -9808,7 +9808,7 @@
         <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
         <v>1.52</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P61">
         <v>6.77</v>
       </c>
       <c r="Q61">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S61">
         <v>1.4</v>
@@ -10306,10 +10306,10 @@
         <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10433,7 +10433,7 @@
         <v>1.22</v>
       </c>
       <c r="T62">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U62">
         <v>2.05</v>
@@ -10457,7 +10457,7 @@
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC62">
         <v>2.22</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK62">
         <v>3.52</v>
@@ -10581,19 +10581,19 @@
         <v>1.85</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q63">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R63">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T63">
         <v>2.6</v>
@@ -10617,13 +10617,13 @@
         <v>3</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB63">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC63">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD63">
         <v>1.27</v>
@@ -10786,7 +10786,7 @@
         <v>2.3</v>
       </c>
       <c r="AC64">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD64">
         <v>1.53</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q65">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R65">
         <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U65">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V65">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z65">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="AA65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB65">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AC65">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AD65">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE65">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG65">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AK65">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11085,7 +11085,7 @@
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
         <v>2.25</v>
@@ -11103,13 +11103,13 @@
         <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>4.69</v>
+        <v>5.08</v>
       </c>
       <c r="AA66">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC66">
         <v>2.41</v>
@@ -11118,7 +11118,7 @@
         <v>1.45</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
         <v>1.57</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
+        <v>2.68</v>
+      </c>
+      <c r="Q67">
+        <v>3.12</v>
+      </c>
+      <c r="R67">
         <v>2.1</v>
       </c>
-      <c r="Q67">
-        <v>4.05</v>
-      </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T67">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U67">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="V67">
         <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z67">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA67">
         <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC67">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD67">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
         <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK67">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O68">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="Q68">
-        <v>3.12</v>
+        <v>3.84</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="U68">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.28</v>
+      </c>
+      <c r="Z68">
+        <v>3.08</v>
+      </c>
+      <c r="AA68">
+        <v>2</v>
+      </c>
+      <c r="AB68">
+        <v>1.8</v>
+      </c>
+      <c r="AC68">
+        <v>3.53</v>
+      </c>
+      <c r="AD68">
+        <v>1.24</v>
+      </c>
+      <c r="AE68">
         <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.31</v>
-      </c>
-      <c r="Z68">
-        <v>2.92</v>
-      </c>
-      <c r="AA68">
-        <v>2.05</v>
-      </c>
-      <c r="AB68">
-        <v>1.66</v>
-      </c>
-      <c r="AC68">
-        <v>3.58</v>
-      </c>
-      <c r="AD68">
-        <v>1.21</v>
-      </c>
-      <c r="AE68">
-        <v>1.03</v>
       </c>
       <c r="AF68">
         <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>1.78</v>
+        <v>2.87</v>
       </c>
       <c r="Q71">
-        <v>4.23</v>
+        <v>2.52</v>
       </c>
       <c r="R71">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S71">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T71">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V71">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -11915,10 +11915,10 @@
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA71">
         <v>1.36</v>
@@ -11933,13 +11933,13 @@
         <v>1.68</v>
       </c>
       <c r="AE71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AG71">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,34 +12045,34 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.11</v>
+        <v>2.81</v>
       </c>
       <c r="O72">
+        <v>3.55</v>
+      </c>
+      <c r="P72">
+        <v>2</v>
+      </c>
+      <c r="Q72">
+        <v>3.45</v>
+      </c>
+      <c r="R72">
+        <v>2.39</v>
+      </c>
+      <c r="S72">
+        <v>1.22</v>
+      </c>
+      <c r="T72">
         <v>3.8</v>
       </c>
-      <c r="P72">
-        <v>2.87</v>
-      </c>
-      <c r="Q72">
-        <v>2.52</v>
-      </c>
-      <c r="R72">
-        <v>2.42</v>
-      </c>
-      <c r="S72">
-        <v>1.17</v>
-      </c>
-      <c r="T72">
-        <v>4.5</v>
-      </c>
       <c r="U72">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12081,28 +12081,28 @@
         <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA72">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB72">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AC72">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
         <v>1.68</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF72">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK72">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,58 +12208,58 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.81</v>
+        <v>3.82</v>
       </c>
       <c r="O73">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P73">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Q73">
-        <v>3.45</v>
+        <v>4.23</v>
       </c>
       <c r="R73">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="S73">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T73">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U73">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V73">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z73">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA73">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB73">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD73">
         <v>1.68</v>
       </c>
       <c r="AE73">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF73">
         <v>1.41</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
+        <v>1.16</v>
+      </c>
+      <c r="AK73">
         <v>1.18</v>
-      </c>
-      <c r="AK73">
-        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12407,10 +12407,10 @@
         <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AA74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB74">
         <v>1.62</v>
@@ -12425,7 +12425,7 @@
         <v>1.02</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG74">
         <v>1.78</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="U76">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="V76">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA76">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>4.32</v>
+        <v>2.83</v>
       </c>
       <c r="AD76">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE76">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK76">
         <v>1.62</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P77">
-        <v>3.15</v>
+        <v>5.25</v>
       </c>
       <c r="Q77">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T77">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="V77">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA77">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC77">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD77">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG77">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.72</v>
+        <v>2.29</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q78">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U78">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
+        <v>1.06</v>
+      </c>
+      <c r="X78">
+        <v>1.03</v>
+      </c>
+      <c r="Y78">
+        <v>1.24</v>
+      </c>
+      <c r="Z78">
+        <v>3.34</v>
+      </c>
+      <c r="AA78">
+        <v>1.92</v>
+      </c>
+      <c r="AB78">
+        <v>1.9</v>
+      </c>
+      <c r="AC78">
+        <v>3.2</v>
+      </c>
+      <c r="AD78">
+        <v>1.26</v>
+      </c>
+      <c r="AE78">
         <v>1.07</v>
       </c>
-      <c r="X78">
-        <v>1</v>
-      </c>
-      <c r="Y78">
-        <v>1.22</v>
-      </c>
-      <c r="Z78">
-        <v>3.58</v>
-      </c>
-      <c r="AA78">
-        <v>1.8</v>
-      </c>
-      <c r="AB78">
-        <v>2</v>
-      </c>
-      <c r="AC78">
-        <v>2.83</v>
-      </c>
-      <c r="AD78">
-        <v>1.33</v>
-      </c>
-      <c r="AE78">
-        <v>1.1</v>
-      </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG78">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="T79">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="U79">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="AA79">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AB79">
+        <v>1.57</v>
+      </c>
+      <c r="AC79">
+        <v>4.38</v>
+      </c>
+      <c r="AD79">
+        <v>1.15</v>
+      </c>
+      <c r="AE79">
+        <v>1.03</v>
+      </c>
+      <c r="AF79">
         <v>1.95</v>
       </c>
-      <c r="AC79">
-        <v>3.1</v>
-      </c>
-      <c r="AD79">
+      <c r="AG79">
+        <v>1.75</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.33</v>
       </c>
-      <c r="AE79">
-        <v>1.08</v>
-      </c>
-      <c r="AF79">
-        <v>1.65</v>
-      </c>
-      <c r="AG79">
-        <v>2.08</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.25</v>
-      </c>
       <c r="AK79">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="O80">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q80">
+        <v>2.5</v>
+      </c>
+      <c r="R80">
         <v>2.2</v>
       </c>
-      <c r="R80">
-        <v>2.15</v>
-      </c>
       <c r="S80">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U80">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB80">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AC80">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD80">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="O82">
-        <v>4.98</v>
+        <v>4.33</v>
       </c>
       <c r="P82">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="Q82">
         <v>1.91</v>
@@ -13699,34 +13699,34 @@
         <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
         <v>1.12</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.16</v>
       </c>
       <c r="Z82">
-        <v>5.08</v>
+        <v>4.75</v>
       </c>
       <c r="AA82">
         <v>1.54</v>
       </c>
       <c r="AB82">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC82">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD82">
         <v>1.56</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
         <v>1.62</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="O83">
-        <v>4.52</v>
+        <v>3.65</v>
       </c>
       <c r="P83">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q83">
         <v>3.5</v>
       </c>
       <c r="R83">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13862,7 +13862,7 @@
         <v>2.04</v>
       </c>
       <c r="V83">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W83">
         <v>1.15</v>
@@ -13871,16 +13871,16 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
       <c r="AA83">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB83">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC83">
         <v>2.12</v>
@@ -14001,49 +14001,49 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O84">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="P84">
+        <v>1.66</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
         <v>1.85</v>
       </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>0</v>
-      </c>
-      <c r="Z84">
-        <v>0</v>
-      </c>
-      <c r="AA84">
+      <c r="AB84">
         <v>1.95</v>
-      </c>
-      <c r="AB84">
-        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86">
@@ -14330,61 +14330,61 @@
         <v>1.35</v>
       </c>
       <c r="O86">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="P86">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q86">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R86">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="S86">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V86">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W86">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z86">
-        <v>6.9</v>
+        <v>6.17</v>
       </c>
       <c r="AA86">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB86">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC86">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AD86">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AE86">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG86">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK86">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
-        <v>3.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q87">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="R87">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U87">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="V87">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="W87">
         <v>1.18</v>
@@ -14523,32 +14523,32 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z87">
-        <v>5.55</v>
+        <v>6.03</v>
       </c>
       <c r="AA87">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB87">
+        <v>2.76</v>
+      </c>
+      <c r="AC87">
+        <v>2.02</v>
+      </c>
+      <c r="AD87">
+        <v>1.71</v>
+      </c>
+      <c r="AE87">
+        <v>1.32</v>
+      </c>
+      <c r="AF87">
+        <v>1.36</v>
+      </c>
+      <c r="AG87">
         <v>2.88</v>
       </c>
-      <c r="AC87">
-        <v>2.16</v>
-      </c>
-      <c r="AD87">
-        <v>1.67</v>
-      </c>
-      <c r="AE87">
-        <v>1.23</v>
-      </c>
-      <c r="AF87">
-        <v>1.44</v>
-      </c>
-      <c r="AG87">
-        <v>2.56</v>
-      </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK87">
-        <v>2.11</v>
+        <v>1.37</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="O88">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>1.73</v>
+        <v>2.83</v>
       </c>
       <c r="R88">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="U88">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V88">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z88">
-        <v>6.17</v>
+        <v>7.4</v>
       </c>
       <c r="AA88">
+        <v>1.25</v>
+      </c>
+      <c r="AB88">
+        <v>3.28</v>
+      </c>
+      <c r="AC88">
+        <v>1.76</v>
+      </c>
+      <c r="AD88">
+        <v>1.98</v>
+      </c>
+      <c r="AE88">
+        <v>1.38</v>
+      </c>
+      <c r="AF88">
+        <v>1.33</v>
+      </c>
+      <c r="AG88">
+        <v>3.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.67</v>
+      </c>
+      <c r="AK88">
         <v>1.4</v>
-      </c>
-      <c r="AB88">
-        <v>3.1</v>
-      </c>
-      <c r="AC88">
-        <v>2.03</v>
-      </c>
-      <c r="AD88">
-        <v>1.76</v>
-      </c>
-      <c r="AE88">
-        <v>1.28</v>
-      </c>
-      <c r="AF88">
-        <v>1.6</v>
-      </c>
-      <c r="AG88">
-        <v>2.25</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.13</v>
-      </c>
-      <c r="AK88">
-        <v>3.4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,65 +14979,65 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O90">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P90">
+        <v>3.05</v>
+      </c>
+      <c r="Q90">
+        <v>2.6</v>
+      </c>
+      <c r="R90">
+        <v>2.25</v>
+      </c>
+      <c r="S90">
+        <v>1.3</v>
+      </c>
+      <c r="T90">
+        <v>3.25</v>
+      </c>
+      <c r="U90">
+        <v>2.46</v>
+      </c>
+      <c r="V90">
+        <v>1.53</v>
+      </c>
+      <c r="W90">
+        <v>1.11</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>1.19</v>
+      </c>
+      <c r="Z90">
+        <v>3.98</v>
+      </c>
+      <c r="AA90">
+        <v>1.66</v>
+      </c>
+      <c r="AB90">
+        <v>2.23</v>
+      </c>
+      <c r="AC90">
+        <v>2.49</v>
+      </c>
+      <c r="AD90">
+        <v>1.48</v>
+      </c>
+      <c r="AE90">
+        <v>1.19</v>
+      </c>
+      <c r="AF90">
+        <v>1.55</v>
+      </c>
+      <c r="AG90">
         <v>2.38</v>
       </c>
-      <c r="Q90">
-        <v>2.7</v>
-      </c>
-      <c r="R90">
-        <v>2.45</v>
-      </c>
-      <c r="S90">
-        <v>1.2</v>
-      </c>
-      <c r="T90">
-        <v>4.5</v>
-      </c>
-      <c r="U90">
-        <v>2.05</v>
-      </c>
-      <c r="V90">
-        <v>1.77</v>
-      </c>
-      <c r="W90">
-        <v>1.2</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.12</v>
-      </c>
-      <c r="Z90">
-        <v>6.25</v>
-      </c>
-      <c r="AA90">
-        <v>1.35</v>
-      </c>
-      <c r="AB90">
-        <v>2.74</v>
-      </c>
-      <c r="AC90">
-        <v>2</v>
-      </c>
-      <c r="AD90">
-        <v>1.75</v>
-      </c>
-      <c r="AE90">
-        <v>1.27</v>
-      </c>
-      <c r="AF90">
-        <v>1.34</v>
-      </c>
-      <c r="AG90">
-        <v>2.99</v>
-      </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O92">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="P92">
-        <v>2.08</v>
+        <v>5.75</v>
       </c>
       <c r="Q92">
-        <v>3.35</v>
+        <v>1.67</v>
       </c>
       <c r="R92">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S92">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T92">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U92">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="V92">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W92">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
+        <v>1.04</v>
+      </c>
+      <c r="Z92">
+        <v>6.9</v>
+      </c>
+      <c r="AA92">
+        <v>1.33</v>
+      </c>
+      <c r="AB92">
+        <v>3.25</v>
+      </c>
+      <c r="AC92">
+        <v>1.89</v>
+      </c>
+      <c r="AD92">
+        <v>1.93</v>
+      </c>
+      <c r="AE92">
+        <v>1.36</v>
+      </c>
+      <c r="AF92">
+        <v>1.44</v>
+      </c>
+      <c r="AG92">
+        <v>2.6</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.09</v>
       </c>
-      <c r="Z92">
-        <v>6.03</v>
-      </c>
-      <c r="AA92">
-        <v>1.43</v>
-      </c>
-      <c r="AB92">
-        <v>2.76</v>
-      </c>
-      <c r="AC92">
-        <v>2.02</v>
-      </c>
-      <c r="AD92">
-        <v>1.71</v>
-      </c>
-      <c r="AE92">
-        <v>1.32</v>
-      </c>
-      <c r="AF92">
-        <v>1.36</v>
-      </c>
-      <c r="AG92">
-        <v>2.88</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.22</v>
-      </c>
       <c r="AK92">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P93">
+        <v>3.19</v>
+      </c>
+      <c r="Q93">
         <v>2.1</v>
       </c>
-      <c r="Q93">
-        <v>2.83</v>
-      </c>
       <c r="R93">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="S93">
         <v>1.11</v>
       </c>
       <c r="T93">
-        <v>4.85</v>
+        <v>5.05</v>
       </c>
       <c r="U93">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V93">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="W93">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z93">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AA93">
+        <v>1.17</v>
+      </c>
+      <c r="AB93">
+        <v>4</v>
+      </c>
+      <c r="AC93">
+        <v>1.5</v>
+      </c>
+      <c r="AD93">
+        <v>2.28</v>
+      </c>
+      <c r="AE93">
+        <v>1.62</v>
+      </c>
+      <c r="AF93">
         <v>1.25</v>
       </c>
-      <c r="AB93">
-        <v>3.28</v>
-      </c>
-      <c r="AC93">
-        <v>1.76</v>
-      </c>
-      <c r="AD93">
-        <v>1.98</v>
-      </c>
-      <c r="AE93">
-        <v>1.38</v>
-      </c>
-      <c r="AF93">
-        <v>1.33</v>
-      </c>
       <c r="AG93">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="O94">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P94">
-        <v>3.19</v>
+        <v>3.9</v>
       </c>
       <c r="Q94">
         <v>2.1</v>
       </c>
       <c r="R94">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="S94">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>5.05</v>
+        <v>3.78</v>
       </c>
       <c r="U94">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="V94">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="W94">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z94">
-        <v>10</v>
+        <v>5.55</v>
       </c>
       <c r="AA94">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AB94">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AC94">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AD94">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE94">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AF94">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK94">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O95">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q95">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S95">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="U95">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>3.98</v>
+        <v>6.25</v>
       </c>
       <c r="AA95">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AB95">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="AC95">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="AD95">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AE95">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF95">
+        <v>1.34</v>
+      </c>
+      <c r="AG95">
+        <v>2.99</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.25</v>
+      </c>
+      <c r="AK95">
         <v>1.55</v>
-      </c>
-      <c r="AG95">
-        <v>2.38</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.33</v>
-      </c>
-      <c r="AK95">
-        <v>1.62</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="O96">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q96">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="R96">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="S96">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="U96">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="V96">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
         <v>1.15</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB96">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AC96">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="AD96">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AE96">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AF96">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG96">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="AK96">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P97">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>5.05</v>
       </c>
       <c r="R97">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T97">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="U97">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
         <v>1.15</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB97">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AC97">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AD97">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AE97">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF97">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AG97">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="AK97">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16452,7 +16452,7 @@
         <v>3.4</v>
       </c>
       <c r="P99">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -16485,10 +16485,10 @@
         <v>3.58</v>
       </c>
       <c r="AA99">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB99">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC99">
         <v>2.74</v>
@@ -16612,13 +16612,13 @@
         <v>1.91</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P100">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q100">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R100">
         <v>2.3</v>
@@ -16630,13 +16630,13 @@
         <v>3.46</v>
       </c>
       <c r="U100">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="V100">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W100">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
@@ -16645,22 +16645,22 @@
         <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA100">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB100">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC100">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AD100">
         <v>1.44</v>
       </c>
       <c r="AE100">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
         <v>1.55</v>
@@ -16793,7 +16793,7 @@
         <v>3.7</v>
       </c>
       <c r="U101">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="V101">
         <v>1.62</v>
@@ -16811,10 +16811,10 @@
         <v>5</v>
       </c>
       <c r="AA101">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB101">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC101">
         <v>2.27</v>
@@ -17264,7 +17264,7 @@
         <v>4.35</v>
       </c>
       <c r="O104">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P104">
         <v>1.57</v>
@@ -17312,7 +17312,7 @@
         <v>1.42</v>
       </c>
       <c r="AE104">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF104">
         <v>1.67</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P105">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q105">
         <v>2.65</v>
@@ -17448,7 +17448,7 @@
         <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
         <v>1.15</v>
@@ -17457,7 +17457,7 @@
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z105">
         <v>5.5</v>
@@ -17466,16 +17466,16 @@
         <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AC105">
         <v>2.3</v>
       </c>
       <c r="AD105">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE105">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17497,7 +17497,7 @@
         <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O106">
         <v>5.15</v>
       </c>
       <c r="P106">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q106">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R106">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V106">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z106">
-        <v>4.15</v>
+        <v>4.67</v>
       </c>
       <c r="AA106">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AC106">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE106">
+        <v>1.17</v>
+      </c>
+      <c r="AF106">
+        <v>1.85</v>
+      </c>
+      <c r="AG106">
+        <v>1.85</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.14</v>
       </c>
-      <c r="AF106">
-        <v>1.86</v>
-      </c>
-      <c r="AG106">
-        <v>1.9</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.16</v>
-      </c>
       <c r="AK106">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>3.38</v>
       </c>
       <c r="U107">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
         <v>1.51</v>
@@ -17786,19 +17786,19 @@
         <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>4.81</v>
+        <v>4.87</v>
       </c>
       <c r="AA107">
         <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC107">
         <v>2.38</v>
       </c>
       <c r="AD107">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE107">
         <v>1.15</v>
@@ -17913,16 +17913,16 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O108">
         <v>3.35</v>
       </c>
       <c r="P108">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="Q108">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R108">
         <v>2.2</v>
@@ -17937,7 +17937,7 @@
         <v>2.54</v>
       </c>
       <c r="V108">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
         <v>1.06</v>
@@ -17952,13 +17952,13 @@
         <v>3.68</v>
       </c>
       <c r="AA108">
+        <v>1.73</v>
+      </c>
+      <c r="AB108">
         <v>1.75</v>
       </c>
-      <c r="AB108">
-        <v>1.94</v>
-      </c>
       <c r="AC108">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="AD108">
         <v>1.4</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="O109">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P109">
         <v>4.87</v>
@@ -18091,49 +18091,49 @@
         <v>2.37</v>
       </c>
       <c r="S109">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T109">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="U109">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="V109">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W109">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z109">
-        <v>5.45</v>
+        <v>5.59</v>
       </c>
       <c r="AA109">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB109">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC109">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD109">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE109">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG109">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,13 +18248,13 @@
         <v>5.5</v>
       </c>
       <c r="Q110">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R110">
         <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T110">
         <v>3.3</v>
@@ -18284,13 +18284,13 @@
         <v>2.15</v>
       </c>
       <c r="AC110">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AD110">
         <v>1.44</v>
       </c>
       <c r="AE110">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF110">
         <v>1.76</v>
@@ -18402,31 +18402,31 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O111">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="P111">
         <v>10.85</v>
       </c>
       <c r="Q111">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R111">
         <v>3.24</v>
       </c>
       <c r="S111">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T111">
         <v>4.65</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V111">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="W111">
         <v>1.29</v>
@@ -18441,25 +18441,25 @@
         <v>7.7</v>
       </c>
       <c r="AA111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB111">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AC111">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD111">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AE111">
         <v>1.46</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18728,58 +18728,58 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O113">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P113">
         <v>12.48</v>
       </c>
       <c r="Q113">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="R113">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T113">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U113">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V113">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W113">
         <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
         <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA113">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AB113">
         <v>1.81</v>
       </c>
       <c r="AC113">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD113">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE113">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
         <v>2.8</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK113">
         <v>3.94</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O114">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q114">
         <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
         <v>1.22</v>
@@ -18912,10 +18912,10 @@
         <v>3.75</v>
       </c>
       <c r="U114">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="V114">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W114">
         <v>1.17</v>
@@ -18924,31 +18924,31 @@
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z114">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="AA114">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB114">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC114">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AD114">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE114">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF114">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG114">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>2.7</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
         <v>2.6</v>
@@ -19084,16 +19084,16 @@
         <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
         <v>1.35</v>
       </c>
       <c r="Z115">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA115">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB115">
         <v>1.84</v>
@@ -19111,7 +19111,7 @@
         <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19223,10 +19223,10 @@
         <v>4.8</v>
       </c>
       <c r="P116">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q116">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R116">
         <v>2.45</v>
@@ -19247,7 +19247,7 @@
         <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
         <v>1.13</v>
@@ -19256,7 +19256,7 @@
         <v>6</v>
       </c>
       <c r="AA116">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB116">
         <v>2.33</v>
@@ -19271,7 +19271,7 @@
         <v>1.25</v>
       </c>
       <c r="AF116">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG116">
         <v>2.25</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK116">
         <v>2.63</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O117">
         <v>3.5</v>
@@ -19878,13 +19878,13 @@
         <v>2.9</v>
       </c>
       <c r="Q120">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="R120">
         <v>1.91</v>
       </c>
       <c r="S120">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T120">
         <v>2.5</v>
@@ -19893,28 +19893,28 @@
         <v>3.25</v>
       </c>
       <c r="V120">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W120">
         <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z120">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AA120">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB120">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC120">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="AD120">
         <v>1.15</v>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK120">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O121">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -20047,13 +20047,13 @@
         <v>2.3</v>
       </c>
       <c r="S121">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T121">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U121">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V121">
         <v>1.43</v>
@@ -20071,13 +20071,13 @@
         <v>3.74</v>
       </c>
       <c r="AA121">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB121">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC121">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AD121">
         <v>1.35</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "84"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q4">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
+        <v>1.4</v>
+      </c>
+      <c r="T4">
+        <v>2.88</v>
+      </c>
+      <c r="U4">
+        <v>3.2</v>
+      </c>
+      <c r="V4">
+        <v>1.36</v>
+      </c>
+      <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.29</v>
+      </c>
+      <c r="Z4">
+        <v>3.3</v>
+      </c>
+      <c r="AA4">
+        <v>2.09</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
+        <v>3.68</v>
+      </c>
+      <c r="AD4">
+        <v>1.25</v>
+      </c>
+      <c r="AE4">
+        <v>1.03</v>
+      </c>
+      <c r="AF4">
+        <v>1.98</v>
+      </c>
+      <c r="AG4">
+        <v>1.74</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["72", "80"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.17</v>
+      </c>
+      <c r="AK4">
+        <v>2.06</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>5</v>
+      </c>
+      <c r="AN4">
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <v>11</v>
+      </c>
+      <c r="AP4">
+        <v>4</v>
+      </c>
+      <c r="AQ4">
         <v>1.48</v>
       </c>
-      <c r="T4">
-        <v>2.42</v>
-      </c>
-      <c r="U4">
-        <v>3.3</v>
-      </c>
-      <c r="V4">
-        <v>1.29</v>
-      </c>
-      <c r="W4">
-        <v>1.02</v>
-      </c>
-      <c r="X4">
-        <v>1.07</v>
-      </c>
-      <c r="Y4">
-        <v>1.44</v>
-      </c>
-      <c r="Z4">
-        <v>2.7</v>
-      </c>
-      <c r="AA4">
-        <v>2.42</v>
-      </c>
-      <c r="AB4">
-        <v>1.52</v>
-      </c>
-      <c r="AC4">
-        <v>4.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.2</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>2.03</v>
-      </c>
-      <c r="AG4">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.33</v>
-      </c>
-      <c r="AK4">
-        <v>1.61</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
-      <c r="AN4">
-        <v>-1</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>-1</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1120,72 +1120,72 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q5">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U5">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AC5">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
         <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "40", "45+2"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "70", "87"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1609,17 +1609,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
         <v>2.69</v>
@@ -1646,25 +1646,25 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA8">
         <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
         <v>1.62</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "25"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="U9">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>5.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
+        <v>1.14</v>
+      </c>
+      <c r="Z10">
+        <v>5.14</v>
+      </c>
+      <c r="AA10">
+        <v>1.6</v>
+      </c>
+      <c r="AB10">
+        <v>2.35</v>
+      </c>
+      <c r="AC10">
+        <v>2.51</v>
+      </c>
+      <c r="AD10">
+        <v>1.49</v>
+      </c>
+      <c r="AE10">
         <v>1.22</v>
       </c>
-      <c r="Z10">
-        <v>3.5</v>
-      </c>
-      <c r="AA10">
-        <v>1.84</v>
-      </c>
-      <c r="AB10">
-        <v>1.9</v>
-      </c>
-      <c r="AC10">
-        <v>3.25</v>
-      </c>
-      <c r="AD10">
-        <v>1.3</v>
-      </c>
-      <c r="AE10">
-        <v>1.07</v>
-      </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O17">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P17">
         <v>1.43</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.54</v>
+        <v>1.83</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>1.82</v>
+        <v>3.8</v>
       </c>
       <c r="Q20">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S20">
+        <v>1.38</v>
+      </c>
+      <c r="T20">
+        <v>2.64</v>
+      </c>
+      <c r="U20">
+        <v>2.83</v>
+      </c>
+      <c r="V20">
+        <v>1.38</v>
+      </c>
+      <c r="W20">
+        <v>1.04</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
         <v>1.22</v>
       </c>
-      <c r="T20">
-        <v>3.18</v>
-      </c>
-      <c r="U20">
-        <v>2.01</v>
-      </c>
-      <c r="V20">
-        <v>1.5</v>
-      </c>
-      <c r="W20">
+      <c r="Z20">
+        <v>2.63</v>
+      </c>
+      <c r="AA20">
+        <v>1.9</v>
+      </c>
+      <c r="AB20">
+        <v>1.8</v>
+      </c>
+      <c r="AC20">
+        <v>2.63</v>
+      </c>
+      <c r="AD20">
+        <v>1.22</v>
+      </c>
+      <c r="AE20">
         <v>1.07</v>
       </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1.18</v>
-      </c>
-      <c r="Z20">
-        <v>3.9</v>
-      </c>
-      <c r="AA20">
-        <v>1.65</v>
-      </c>
-      <c r="AB20">
-        <v>2.06</v>
-      </c>
-      <c r="AC20">
-        <v>2.2</v>
-      </c>
-      <c r="AD20">
-        <v>1.33</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
       <c r="AF20">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AK20">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.83</v>
+        <v>3.54</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="U21">
-        <v>2.83</v>
+        <v>2.01</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC21">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q50">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S50">
         <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
         <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC50">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AD50">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
         <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AA51">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
+        <v>1.56</v>
+      </c>
+      <c r="AG51">
+        <v>2.18</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.3</v>
+      </c>
+      <c r="AK51">
         <v>1.75</v>
-      </c>
-      <c r="AG51">
-        <v>2</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.2</v>
-      </c>
-      <c r="AK51">
-        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,34 +11882,34 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.11</v>
+        <v>2.81</v>
       </c>
       <c r="O71">
+        <v>3.55</v>
+      </c>
+      <c r="P71">
+        <v>2</v>
+      </c>
+      <c r="Q71">
+        <v>3.45</v>
+      </c>
+      <c r="R71">
+        <v>2.39</v>
+      </c>
+      <c r="S71">
+        <v>1.22</v>
+      </c>
+      <c r="T71">
         <v>3.8</v>
       </c>
-      <c r="P71">
-        <v>2.87</v>
-      </c>
-      <c r="Q71">
-        <v>2.52</v>
-      </c>
-      <c r="R71">
-        <v>2.42</v>
-      </c>
-      <c r="S71">
-        <v>1.17</v>
-      </c>
-      <c r="T71">
-        <v>4.5</v>
-      </c>
       <c r="U71">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V71">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11918,28 +11918,28 @@
         <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AA71">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB71">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AC71">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD71">
         <v>1.68</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF71">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AG71">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,34 +12045,34 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.81</v>
+        <v>2.11</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="Q72">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="R72">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T72">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V72">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12081,28 +12081,28 @@
         <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA72">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB72">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD72">
         <v>1.68</v>
       </c>
       <c r="AE72">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AG72">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AK72">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q76">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R76">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
         <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U76">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V76">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W76">
+        <v>1.06</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
+        <v>1.24</v>
+      </c>
+      <c r="Z76">
+        <v>3.34</v>
+      </c>
+      <c r="AA76">
+        <v>1.92</v>
+      </c>
+      <c r="AB76">
+        <v>1.9</v>
+      </c>
+      <c r="AC76">
+        <v>3.2</v>
+      </c>
+      <c r="AD76">
+        <v>1.26</v>
+      </c>
+      <c r="AE76">
         <v>1.07</v>
       </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>1.22</v>
-      </c>
-      <c r="Z76">
-        <v>3.58</v>
-      </c>
-      <c r="AA76">
-        <v>1.8</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76">
-        <v>2.83</v>
-      </c>
-      <c r="AD76">
-        <v>1.33</v>
-      </c>
-      <c r="AE76">
-        <v>1.1</v>
-      </c>
       <c r="AF76">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG76">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="O77">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T78">
-        <v>2.96</v>
+        <v>2.41</v>
       </c>
       <c r="U78">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.4</v>
+      </c>
+      <c r="Z78">
+        <v>2.75</v>
+      </c>
+      <c r="AA78">
+        <v>2.29</v>
+      </c>
+      <c r="AB78">
+        <v>1.57</v>
+      </c>
+      <c r="AC78">
+        <v>4.38</v>
+      </c>
+      <c r="AD78">
+        <v>1.15</v>
+      </c>
+      <c r="AE78">
         <v>1.03</v>
       </c>
-      <c r="Y78">
-        <v>1.24</v>
-      </c>
-      <c r="Z78">
-        <v>3.34</v>
-      </c>
-      <c r="AA78">
-        <v>1.92</v>
-      </c>
-      <c r="AB78">
-        <v>1.9</v>
-      </c>
-      <c r="AC78">
-        <v>3.2</v>
-      </c>
-      <c r="AD78">
-        <v>1.26</v>
-      </c>
-      <c r="AE78">
-        <v>1.07</v>
-      </c>
       <c r="AF78">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK78">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="O79">
+        <v>3.88</v>
+      </c>
+      <c r="P79">
+        <v>5.25</v>
+      </c>
+      <c r="Q79">
+        <v>2.15</v>
+      </c>
+      <c r="R79">
+        <v>2.15</v>
+      </c>
+      <c r="S79">
+        <v>1.41</v>
+      </c>
+      <c r="T79">
+        <v>2.88</v>
+      </c>
+      <c r="U79">
+        <v>2.71</v>
+      </c>
+      <c r="V79">
+        <v>1.36</v>
+      </c>
+      <c r="W79">
+        <v>1.07</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.32</v>
+      </c>
+      <c r="Z79">
+        <v>3.08</v>
+      </c>
+      <c r="AA79">
+        <v>1.94</v>
+      </c>
+      <c r="AB79">
+        <v>1.74</v>
+      </c>
+      <c r="AC79">
         <v>3.2</v>
       </c>
-      <c r="P79">
-        <v>3.1</v>
-      </c>
-      <c r="Q79">
-        <v>2.8</v>
-      </c>
-      <c r="R79">
-        <v>2.08</v>
-      </c>
-      <c r="S79">
-        <v>1.48</v>
-      </c>
-      <c r="T79">
-        <v>2.41</v>
-      </c>
-      <c r="U79">
-        <v>3</v>
-      </c>
-      <c r="V79">
-        <v>1.29</v>
-      </c>
-      <c r="W79">
-        <v>1.06</v>
-      </c>
-      <c r="X79">
-        <v>1.02</v>
-      </c>
-      <c r="Y79">
-        <v>1.4</v>
-      </c>
-      <c r="Z79">
-        <v>2.75</v>
-      </c>
-      <c r="AA79">
+      <c r="AD79">
+        <v>1.26</v>
+      </c>
+      <c r="AE79">
+        <v>1.1</v>
+      </c>
+      <c r="AF79">
+        <v>1.91</v>
+      </c>
+      <c r="AG79">
+        <v>1.8</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.25</v>
+      </c>
+      <c r="AK79">
         <v>2.29</v>
-      </c>
-      <c r="AB79">
-        <v>1.57</v>
-      </c>
-      <c r="AC79">
-        <v>4.38</v>
-      </c>
-      <c r="AD79">
-        <v>1.15</v>
-      </c>
-      <c r="AE79">
-        <v>1.03</v>
-      </c>
-      <c r="AF79">
-        <v>1.95</v>
-      </c>
-      <c r="AG79">
-        <v>1.75</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.33</v>
-      </c>
-      <c r="AK79">
-        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O80">
         <v>3.3</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q80">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="U80">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z80">
         <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB80">
         <v>2</v>
       </c>
       <c r="AC80">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD80">
         <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O87">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q87">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="U87">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="V87">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="W87">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z87">
-        <v>6.03</v>
+        <v>7.4</v>
       </c>
       <c r="AA87">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AB87">
-        <v>2.76</v>
+        <v>3.28</v>
       </c>
       <c r="AC87">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AD87">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AE87">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG87">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK87">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.65</v>
+        <v>1.43</v>
       </c>
       <c r="O88">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>4.85</v>
       </c>
       <c r="Q88">
-        <v>2.83</v>
+        <v>1.97</v>
       </c>
       <c r="R88">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="S88">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="T88">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="V88">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="W88">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z88">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA88">
+        <v>1.4</v>
+      </c>
+      <c r="AB88">
+        <v>2.87</v>
+      </c>
+      <c r="AC88">
+        <v>2.05</v>
+      </c>
+      <c r="AD88">
+        <v>1.71</v>
+      </c>
+      <c r="AE88">
         <v>1.25</v>
       </c>
-      <c r="AB88">
-        <v>3.28</v>
-      </c>
-      <c r="AC88">
-        <v>1.76</v>
-      </c>
-      <c r="AD88">
-        <v>1.98</v>
-      </c>
-      <c r="AE88">
-        <v>1.38</v>
-      </c>
       <c r="AF88">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AG88">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="P89">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q89">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="S89">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="U89">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="V89">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="W89">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z89">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA89">
+        <v>1.29</v>
+      </c>
+      <c r="AB89">
+        <v>3.4</v>
+      </c>
+      <c r="AC89">
+        <v>1.73</v>
+      </c>
+      <c r="AD89">
+        <v>2.04</v>
+      </c>
+      <c r="AE89">
         <v>1.4</v>
       </c>
-      <c r="AB89">
-        <v>2.87</v>
-      </c>
-      <c r="AC89">
-        <v>2.05</v>
-      </c>
-      <c r="AD89">
-        <v>1.71</v>
-      </c>
-      <c r="AE89">
-        <v>1.25</v>
-      </c>
       <c r="AF89">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AG89">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="O90">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="P90">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="Q90">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="S90">
+        <v>1.11</v>
+      </c>
+      <c r="T90">
+        <v>5.05</v>
+      </c>
+      <c r="U90">
+        <v>1.68</v>
+      </c>
+      <c r="V90">
+        <v>2.08</v>
+      </c>
+      <c r="W90">
         <v>1.3</v>
       </c>
-      <c r="T90">
-        <v>3.25</v>
-      </c>
-      <c r="U90">
-        <v>2.46</v>
-      </c>
-      <c r="V90">
-        <v>1.53</v>
-      </c>
-      <c r="W90">
-        <v>1.11</v>
-      </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="Z90">
-        <v>3.98</v>
+        <v>10</v>
       </c>
       <c r="AA90">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="AB90">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="AC90">
-        <v>2.49</v>
+        <v>1.5</v>
       </c>
       <c r="AD90">
-        <v>1.48</v>
+        <v>2.28</v>
       </c>
       <c r="AE90">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AF90">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AG90">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="O91">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="P91">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q91">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="S91">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T91">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="U91">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="V91">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="W91">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z91">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AA91">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB91">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AC91">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AD91">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AE91">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF91">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG91">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="O92">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="P92">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q92">
+        <v>2.1</v>
+      </c>
+      <c r="R92">
+        <v>2.34</v>
+      </c>
+      <c r="S92">
+        <v>1.22</v>
+      </c>
+      <c r="T92">
+        <v>3.78</v>
+      </c>
+      <c r="U92">
+        <v>2.11</v>
+      </c>
+      <c r="V92">
+        <v>1.66</v>
+      </c>
+      <c r="W92">
+        <v>1.18</v>
+      </c>
+      <c r="X92">
+        <v>1.02</v>
+      </c>
+      <c r="Y92">
+        <v>1.08</v>
+      </c>
+      <c r="Z92">
+        <v>5.55</v>
+      </c>
+      <c r="AA92">
+        <v>1.4</v>
+      </c>
+      <c r="AB92">
+        <v>2.88</v>
+      </c>
+      <c r="AC92">
+        <v>2.16</v>
+      </c>
+      <c r="AD92">
         <v>1.67</v>
       </c>
-      <c r="R92">
-        <v>2.9</v>
-      </c>
-      <c r="S92">
-        <v>1.14</v>
-      </c>
-      <c r="T92">
-        <v>4.6</v>
-      </c>
-      <c r="U92">
-        <v>1.94</v>
-      </c>
-      <c r="V92">
-        <v>1.85</v>
-      </c>
-      <c r="W92">
-        <v>1.25</v>
-      </c>
-      <c r="X92">
-        <v>1.01</v>
-      </c>
-      <c r="Y92">
-        <v>1.04</v>
-      </c>
-      <c r="Z92">
-        <v>6.9</v>
-      </c>
-      <c r="AA92">
-        <v>1.33</v>
-      </c>
-      <c r="AB92">
-        <v>3.25</v>
-      </c>
-      <c r="AC92">
-        <v>1.89</v>
-      </c>
-      <c r="AD92">
-        <v>1.93</v>
-      </c>
       <c r="AE92">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AF92">
         <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK92">
-        <v>3.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="O93">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P93">
-        <v>3.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q93">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="R93">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S93">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T93">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="U93">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="V93">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="W93">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z93">
-        <v>10</v>
+        <v>6.03</v>
       </c>
       <c r="AA93">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AB93">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="AC93">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AD93">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="AE93">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AF93">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AG93">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="O94">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="P94">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q94">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R94">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T94">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="U94">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="V94">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="W94">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z94">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA94">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB94">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AC94">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="AD94">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AE94">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AF94">
         <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK94">
-        <v>2.11</v>
+        <v>3.25</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,65 +15794,65 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O95">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P95">
+        <v>3.05</v>
+      </c>
+      <c r="Q95">
+        <v>2.6</v>
+      </c>
+      <c r="R95">
+        <v>2.25</v>
+      </c>
+      <c r="S95">
+        <v>1.3</v>
+      </c>
+      <c r="T95">
+        <v>3.25</v>
+      </c>
+      <c r="U95">
+        <v>2.46</v>
+      </c>
+      <c r="V95">
+        <v>1.53</v>
+      </c>
+      <c r="W95">
+        <v>1.11</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>1.19</v>
+      </c>
+      <c r="Z95">
+        <v>3.98</v>
+      </c>
+      <c r="AA95">
+        <v>1.66</v>
+      </c>
+      <c r="AB95">
+        <v>2.23</v>
+      </c>
+      <c r="AC95">
+        <v>2.49</v>
+      </c>
+      <c r="AD95">
+        <v>1.48</v>
+      </c>
+      <c r="AE95">
+        <v>1.19</v>
+      </c>
+      <c r="AF95">
+        <v>1.55</v>
+      </c>
+      <c r="AG95">
         <v>2.38</v>
       </c>
-      <c r="Q95">
-        <v>2.7</v>
-      </c>
-      <c r="R95">
-        <v>2.45</v>
-      </c>
-      <c r="S95">
-        <v>1.2</v>
-      </c>
-      <c r="T95">
-        <v>4.5</v>
-      </c>
-      <c r="U95">
-        <v>2.05</v>
-      </c>
-      <c r="V95">
-        <v>1.77</v>
-      </c>
-      <c r="W95">
-        <v>1.2</v>
-      </c>
-      <c r="X95">
-        <v>1.01</v>
-      </c>
-      <c r="Y95">
-        <v>1.12</v>
-      </c>
-      <c r="Z95">
-        <v>6.25</v>
-      </c>
-      <c r="AA95">
-        <v>1.35</v>
-      </c>
-      <c r="AB95">
-        <v>2.74</v>
-      </c>
-      <c r="AC95">
-        <v>2</v>
-      </c>
-      <c r="AD95">
-        <v>1.75</v>
-      </c>
-      <c r="AE95">
-        <v>1.27</v>
-      </c>
-      <c r="AF95">
-        <v>1.34</v>
-      </c>
-      <c r="AG95">
-        <v>2.99</v>
-      </c>
       <c r="AH95" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK95">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P96">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="Q96">
-        <v>3.3</v>
+        <v>5.05</v>
       </c>
       <c r="R96">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T96">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="U96">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W96">
         <v>1.15</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z96">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AA96">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AC96">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AD96">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AE96">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF96">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AG96">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="AK96">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="O97">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q97">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="S97">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="V97">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
         <v>1.15</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AA97">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AC97">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="AD97">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG97">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="AK97">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="O108">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P108">
-        <v>2.83</v>
+        <v>5.5</v>
       </c>
       <c r="Q108">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U108">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V108">
+        <v>1.53</v>
+      </c>
+      <c r="W108">
+        <v>1.12</v>
+      </c>
+      <c r="X108">
+        <v>1.02</v>
+      </c>
+      <c r="Y108">
+        <v>1.16</v>
+      </c>
+      <c r="Z108">
+        <v>4.15</v>
+      </c>
+      <c r="AA108">
+        <v>1.6</v>
+      </c>
+      <c r="AB108">
+        <v>2.15</v>
+      </c>
+      <c r="AC108">
+        <v>2.15</v>
+      </c>
+      <c r="AD108">
         <v>1.44</v>
       </c>
-      <c r="W108">
-        <v>1.06</v>
-      </c>
-      <c r="X108">
-        <v>1.01</v>
-      </c>
-      <c r="Y108">
-        <v>1.2</v>
-      </c>
-      <c r="Z108">
-        <v>3.68</v>
-      </c>
-      <c r="AA108">
-        <v>1.73</v>
-      </c>
-      <c r="AB108">
-        <v>1.75</v>
-      </c>
-      <c r="AC108">
-        <v>2.91</v>
-      </c>
-      <c r="AD108">
-        <v>1.4</v>
-      </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG108">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
+        <v>2.13</v>
+      </c>
+      <c r="O110">
+        <v>3.35</v>
+      </c>
+      <c r="P110">
+        <v>2.83</v>
+      </c>
+      <c r="Q110">
+        <v>2.88</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>1.3</v>
+      </c>
+      <c r="T110">
+        <v>2.85</v>
+      </c>
+      <c r="U110">
+        <v>2.54</v>
+      </c>
+      <c r="V110">
+        <v>1.44</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.01</v>
+      </c>
+      <c r="Y110">
+        <v>1.2</v>
+      </c>
+      <c r="Z110">
+        <v>3.68</v>
+      </c>
+      <c r="AA110">
+        <v>1.73</v>
+      </c>
+      <c r="AB110">
+        <v>1.75</v>
+      </c>
+      <c r="AC110">
+        <v>2.91</v>
+      </c>
+      <c r="AD110">
         <v>1.4</v>
       </c>
-      <c r="O110">
-        <v>4.4</v>
-      </c>
-      <c r="P110">
-        <v>5.5</v>
-      </c>
-      <c r="Q110">
-        <v>1.91</v>
-      </c>
-      <c r="R110">
-        <v>2.3</v>
-      </c>
-      <c r="S110">
-        <v>1.22</v>
-      </c>
-      <c r="T110">
-        <v>3.3</v>
-      </c>
-      <c r="U110">
-        <v>2.23</v>
-      </c>
-      <c r="V110">
+      <c r="AE110">
+        <v>1.1</v>
+      </c>
+      <c r="AF110">
+        <v>1.6</v>
+      </c>
+      <c r="AG110">
+        <v>2.18</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.24</v>
+      </c>
+      <c r="AK110">
         <v>1.53</v>
-      </c>
-      <c r="W110">
-        <v>1.12</v>
-      </c>
-      <c r="X110">
-        <v>1.02</v>
-      </c>
-      <c r="Y110">
-        <v>1.16</v>
-      </c>
-      <c r="Z110">
-        <v>4.15</v>
-      </c>
-      <c r="AA110">
-        <v>1.6</v>
-      </c>
-      <c r="AB110">
-        <v>2.15</v>
-      </c>
-      <c r="AC110">
-        <v>2.15</v>
-      </c>
-      <c r="AD110">
-        <v>1.44</v>
-      </c>
-      <c r="AE110">
-        <v>1.11</v>
-      </c>
-      <c r="AF110">
-        <v>1.76</v>
-      </c>
-      <c r="AG110">
-        <v>1.94</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.05</v>
-      </c>
-      <c r="AK110">
-        <v>2.52</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1785,22 +1785,22 @@
         <v>3.15</v>
       </c>
       <c r="Q9">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="U9">
         <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1815,25 +1815,25 @@
         <v>3.5</v>
       </c>
       <c r="AA9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC9">
         <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1916,54 +1916,54 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
         <v>2.4</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
         <v>1.15</v>
@@ -1975,32 +1975,32 @@
         <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>5.14</v>
+        <v>5.21</v>
       </c>
       <c r="AA10">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
         <v>2.35</v>
       </c>
       <c r="AC10">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD10">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+7", "60"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2012,34 +2012,34 @@
         <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2108,46 +2108,46 @@
         <v>4.2</v>
       </c>
       <c r="P11">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q11">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AA11">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC11">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD11">
         <v>1.33</v>
@@ -2156,14 +2156,14 @@
         <v>1.2</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
         <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "35", "56", "68", "84", "88"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2172,37 +2172,37 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>2.71</v>
+        <v>2.49</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,39 +2242,39 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O12">
         <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
         <v>2.3</v>
@@ -2292,7 +2292,7 @@
         <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,13 +2304,13 @@
         <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AB12">
         <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
         <v>1.45</v>
@@ -2322,50 +2322,50 @@
         <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "52"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "76"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,84 +2408,84 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="P13">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>2.7</v>
       </c>
       <c r="S13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T13">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z13">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA13">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB13">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AC13">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD13">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2494,41 +2494,41 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "32", "62"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,23 +2571,23 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2597,58 +2597,58 @@
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.64</v>
+        <v>2.99</v>
       </c>
       <c r="U14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2657,41 +2657,41 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "86"]</t>
         </is>
       </c>
       <c r="AJ14">
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2763,55 +2763,55 @@
         <v>2.35</v>
       </c>
       <c r="Q15">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U15">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="V15">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z15">
-        <v>6.91</v>
+        <v>7.34</v>
       </c>
       <c r="AA15">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AB15">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="AC15">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD15">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AE15">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AF15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG15">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2913,32 +2913,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
         <v>2.6</v>
       </c>
       <c r="O16">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="P16">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q16">
         <v>3.3</v>
       </c>
       <c r="R16">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="S16">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="T16">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="U16">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="V16">
         <v>1.18</v>
@@ -2947,77 +2947,77 @@
         <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Y16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA16">
+        <v>3.2</v>
+      </c>
+      <c r="AB16">
+        <v>1.27</v>
+      </c>
+      <c r="AC16">
+        <v>6.35</v>
+      </c>
+      <c r="AD16">
+        <v>1.06</v>
+      </c>
+      <c r="AE16">
+        <v>1.01</v>
+      </c>
+      <c r="AF16">
+        <v>2.39</v>
+      </c>
+      <c r="AG16">
+        <v>1.44</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>["29"]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.45</v>
+      </c>
+      <c r="AK16">
+        <v>1.34</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
         <v>3</v>
       </c>
-      <c r="AB16">
-        <v>1.36</v>
-      </c>
-      <c r="AC16">
-        <v>7</v>
-      </c>
-      <c r="AD16">
-        <v>1.07</v>
-      </c>
-      <c r="AE16">
-        <v>1.02</v>
-      </c>
-      <c r="AF16">
-        <v>2.25</v>
-      </c>
-      <c r="AG16">
-        <v>1.5</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.36</v>
-      </c>
-      <c r="AK16">
-        <v>1.38</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3086,7 +3086,7 @@
         <v>4.4</v>
       </c>
       <c r="P17">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,46 +4282,46 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>2.65</v>
       </c>
       <c r="P25">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P26">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R26">
         <v>1.8</v>
@@ -4604,7 +4604,7 @@
         <v>2.21</v>
       </c>
       <c r="AG26">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O28">
         <v>4.8</v>
@@ -4885,52 +4885,52 @@
         <v>1.74</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="U28">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="AG28">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>2.77</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
         <v>1.38</v>
@@ -5057,7 +5057,7 @@
         <v>2.76</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
         <v>1.33</v>
@@ -5109,7 +5109,7 @@
         <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
         <v>3</v>
@@ -5232,7 +5232,7 @@
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
         <v>3.08</v>
@@ -5253,7 +5253,7 @@
         <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
         <v>1.91</v>
@@ -5272,7 +5272,7 @@
         <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P39">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q39">
         <v>5.25</v>
@@ -6693,7 +6693,7 @@
         <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6711,13 +6711,13 @@
         <v>2.59</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
         <v>1.68</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
         <v>1.51</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK39">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7339,10 +7339,10 @@
         <v>2.67</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W43">
         <v>1.07</v>
@@ -7351,31 +7351,31 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AD43">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -8308,22 +8308,22 @@
         <v>3.48</v>
       </c>
       <c r="R49">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S49">
         <v>1.5</v>
       </c>
       <c r="T49">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="U49">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V49">
         <v>1.3</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
         <v>1.05</v>
@@ -8335,16 +8335,16 @@
         <v>2.62</v>
       </c>
       <c r="AA49">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB49">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC49">
         <v>4.3</v>
       </c>
       <c r="AD49">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE49">
         <v>1.03</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="AA51">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
         <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q52">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
         <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG52">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10270,13 +10270,13 @@
         <v>1.4</v>
       </c>
       <c r="T61">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U61">
         <v>2.99</v>
       </c>
       <c r="V61">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W61">
         <v>1.07</v>
@@ -10285,16 +10285,16 @@
         <v>1.06</v>
       </c>
       <c r="Y61">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z61">
         <v>2.78</v>
       </c>
       <c r="AA61">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AB61">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC61">
         <v>4.2</v>
@@ -10306,10 +10306,10 @@
         <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG61">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -11734,16 +11734,16 @@
         <v>2.8</v>
       </c>
       <c r="S70">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T70">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U70">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V70">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="W70">
         <v>1.26</v>
@@ -11761,13 +11761,13 @@
         <v>1.25</v>
       </c>
       <c r="AB70">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC70">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD70">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE70">
         <v>1.42</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK70">
         <v>2.32</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="U78">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="V78">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC78">
-        <v>4.38</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S79">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U79">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z79">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="AA79">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AB79">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC79">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="AD79">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE79">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK79">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>1.59</v>
+      </c>
+      <c r="O80">
+        <v>3.88</v>
+      </c>
+      <c r="P80">
+        <v>5.25</v>
+      </c>
+      <c r="Q80">
         <v>2.15</v>
       </c>
-      <c r="O80">
-        <v>3.3</v>
-      </c>
-      <c r="P80">
-        <v>2.8</v>
-      </c>
-      <c r="Q80">
-        <v>2.7</v>
-      </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T80">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U80">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="V80">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
         <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z80">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA80">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB80">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC80">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD80">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE80">
         <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG80">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="P87">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q87">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="R87">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="S87">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T87">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="U87">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V87">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W87">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z87">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA87">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB87">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC87">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AD87">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE87">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF87">
         <v>1.33</v>
       </c>
       <c r="AG87">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="O88">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P88">
-        <v>4.85</v>
+        <v>3.19</v>
       </c>
       <c r="Q88">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="R88">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="S88">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="T88">
+        <v>5.05</v>
+      </c>
+      <c r="U88">
+        <v>1.68</v>
+      </c>
+      <c r="V88">
+        <v>2.08</v>
+      </c>
+      <c r="W88">
+        <v>1.3</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.05</v>
+      </c>
+      <c r="Z88">
+        <v>10</v>
+      </c>
+      <c r="AA88">
+        <v>1.17</v>
+      </c>
+      <c r="AB88">
         <v>4</v>
       </c>
-      <c r="U88">
-        <v>2.02</v>
-      </c>
-      <c r="V88">
-        <v>1.72</v>
-      </c>
-      <c r="W88">
-        <v>1.18</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.07</v>
-      </c>
-      <c r="Z88">
-        <v>5.8</v>
-      </c>
-      <c r="AA88">
-        <v>1.4</v>
-      </c>
-      <c r="AB88">
-        <v>2.87</v>
-      </c>
       <c r="AC88">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AD88">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="AE88">
+        <v>1.62</v>
+      </c>
+      <c r="AF88">
         <v>1.25</v>
       </c>
-      <c r="AF88">
-        <v>1.48</v>
-      </c>
       <c r="AG88">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="O89">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P89">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R89">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="S89">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>4.7</v>
+        <v>3.78</v>
       </c>
       <c r="U89">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="V89">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="W89">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>8</v>
+        <v>5.55</v>
       </c>
       <c r="AA89">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC89">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AD89">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE89">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AF89">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG89">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O90">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>3.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q90">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="R90">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="S90">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="U90">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="V90">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="W90">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="AA90">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AB90">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AC90">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AD90">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="AE90">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AF90">
+        <v>1.34</v>
+      </c>
+      <c r="AG90">
+        <v>2.99</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.25</v>
       </c>
-      <c r="AG90">
-        <v>3.8</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.17</v>
-      </c>
       <c r="AK90">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P91">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="R91">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="S91">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T91">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="U91">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="V91">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="W91">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>6.25</v>
+        <v>7.4</v>
       </c>
       <c r="AA91">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AB91">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AC91">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD91">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AE91">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF91">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG91">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK91">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="O92">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P92">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q92">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="R92">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T92">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U92">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="V92">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="W92">
         <v>1.18</v>
@@ -15338,31 +15338,31 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z92">
-        <v>5.55</v>
+        <v>5.8</v>
       </c>
       <c r="AA92">
         <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AC92">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AD92">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG92">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK92">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O93">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="P93">
-        <v>2.08</v>
+        <v>5.75</v>
       </c>
       <c r="Q93">
-        <v>3.35</v>
+        <v>1.67</v>
       </c>
       <c r="R93">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S93">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T93">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U93">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="V93">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W93">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
+        <v>1.04</v>
+      </c>
+      <c r="Z93">
+        <v>6.9</v>
+      </c>
+      <c r="AA93">
+        <v>1.33</v>
+      </c>
+      <c r="AB93">
+        <v>3.25</v>
+      </c>
+      <c r="AC93">
+        <v>1.89</v>
+      </c>
+      <c r="AD93">
+        <v>1.93</v>
+      </c>
+      <c r="AE93">
+        <v>1.36</v>
+      </c>
+      <c r="AF93">
+        <v>1.44</v>
+      </c>
+      <c r="AG93">
+        <v>2.6</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>1.09</v>
       </c>
-      <c r="Z93">
-        <v>6.03</v>
-      </c>
-      <c r="AA93">
-        <v>1.43</v>
-      </c>
-      <c r="AB93">
-        <v>2.76</v>
-      </c>
-      <c r="AC93">
-        <v>2.02</v>
-      </c>
-      <c r="AD93">
-        <v>1.71</v>
-      </c>
-      <c r="AE93">
-        <v>1.32</v>
-      </c>
-      <c r="AF93">
-        <v>1.36</v>
-      </c>
-      <c r="AG93">
-        <v>2.88</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.22</v>
-      </c>
       <c r="AK93">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O94">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="P94">
-        <v>5.75</v>
+        <v>2.08</v>
       </c>
       <c r="Q94">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="R94">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S94">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T94">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U94">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="V94">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W94">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z94">
-        <v>6.9</v>
+        <v>6.03</v>
       </c>
       <c r="AA94">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AB94">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="AC94">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AD94">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AE94">
+        <v>1.32</v>
+      </c>
+      <c r="AF94">
         <v>1.36</v>
       </c>
-      <c r="AF94">
-        <v>1.44</v>
-      </c>
       <c r="AG94">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>3.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="O109">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>4.87</v>
+        <v>2.83</v>
       </c>
       <c r="Q109">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R109">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="U109">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="V109">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z109">
-        <v>5.59</v>
+        <v>3.68</v>
       </c>
       <c r="AA109">
+        <v>1.73</v>
+      </c>
+      <c r="AB109">
+        <v>1.75</v>
+      </c>
+      <c r="AC109">
+        <v>2.91</v>
+      </c>
+      <c r="AD109">
         <v>1.4</v>
       </c>
-      <c r="AB109">
-        <v>2.7</v>
-      </c>
-      <c r="AC109">
-        <v>2.05</v>
-      </c>
-      <c r="AD109">
+      <c r="AE109">
+        <v>1.1</v>
+      </c>
+      <c r="AF109">
+        <v>1.6</v>
+      </c>
+      <c r="AG109">
+        <v>2.18</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.24</v>
+      </c>
+      <c r="AK109">
         <v>1.53</v>
-      </c>
-      <c r="AE109">
-        <v>1.2</v>
-      </c>
-      <c r="AF109">
-        <v>1.48</v>
-      </c>
-      <c r="AG109">
-        <v>2.45</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.17</v>
-      </c>
-      <c r="AK109">
-        <v>2.38</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="O110">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="P110">
-        <v>2.83</v>
+        <v>4.87</v>
       </c>
       <c r="Q110">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T110">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="U110">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
+        <v>1.08</v>
+      </c>
+      <c r="Z110">
+        <v>5.59</v>
+      </c>
+      <c r="AA110">
+        <v>1.4</v>
+      </c>
+      <c r="AB110">
+        <v>2.7</v>
+      </c>
+      <c r="AC110">
+        <v>2.05</v>
+      </c>
+      <c r="AD110">
+        <v>1.53</v>
+      </c>
+      <c r="AE110">
         <v>1.2</v>
       </c>
-      <c r="Z110">
-        <v>3.68</v>
-      </c>
-      <c r="AA110">
-        <v>1.73</v>
-      </c>
-      <c r="AB110">
-        <v>1.75</v>
-      </c>
-      <c r="AC110">
-        <v>2.91</v>
-      </c>
-      <c r="AD110">
-        <v>1.4</v>
-      </c>
-      <c r="AE110">
-        <v>1.1</v>
-      </c>
       <c r="AF110">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG110">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18740,49 +18740,49 @@
         <v>1.53</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T113">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U113">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V113">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W113">
         <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
         <v>1.26</v>
       </c>
       <c r="Z113">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA113">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB113">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC113">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD113">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AG113">
         <v>1.33</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK113">
         <v>3.94</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -1744,139 +1744,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O9">
-        <v>3.48</v>
+        <v>3.95</v>
       </c>
       <c r="P9">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>3.5</v>
+        <v>5.21</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AB9">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["45+7", "60"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
+        <v>1.19</v>
+      </c>
+      <c r="AK9">
+        <v>2.05</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>3</v>
+      </c>
+      <c r="AN9">
+        <v>4</v>
+      </c>
+      <c r="AO9">
+        <v>12</v>
+      </c>
+      <c r="AP9">
+        <v>13</v>
+      </c>
+      <c r="AQ9">
+        <v>1.41</v>
+      </c>
+      <c r="AR9">
         <v>1.4</v>
       </c>
-      <c r="AK9">
-        <v>1.55</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1</v>
-      </c>
-      <c r="AN9">
-        <v>-1</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>-1</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
       <c r="AS9">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,19 +1907,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
         <v>2</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1939,107 +1939,107 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.95</v>
+        <v>3.48</v>
       </c>
       <c r="P10">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="U10">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>5.21</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AC10">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="AD10">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
+        <v>1.73</v>
+      </c>
+      <c r="AG10">
+        <v>2.1</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>["27", "53", "64", "84"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>["81", "88"]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.4</v>
+      </c>
+      <c r="AK10">
         <v>1.55</v>
       </c>
-      <c r="AG10">
-        <v>2.26</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>["45+7", "60"]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.19</v>
-      </c>
-      <c r="AK10">
-        <v>2.05</v>
-      </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AP10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AR10">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AS10">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="AT10">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "72"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "18", "47", "56"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -3220,48 +3220,48 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
         <v>3.53</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="U18">
         <v>2.13</v>
@@ -3270,46 +3270,46 @@
         <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>2.9</v>
+        <v>3.76</v>
       </c>
       <c r="AA18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AC18">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
         <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "90+8"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3398,72 +3398,72 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
         <v>5.25</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P19">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
         <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AC19">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="AD19">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3472,41 +3472,41 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>2.52</v>
       </c>
       <c r="AK19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
         <v>1.38</v>
@@ -3590,7 +3590,7 @@
         <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
         <v>1.38</v>
@@ -3611,13 +3611,13 @@
         <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
         <v>1.07</v>
@@ -3630,46 +3630,46 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "49"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,68 +3728,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>3.54</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="Q21">
-        <v>3.75</v>
+        <v>6.45</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
         <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,37 +3802,37 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3863,139 +3863,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>3.54</v>
       </c>
       <c r="O22">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="Q22">
-        <v>6.45</v>
+        <v>4.3</v>
       </c>
       <c r="R22">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U22">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD22">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "48"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "86"]</t>
         </is>
       </c>
       <c r="AJ22">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="AK22">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4054,111 +4054,111 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O23">
+        <v>2.9</v>
+      </c>
+      <c r="P23">
+        <v>2.35</v>
+      </c>
+      <c r="Q23">
+        <v>3.47</v>
+      </c>
+      <c r="R23">
+        <v>1.92</v>
+      </c>
+      <c r="S23">
+        <v>1.44</v>
+      </c>
+      <c r="T23">
+        <v>2.5</v>
+      </c>
+      <c r="U23">
+        <v>3.25</v>
+      </c>
+      <c r="V23">
+        <v>1.3</v>
+      </c>
+      <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
+        <v>1.06</v>
+      </c>
+      <c r="Y23">
+        <v>1.37</v>
+      </c>
+      <c r="Z23">
+        <v>2.66</v>
+      </c>
+      <c r="AA23">
+        <v>2.37</v>
+      </c>
+      <c r="AB23">
+        <v>1.53</v>
+      </c>
+      <c r="AC23">
+        <v>4.8</v>
+      </c>
+      <c r="AD23">
+        <v>1.15</v>
+      </c>
+      <c r="AE23">
+        <v>1.05</v>
+      </c>
+      <c r="AF23">
+        <v>1.95</v>
+      </c>
+      <c r="AG23">
+        <v>1.75</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.36</v>
+      </c>
+      <c r="AK23">
+        <v>1.3</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>5</v>
+      </c>
+      <c r="AN23">
         <v>3</v>
       </c>
-      <c r="P23">
-        <v>2.37</v>
-      </c>
-      <c r="Q23">
-        <v>3.5</v>
-      </c>
-      <c r="R23">
-        <v>1.91</v>
-      </c>
-      <c r="S23">
-        <v>1.52</v>
-      </c>
-      <c r="T23">
-        <v>2.32</v>
-      </c>
-      <c r="U23">
-        <v>3.5</v>
-      </c>
-      <c r="V23">
-        <v>1.25</v>
-      </c>
-      <c r="W23">
-        <v>1.03</v>
-      </c>
-      <c r="X23">
-        <v>1.07</v>
-      </c>
-      <c r="Y23">
-        <v>1.41</v>
-      </c>
-      <c r="Z23">
-        <v>2.52</v>
-      </c>
-      <c r="AA23">
-        <v>2.35</v>
-      </c>
-      <c r="AB23">
-        <v>1.57</v>
-      </c>
-      <c r="AC23">
-        <v>4.6</v>
-      </c>
-      <c r="AD23">
-        <v>1.13</v>
-      </c>
-      <c r="AE23">
-        <v>1.04</v>
-      </c>
-      <c r="AF23">
-        <v>1.97</v>
-      </c>
-      <c r="AG23">
-        <v>1.73</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.4</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4373,14 +4373,14 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "90+3"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "90+1"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4716,25 +4716,25 @@
         <v>4.65</v>
       </c>
       <c r="P27">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q27">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
         <v>1.08</v>
@@ -4743,25 +4743,25 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
         <v>2.25</v>
@@ -4771,46 +4771,46 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>["16", "88", "90+4"]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "53", "85"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "83"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5342,36 +5342,36 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P31">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Q31">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>2.45</v>
@@ -5383,31 +5383,31 @@
         <v>4</v>
       </c>
       <c r="U31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA31">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB31">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC31">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
         <v>1.58</v>
@@ -5416,53 +5416,53 @@
         <v>1.18</v>
       </c>
       <c r="AF31">
+        <v>1.63</v>
+      </c>
+      <c r="AG31">
+        <v>2.12</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>["4", "13", "40", "67", "86"]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.18</v>
+      </c>
+      <c r="AK31">
+        <v>1.12</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>4</v>
+      </c>
+      <c r="AN31">
+        <v>9</v>
+      </c>
+      <c r="AO31">
+        <v>14</v>
+      </c>
+      <c r="AP31">
+        <v>20</v>
+      </c>
+      <c r="AQ31">
         <v>1.58</v>
       </c>
-      <c r="AG31">
-        <v>2.21</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.2</v>
-      </c>
-      <c r="AK31">
-        <v>1.14</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,57 +5502,57 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O32">
         <v>6.2</v>
       </c>
       <c r="P32">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="Q32">
         <v>1.57</v>
       </c>
       <c r="R32">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
         <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W32">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5561,71 +5561,71 @@
         <v>1.09</v>
       </c>
       <c r="Z32">
-        <v>6.22</v>
+        <v>6.01</v>
       </c>
       <c r="AA32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB32">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AD32">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF32">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG32">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "73", "90+2"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK32">
-        <v>4.82</v>
+        <v>4.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5694,28 +5694,28 @@
         <v>2.95</v>
       </c>
       <c r="P33">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="R33">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5727,7 +5727,7 @@
         <v>2.86</v>
       </c>
       <c r="AA33">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
         <v>1.66</v>
@@ -5749,46 +5749,46 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80", "84", "90+5", "90+5"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,30 +5828,30 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O34">
         <v>3.36</v>
@@ -5860,43 +5860,43 @@
         <v>2.74</v>
       </c>
       <c r="Q34">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="R34">
         <v>1.81</v>
       </c>
       <c r="S34">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T34">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="U34">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="V34">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z34">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AA34">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB34">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC34">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD34">
         <v>1.17</v>
@@ -5905,53 +5905,53 @@
         <v>1</v>
       </c>
       <c r="AF34">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "84"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "36", "64", "90+6"]</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK34">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,36 +5991,36 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O35">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="P35">
-        <v>13.4</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "45", "53", "72"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6157,127 +6157,127 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
         <v>2.7</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
         <v>2.38</v>
       </c>
       <c r="Q36">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.2</v>
+      </c>
+      <c r="U36">
+        <v>2.51</v>
+      </c>
+      <c r="V36">
+        <v>1.44</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>3.86</v>
+      </c>
+      <c r="AA36">
+        <v>1.7</v>
+      </c>
+      <c r="AB36">
+        <v>2.1</v>
+      </c>
+      <c r="AC36">
+        <v>2.83</v>
+      </c>
+      <c r="AD36">
         <v>1.35</v>
       </c>
-      <c r="T36">
-        <v>3</v>
-      </c>
-      <c r="U36">
-        <v>2.72</v>
-      </c>
-      <c r="V36">
-        <v>1.4</v>
-      </c>
-      <c r="W36">
-        <v>1.1</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.24</v>
-      </c>
-      <c r="Z36">
-        <v>3.34</v>
-      </c>
-      <c r="AA36">
-        <v>1.9</v>
-      </c>
-      <c r="AB36">
-        <v>1.9</v>
-      </c>
-      <c r="AC36">
-        <v>3.22</v>
-      </c>
-      <c r="AD36">
-        <v>1.27</v>
-      </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
+        <v>1.6</v>
+      </c>
+      <c r="AG36">
+        <v>2.25</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>["25", "53"]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.46</v>
+      </c>
+      <c r="AK36">
+        <v>1.35</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>5</v>
+      </c>
+      <c r="AN36">
+        <v>5</v>
+      </c>
+      <c r="AO36">
+        <v>17</v>
+      </c>
+      <c r="AP36">
+        <v>16</v>
+      </c>
+      <c r="AQ36">
         <v>1.73</v>
       </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.43</v>
-      </c>
-      <c r="AK36">
-        <v>1.33</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6346,7 +6346,7 @@
         <v>3.35</v>
       </c>
       <c r="P37">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -6358,10 +6358,10 @@
         <v>1.34</v>
       </c>
       <c r="T37">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V37">
         <v>1.4</v>
@@ -6382,7 +6382,7 @@
         <v>1.88</v>
       </c>
       <c r="AB37">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
         <v>3.08</v>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "55", "63", "67"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6492,24 +6492,24 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
         <v>3.7</v>
       </c>
       <c r="P38">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
         <v>2.1</v>
@@ -6524,13 +6524,13 @@
         <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6542,10 +6542,10 @@
         <v>3.54</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
         <v>2.82</v>
@@ -6554,7 +6554,7 @@
         <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
         <v>1.75</v>
@@ -6564,46 +6564,46 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80", "90+6"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6646,23 +6646,23 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "22", "54"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6809,30 +6809,30 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O40">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>1.48</v>
@@ -6844,16 +6844,16 @@
         <v>2.62</v>
       </c>
       <c r="S40">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U40">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W40">
         <v>1.16</v>
@@ -6865,19 +6865,19 @@
         <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>6.21</v>
+        <v>6.59</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AC40">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AD40">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE40">
         <v>1.28</v>
@@ -6886,7 +6886,7 @@
         <v>1.49</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "50", "60", "89"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,26 +6969,26 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7001,22 +7001,22 @@
         <v>4.4</v>
       </c>
       <c r="Q41">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
         <v>2.24</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U41">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W41">
         <v>1.1</v>
@@ -7028,13 +7028,13 @@
         <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA41">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB41">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AC41">
         <v>2.88</v>
@@ -7053,16 +7053,16 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "28", "80"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "63"]</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>2.14</v>
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7135,84 +7135,84 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
         <v>2.62</v>
       </c>
       <c r="Q42">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="R42">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="S42">
+        <v>1.2</v>
+      </c>
+      <c r="T42">
+        <v>3.85</v>
+      </c>
+      <c r="U42">
+        <v>2</v>
+      </c>
+      <c r="V42">
+        <v>1.73</v>
+      </c>
+      <c r="W42">
         <v>1.22</v>
       </c>
-      <c r="T42">
-        <v>3.6</v>
-      </c>
-      <c r="U42">
-        <v>2.02</v>
-      </c>
-      <c r="V42">
-        <v>1.65</v>
-      </c>
-      <c r="W42">
-        <v>1.18</v>
-      </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AB42">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AD42">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG42">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7221,41 +7221,41 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "52"]</t>
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AK42">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7327,49 +7327,49 @@
         <v>2.3</v>
       </c>
       <c r="Q43">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R43">
+        <v>2.15</v>
+      </c>
+      <c r="S43">
+        <v>1.32</v>
+      </c>
+      <c r="T43">
+        <v>3.25</v>
+      </c>
+      <c r="U43">
+        <v>2.46</v>
+      </c>
+      <c r="V43">
+        <v>1.51</v>
+      </c>
+      <c r="W43">
+        <v>1.08</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.2</v>
+      </c>
+      <c r="Z43">
+        <v>4.33</v>
+      </c>
+      <c r="AA43">
+        <v>1.61</v>
+      </c>
+      <c r="AB43">
         <v>2.25</v>
       </c>
-      <c r="S43">
-        <v>1.34</v>
-      </c>
-      <c r="T43">
-        <v>2.67</v>
-      </c>
-      <c r="U43">
-        <v>2.63</v>
-      </c>
-      <c r="V43">
-        <v>1.47</v>
-      </c>
-      <c r="W43">
-        <v>1.07</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.22</v>
-      </c>
-      <c r="Z43">
-        <v>4.1</v>
-      </c>
-      <c r="AA43">
-        <v>1.7</v>
-      </c>
-      <c r="AB43">
-        <v>2.1</v>
-      </c>
       <c r="AC43">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD43">
         <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK43">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7458,36 +7458,36 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "7", "58", "71"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ44">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7787,13 +7787,13 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -7803,29 +7803,29 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O46">
         <v>5.25</v>
       </c>
       <c r="P46">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q46">
-        <v>8.5</v>
+        <v>9.24</v>
       </c>
       <c r="R46">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="S46">
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
         <v>2.25</v>
@@ -7846,13 +7846,13 @@
         <v>4.55</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AD46">
         <v>1.48</v>
@@ -7861,10 +7861,10 @@
         <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7873,41 +7873,41 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16"]</t>
         </is>
       </c>
       <c r="AJ46">
         <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,30 +7947,30 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O47">
         <v>3.4</v>
@@ -7979,7 +7979,7 @@
         <v>2.89</v>
       </c>
       <c r="Q47">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="R47">
         <v>2.3</v>
@@ -7988,16 +7988,16 @@
         <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,32 +8006,32 @@
         <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>4.78</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB47">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
         <v>2.56</v>
       </c>
       <c r="AD47">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
         <v>2.32</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "68", "90+6"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -8043,34 +8043,34 @@
         <v>1.35</v>
       </c>
       <c r="AK47">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,48 +8110,48 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P48">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q48">
         <v>2.12</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
         <v>2.47</v>
@@ -8194,16 +8194,16 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "48"]</t>
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
         <v>2.25</v>
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8273,26 +8273,26 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8311,16 +8311,16 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T49">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U49">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V49">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W49">
         <v>1.03</v>
@@ -8353,16 +8353,16 @@
         <v>1.91</v>
       </c>
       <c r="AG49">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "87", "90+2"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "60"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8427,19 +8427,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -8451,115 +8451,115 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>3.41</v>
       </c>
       <c r="R50">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
         <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W50">
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
+        <v>2.09</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>["66"]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.3</v>
+      </c>
+      <c r="AK50">
+        <v>1.33</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>1</v>
+      </c>
+      <c r="AN50">
         <v>2</v>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.2</v>
-      </c>
-      <c r="AK50">
-        <v>2.02</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8590,139 +8590,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD51">
         <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "71"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "33", "42"]</t>
         </is>
       </c>
       <c r="AJ51">
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8753,22 +8753,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -8777,115 +8777,115 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O52">
+        <v>3.6</v>
+      </c>
+      <c r="P52">
+        <v>4</v>
+      </c>
+      <c r="Q52">
+        <v>2.08</v>
+      </c>
+      <c r="R52">
+        <v>2.32</v>
+      </c>
+      <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
         <v>3.5</v>
       </c>
-      <c r="P52">
-        <v>3.2</v>
-      </c>
-      <c r="Q52">
-        <v>2.5</v>
-      </c>
-      <c r="R52">
+      <c r="U52">
         <v>2.3</v>
       </c>
-      <c r="S52">
-        <v>1.3</v>
-      </c>
-      <c r="T52">
-        <v>3.25</v>
-      </c>
-      <c r="U52">
-        <v>2.5</v>
-      </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
-        <v>3.94</v>
+        <v>4.8</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF52">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "45+1"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "84"]</t>
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AL52">
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>1.2</v>
       </c>
       <c r="Q53">
-        <v>9.4</v>
+        <v>9.35</v>
       </c>
       <c r="R53">
         <v>2.83</v>
@@ -8966,43 +8966,43 @@
         <v>1.18</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U53">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="V53">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
         <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z53">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA53">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AC53">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AD53">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG53">
         <v>1.7</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK53">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O54">
         <v>3.38</v>
@@ -9120,7 +9120,7 @@
         <v>2.81</v>
       </c>
       <c r="Q54">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="R54">
         <v>1.93</v>
@@ -9144,16 +9144,16 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z54">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="AA54">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB54">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC54">
         <v>4</v>
@@ -9184,7 +9184,7 @@
         <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O55">
         <v>3.5</v>
       </c>
       <c r="P55">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC55">
         <v>2.25</v>
@@ -9446,19 +9446,19 @@
         <v>1.84</v>
       </c>
       <c r="Q56">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
         <v>1.56</v>
@@ -9470,10 +9470,10 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA56">
         <v>1.5</v>
@@ -9482,19 +9482,19 @@
         <v>2.4</v>
       </c>
       <c r="AC56">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD56">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE56">
         <v>1.17</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
         <v>3.5</v>
       </c>
       <c r="P57">
+        <v>2.35</v>
+      </c>
+      <c r="Q57">
+        <v>3.15</v>
+      </c>
+      <c r="R57">
         <v>2.4</v>
       </c>
-      <c r="Q57">
-        <v>3.22</v>
-      </c>
-      <c r="R57">
-        <v>2.38</v>
-      </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U57">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W57">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB57">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
         <v>1.44</v>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O58">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="P58">
         <v>3.6</v>
@@ -9775,13 +9775,13 @@
         <v>2.3</v>
       </c>
       <c r="R58">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="T58">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="U58">
         <v>2.25</v>
@@ -9793,31 +9793,31 @@
         <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA58">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AB58">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AC58">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AD58">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG58">
         <v>2.4</v>
@@ -9926,37 +9926,37 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="O59">
         <v>3.4</v>
       </c>
       <c r="P59">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q59">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R59">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T59">
         <v>2.9</v>
       </c>
       <c r="U59">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="V59">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W59">
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y59">
         <v>1.27</v>
@@ -9965,7 +9965,7 @@
         <v>3.3</v>
       </c>
       <c r="AA59">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB59">
         <v>1.76</v>
@@ -9974,16 +9974,16 @@
         <v>3.6</v>
       </c>
       <c r="AD59">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF59">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG59">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,25 +10095,25 @@
         <v>3.45</v>
       </c>
       <c r="P60">
-        <v>4.04</v>
+        <v>4.34</v>
       </c>
       <c r="Q60">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="R60">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S60">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T60">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U60">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="V60">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W60">
         <v>1.04</v>
@@ -10122,31 +10122,31 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z60">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA60">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB60">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC60">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AD60">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE60">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG60">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10282,7 +10282,7 @@
         <v>1.07</v>
       </c>
       <c r="X61">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
         <v>1.38</v>
@@ -10297,10 +10297,10 @@
         <v>1.65</v>
       </c>
       <c r="AC61">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE61">
         <v>1.04</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
         <v>2.5</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O63">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
         <v>3.75</v>
       </c>
       <c r="Q63">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S63">
         <v>1.42</v>
@@ -10623,10 +10623,10 @@
         <v>1.7</v>
       </c>
       <c r="AC63">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AD63">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE63">
         <v>1.04</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
         <v>1.8</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="O64">
         <v>3.5</v>
@@ -10759,7 +10759,7 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U64">
         <v>2.29</v>
@@ -10780,25 +10780,25 @@
         <v>4.65</v>
       </c>
       <c r="AA64">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB64">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AD64">
         <v>1.53</v>
       </c>
       <c r="AE64">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
         <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="Q67">
-        <v>3.12</v>
+        <v>3.68</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="U67">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W67">
+        <v>1.06</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.28</v>
+      </c>
+      <c r="Z67">
+        <v>3.08</v>
+      </c>
+      <c r="AA67">
+        <v>2</v>
+      </c>
+      <c r="AB67">
+        <v>1.8</v>
+      </c>
+      <c r="AC67">
+        <v>3.55</v>
+      </c>
+      <c r="AD67">
+        <v>1.24</v>
+      </c>
+      <c r="AE67">
         <v>1.05</v>
-      </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.31</v>
-      </c>
-      <c r="Z67">
-        <v>2.92</v>
-      </c>
-      <c r="AA67">
-        <v>2.05</v>
-      </c>
-      <c r="AB67">
-        <v>1.66</v>
-      </c>
-      <c r="AC67">
-        <v>3.58</v>
-      </c>
-      <c r="AD67">
-        <v>1.21</v>
-      </c>
-      <c r="AE67">
-        <v>1.03</v>
       </c>
       <c r="AF67">
         <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
+        <v>1.25</v>
+      </c>
+      <c r="AK67">
         <v>1.31</v>
-      </c>
-      <c r="AK67">
-        <v>1.42</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
+        <v>2.68</v>
+      </c>
+      <c r="Q68">
+        <v>3.12</v>
+      </c>
+      <c r="R68">
+        <v>2.1</v>
+      </c>
+      <c r="S68">
+        <v>1.37</v>
+      </c>
+      <c r="T68">
+        <v>2.69</v>
+      </c>
+      <c r="U68">
+        <v>2.81</v>
+      </c>
+      <c r="V68">
+        <v>1.36</v>
+      </c>
+      <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.31</v>
+      </c>
+      <c r="Z68">
+        <v>3.15</v>
+      </c>
+      <c r="AA68">
         <v>2.05</v>
       </c>
-      <c r="Q68">
-        <v>3.84</v>
-      </c>
-      <c r="R68">
-        <v>2.05</v>
-      </c>
-      <c r="S68">
-        <v>1.36</v>
-      </c>
-      <c r="T68">
-        <v>2.91</v>
-      </c>
-      <c r="U68">
-        <v>3</v>
-      </c>
-      <c r="V68">
-        <v>1.38</v>
-      </c>
-      <c r="W68">
-        <v>1.06</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.28</v>
-      </c>
-      <c r="Z68">
-        <v>3.08</v>
-      </c>
-      <c r="AA68">
-        <v>2</v>
-      </c>
       <c r="AB68">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC68">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="AD68">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
         <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK68">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11562,7 +11562,7 @@
         <v>4.7</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q69">
         <v>1.85</v>
@@ -11571,49 +11571,49 @@
         <v>2.62</v>
       </c>
       <c r="S69">
+        <v>1.15</v>
+      </c>
+      <c r="T69">
+        <v>4.35</v>
+      </c>
+      <c r="U69">
+        <v>2.03</v>
+      </c>
+      <c r="V69">
+        <v>1.8</v>
+      </c>
+      <c r="W69">
         <v>1.17</v>
       </c>
-      <c r="T69">
-        <v>4.1</v>
-      </c>
-      <c r="U69">
-        <v>2.07</v>
-      </c>
-      <c r="V69">
-        <v>1.76</v>
-      </c>
-      <c r="W69">
-        <v>1.16</v>
-      </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB69">
         <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD69">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE69">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF69">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG69">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.17</v>
       </c>
       <c r="AK69">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11734,16 +11734,16 @@
         <v>2.8</v>
       </c>
       <c r="S70">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T70">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U70">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V70">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W70">
         <v>1.26</v>
@@ -11764,10 +11764,10 @@
         <v>3.5</v>
       </c>
       <c r="AC70">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD70">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE70">
         <v>1.42</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
         <v>2.32</v>
@@ -11894,19 +11894,19 @@
         <v>3.45</v>
       </c>
       <c r="R71">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S71">
         <v>1.22</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
         <v>2.1</v>
       </c>
       <c r="V71">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
         <v>1.18</v>
@@ -11930,7 +11930,7 @@
         <v>2.1</v>
       </c>
       <c r="AD71">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE71">
         <v>1.28</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.11</v>
+        <v>3.82</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P72">
-        <v>2.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>2.52</v>
+        <v>4.22</v>
       </c>
       <c r="R72">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="S72">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T72">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U72">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V72">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W72">
         <v>1.17</v>
@@ -12078,31 +12078,31 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z72">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA72">
         <v>1.36</v>
       </c>
       <c r="AB72">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC72">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AD72">
         <v>1.68</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AG72">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK72">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,28 +12208,28 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="O73">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P73">
-        <v>1.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q73">
-        <v>4.23</v>
+        <v>2.96</v>
       </c>
       <c r="R73">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S73">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T73">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U73">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="V73">
         <v>1.7</v>
@@ -12241,10 +12241,10 @@
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA73">
         <v>1.36</v>
@@ -12253,19 +12253,19 @@
         <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD73">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE73">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF73">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG73">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AK73">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,22 +12371,22 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P74">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q74">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S74">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T74">
         <v>2.62</v>
@@ -12395,40 +12395,40 @@
         <v>3.1</v>
       </c>
       <c r="V74">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W74">
         <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y74">
         <v>1.4</v>
       </c>
       <c r="Z74">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AA74">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB74">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC74">
-        <v>3.96</v>
+        <v>4.69</v>
       </c>
       <c r="AD74">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF74">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG74">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK74">
         <v>1.3</v>
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="O75">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q75">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R75">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T75">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V75">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W75">
         <v>1.2</v>
@@ -12570,19 +12570,19 @@
         <v>1.08</v>
       </c>
       <c r="Z75">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB75">
         <v>2.88</v>
       </c>
       <c r="AC75">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AD75">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE75">
         <v>1.28</v>
@@ -12607,7 +12607,7 @@
         <v>1.12</v>
       </c>
       <c r="AK75">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="O76">
         <v>3.4</v>
@@ -12706,71 +12706,71 @@
         <v>3.15</v>
       </c>
       <c r="Q76">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R76">
         <v>2.2</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T76">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="U76">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
         <v>1.03</v>
       </c>
       <c r="Y76">
+        <v>1.26</v>
+      </c>
+      <c r="Z76">
+        <v>3.2</v>
+      </c>
+      <c r="AA76">
+        <v>2.06</v>
+      </c>
+      <c r="AB76">
+        <v>1.78</v>
+      </c>
+      <c r="AC76">
+        <v>3.34</v>
+      </c>
+      <c r="AD76">
         <v>1.24</v>
       </c>
-      <c r="Z76">
-        <v>3.34</v>
-      </c>
-      <c r="AA76">
-        <v>1.92</v>
-      </c>
-      <c r="AB76">
+      <c r="AE76">
+        <v>1.06</v>
+      </c>
+      <c r="AF76">
+        <v>1.78</v>
+      </c>
+      <c r="AG76">
         <v>1.9</v>
       </c>
-      <c r="AC76">
-        <v>3.2</v>
-      </c>
-      <c r="AD76">
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.26</v>
       </c>
-      <c r="AE76">
-        <v>1.07</v>
-      </c>
-      <c r="AF76">
-        <v>1.72</v>
-      </c>
-      <c r="AG76">
-        <v>1.98</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.28</v>
-      </c>
       <c r="AK76">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q77">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="T77">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="U77">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V77">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="AA77">
+        <v>2.25</v>
+      </c>
+      <c r="AB77">
+        <v>1.57</v>
+      </c>
+      <c r="AC77">
+        <v>4.35</v>
+      </c>
+      <c r="AD77">
+        <v>1.16</v>
+      </c>
+      <c r="AE77">
+        <v>1.01</v>
+      </c>
+      <c r="AF77">
         <v>1.85</v>
       </c>
-      <c r="AB77">
-        <v>2</v>
-      </c>
-      <c r="AC77">
-        <v>3.1</v>
-      </c>
-      <c r="AD77">
+      <c r="AG77">
+        <v>1.83</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.33</v>
       </c>
-      <c r="AE77">
-        <v>1.08</v>
-      </c>
-      <c r="AF77">
-        <v>1.65</v>
-      </c>
-      <c r="AG77">
-        <v>2.08</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.25</v>
-      </c>
       <c r="AK77">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,22 +13023,22 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q78">
         <v>2.7</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
         <v>2.84</v>
@@ -13050,7 +13050,7 @@
         <v>1.43</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
+        <v>2.05</v>
+      </c>
+      <c r="O79">
+        <v>3.25</v>
+      </c>
+      <c r="P79">
+        <v>3.3</v>
+      </c>
+      <c r="Q79">
+        <v>2.4</v>
+      </c>
+      <c r="R79">
         <v>2.2</v>
       </c>
-      <c r="O79">
-        <v>3.2</v>
-      </c>
-      <c r="P79">
+      <c r="S79">
+        <v>1.3</v>
+      </c>
+      <c r="T79">
         <v>3.1</v>
       </c>
-      <c r="Q79">
-        <v>2.8</v>
-      </c>
-      <c r="R79">
-        <v>2.08</v>
-      </c>
-      <c r="S79">
-        <v>1.48</v>
-      </c>
-      <c r="T79">
-        <v>2.41</v>
-      </c>
       <c r="U79">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V79">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="AA79">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="AB79">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AC79">
-        <v>4.38</v>
+        <v>3</v>
       </c>
       <c r="AD79">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF79">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>3.88</v>
       </c>
       <c r="P80">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q80">
         <v>2.15</v>
@@ -13364,22 +13364,22 @@
         <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
         <v>2.88</v>
       </c>
       <c r="U80">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="V80">
         <v>1.36</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
         <v>1.32</v>
@@ -13388,10 +13388,10 @@
         <v>3.08</v>
       </c>
       <c r="AA80">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB80">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC80">
         <v>3.2</v>
@@ -13400,7 +13400,7 @@
         <v>1.26</v>
       </c>
       <c r="AE80">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
         <v>1.91</v>
@@ -13684,49 +13684,49 @@
         <v>5.3</v>
       </c>
       <c r="Q82">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R82">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T82">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U82">
         <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA82">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB82">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC82">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD82">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE82">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF82">
         <v>1.62</v>
@@ -13748,7 +13748,7 @@
         <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="O83">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q83">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R83">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13862,19 +13862,19 @@
         <v>2.04</v>
       </c>
       <c r="V83">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W83">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
         <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>5.39</v>
+        <v>5.46</v>
       </c>
       <c r="AA83">
         <v>1.44</v>
@@ -13889,7 +13889,7 @@
         <v>1.62</v>
       </c>
       <c r="AE83">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF83">
         <v>1.42</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AK83">
         <v>1.18</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O84">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="P84">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB84">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O85">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="P85">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q85">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R85">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="S85">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T85">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U85">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V85">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="W85">
         <v>1.4</v>
@@ -14197,28 +14197,28 @@
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z85">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA85">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AB85">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AC85">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AD85">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AE85">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF85">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG85">
         <v>3</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK85">
-        <v>4.12</v>
+        <v>3.22</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="O86">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P86">
         <v>6.5</v>
       </c>
       <c r="Q86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R86">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="S86">
         <v>1.2</v>
@@ -14348,7 +14348,7 @@
         <v>4</v>
       </c>
       <c r="U86">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V86">
         <v>1.75</v>
@@ -14363,7 +14363,7 @@
         <v>1.07</v>
       </c>
       <c r="Z86">
-        <v>6.17</v>
+        <v>6.6</v>
       </c>
       <c r="AA86">
         <v>1.4</v>
@@ -14372,19 +14372,19 @@
         <v>3.1</v>
       </c>
       <c r="AC86">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD86">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE86">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF86">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG86">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.13</v>
       </c>
       <c r="AK86">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14496,58 +14496,58 @@
         <v>4.25</v>
       </c>
       <c r="P87">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q87">
         <v>2</v>
       </c>
       <c r="R87">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S87">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T87">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="U87">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V87">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="W87">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z87">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA87">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB87">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC87">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AD87">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AE87">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG87">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="O88">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="Q88">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R88">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="S88">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>5.05</v>
+        <v>3.9</v>
       </c>
       <c r="U88">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="V88">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="W88">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>10</v>
+        <v>5.55</v>
       </c>
       <c r="AA88">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AC88">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AD88">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE88">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK88">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="O89">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P89">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="R89">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S89">
+        <v>1.18</v>
+      </c>
+      <c r="T89">
+        <v>4.8</v>
+      </c>
+      <c r="U89">
+        <v>2</v>
+      </c>
+      <c r="V89">
+        <v>1.83</v>
+      </c>
+      <c r="W89">
         <v>1.22</v>
       </c>
-      <c r="T89">
-        <v>3.78</v>
-      </c>
-      <c r="U89">
-        <v>2.11</v>
-      </c>
-      <c r="V89">
-        <v>1.66</v>
-      </c>
-      <c r="W89">
-        <v>1.18</v>
-      </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z89">
-        <v>5.55</v>
+        <v>6.83</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB89">
         <v>2.88</v>
       </c>
       <c r="AC89">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AD89">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AE89">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF89">
+        <v>1.36</v>
+      </c>
+      <c r="AG89">
+        <v>3.1</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.44</v>
       </c>
-      <c r="AG89">
-        <v>2.56</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.18</v>
-      </c>
       <c r="AK89">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O90">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="P90">
-        <v>2.38</v>
+        <v>4.95</v>
       </c>
       <c r="Q90">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="R90">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T90">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U90">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V90">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z90">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AA90">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AC90">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AD90">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE90">
         <v>1.27</v>
       </c>
       <c r="AF90">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O91">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="Q91">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="V91">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="W91">
+        <v>1.13</v>
+      </c>
+      <c r="X91">
+        <v>1.02</v>
+      </c>
+      <c r="Y91">
+        <v>1.17</v>
+      </c>
+      <c r="Z91">
+        <v>4.3</v>
+      </c>
+      <c r="AA91">
+        <v>1.58</v>
+      </c>
+      <c r="AB91">
+        <v>2.39</v>
+      </c>
+      <c r="AC91">
+        <v>2.33</v>
+      </c>
+      <c r="AD91">
+        <v>1.56</v>
+      </c>
+      <c r="AE91">
         <v>1.22</v>
       </c>
-      <c r="X91">
-        <v>1.01</v>
-      </c>
-      <c r="Y91">
-        <v>1.03</v>
-      </c>
-      <c r="Z91">
-        <v>7.4</v>
-      </c>
-      <c r="AA91">
-        <v>1.25</v>
-      </c>
-      <c r="AB91">
-        <v>3.28</v>
-      </c>
-      <c r="AC91">
-        <v>1.76</v>
-      </c>
-      <c r="AD91">
-        <v>1.98</v>
-      </c>
-      <c r="AE91">
-        <v>1.38</v>
-      </c>
       <c r="AF91">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AG91">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.43</v>
+        <v>2.65</v>
       </c>
       <c r="O92">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P92">
-        <v>4.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q92">
-        <v>1.97</v>
+        <v>2.84</v>
       </c>
       <c r="R92">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S92">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="T92">
-        <v>4</v>
+        <v>5.55</v>
       </c>
       <c r="U92">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="V92">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="W92">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z92">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA92">
+        <v>1.19</v>
+      </c>
+      <c r="AB92">
+        <v>3.8</v>
+      </c>
+      <c r="AC92">
+        <v>1.76</v>
+      </c>
+      <c r="AD92">
+        <v>2.08</v>
+      </c>
+      <c r="AE92">
+        <v>1.53</v>
+      </c>
+      <c r="AF92">
+        <v>1.25</v>
+      </c>
+      <c r="AG92">
+        <v>3.5</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.65</v>
+      </c>
+      <c r="AK92">
         <v>1.4</v>
-      </c>
-      <c r="AB92">
-        <v>2.87</v>
-      </c>
-      <c r="AC92">
-        <v>2.05</v>
-      </c>
-      <c r="AD92">
-        <v>1.71</v>
-      </c>
-      <c r="AE92">
-        <v>1.25</v>
-      </c>
-      <c r="AF92">
-        <v>1.48</v>
-      </c>
-      <c r="AG92">
-        <v>2.47</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.17</v>
-      </c>
-      <c r="AK92">
-        <v>2.5</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15474,7 +15474,7 @@
         <v>5.3</v>
       </c>
       <c r="P93">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q93">
         <v>1.67</v>
@@ -15483,16 +15483,16 @@
         <v>2.9</v>
       </c>
       <c r="S93">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T93">
         <v>4.6</v>
       </c>
       <c r="U93">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="V93">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W93">
         <v>1.25</v>
@@ -15510,16 +15510,16 @@
         <v>1.33</v>
       </c>
       <c r="AB93">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC93">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AD93">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AE93">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF93">
         <v>1.44</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="O94">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P94">
+        <v>3.19</v>
+      </c>
+      <c r="Q94">
+        <v>2.1</v>
+      </c>
+      <c r="R94">
+        <v>2.9</v>
+      </c>
+      <c r="S94">
+        <v>1.11</v>
+      </c>
+      <c r="T94">
+        <v>5.05</v>
+      </c>
+      <c r="U94">
+        <v>1.68</v>
+      </c>
+      <c r="V94">
         <v>2.08</v>
       </c>
-      <c r="Q94">
-        <v>3.35</v>
-      </c>
-      <c r="R94">
-        <v>2.5</v>
-      </c>
-      <c r="S94">
-        <v>1.2</v>
-      </c>
-      <c r="T94">
+      <c r="W94">
+        <v>1.3</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
+        <v>1.05</v>
+      </c>
+      <c r="Z94">
+        <v>10</v>
+      </c>
+      <c r="AA94">
+        <v>1.17</v>
+      </c>
+      <c r="AB94">
         <v>4</v>
       </c>
-      <c r="U94">
-        <v>2.01</v>
-      </c>
-      <c r="V94">
-        <v>1.73</v>
-      </c>
-      <c r="W94">
-        <v>1.18</v>
-      </c>
-      <c r="X94">
-        <v>1.02</v>
-      </c>
-      <c r="Y94">
-        <v>1.09</v>
-      </c>
-      <c r="Z94">
-        <v>6.03</v>
-      </c>
-      <c r="AA94">
-        <v>1.43</v>
-      </c>
-      <c r="AB94">
-        <v>2.76</v>
-      </c>
       <c r="AC94">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AD94">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="AE94">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AF94">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG94">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.18</v>
+        <v>2.86</v>
       </c>
       <c r="O95">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q95">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S95">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U95">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z95">
-        <v>3.98</v>
+        <v>5.56</v>
       </c>
       <c r="AA95">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="AC95">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD95">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AF95">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>1.46</v>
       </c>
       <c r="Q96">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="R96">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="S96">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T96">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U96">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V96">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W96">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA96">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB96">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AC96">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AD96">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE96">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF96">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG96">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
         <v>1.08</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="O97">
         <v>3.4</v>
@@ -16129,10 +16129,10 @@
         <v>2.14</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>4.13</v>
       </c>
       <c r="R97">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16141,40 +16141,40 @@
         <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W97">
         <v>1.15</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z97">
-        <v>4.7</v>
+        <v>5.13</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB97">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AC97">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD97">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE97">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF97">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AG97">
         <v>2.5</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AK97">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="O98">
+        <v>3.1</v>
+      </c>
+      <c r="P98">
+        <v>2.68</v>
+      </c>
+      <c r="Q98">
         <v>3.2</v>
-      </c>
-      <c r="P98">
-        <v>2.56</v>
-      </c>
-      <c r="Q98">
-        <v>3.25</v>
       </c>
       <c r="R98">
         <v>2.1</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="U98">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W98">
         <v>1.06</v>
@@ -16316,19 +16316,19 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB98">
         <v>1.79</v>
       </c>
       <c r="AC98">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD98">
         <v>1.3</v>
@@ -16340,7 +16340,7 @@
         <v>1.73</v>
       </c>
       <c r="AG98">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK98">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O100">
         <v>3.55</v>
@@ -16618,55 +16618,55 @@
         <v>3.2</v>
       </c>
       <c r="Q100">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="U100">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V100">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA100">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB100">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC100">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD100">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG100">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,19 +16781,19 @@
         <v>2.8</v>
       </c>
       <c r="Q101">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R101">
         <v>2.38</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U101">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V101">
         <v>1.62</v>
@@ -16808,28 +16808,28 @@
         <v>1.13</v>
       </c>
       <c r="Z101">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA101">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB101">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AC101">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD101">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE101">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG101">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16941,13 +16941,13 @@
         <v>4.4</v>
       </c>
       <c r="P102">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q102">
         <v>1.85</v>
       </c>
       <c r="R102">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S102">
         <v>1.29</v>
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
         <v>5.7</v>
       </c>
       <c r="P103">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="Q103">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R103">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T103">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U103">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V103">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W103">
         <v>1.2</v>
@@ -17131,31 +17131,31 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z103">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB103">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC103">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD103">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AE103">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF103">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK103">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O105">
         <v>3.7</v>
       </c>
       <c r="P105">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q105">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="R105">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="S105">
         <v>1.28</v>
@@ -17448,16 +17448,16 @@
         <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W105">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
         <v>5.5</v>
@@ -17466,16 +17466,16 @@
         <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AC105">
         <v>2.3</v>
       </c>
       <c r="AD105">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE105">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK105">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="P109">
-        <v>2.83</v>
+        <v>4.87</v>
       </c>
       <c r="Q109">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R109">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T109">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="U109">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
+        <v>1.08</v>
+      </c>
+      <c r="Z109">
+        <v>5.59</v>
+      </c>
+      <c r="AA109">
+        <v>1.4</v>
+      </c>
+      <c r="AB109">
+        <v>2.7</v>
+      </c>
+      <c r="AC109">
+        <v>2.05</v>
+      </c>
+      <c r="AD109">
+        <v>1.53</v>
+      </c>
+      <c r="AE109">
         <v>1.2</v>
       </c>
-      <c r="Z109">
-        <v>3.68</v>
-      </c>
-      <c r="AA109">
-        <v>1.73</v>
-      </c>
-      <c r="AB109">
-        <v>1.75</v>
-      </c>
-      <c r="AC109">
-        <v>2.91</v>
-      </c>
-      <c r="AD109">
-        <v>1.4</v>
-      </c>
-      <c r="AE109">
-        <v>1.1</v>
-      </c>
       <c r="AF109">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG109">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="O110">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P110">
-        <v>4.87</v>
+        <v>2.83</v>
       </c>
       <c r="Q110">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S110">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="U110">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="V110">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z110">
-        <v>5.59</v>
+        <v>3.68</v>
       </c>
       <c r="AA110">
+        <v>1.73</v>
+      </c>
+      <c r="AB110">
+        <v>1.75</v>
+      </c>
+      <c r="AC110">
+        <v>2.91</v>
+      </c>
+      <c r="AD110">
         <v>1.4</v>
       </c>
-      <c r="AB110">
-        <v>2.7</v>
-      </c>
-      <c r="AC110">
-        <v>2.05</v>
-      </c>
-      <c r="AD110">
+      <c r="AE110">
+        <v>1.1</v>
+      </c>
+      <c r="AF110">
+        <v>1.6</v>
+      </c>
+      <c r="AG110">
+        <v>2.18</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.24</v>
+      </c>
+      <c r="AK110">
         <v>1.53</v>
-      </c>
-      <c r="AE110">
-        <v>1.2</v>
-      </c>
-      <c r="AF110">
-        <v>1.48</v>
-      </c>
-      <c r="AG110">
-        <v>2.45</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.17</v>
-      </c>
-      <c r="AK110">
-        <v>2.38</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18568,61 +18568,61 @@
         <v>1.85</v>
       </c>
       <c r="O112">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P112">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="Q112">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R112">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T112">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="U112">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V112">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA112">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB112">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC112">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="AD112">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE112">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF112">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AG112">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK112">
         <v>2</v>
@@ -18782,7 +18782,7 @@
         <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AG113">
         <v>1.33</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q115">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="R115">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U115">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="V115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA115">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AB115">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AC115">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD115">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE115">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK115">
         <v>1.4</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O116">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P116">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q116">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R116">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S116">
         <v>1.25</v>
@@ -19244,10 +19244,10 @@
         <v>1.62</v>
       </c>
       <c r="W116">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
         <v>1.13</v>
@@ -19256,7 +19256,7 @@
         <v>6</v>
       </c>
       <c r="AA116">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB116">
         <v>2.33</v>
@@ -19274,7 +19274,7 @@
         <v>1.62</v>
       </c>
       <c r="AG116">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK116">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19383,77 +19383,77 @@
         <v>3.15</v>
       </c>
       <c r="O117">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q117">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="R117">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S117">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U117">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="V117">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W117">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
+        <v>1.01</v>
+      </c>
+      <c r="Y117">
+        <v>1.3</v>
+      </c>
+      <c r="Z117">
+        <v>3.25</v>
+      </c>
+      <c r="AA117">
+        <v>2</v>
+      </c>
+      <c r="AB117">
+        <v>1.7</v>
+      </c>
+      <c r="AC117">
+        <v>3.58</v>
+      </c>
+      <c r="AD117">
+        <v>1.21</v>
+      </c>
+      <c r="AE117">
         <v>1.04</v>
       </c>
-      <c r="Y117">
-        <v>1.22</v>
-      </c>
-      <c r="Z117">
-        <v>3.5</v>
-      </c>
-      <c r="AA117">
-        <v>1.87</v>
-      </c>
-      <c r="AB117">
-        <v>1.9</v>
-      </c>
-      <c r="AC117">
-        <v>2.92</v>
-      </c>
-      <c r="AD117">
+      <c r="AF117">
+        <v>1.75</v>
+      </c>
+      <c r="AG117">
+        <v>1.95</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
+        <v>1.27</v>
+      </c>
+      <c r="AK117">
         <v>1.31</v>
-      </c>
-      <c r="AE117">
-        <v>1.08</v>
-      </c>
-      <c r="AF117">
-        <v>1.7</v>
-      </c>
-      <c r="AG117">
-        <v>2.05</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.22</v>
-      </c>
-      <c r="AK117">
-        <v>1.22</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,37 +19552,37 @@
         <v>2.18</v>
       </c>
       <c r="Q118">
-        <v>3.92</v>
+        <v>3.83</v>
       </c>
       <c r="R118">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="S118">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T118">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U118">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V118">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W118">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
         <v>1.06</v>
       </c>
       <c r="Y118">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z118">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AA118">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB118">
         <v>1.5</v>
@@ -19594,13 +19594,13 @@
         <v>1.13</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
         <v>1.99</v>
       </c>
       <c r="AG118">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK118">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,19 +19706,19 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O119">
         <v>2.8</v>
       </c>
       <c r="P119">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
       </c>
       <c r="R119">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S119">
         <v>1.54</v>
@@ -19730,7 +19730,7 @@
         <v>3.52</v>
       </c>
       <c r="V119">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W119">
         <v>1.02</v>
@@ -19742,19 +19742,19 @@
         <v>1.53</v>
       </c>
       <c r="Z119">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AA119">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AB119">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC119">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AD119">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE119">
         <v>1.01</v>

--- a/jogos_2026-10-09.xlsx
+++ b/jogos_2026-10-09.xlsx
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7640,29 +7640,29 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
         <v>2.05</v>
       </c>
       <c r="O45">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P45">
         <v>3.29</v>
       </c>
       <c r="Q45">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
         <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U45">
         <v>3.2</v>
@@ -7671,16 +7671,16 @@
         <v>1.22</v>
       </c>
       <c r="W45">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
         <v>1.36</v>
       </c>
       <c r="Z45">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA45">
         <v>2.25</v>
@@ -7689,19 +7689,19 @@
         <v>1.61</v>
       </c>
       <c r="AC45">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AD45">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE45">
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG45">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,37 +7714,37 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK45">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -8940,11 +8940,11 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "87", "90"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9088,26 +9088,26 @@
         </is>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "24", "76"]</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "38"]</t>
         </is>
       </c>
       <c r="AJ54">
@@ -9190,16 +9190,16 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ54">
         <v>0</v>
@@ -9254,13 +9254,13 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AJ55">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9414,26 +9414,26 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AJ56">
@@ -9516,28 +9516,28 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9577,13 +9577,13 @@
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
@@ -9679,28 +9679,28 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN57">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO57">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP57">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
@@ -9842,28 +9842,28 @@
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN58">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO58">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP58">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
@@ -9906,13 +9906,13 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ59">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10066,13 +10066,13 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
@@ -10168,28 +10168,28 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10229,13 +10229,13 @@
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
@@ -10331,28 +10331,28 @@
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN61">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10392,42 +10392,42 @@
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O62">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P62">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Q62">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R62">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="S62">
         <v>1.22</v>
@@ -10436,10 +10436,10 @@
         <v>4.5</v>
       </c>
       <c r="U62">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V62">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
         <v>1.15</v>
@@ -10448,74 +10448,74 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB62">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AC62">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF62">
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "90", "90+6"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ62">
         <v>1.06</v>
       </c>
       <c r="AK62">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="AL62">
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10555,26 +10555,26 @@
         </is>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "9"]</t>
         </is>
       </c>
       <c r="AJ63">
@@ -10657,28 +10657,28 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -10718,26 +10718,26 @@
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N64">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "38", "87"]</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "79", "82"]</t>
         </is>
       </c>
       <c r="AJ64">
@@ -10820,28 +10820,28 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN64">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO64">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP64">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -10884,13 +10884,13 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -10900,62 +10900,62 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N65">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
+        <v>3.75</v>
+      </c>
+      <c r="P65">
+        <v>1.88</v>
+      </c>
+      <c r="Q65">
         <v>3.7</v>
       </c>
-      <c r="P65">
-        <v>1.97</v>
-      </c>
-      <c r="Q65">
-        <v>3.5</v>
-      </c>
       <c r="R65">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S65">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T65">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U65">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V65">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W65">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z65">
-        <v>6.15</v>
+        <v>6.45</v>
       </c>
       <c r="AA65">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB65">
         <v>3.05</v>
       </c>
       <c r="AC65">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AD65">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AE65">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
         <v>1.36</v>
@@ -10970,41 +10970,41 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "20"]</t>
         </is>
       </c>
       <c r="AJ65">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AK65">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL65">
         <v>0</v>
       </c>
       <c r="AM65">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN65">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO65">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP65">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ65">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AR65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS65">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AT65">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
@@ -11044,13 +11044,13 @@
         </is>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -11063,29 +11063,29 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="R66">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="S66">
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U66">
         <v>2.25</v>
@@ -11094,7 +11094,7 @@
         <v>1.57</v>
       </c>
       <c r="W66">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,41 +11103,41 @@
         <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>5.08</v>
+        <v>5.2</v>
       </c>
       <c r="AA66">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB66">
         <v>2.45</v>
       </c>
       <c r="AC66">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AD66">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
+          <t>["9"]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
         <v>2</v>
@@ -11146,28 +11146,28 @@
         <v>0</v>
       </c>
       <c r="AM66">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN66">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO66">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP66">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ66">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AR66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS66">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT66">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -11222,11 +11222,11 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N67">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "55"]</t>
         </is>
       </c>
       <c r="AJ67">
@@ -11309,28 +11309,28 @@
         <v>0</v>
       </c>
       <c r="AM67">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN67">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO67">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP67">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ67">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AR67">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS67">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT67">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -11385,11 +11385,11 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N68">
@@ -11454,12 +11454,12 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ68">
@@ -11472,28 +11472,28 @@
         <v>0</v>
       </c>
       <c r="AM68">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN68">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO68">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP68">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N69">
@@ -11635,28 +11635,28 @@
         <v>0</v>
       </c>
       <c r="AM69">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN69">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO69">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP69">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS69">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
@@ -11696,26 +11696,26 @@
         </is>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N70">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "42"]</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "13", "47"]</t>
         </is>
       </c>
       <c r="AJ70">
@@ -11798,28 +11798,28 @@
         <v>0</v>
       </c>
       <c r="AM70">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN70">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO70">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP70">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ70">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS70">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT70">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
@@ -11859,26 +11859,26 @@
         </is>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N71">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "49", "69"]</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
@@ -11961,28 +11961,28 @@
         <v>0</v>
       </c>
       <c r="AM71">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN71">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO71">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP71">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR71">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS71">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT71">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
@@ -12013,19 +12013,19 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -12034,39 +12034,39 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N72">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>1.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q72">
-        <v>4.22</v>
+        <v>2.96</v>
       </c>
       <c r="R72">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S72">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T72">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="V72">
         <v>1.7</v>
@@ -12078,74 +12078,74 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA72">
         <v>1.36</v>
       </c>
       <c r="AB72">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="AD72">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG72">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ72">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AK72">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
       </c>
       <c r="AM72">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN72">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO72">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP72">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ72">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR72">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS72">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT72">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
@@ -12176,60 +12176,60 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N73">
-        <v>2.11</v>
+        <v>3.82</v>
       </c>
       <c r="O73">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P73">
-        <v>2.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q73">
-        <v>2.96</v>
+        <v>4.22</v>
       </c>
       <c r="R73">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S73">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T73">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U73">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V73">
         <v>1.7</v>
@@ -12241,31 +12241,31 @@
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z73">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA73">
         <v>1.36</v>
       </c>
       <c r="AB73">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC73">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AD73">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE73">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF73">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG73">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12274,41 +12274,41 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "55", "83"]</t>
         </is>
       </c>
       <c r="AJ73">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AK73">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AL73">
         <v>0</v>
       </c>
       <c r="AM73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN73">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO73">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP73">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ73">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS73">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT73">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -12363,11 +12363,11 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N74">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ74">
@@ -12450,28 +12450,28 @@
         <v>0</v>
       </c>
       <c r="AM74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN74">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO74">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP74">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR74">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS74">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT74">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
@@ -12511,26 +12511,26 @@
         </is>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N75">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "35", "77"]</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
@@ -12613,28 +12613,28 @@
         <v>0</v>
       </c>
       <c r="AM75">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO75">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP75">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS75">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT75">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
@@ -12674,26 +12674,26 @@
         </is>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N76">
@@ -12758,12 +12758,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "55", "76"]</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "90"]</t>
         </is>
       </c>
       <c r="AJ76">
@@ -12776,28 +12776,28 @@
         <v>0</v>
       </c>
       <c r="AM76">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN76">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO76">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP76">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
@@ -12828,25 +12828,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -12856,68 +12856,68 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N77">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q77">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R77">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="U77">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="V77">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>4.35</v>
+        <v>2.83</v>
       </c>
       <c r="AD77">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12926,11 +12926,11 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
         <v>1.62</v>
@@ -12939,28 +12939,28 @@
         <v>0</v>
       </c>
       <c r="AM77">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN77">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO77">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP77">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ77">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR77">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS77">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT77">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
@@ -12991,22 +12991,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -13015,85 +13015,85 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P78">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q78">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
+        <v>2.11</v>
+      </c>
+      <c r="S78">
+        <v>1.47</v>
+      </c>
+      <c r="T78">
+        <v>2.44</v>
+      </c>
+      <c r="U78">
+        <v>3</v>
+      </c>
+      <c r="V78">
+        <v>1.29</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.4</v>
+      </c>
+      <c r="Z78">
+        <v>2.75</v>
+      </c>
+      <c r="AA78">
         <v>2.25</v>
       </c>
-      <c r="S78">
-        <v>1.3</v>
-      </c>
-      <c r="T78">
-        <v>2.84</v>
-      </c>
-      <c r="U78">
-        <v>2.57</v>
-      </c>
-      <c r="V78">
-        <v>1.43</v>
-      </c>
-      <c r="W78">
-        <v>1.11</v>
-      </c>
-      <c r="X78">
-        <v>1</v>
-      </c>
-      <c r="Y78">
-        <v>1.22</v>
-      </c>
-      <c r="Z78">
-        <v>3.58</v>
-      </c>
-      <c r="AA78">
-        <v>1.8</v>
-      </c>
       <c r="AB78">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC78">
-        <v>2.83</v>
+        <v>4.35</v>
       </c>
       <c r="AD78">
+        <v>1.16</v>
+      </c>
+      <c r="AE78">
+        <v>1.01</v>
+      </c>
+      <c r="AF78">
+        <v>1.85</v>
+      </c>
+      <c r="AG78">
+        <v>1.83</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>["8"]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>["75"]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.33</v>
-      </c>
-      <c r="AE78">
-        <v>1.1</v>
-      </c>
-      <c r="AF78">
-        <v>1.62</v>
-      </c>
-      <c r="AG78">
-        <v>2.16</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.24</v>
       </c>
       <c r="AK78">
         <v>1.62</v>
@@ -13102,28 +13102,28 @@
         <v>0</v>
       </c>
       <c r="AM78">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN78">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO78">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP78">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ78">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR78">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS78">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT78">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
@@ -13154,139 +13154,139 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N79">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="O79">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="P79">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q79">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="R79">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U79">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
+        <v>1.08</v>
+      </c>
+      <c r="X79">
+        <v>1.03</v>
+      </c>
+      <c r="Y79">
+        <v>1.32</v>
+      </c>
+      <c r="Z79">
+        <v>3.08</v>
+      </c>
+      <c r="AA79">
+        <v>1.9</v>
+      </c>
+      <c r="AB79">
+        <v>1.78</v>
+      </c>
+      <c r="AC79">
+        <v>3.2</v>
+      </c>
+      <c r="AD79">
+        <v>1.26</v>
+      </c>
+      <c r="AE79">
         <v